--- a/docs/ОПЛАТЫ-СРАВНЕНИЕ.xlsx
+++ b/docs/ОПЛАТЫ-СРАВНЕНИЕ.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шортлист" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Посредники'!$A$1:$P$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Шортлист'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Посредники'!$A$1:$P$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Шортлист'!$A$1:$F$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3878,72 +3878,72 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Paddle</t>
+          <t>Paddle (Paddle.com Market Ltd / Paddle Payments Ltd / Paddle.com Inc.)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>MoR (merchant of record)</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Серая зона: VPN and Proxies — Restricted Category, нужен enhanced due diligence</t>
+          <t>серая зона: VPN и прокси прямо названы в п.19 списка Prohibited Categories, но с пометкой «(Restricted Category)» — продавать можно только после усиленного due diligence и одобрения Paddle. Формально это не бан, но и не разрешение: заявка рассматривается вручную, отказ возможен на этапе Domain Review по AUP.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Мир, кроме РФ и Беларуси</t>
+          <t>Продавцы из РФ и Беларуси НЕ принимаются: «Software businesses from Russia/Belarus or any of the sanctioned regions ... won't be able to sign up for an account»; выплата на счёт в РФ невозможна («If your payout account is based in Russia it is unlikely that we will be able to send your payout»). Россия также в списке Unsupported countries для покупателей — транзакции из РФ блокируются на checkout с апреля 2023. Резидент РФ (физлицо/самозанятый) — нет. Юрлицо в KZ/AM/GE/KG/UAE формально допустимо (эти страны в supported list), ИП/физлицо/sole trader допускаются: верификация бизнеса «not required for individuals or sole traders».</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Карты, PayPal, локальные методы — через MoR</t>
+          <t>Карты (Visa/Mastercard/Amex и др.), PayPal, Apple Pay, Google Pay, Alipay, WeChat Pay, iDEAL|Wero, Bancontact, BLIK, MB WAY, Pix, UPI, Samsung Pay, KakaoPay, Naver Pay, Payco, корейские локальные карты, банковский перевод (для инвойсов). Метод показывается автоматически по стране/валюте/устройству, включается в Paddle &gt; Checkout &gt; Checkout configuration. Крипты нет.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>5% + $0.50 за транзакцию; резерв и chargeback fee не раскрыты</t>
+          <t>Pay-as-you-go: 5% + $0.50 за транзакцию Paddle Checkout (подтверждено на https://www.paddle.com/pricing, проверено 2026-10-05); Paddle Invoicing с оплатой банковским переводом — 3.5%; Checkout Recovery — 10% от успешно восстановленной корзины; FX-маржа 2% (USD/EUR/GBP), 2.5% (CZK/DKK/NOK/THB), 3% (прочие валюты), плюс до 1.5% при выплате в валюте, отличной от Payment Currency; $15/€15/£15 за международный банковский перевод; chargeback/Pre-Chargeback Alert — до 20 GBP/USD/EUR или 40 AUD/CAD. Месячной платы нет — «No monthly fees, migration fees, or hidden extras». При среднем чеке ниже $10 — только индивидуальные условия.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Нет setup fee и ежемесячной платы</t>
+          <t>нет: публичной платы за онбординг/подключение нет, pricing-страница заявляет «No monthly fees, migration fees, or hidden extras». Paddle вправе взимать Dormancy Charge при отсутствии продаж 6 месяцев.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Не раскрыт</t>
+          <t>Публичного rolling reserve % нет — по запросу (не публикуется). Де-факто: баланс конвертируется в выплату 1-го числа и уходит до 15-го, т.е. холд до ~15 дней. Ключевое: при приостановке/расторжении Paddle вправе удерживать Supplier Fees для покрытия будущих chargeback и возвратов по подпискам; удержанное высвобождается не позднее чем через 6 месяцев после termination или после окончания последней подписки (п.17.2 и 17.4 Master Services Agreement).</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Net-30/ежемесячно на банковский счёт, USD/EUR/GBP; минимум не раскрыт</t>
+          <t>Валюта: USD, EUR, GBP, CAD или AUD. Расписание: раз в месяц — при превышении порога баланс 1-го числа становится выплатой, деньги отправляются до 15-го, зачисление до 3 рабочих дней. Минимум $100/€100/£100, порог настраивается вплоть до $100 000; при недоборе переносится на следующий месяц. Направления: банковский wire или Payoneer; Wise/ePayments-подобные сервисы принимаются, если дают IBAN/SWIFT. Доп. $15 за международный перевод в отдельных странах.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Юрлицо в поддерживаемой юрисдикции; РФ в unsupported countries -&gt; нет; VAT-номер не нужен</t>
+          <t>Юрлицо ИЛИ физлицо/ИП (sole trader) — для individuals/sole traders бизнес-верификация не требуется. KYC/KYB: обязательный Domain Review + Identity Verification + Business Identification (регистрационные документы и владельцы с долей &gt;25%) через сторонний сервис, плюс Supplier Information (финстатус, акционеры, UBO) по запросу. Обязателен живой сайт на HTTPS с описанием продукта, ценами, T&amp;C, Refund Policy, Privacy Policy и именем компании (для самозанятого — «legal name preferred»); продавать можно только через одобренные Supplier URLs, продажи вне одобренных доменов прямо запрещены. VAT/налоговый номер: требуется информировать Paddle при VAT-регистрации в ЕС и при её изменении. История процессинга не обязательна: «Processing statement ... If you don't have this due to being a new business, we'll take that into account during our review».</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>да: подписки и мульти-продуктовые планы, бесплатные триалы, купоны/скидки, proration, dunning и payment recovery (Paddle Retain + Checkout Recovery), сохранение способов оплаты (saved payment methods) для повторных списаний; chargeback liability, refunds и buyer support — на стороне Paddle как MoR.</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Hosted checkout, REST API, вебхуки; сложность 2/5</t>
+          <t>API Paddle Billing, hosted checkout, overlay и inline checkout, webhooks, sandbox, отдельный домен для checkout; документация лучшая в группе (developer.paddle.com, есть .md-версии каждой страницы, Docs MCP, Postman-коллекция). Telegram-бот без сайта НЕ подходит: обязателен одобренный домен и запрет продаж вне одобренных Supplier URLs; checkout можно открывать только с согласованных домена/поддомена. Сложность интеграции: 2 — drop-in hosted checkout + webhooks, код простой; реальная сложность не в интеграции, а в прохождении Domain Review/AUP..</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>РФ-резиденту недоступно; по VPN — доп. проверка и право отказать</t>
+          <t>Отказ на Domain Review по AUP (VPN = Restricted Category, а также запреты на «human services», advertising, community access); продавцы и покупатели РФ/Беларуси исключены; Paddle вправе удерживать Supplier Fees и не платить за «fraudulent, unlawful or illegal» продукты; termination по требованию платёжного провайдера, при попадании в Mastercard MATCH-лист; fee до 20 за chargeback/pre-alert; 14-дневные возвраты по усмотрению Paddle; жёсткая реакция на высокий chargeback rate; санкционный/гео-риск для российской аудитории. ПРАКТИКА: Paddle известен строгим ревью домена и AUP: публичная жалоба от 06.04.2026 на vendorabuse.com описывает «Massive Rejection List» и отказ уже после настройки аккаунта; гайд Boathouse описывает массовые отказы и повторные запросы информации. Требование истории процессинга отсутствует (новым бизнесам делают скидку), но по VPN-категории риск отказа высок. Позитивный сигнал: AdGuard (включая AdGuard VPN) — публичный кейс клиента Paddle, т.е. privacy/VPN-adjacent продукты Paddle всё же онбордит.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>https://www.paddle.com/help/start/intro-to-paddle/what-am-i-not-allowed-to-sell-on-paddle, https://www.paddle.com/pricing, https://www.paddle.com/help/start/intro-to-paddle/which-countries-are-supported-by-paddle</t>
+          <t>https://www.paddle.com/help/start/intro-to-paddle/what-am-i-not-allowed-to-sell-on-paddle, https://www.paddle.com/legal/terms, https://www.paddle.com/pricing, https://www.paddle.com/help/legal/sanctions/impact-of-sanctions-on-russia-and-belarus, https://www.paddle.com/help/start/account-verification/what-is-domain-verification, https://developer.paddle.com/concepts/payment-methods/</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -3955,82 +3955,82 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>lemon-squeezy</t>
+          <t>lemonsqueezy</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Lemon Squeezy (Sold through Link, LLC f/k/a Lemon Squeezy LLC — Stripe company)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>MoR (merchant of record)</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: прямой формулировки про VPN нет, но запрещены Services of any kind</t>
+          <t>MoR/SaaS-биллинг</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>серая зона: VPN, прокси и обход блокировок нигде не названы — ни в Prohibited Products, ни в Appendix A ToS, ни в списке Stripe (обновление 22.09.2026). Но под запрет попадают «Services of any kind», а VPN-подписка — это услуга, а не цифровой товар, плюс действует общий пункт «Any products restricted by our payment processing partners». Риск отказа/suspension высокий, но формального бана по слову «VPN» нет.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>РФ нет ни как продавцу, ни как покупателю</t>
+          <t>Резидент/юрлицо РФ — нет: банковские выплаты в РФ не поддерживаются, PayPal в РФ недоступен, а РФ входит в «Unsupported countries for purchases» — покупатели из России не смогут оплатить вообще, что критично для основной аудитории проекта. Банковские выплаты поддерживаются в Казахстане, Армении, ОАЭ, Турции, Узбекистане и др.; Грузии и Кыргызстана в списке банковских выплат нет (только PayPal, 200+ стран). Требование к мерчанту: возможность получать банковский или PayPal-выплаты в поддерживаемой стране.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Карты, PayPal — через MoR</t>
+          <t>До 21 платёжного метода, включая карты, PayPal и локальные методы (16 методов «из коробки»); PayPal-подписки поддерживаются, 95+ валют. Крипты и SBP нет.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>5% + $0.50; +1,5% за международные; +1,5% PayPal; +0,5% за подписки</t>
+          <t>5% + 50¢ за транзакцию; +1.5% за международные (вне США) платежи; +1.5% за PayPal; +0.5% за подписочные платежи (итого для Kometa-кейса ~7%+ на международных подписках). Chargeback — $15 dispute fee. Payout fees: банк вне США 1% за выплату, PayPal $0.50 (США) / 3% (максимум $30) вне США. Маркетинговые сборы: +5% за восстановленные корзины, +3%/+2% affiliate. Месячной платы нет; для чеков ниже $10 — custom pricing.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Нет setup fee</t>
+          <t>не подтверждено (публичной платы за онбординг/подключение нет, регистрация бесплатна)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Не раскрыт</t>
+          <t>Фиксированного rolling reserve % нет. Действует 13-дневный холд net sales: выплаты формируются 1-го и 15-го, становятся доступны 14-го и 28-го. ToS даёт LS право задерживать выплаты для risk assessment, приостанавливать аккаунты и «refund payouts without warning if there is evidence of fraud»; LS также вправе вернуть деньги покупателю в течение 60 дней по своему усмотрению.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Stripe-выплата бесплатна в США, +1% вне США; PayPal $0.50 в США / 3% вне (макс $30); Армения и Казахстан в списке, Грузии и Кыргызстана нет</t>
+          <t>Валюта: USD (банковский перевод конвертируется в локальную валюту по mid-market курсу; PayPal — всегда USD). Расписание: дважды в месяц — 1-го и 15-го формируется выплата, деньги уходят 14-го и 28-го, зачисление 1–5 дней. Минимальный порог $50 (недобор переносится на следующий цикл). Направления: банковский счёт или PayPal (Personal/Business, верифицированный).</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Юрлицо; РФ в unsupported countries; выплаты только в поддерживаемые страны</t>
+          <t>Юрлицо не требуется — регистрация возможна как физлицо, но обязательна возможность получать выплаты на банк/PayPal в поддерживаемой стране; при подключении банковских выплат возможна проверка личности («you may be asked to verify your identity for fraud prevention»). VAT/налоговый номер не обязателен — LS как MoR сам считает и платит налоги; налоговые данные можно добавить в payout invoice. Сайт: ToS 3.4(d) разрешает использовать сервис только для продажи собственных продуктов «through the website» — модель «только Telegram-бот» не предусмотрена, нужен стор/сайт (LS даёт hosted storefront и checkout-ссылки).</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>да: подписки с недельным/месячным/годовым циклом, бесплатные триалы, dunning и восстановление брошенных корзин и неудачных платежей, PayPal-подписки, лицензионные ключи, customer portal; карточные данные держит LS как MoR, MIT/автосписания поддерживаются.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Hosted checkout, Lemon.js, REST API, вебхуки; сложность 1/5</t>
+          <t>REST API + webhooks + hosted checkout, overlay checkout, hosted storefront, custom domain; документация хорошая (docs.lemonsqueezy.com, отдельные API-доки, официальный Laravel-пакет). Telegram-бот без сайта: checkout-ссылку технически можно отправить в бота, но LS ожидает собственный сайт/стор, а покупатели из РФ заблокированы на уровне платформы. Сложность интеграции: 2 — hosted checkout + API/webhooks, интеграция простая; сложность в модерации стора и в гео-ограничениях..</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Формулировка Services of any kind даёт право отказать; РФ-аудитория не обслуживается как покупатель</t>
+          <t>Критично: РФ исключена и как рынок покупателя (unsupported countries for purchases), и как страна выплат — основная аудитория Kometa не сможет платить. Платформа в переходном периоде: команда LS строит Stripe Managed Payments, поддержка замедлена, планируется миграция пользователей. Suspension без предупреждения за prohibited products, $15 dispute fee, 60-дневное право на возврат, задержка выплат для risk assessment, жалобы на агрессивный fraud-фильтр, блокирующий реальных покупателей. ПРАКТИКА: Онбордит небольшие цифровые бизнесы без истории процессинга, но по VPN-кейсам публичных подтверждений приёма нет — не подтверждено. Известны жалобы на fraud-детект, отклоняющий реальных покупателей (onetwothreesend.com). В терминах ToS LS — «reseller»/supplier-модель с выплатами дважды в месяц.</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>https://docs.lemonsqueezy.com/help/getting-started/prohibited-products, https://docs.lemonsqueezy.com/help/getting-started/fees, https://docs.lemonsqueezy.com/help/getting-started/supported-countries</t>
+          <t>https://docs.lemonsqueezy.com/help/getting-started/prohibited-products, https://www.lemonsqueezy.com/terms, https://docs.lemonsqueezy.com/help/getting-started/getting-paid, https://docs.lemonsqueezy.com/help/getting-started/fees, https://docs.lemonsqueezy.com/help/getting-started/supported-countries, https://www.lemonsqueezy.com/blog/2026-update</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>FastSpring</t>
+          <t>FastSpring (Bright Market, LLC dba FastSpring; FastSpring B.V.; SalesRight Technologies ULC)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>MoR (merchant of record)</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: публичного списка с VPN нет</t>
+          <t>MoR/SaaS-биллинг</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>серая зона: VPN, прокси, «circumvention» и privacy-инструменты не упомянуты ни в Vendor ToS (§4.5), ни в Digital Retailer Terms (§6.2), ни в Restricted Countries. Запрещены только adult, tobacco, pharma, gambling, hate/violence, third-party processing и «any form of unlawful activity»; есть широкая формулировка про продукты, которые «do not contain devices which are intended to be used to perform illegal activities». Явного разрешения нет — решение принимает ручной underwriting.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>РФ не подтверждено</t>
+          <t>Резидент/юрлицо РФ — нет: Россия в списке «Prohibited Countries and Territories» (Беларусь, Куба, Иран, КНДР, Палестина, Россия, Сомали, Сирия, Крым/Донецк/Луганск; Венесуэла — только для продавцов). Запрет распространяется и на продавцов, и на покупателей. Страны KZ, AM, GE, KG, UAE в запретном списке не значатся → формально допустимы при соблюдении санкционных требований США (в ToS при этом сохранился технический «Addendum for Vendors in Russia», который перекрывается Restricted Countries).</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Карты, PayPal, локальные методы — через MoR</t>
+          <t>Карты, PayPal, SEPA/ACH банковские переводы и wire transfer (подтверждено справочными страницами SEPA/ACH и Wire Payments), локализованные методы и электронные кошельки; для ACH и wire заявлены скидки. Полный актуальный перечень методов на сайте не публикуется — не подтверждено. Крипты нет.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>По запросу (revenue-sharing, ставка на встрече с менеджером)</t>
+          <t>по запросу (не публикуется) — pricing-страница перешла на «Build A Custom Quote»: единая flat-rate ставка зависит от GTV, числа транзакций и географии, публичных процентов больше нет (прежние публичные 5.9% + 95¢ не подтверждаются текущим сайтом). Опубликованы только дополнительные сборы: $20 за chargeback, $20 за chargeback prevention alert, FX-конвертация 3.5% (AUD/CAD/CHF/DKK/EUR/GBP/HKD/JPY/NZD/SEK/SGD/USD/ZAR) и 5.5% (прочие), $10 за возврат чеком и $30 за ручной банковский перевод, $15 за return SEPA/ACH, $20/мес за Abandoned Account, комиссии Hyperwallet по тарифам провайдера.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Не публикуется</t>
+          <t>$150 Vendor Risk Verification Fee — «no more than annually», применяется к продавцам с годовым GTV менее $5,000 после первого года работы на платформе (ближайший аналог setup fee; иных стартовых платежей не публикуется).</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Не раскрыт</t>
+          <t>Фиксированного rolling reserve % нет — по запросу (не публикуется). Прямо оговорено: «FastSpring has the right to implement a hold on your payouts as soon as we onboard your account» — холд может быть выставлен сразу при онбординге и снимается по усмотрению FastSpring. Резервы дискреционные: FastSpring может удерживать часть баланса для покрытия будущих chargeback/refund/assessments, а после расторжения — до 180 дней (в исключительных случаях до одного года).</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>На счёт продавца; график, минимум и валюты не раскрыты</t>
+          <t>Валюта: USD (если иное не согласовано в Order Form); расходы на FX-конвертацию — на продавце. Расписание: дважды в месяц — период 1 (1–14 число) и период 2 (15-е — конец месяца), выплата примерно на 15-й календарный день после конца периода. Минимум $25 за период, $100 при международном wire. Направления: банковский перевод/wire, возможны выплаты через Hyperwallet.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Юрлицо (Bright Market LLC US, FastSpring Limited UK, FastSpring B.V. NL)</t>
+          <t>Требуется бизнес-регистрация: Vendor ToS §4.1 прямо перечисляет «personal information of Vendor's beneficial owners, business registration information, tax identification number, and bank account information»; заполняется Tax Questionnaire (W-8/W-9) для налогового статуса; онбординг и underwriting — на усмотрение FastSpring, при отказе причины не сообщаются. Наличие сайта подразумевается (в форме квоты поле «Website» обязательно). Возможность онбординга физлица/самозанятого и требования к VAT/GST-номеру публично не описаны — не подтверждено.</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>да: subscription management и recurring payments, восстановление неудачных платежей/dunning, апгрейды-даунгрейды, B2B digital invoicing и interactive quotes; как MoR FastSpring держит карточные данные, берёт на себя налоги, chargeback liability и buyer support.</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Hosted checkout, Store Builder Library, API, вебхуки; сложность 2/5</t>
+          <t>REST API, webhooks, Store Builder Library, hosted и embedded/branded checkout, тестовая среда, подробная документация (developer.fastspring.com, есть llms.txt-индекс и code samples). Продажа возможна только через продукты, зарегистрированные в дашборде FastSpring; Telegram-бот без сайта — не подтверждено (сайт ожидается при онбординге/квоте). Сложность интеграции: 3 — API и Store Builder Library мощные, но онбординг sales-led (квота), underwriting и настройка стора требуют времени..</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Ставка обсуждается индивидуально; политика по VPN не опубликована -&gt; риск отказа</t>
+          <t>Дискреционные резервы и возможность холда выплат с первого дня работы; termination без обязательства объяснять причины (в т.ч. по указанию платёжного процессора/спонсорского банка); продавцы и покупатели РФ исключены; риск-скрининг может отменять заказы и блокировать платежи покупателей; все assessments карточных брендов перекладываются на продавца; при excessive chargeback FastSpring вправе приостановить продажи. ПРАКТИКА: Онбордит малые и средние цифровые бизнесы, но через underwriting, а не самообслуживание: есть публичные жалобы продавцов на отмену/отклонение заказов из-за risk-скрининга (KB Avid, форум Sonic Charge). Рейтинг на Trustpilot — около 2.9/5 (2026, сторонний источник). Гарантий онбординга нового бизнеса без истории процессинга нет — не подтверждено.</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>https://fastspring.com/pricing, https://fastspring.com/legal/, https://developer.fastspring.com/</t>
+          <t>https://fastspring.com/terms-use/seller-terms-service/, https://fastspring.com/terms-use/seller-terms-service/digital-retailer/, https://fastspring.com/terms-use/restricted-countries/, https://fastspring.com/additional-fees/, https://fastspring.com/pricing/, https://fastspring.com/llms.txt</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -4119,82 +4119,82 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>paypro-global</t>
+          <t>payproglobal</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PayPro Global</t>
+          <t>PayPro Global, Inc. (Toronto, Ontario, Canada)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>MoR (merchant of record)</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>НЕТ: прямой запрет — circumvent locks or geographic or IP-based restrictions, including through usage of VPN, proxy or anonymous user facilities</t>
+          <t>нет — прямой и широкий запрет: сервисы, позволяющие обходить гео-/IP-ограничения через VPN, прокси или анонимные сервисы, включены в официальный Prohibited Products List. В текущем виде VPN-продукт Kometa через PayPro Global провести нельзя.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>РФ не подтверждено</t>
+          <t>не подтверждено: перечень стран, из которых PayPro Global принимает продавцов, публично не раскрыт (в документах и на сайте его нет). На сайте заявлены продажи в 200+ странах, но это сторона покупателя. РФ и Беларусь в публичных документах не упоминаются вовсе; формально юрлица в KZ/AM/GE/KG/UAE не исключены, однако подтверждения нет.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Карты, PayPal, WebMoney, Wire — через MoR</t>
+          <t>72 метода и 140+ валют: карты Visa, Mastercard, Amex, Maestro, JCB, UnionPay, Discover, Diners Club, CarteBleue; электронные кошельки PayPal, Apple Pay, Google Pay, Alipay, WeChat Pay, MercadoPago, WebMoney, Bancontact/MrCash, ToditoCash, DragonPay, Mach Pay, Solo; instant payments iDEAL, Sofort, Trustly, EPS, Przelewy24, Pix, Multibanco, Nordea, OP-Pohjola, CIMB Clicks, Finnish Banks; банковские переводы и Purchase Order; наличные Boleto Bancario и OXXO. Крипты нет.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>По запросу; публично раскрыты только payout-комиссии: Payoneer $2, WebMoney 3,5% + $5, Wire $21, ACH $3, PayPal 2% (макс $20)</t>
+          <t>по запросу (не публикуется): страница Pricing не содержит цифр («You won't see a price tag»), комиссия определена в Exhibit A Reseller Agreement, который публично не приложен к PDF. Опубликованы только: chargeback fee $15.00 плюс процессорные сборы, списываемые с продавца; покупатель вправе вернуть деньги в течение 14 дней за счёт продавца; расходы на affiliate commission вычитаются из Proceeds.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Не публикуется</t>
+          <t>не подтверждено (публичной платы за подключение/онбординг нет)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Не раскрыт</t>
+          <t>Фиксированного rolling reserve % нет — по запросу (не публикуется). Есть termination-hold: после расторжения договора выплаты Net Proceeds приостанавливаются на 6 месяцев, затем вся сумма выплачивается одним платежом (RA §4.9); при нехватке полученных средств на покрытие chargeback и возвратов PayPro вправе заморозить аккаунт и зачесть суммы из будущих выплат (RA §4.7), а при подозрении на фрод — удерживать все выплаты до завершения проверки.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>15-го числа каждого месяца, остаток прошлого месяца минус payout-комиссии</t>
+          <t>Ежемесячно, в течение 15 дней после окончания календарного месяца, в котором получены Proceeds; минимальная выплата $400 — суммы меньше порога аккумулируются до его достижения (RA §4.3–4.4). Способ выплаты выбирается и согласуется через кабинет (банк/иные методы), конкретные валюты и направления (Wise/Payoneer/крипта) в публичном Reseller Agreement не указаны — не подтверждено.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Зарегистрированная компания; VAT/GST берёт на себя</t>
+          <t>не подтверждено: Reseller Agreement оперирует понятием «Author» (автор ПО) и требует наличия прав на продукт/ресейлерской сертификации, но требований к юрлицу, допустимости физлица/самозанятого, VAT/GST-номеру и глубине KYC/KYB в публичных документах нет. Продукт регистрируется на платформе; наличие сайта/страницы продукта подразумевается, но явного требования не опубликовано. Онбординг sales-led: форма sign-up ведёт на демо/квоту.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>да: полный subscription management, ручные и автоматические продления, dunning, smart retries, free trials, customer portal, купоны, бандлы и volume discounts, License Management (страница Pricing). Как MoR держит карточные данные и отвечает за налоги/chargeback.</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Checkout pages, API, вебхуки, подписки и лицензии; сложность 2/5</t>
+          <t>API + IPN/webhooks + hosted checkout pages с кастомизацией полей и брендинга, 30+ языков, 140+ валют, cascading-роутинг для повышения авторизации; документация — developers.payproglobal.com (API reference, webhooks, checkout pages). Пригодность Telegram-бота без сайта — не подтверждено: публичных требований к сайту нет, но модель онбординга предполагает демо с продавцом и регистрацию продукта. Сложность интеграции: 3 — hosted checkout и API есть, но онбординг sales-led, документация заметно беднее, чем у Paddle/Stripe, а любая интеграция требует согласования с командой..</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>VPN прямо в списке запрещённых продуктов — не подключаться</t>
+          <t>VPN прямо запрещён — продукт в текущем виде не пройдёт комплаенс; 6-месячная заморозка выплат после расторжения; заморозка аккаунта при нехватке средств на chargeback/refunds; минимальный порог выплаты $400 — при чеке 199–1590 ₽ это очень долгое накопление; широкий список запретов (веб-хостинг, файлообмен, стриминг/IPTV, remote tech support, stored value); договор регулируется правом Онтарио (Канада), споры — арбитраж в Торонто. ПРАКТИКА: Заявлено 3000+ SaaS-бизнесов и клиенты вроде Epic Games/Garena/Clario, ссылки на отзывы G2, есть PCI-DSS и GDPR-бейджи. Независимых подтверждений онбординга малого бизнеса без истории процессинга и жалоб на заморозки/удержания в ходе проверки найти не удалось — не подтверждено.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>https://docs.payproglobal.com/documents/legal/prohibitedProducts.pdf, https://payproglobal.com/faq/</t>
+          <t>https://docs.payproglobal.com/documents/legal/prohibitedProducts.pdf, https://payproglobal.com/legal/, https://docs.payproglobal.com/documents/legal/PayProGlobalResellerAgreement.pdf, https://payproglobal.com/pricing/, https://payproglobal.com/payment-methods/, https://connect.payproglobal.com/sign-up/</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
@@ -4211,477 +4211,477 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>MoR (merchant of record)</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: в публичных политиках VPN, proxy и circumvent не упоминаются</t>
+          <t>MoR/SaaS-биллинг</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>да (с оговоркой). В письменной Acceptable Conduct Policy слова VPN/proxy/anonymizer НЕТ — список запретов общий и прямо назван неисчерпывающим, формально это «серая зона» текста. Но фактически VPN принимается: у Cleverbridge есть отдельная вертикаль Cybersecurity, и VPN-провайдер CyberGhost обслуживается через чекаут cleverbridge.com (живой поддомен cyberghostvpn-s.cleverbridge.com, ссылка на чекаут CyberGhost Premium на cleverbridge.com/848/). Для Kometa это означает: VPN не запрещён, но решение принимается на KYC/due-diligence по продукту и рынкам.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>США и Германия (юрконтур); РФ не подтверждено</t>
+          <t>Контрактные лица: Cleverbridge GmbH (Tunisstraße 19-23, Кёльн, ФРГ, HRB 111750, VAT DE244822460), Cleverbridge Inc. (Чикаго, США), Cleverbridge Ltd. (Бирмингем, Великобритания, рег. №16655837); платежное юрлицо — Cleverbridge Financial Services GmbH (Кёльн, регулятор — BaFin, HRB 87383). Приём резидента РФ / российской компании: не подтверждено — прямой страновой запрет для клиента в AUP и MSA не найден, но онбординг включает проверки санкций, PEP и публичной информации (onboarding-path, раздел 4), а раздел 12.1 MoR-термс даёт право отклонять заказы из санкционных стран. Практически для резидента РФ это крайне вероятный блокер, однако формального подтверждения нет. Приём юрлиц Казахстана/Армении/Грузии/Кыргызстана/ОАЭ исследованиями не подтверждён и не опровергнут — не подтверждено.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Карты и локальные методы — через MoR</t>
+          <t>Карты, PayPal, прямое дебетование (direct debit), банковский перевод, оплата по счёту (invoice), локальные методы; заявлено покрытие 190+ (по MoR-термс/маркетингу — до 240) рынков и 59 валют. Криптовалюты в проверенных источниках не упоминаются — не подтверждено.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>по запросу (не публикуется). Официальная страница https://grow.cleverbridge.com/pricing не содержит тарифов: «Get custom pricing»/«Get a Quote». В MoR-термс (п.7.1) Resale Fee = процент из Fees Table × Total Cart Value + фиксированная сумма, где и процент, и фикс заданы в индивидуальном Subscription Schedule; там же — FX-надбавка за конвертацию. Сторонний бенчмарк (Vendr, обновлено февраль 2026, НЕ официальные данные): 3,5–8% от GMV, медиана сделки $3,482/год; начальные котировки мид-маркет 5–7%, согласованные 4–6%; enterprise 2,5–5% + платформенная плата $50k–200k/год; сквозные платёжные издержки 2–3%; FX 1–2% сверх спота; заявлено, что TCO на 20–40% выше заявленной ставки.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Не публикуется</t>
+          <t>по запросу (не публикуется). Официально не опубликован. Сторонний бенчмарк Vendr: разовые внедрение/онбординг $10,000–$100,000+ в зависимости от сложности; поддержка/аккаунт-менеджмент $15,000–$50,000+/год.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Не раскрыт</t>
+          <t>Опубликован частично. MoR-термс, п.5.8 (Post-Termination/Product Suspension Temporary Withholding): при уведомлении о расторжении/непродлении/приостановке продукта Cleverbridge вправе удержать сумму всех Refunds и Chargebacks за 6 месяцев, предшествующих уведомлению, причём эта сумма удваивается, если расторжение/приостановка происходит в течение 6 месяцев после даты вступления Subscription Schedule в силу; плюс 3% всей выручки по товарам с отложенной поставкой (ваучеры). Неиспользованный остаток возвращается через 6 месяцев после вступления расторжения в силу (по отложенной поставке — через 6 недель). Отдельно (п.6.1): если сумма чарджбэков и рефандов превышает причитающееся клиенту, клиент доплачивает в течение 30 дней. Постоянного «rolling reserve %» в договоре нет — вместо него пост-терминационный ретейнер.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Публично не раскрыты</t>
+          <t>Ежемесячно. Клиринг-период — месяц; выплата перечисляется на указанный банковский счёт не позднее 16-го числа следующего месяца (если 16-е — выходной/праздник, то в следующий рабочий день); зачисление в банк занимает 1–5 дней. Само-биллинг инвойс/кредит-нота формируется автоматически, к нему прилагается clearing report. Валюта выплаты задаётся в Subscription Schedule; выплаты идут за вычетом налогов (в т.ч. withholding tax, digital services taxes). Способы: только банковский счёт (Wise/Payoneer/крипта в проверенных документах не упоминаются — не подтверждено). Есть право set-off (п.6.2).</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Ориентирован на крупных software/SaaS-вендоров; юрлицо</t>
+          <t>Нужно юрлицо/компания: онбординг-чеклист требует company-register extract, учредительные документы, подтверждение зарегистрированного/операционного адреса, ownership structure chart, ID документы, proof of authority to represent. Возможность оформления на физлицо/самозанятого: не подтверждено (все формулировки — «your company»/«the business, its owners and representatives»; отдельного individual-пути, в отличие от 2Checkout, в документации нет). KYC/KYB: полноценный — идентичность компании, ownership/control/authority, санкционные и PEP-проверки, проверка продуктов/клиентского пути/целевых рынков, платёжные, fraud, кредитные, налоговые, юридические и репутационные факторы; возможен исход «Not approved» или «Approved with conditions». Обязателен полноценный сайт: product pages, прозрачные цены и условия подписки, checkout URLs/скриншоты, fulfillment, post-purchase письма, доступная поддержка, refund/cancellation policy, ToS, privacy notice. Экспорт-контроль: требуется предоставить ECCN/EAR99-классификацию продукта. Налоговый номер: VAT ID компании нужен для контрактного лица (у самой Cleverbridge GmbH VAT DE244822460); требование VAT/GST именно от клиента прямо не сформулировано — не подтверждено.</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Да. Подписки и продления — ядро платформы (разделы документации Subscriptions, Customer incentives, Protect and recover revenue). В онбординг-чеклисте прямо перечислены «subscription length and renewal frequency», «trial terms and introductory pricing», «cancellation and refund terms». Есть chargeback prevention, revenue assurance и dunning-инструменты. Токенизация/MIT прямо не описана в проверенных страницах — не подтверждено, но рекуррентное продление заявлено.</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Enterpise-онбординг: менеджер, согласование договора; сложность 4/5</t>
+          <t>Хостед-чекаут Online Store + Commerce Assistant (CA)/Subscription Commerce Manager (SCM) для управления продуктами, REST API (dev.cleverbridge.com), вебхуки (PaidOrderNotification), готовые интеграции с CRM/ERP/бухгалтерией/аналитикой, SFTP-выгрузка клиринг-файлов. Telegram-бот без сайта: скорее всего не подойдёт — онбординг прямо требует product pages, product/checkout URLs, скриншоты чекаута, ToS, privacy notice и refund policy; в разделе «Restrictions and special requirements» отдельно запрашивают информацию о категориях, которые платёжные провайдеры и карточные сети считают повышенно рискованными. Приемлемость bot-only витрины без сайта не подтверждена — не подтверждено. Сложность интеграции: 4 — хостед-чекаут снижает объём кода, но вход энтерпрайзный: обязательный sales-процесс, KYC/due diligence с исходом «Not approved», обязательный сайт и кастомная имплементация (по сторонним оценкам — недели-месяцы)..</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Долгое подключение; тематика VPN не подтверждена; не для микробизнеса</t>
+          <t>1) Энтерпрайз-андеррайтинг: возможен отказ или одобрение с условиями (лимиты по продуктам, рынкам, объёмам). 2) Пост-терминационный ретейнер: удержание суммы всех рефандов и чарджбэков за 6 месяцев (с удвоением при расторжении в первые 6 месяцев) и возврат остатка только через 6 месяцев — деньги могут «зависнуть» надолго. 3) Chargeback Limit = 0,5% (низший из порогов Mastercard ECP/EFM и Visa VAMP); при превышении — приостановка методов оплаты, продажи продукта и автосписаний, а также Termination for Cause. 4) Set-off и право списывать любые причитающиеся суммы. 5) Санкционный/географический риск: проверки санкций и PEP, право отклонять заказы из санкционных стран; резидент РФ — вероятный отказ. 6) Односторонняя приостановка продукта «in its sole discretion» при любом юридическом или коммерческом риске (п.2.2 MoR-термс). 7) Риск, что бот без сайта не пройдёт review. ПРАКТИКА: Модель — enterprise-first, не self-service: продажи только через «Talk to Sales»/«Get a Quote», публичного тарифного плана и онлайн-регистрации нет. Независимые источники подтверждают: сравнение конкурента Dodo Payments прямо указывает «Custom pricing only. Requires sales call and volume commitment», «No self-service. Requires enterprise sales process and custom implementation», «Weeks to months for enterprise implementation» (это маркетинг конкурента — предвзято, но направление подтверждается отсутствием цен на сайте). Vendr: медианный контракт $3,482/год при разовом внедрении $10k–100k+. Клиентская база — крупные вендоры: Red Hat, SUSE, Sony, Veeam, Tenable, Jamf, Ashampoo, Parallels, CyberGhost. Жалоб на замороженные средства или внезапные расторжения конкретно по Cleverbridge в ходе исследования НЕ найдено — в отличие от Digital River/MyCommerce. Онбординг малого бизнеса без истории процессинга прямо не подтверждён и не опровергнут — не подтверждено.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>https://grow.cleverbridge.com/hubfs/Acceptable%20Conduct%20Policy%20as%20of%20Sept%202022.pdf, https://grow.cleverbridge.com/hubfs/Cleverbridge%20Master%20Subscription%20Agreement.pdf, https://www.cleverbridge.com/corporate/pricing/</t>
+          <t>https://grow.cleverbridge.com/hubfs/Acceptable%20Conduct%20Policy%20as%20of%20Sept%202022.pdf, https://grow.cleverbridge.com/hubfs/Cleverbridge%20Solution%20Specific%20Terms%20%E2%80%93%20Merchant%20of%20Record.pdf, https://docs.cleverbridge.com/docs/get-started/become-a-cleverbridge-client/onboarding-path/, https://docs.cleverbridge.com/docs/cleveressentials/clearing-and-payouts/, https://www.netify.ai/resources/hostnames/cyberghostvpn-s.cleverbridge.com, https://www.vendr.com/marketplace/cleverbridge</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2checkout</t>
+          <t>mycommerce</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2Checkout / Verifone</t>
+          <t>MyCommerce (Digital River MyCommerce / Share-It)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>MoR + PSP</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: VPN в Prohibited Product List не назван, ближайшее — Remote Access Services</t>
+          <t>MoR/SaaS-биллинг</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>серая зона, но вопрос практический смысла не имеет: в 2026 г. действующей политики нет, потому что сервиса нет. Платформа MyCommerce — это торговая марка германского юрлица Digital River GmbH (оно же Share-It), которое ушло в неплатёжеспособность; домен mycommerce.com теперь занят не связанным с платежами испаноязычным классифайдом («Compra y Vende de Todo, a Todos», © 2026 MyCommerce). VPN отдельно не запрещался и не разрешался; MoR исторически продавал софт и антивирусы (EnigmaSoft SpyHunter), но онбординг новых мерчантов прекращён.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>РФ не подтверждено</t>
+          <t>Исторически: контрактное лицо для не-США мерчантов — Digital River GmbH, Scheidtweilerstraße 4, 50933 Кёльн, Германия; для США/Канады — Minnesota. Territory по MSA: «All countries in the world except (i) countries to which export or re-export of any Product is prohibited... and (ii) countries excluded by you». Применимое право: Германия, исключительная подсудность Кёльн (для не-США). В 2026 г. онбординг не ведётся — приём резидента РФ, как и любых других стран, не подтверждено (сервис не работает).</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Карты, PayPal, локальные методы</t>
+          <t>не подтверждено. Платформа как MoR реселлила цифровые товары и принимала карты, PayPal и локальные методы, но проверяемого актуального перечня на 2026 г. нет — сайт и документация мерчанта больше не существуют.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>по запросу (не публикуется). MSA п.5(a): DR Margin — «the revenue share percentage and/or flat fee that you select upon registration», то есть индивидуальная ставка, публичного тарифа нет. Показательно для оценки: по сообщениям мерчантов на Hacker News (октябрь 2024) маржа MyCommerce составляла «between 5 and 10%, depending on order size and how much of currency exchange they take». Chargeback fee также не публиковался: «in an amount agreed between the parties and/or further described in the Administration Interface».</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Не публикуется</t>
+          <t>не подтверждено (публичного setup/onboarding fee нет). Известно обратное: в 2024 г. компания ввела новые платежи В СВОЮ ПОЛЬЗУ — по сообщению мерчанта на Hacker News от 18.10.2024 в новых условиях появилась месячная плата «US$100/month for me - unsure if it varies per customer», почасовая плата за поддержку и повышенный порог выплат, причём суммы комиссий не были указаны в письмах и поддержка не могла их назвать.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Не раскрыт</t>
+          <t>Фиксированного процента нет — удержание дискреционное. MSA п.5(e): «Digital River may determine to exceptionally holdback some or all of the money that is in your account if Digital River has reason to believe that it might be necessary to cover future refunds, charges against your account, or other liabilities... Digital River will keep any held-back amounts only for a reasonable time as determined in our sole discretion». Плюс п.14(k) (Change in Circumstances): при подозрении на нарушение закона или существенный риск Digital River вправе потребовать создать reserve account, ввести задержку периодических выплат, приостановить чекаут или расторгнуть договор.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Публично не раскрыты</t>
+          <t>По договору: отчёт (statement) формируется в течение 30 календарных дней после окончания календарного месяца, выплата Net Purchase Price — в течение 30 дней после Statement Date, то есть фактически до ~T+60 от конца месяца (это подтверждается жалобами: в 2024 г. условия были ухудшены «payments will now be sent 60 days instead of 15 days after the month»). Валюта — remittance currency, выбираемая в Administration Interface. Минимальный порог выплаты повышался; по сообщению мерчанта в октябре 2024 г. — US$2500. На практике: выплаты прекратились с июля 2024 г. и не были восстановлены; заявления о неплатёжеспособности, затем insolvency. Способ — банковский перевод.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Юрлицо, KYC; для high-risk — согласование risk-командой Verifone</t>
+          <t>Юрлицо: MSA адресован «you» и «Company»; п.9(b) требует от клиента гарантий прав на продукты; п.14(c) обязывает предоставить экспортные классификации (ECL, USML, HTS) и назначить ответственного за экспорт-контроль. Возможность оформления на физлицо/самозанятого: не подтверждено. Налоги: клиент сам отвечает за сбор и перечисление sales/GST/VAT по продаже продуктов Digital River и по запросу выдаёт валидный tax invoice на VAT. KYC: в 2024 г. Digital River массово разослал требования пройти новые KYC-формы («Digital River emailed out of the blue a few months back saying we need to do new Know-Your-Customer paperwork. The forms are painful... it seems to take a week or more for any response to a ticket»). Требования к сайту — не подтверждено.</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Исторически да: платформа поддерживала подписки, продления, лицензионные ключи и возвраты/отмены подписок (MSA п.4(d), 4(f) про Extended Download Service), а также авто-renewal. Управление dunning, free trials и токенизацией/MIT в проверенных источниках не описано — не подтверждено. В 2026 г. неприменимо ввиду отсутствия сервиса.</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Hosted checkout, API, подписки 2Subscribe; сложность 3/5</t>
+          <t>не подтверждено для 2026 г. Исторически: hosted checkout («Checkout Solution»), Administration Interface для управления продуктами, отчётность, email/download-фулфилмент, возможность самостоятельного фулфилмента клиентом (MSA п.4(e)), возвраты и обработка chargeback'ов в течение 2 месяцев после расторжения (п.6(c)). Telegram-бот без сайта: не подтверждено и, учитывая состояние сервиса, неактуально. Сложность интеграции: 5 — интеграция перестала иметь смысл: платформа не работает, онбординг отсутствует, деньги мерчантов не выплачены; любой новый контракт невозможен..</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Оговорка: бизнес может быть не одобрен независимо от списка</t>
+          <t>Максимальный риск, реализовавшийся полностью: 1) Прекращение выплат — мерчанты не получали деньги с июля 2024 г.; суммы потерь в публичных сообщениях: $20k, «a few grand», «tens of thousands», $90,000 у одной компании. 2) Односторонний пересмотр договора: в августе-сентябре 2024 г. срок выплат растянут с 15 до 60 дней, введена месячная плата (~$100/мес), почасовая плата за поддержку, повышен порог выплат — без явного указания сумм в уведомлениях. 3) Инсолвентность и банкротство: Digital River GmbH подала заявление о несостоятельности (объявлено EnigmaSoft 30.01.2025); Digital River начала сворачивание 28.01.2025. 4) Юридический риск для не-США мерчантов: подсудность Кёльн, Германия; мерчанты отмечали, что «the German entity probably has no assets», а иски экономически бессмысленны. 5) Налоговый риск: в ряде юрисдикций (пример Сербии в обсуждении) выданный инвойс считается реализованным доходом даже без оплаты. 6) Репутационный: открытые публичные обвинения в мошенничестве и «ponzi scheme» на Hacker News, коллективные обращения к юристам в Кёльне (Strafanzeige, Insolvenzantrag, dinglicher Arrest — инициатива Byteplant), обсуждения class action. ПРАКТИКА: Нет — и это самый яркий негативный кейс в подборке. Малый бизнес принимался десятилетиями (мерчанты «since 2001», «since 2002 (when it was still SWReg)», «20+ years», «since 2005», «since 2016»), но без какой-либо защиты: выплаты прекратились без предупреждения, поддержка не помогала, условия ухудшены задним числом. Прямые цитаты мерчантов (Hacker News, 18.10.2024): «We're a small family company and the $20k MyCommerce owes us is a big deal»; «They now owe us tens of thousands of dollars. And with the massive exodus, I do not have high hopes to get any of that money at all»; «My balance is above their new payout threshold (US$2500), but it wouldn't surprise me if they sit on the money and let the monthly fees eat into it until it's back below the threshold»; «We have no illusions we'll ever get the money DR/MyCommerce owes us». Дополнительно обсуждалось, что гибель могли ускорить последствия бана Kaspersky в США (крупнейший клиент) и долг перед кредитором Cerberus Business Finance.</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20240910215446/https://www.2checkout.com/legal/acceptance/</t>
+          <t>https://www.datanumen.com/downloads/lawcase/mycommerce-master-services-agreement-6.1.pdf, https://www.theregister.com/software/2024/10/15/digital-river-delays-sales-payments-to-vendors-since-july/, https://news.ycombinator.com/item?id=41847953, https://en.wikipedia.org/wiki/Digital_River</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>segpay</t>
+          <t>2checkout</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SegPay</t>
+          <t>2Checkout (Verifone) — планы 2Sell / 2Subscribe / 2Monetize / Enterprise</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>High-risk эквайринг</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: публичные страницы закрыты антибот-защитой, AUP проверить не удалось</t>
+          <t>MoR/SaaS-биллинг — гибрид: 2Monetize это полноценный Merchant of Record (включая global tax &amp; regulatory compliance), а 2Sell/2Subscribe — обычный PSP-шлюз. Это НЕ high-risk эквайринг.</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>серая зона (де-факто отказ): слова «VPN» в Prohibited Product List нет, но VPN попадает под п.44 «Remote Access Services, Technical Support Services», а сам список оговорён как «merely representative, but not exhaustive» и «your business practices, products and services may not be approved ... regardless of whether they appear below». Плюс полный запрет РФ и запрет приёма мерчантов из Грузии.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>РФ не подтверждено</t>
+          <t>Обслуживает мерчантов в большинстве стран мира, НО Россия прямо исключена: в разделе «OFAC-Sanctioned Countries» указано «The Russian Federation», а политика гласит «2Checkout does not accept merchants or businesses from these prohibited countries». Вывод: российский резидент и российское юрлицо подключиться не могут — это жёсткий стоп, а не серая зона. Отдельно для аккаунтов 2Sell/2Subscribe закрыт список стран, в который входит Грузия (Georgia); для 2Monetize ограничение по стране иное. Казахстан, Армения, Кыргызстан и ОАЭ ни в санкционном, ни в PSP-стоп-листах не значатся — оттуда подключение теоретически возможно. Обслуживание покупателей (shopper transactions) из ограниченных стран «allowed based on internal risk assessment». Важно: физлицо без компании допускается — «Can I create a 2Checkout account as an individual, without a company? Yes, this option is currently available in the application form for any type of account you may choose to apply for.»</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Карты, профильный рекуррент</t>
+          <t>45+ методов по заявлению вендора: карты (Visa/Mastercard/Amex), PayPal и PayPal Express, Apple Pay, Google Pay, iDEAL, Trustly, Boleto/Pix, Alipay, WeChat Pay, банковские переводы, Direct Debit, чеки/eChecks, локальные методы (зависят от тарифа и страны мерчанта). Формулировка тарифной страницы: «The prices are for standard payment methods like Credit Cards and Paypal. For advanced localized payment methods (Eg: Boleto Bancario, Kombini) there are separate price points». Рекуррент поддерживается не по всем методам.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>2Sell — 3.5% + $0.35 за успешную продажу; 2Subscribe — 4.5% + $0.45; 2Monetize — «Tailored pricing» (не публикуется); 4Enterprise — «Custom Pricing». Дополнительно: «In specific countries an additional 2% fee applies to accept payments from shoppers outside your own country» (список стран в Knowledge Center). Chargeback: «If your chargeback rate is less than 0.65%, the chargeback fee is $36/€31/£30. If your chargeback rate is 0.65% or more, the chargeback fee is $50/€50/£50» — то есть пороговая схема. Платёж на банковский счёт (wire) — 15 USD/GBP/EUR, только для 2Sell и 2Subscribe; PayPal — без комиссии 2Checkout; Pre-paid 2Checkout MasterCard (Payoneer) — без комиссии 2Checkout. Месячная абонплата/минимум оборота не публикуется. Минимальный порог выплаты: 50 USD/EUR/GBP (2Sell, 2Subscribe) или 100 USD/EUR/GBP (reseller на 2Monetize).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>нет — на тарифной странице прямо: «There are no hidden fees and no extra charges for fraud protection or recurring payments. Pay only for what you use.» При этом оговорено: «If you need advanced support to get up and running, you might be charged a fee for professional services» — размер платы за professional services не публикуется.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>Есть, и это rolling reserve: «a percentage of your total sales is held in your account at all times. This amount is called a deposit and varies for each merchant; it corresponds to a set percentage of sales that has been designated to stay in your 2Checkout merchant account on a rolling 90-day basis.» Конкретный процент не публикуется — «Deposit rates are set in proportion to the level of risk of each merchant» → по запросу (не публикуется). Риск-профиль оценивается вручную, для intangible goods депозит выше. Депозит растёт при всплеске chargeback/refund.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Публично не раскрыты</t>
+          <t>Периодичность по умолчанию: 2Sell и 2Subscribe — еженедельно (выплаты 16-го и 23-го числа текущего месяца, 1-го и 8-го числа следующего); 2Monetize — ежемесячно (16-го числа следующего месяца). Изменение периода — только с одобрения 2Checkout Finance. Минимум 50 или 100 USD/EUR/GBP в зависимости от пакета. Wire — 2–5 рабочих дней, PayPal — instant, Payoneer — 1 рабочий день. Доступна только ОДНА валюта выплаты: USD, EUR или GBP. Критично: «All requests for modifying or changing the payout details of your account must be approved by the 2Checkout's Financial department... While your request is pending approval from the 2Checkout Financial department, your account will be placed in 'Restricted' mode (which means that you are able to process new sales, but your payouts will be temporarily put on hold).» Проверка новых реквизитов — до 2 дней.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Юрлицо в US/EU, KYC/KYB</t>
+          <t>Юрлицо не обязательно: физлицо без компании допускается («Yes, this option is currently available in the application form for any type of account»). KYC для individuals: «Valid government-issued ID such as a passport or national identity card» + «Valid address proof, such as electricity bill, telephone bill (no older than two months from the date when you upload the scanned copies)» + дополнительные документы. Для компаний: «Company ownership documents (such as Articles of Incorporation or Organization, showing beneficial ownership)», налоговые документы («Europe - TIN», «US - SSN / TIN / PTIN»), «Valid government-issued ID... Include DOB, for anybody with 10% or more ownership in the company». Все документы — сканы, не просроченные. Обязательно одобрение underwriting-команды (до этого аккаунт в demo mode). Сайт: обязателен URL — buy-link вставляется «into the web page that will host the purchase button/link»; для 2Sell/2Subscribe можно несколько URL, «The request to add a new URL on the account requires risk review and approval»; для 2Monetize «this is limited to pointing towards 1 URL» и каждый новый сайт требует отдельного аккаунта. Требуются размещённые на сайте refund policy и privacy policy, полное описание продукта и сроков доставки.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Да, это сильная сторона 2Subscribe/2Monetize: полный жизненный цикл подписки («Cover entire subscription lifecycle», renewal flows, upgrades, «Manage renewals and upgrades»), dunning/churn-prevention («Subscription churn prevention campaigns», «For Increased Renewal Recovery» как add-on), free trials (отдельные флоу «ConvertPlus trials flow», «Inline trials flow», «Trial conversion links», «Trial and regular products in the same shopping cart»), автопродление и 3D Secure flow, токенизация и MIT — «Payment flow with 2Pay token», «Use UniTokens», «Payment flow with 1-Click purchase», «Copy payment info», «Place a renewal order», «Place order with existing payment methods». Есть аналитика подписок и churn.</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Hosted-страница оплаты + API; сложность 3/5</t>
+          <t>Способы: хостируемый checkout (ConvertPlus, InLine Checkout, Default Flows), buy-links / payment links (в т.ч. генерация ссылок из панели), REST/JSON-RPC API 6.0, legacy SOAP API 6.0, webhooks, тестовые заказы и sandbox, 120+ готовых коннекторов (WooCommerce, Shopify, Magento 2, WHMCS, Wix, Ecwid, PrestaShop и др.). Документация обширная и качественная (docs.2checkout.com с Markdown-версиями и llms.txt). Магазин без сайта: сам buy-link технически можно разместить где угодно, но аккаунт всё равно требует зарегистрированный и одобренный URL, а под 2Monetize — ровно один сайт на аккаунт; поэтому чисто Telegram-бот без сайта, скорее всего, не пройдёт underwriting. Практический обход — сделать простой сайт-витрину с refund/privacy policy и вести трафик из бота. Сложность интеграции: 3 — документация и хостируемый checkout/buy-links делают техническую часть простой, но обязателен одобренный сайт-URL, ручной underwriting и KYC; для Telegram-бота без сайта узкое место — комплаенс, а не код..</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Публичных данных о VPN-политике нет; профильный high-risk (adult, подписки)</t>
+          <t>Ключевой стоп-фактор — Россия в разделе «OFAC-Sanctioned Countries»: российское юрлицо и резидент не подключаются вообще. VPN прямо не назван, но «Remote Access Services» в PPL запрещены, а список неисчерпывающий → очень высокий риск отказа по underwriting. PPL не обновлялась с июня 2021 («Last update: June, 2021») — политика устаревшая относительно 2026 года, что добавляет неопределённости: трактовка «Remote Access Services» может быть и мягче, и жёстче. Rolling reserve 90 дней постоянно замораживает часть оборота в пользу 2Checkout, процент непрозрачен. Смена реквизитов переводит аккаунт в restricted mode с заморозкой выплат. Возможны скрытые расходы на professional services. Грузия недоступна для 2Sell/2Subscribe — это вычёркивает одну из рассматриваемых юрисдикций. ПРАКТИКА: История обработки платежей не требуется: 2Sell/2Subscribe рассчитаны на малый и средний бизнес, регистрация бесплатная, сразу доступен demo mode и весь функционал, underwriting обещает связаться «right away». Но: обязательный ручной risk-review даже для добавления второго URL, rolling reserve 90 дней, и известная практика заморозки выплат при любом изменении payout-реквизитов до одобрения Finance. Репутацию по независимым агрегаторам отзывов подтвердить не удалось: Trustpilot и ряд review-сайтов при прямой проверке отдали HTTP 403 (Vercel Security Checkpoint), поэтому тезис о низких оценках я оставляю неподтверждённым. Для проекта «Kometa» практическая часть нерелевантна: РФ запрещена.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>https://segpay.com/, https://gethelp.segpay.com/</t>
+          <t>https://www.2checkout.com/legal/acceptance/, https://www.2checkout.com/pricing/, https://docs.2checkout.com/get-started/getting-started/help-and-faqs.md, https://docs.2checkout.com/get-started/getting-started/payouts.md, https://docs.2checkout.com/payments/payments/refunds-and-chargebacks/chargeback-fees.md, https://docs.2checkout.com/get-started/getting-started/activate-your-account/account-identity-verification.md, https://docs.2checkout.com/get-started/getting-started/publish-your-docs.md, https://docs.2checkout.com/llms.txt, https://web.archive.org/web/20251112015514/https://verifone.cloud/docs/2checkout/Onboarding/Get-started-with-your-2Checkout-account/Restricted-countries-and-territories, https://www.globenewswire.com/fr/news-release/2026/06/16/3312511/0/en/2Checkout-s-CommerceNow-10-Years-of-Digital-Commerce-Strategy-Free-and-Live-June-23.html, https://www.2checkout.com/lp/navigating-the-digital-river-shutdown-and-your-next-steps.html</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ccbill</t>
+          <t>digitalriver</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CCBill</t>
+          <t>Digital River (платформа MyCommerce) — Digital River, Inc. / Digital River GmbH</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>High-risk эквайринг</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Серая зона: VPN в AUP не запрещён, но запрещены shell accounts и поддержка ботов</t>
+          <t>MoR/SaaS-биллинг — исторически enterprise Merchant of Record. ФАКТИЧЕСКИ НЕ ДЕЙСТВУЮЩИЙ провайдер: компания ликвидирована (Chapter 7, май 2025).</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>нет (сервис не работает): компания ликвидирована, подключать мерчантов некому. По историческим документам (список «Prohibited Good and Services», black list / gray list) VPN, virtual private network, proxy, anonymizer и circumvention дословно НЕ названы. Ближайшие релевантные пункты: в black list — «Webhosting companies» и «IT Services help desks»; в gray list — «Professional services (including, but not limited to: Advertising, consulting, dating, domain registration, educational, financial, legal, medical, lending, collections, tech support, travel, real estate. NOTE: software-as-a-service IS permitted)». Прямого запрета на VPN в опубликованных списках нет, но компания мертва, поэтому практического значения это не имеет.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>РФ не подтверждено</t>
+          <t>Исторически — enterprise-мерчанты преимущественно из США, ЕС и Азии; работа шла через Digital River, Inc. (Миннетонка, Миннесота, США), Digital River GmbH (Кёльн, Германия), Digital River Ireland Ltd. и Digital River International S.à r.l. Малый бизнес и российские мерчанты на MyCommerce практически не подключались. Сейчас приём мерчантов невозможен: американские офисы закрыты, увольнения 122 сотрудников вступили в силу 28.03.2025, немецкие юрлица Digital River GmbH и Digital River Holding GmbH подали заявление о несостоятельности в суд Кёльна, идёт «wind down» по каждой иностранной юрисдикции. Формулировка из письма CEO: «This process began with the suspension of services to the majority of our global customers». Российский резидент/юрлицо — недоступно, как и любое другое.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Карты, рекуррент — ядро продукта</t>
+          <t>по запросу (не публикуется) — публичной страницы со списком методов больше нет, домен не работает. Исторически MoR-модель предполагала широкий набор карт, PayPal и локальных методов для целевых рынков клиента, но конкретный список зависел от enterprise-контракта и не публиковался.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>По запросу; публично только структура издержек (interchange, brand assessments, processor markup)</t>
+          <t>по запросу (не публикуется) — Digital River никогда не публиковал публичных тарифов, работал исключительно по индивидуальным enterprise-контрактам (revenue share). Публичных процентов, транзакционных сборов, chargeback-сборов или месячных минимумов нет ни на сайте, ни в архивах. Мониторинговые обзоры и сравнения («Digital River alternatives») указывают только «custom pricing».</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>по запросу (не публикуется) — публичных условий резерва не было. Косвенно известно, что компания перешла на «new deals with shorter payment terms» и испытывала дефицит оборотного капитала, что и привело к невыплатам мерчантам.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Публично не раскрыты; типичны weekly/2-weekly settlement и holdback</t>
+          <t>по запросу (не публикуется). Ключевой задокументированный факт вместо условий: с июля 2024 Digital River перестал выплачивать мерчантам MyCommerce деньги за проданные цифровые продукты — The Register, 15.10.2024: «Digital River runs dry, hasn't paid developers for sales since July», при этом «Vendor told El Reg the biz's law firm claims merchant debts aren't valid obligations». То есть выплаты не просто задержались — юрфирма компании оспаривала сам факт долга.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Юрлицо, KYB, сайт с раскрытием условий подписки и триалов</t>
+          <t>по запросу (не публикуется). Исторически модель была обратной обычному PSP: Digital River сам был MoR и подписывал enterprise-контракт с крупными вендорами (Adobe, American Express, DHL, Kaspersky Lab в качестве клиентов упоминались), онбординг был длительным, требовал юрлица и переговоров с sales. Подключение физлица или самозанятого было невозможно, и модели «бот без сайта» тоже — продукт продавался через полноценный фирменный storefront (DRHM) или через MyCommerce с обязательным сайтом и юридическими документами.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Исторически да — подписки были одним из двух профильных направлений: в письме CEO прямо сказано «While we've worked diligently to consolidate our operations and strengthen our focus on our Digital and Subscription businesses», а в архиве есть материалы «Subscription Solutions» и «MyCommerce Overview». То есть recurring billing, renewal и подписочная аналитика поддерживались. Но сервис остановлен: выплаты прекратились с июля 2024, а в январе 2025 началась ликвидация. Практически рекуррент недоступен.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Hosted payment page, REST API, вебхуки; сложность 3/5</t>
+          <t>Интеграция невозможна. Ранее существовали MyCommerce API, storefront DRHM и партнёрские интеграции, документация была на docs.digitalriver.com. На 2026-10-05 домен www.digitalriver.com не обслуживается: HTTP 403 с ошибкой Cloudflare «DNS points to prohibited IP» (Error 1000, Ray ID a45f4bf12de8d29c) — это не блокировка бота, а признак того, что домен больше не размещён корректно. Домен digitalriver.com.au, на котором лежал Acceptable Usage Policy (drn_aup.pdf), вообще не резолвится (ENOTFOUND). Технически подключаться некуда. Сложность интеграции: 5 — интеграция физически невозможна: компания в процедуре Chapter 7, сервисы остановлены («suspension of services to the majority of our global customers»), основной домен отдаёт Cloudflare Error 1000, австралийский домен с AUP не резолвится..</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>VPN-сайт может быть сочтён «shell account» (VPS/прокси-инфраструктура)</t>
+          <t>Максимально возможный риск — полная и невозвратная потеря выручки, и он уже реализовался. Хронология: июль 2024 — прекращение выплат мерчантам MyCommerce; 15.10.2024 — публикация The Register о невыплатах, компания оспаривает долги; лето 2024 — приход кризис-менеджера Барри Касоффа на пост CEO; 27–28.01.2025 — WARN-письмо о закрытии, 122 увольнения с 28.03.2025, «we have been unable to identify a path forward that would allow Digital River to continue operating»; 29.01.2025 — заявление о несостоятельности Digital River GmbH и Digital River Holding GmbH в суд Кёльна; май 2025 — Chapter 7. Дополнительно: против бывшего CEO Барри Касоффа подан иск многолетним клиентом с обвинением в мошенничестве на $18 млн (Star Tribune; в URL материала фигурирует Kaspersky Lab). Фактор краха — в том числе торговое эмбарго США против Kaspersky, одного из крупнейших клиентов. ПРАКТИКА: Нет, и это главный вывод. Digital River не подключал малый бизнес без истории — это был enterprise-MoR с продажами через sales. Более того, он стал учебным примером counterparty risk в MoR-модели: компания принимала деньги конечных покупателей, оставляла их у себя и перестала рассчитываться с мерчантами, а затем ушла в Chapter 7, где требования мерчантов оказались в общей очереди кредиторов. Свежие обзоры так и формулируют проблему — «When the Merchant of Record Fails: Counterparty Risk Nobody Prices In». Для нашего проекта это не кандидат, а предупреждение: при выборе MoR критично смотреть на его финансовую устойчивость, а не только на комиссию.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>https://ccbill.com/cs/client/policies/ccbill/acceptable_use.html, https://ccbill.com/pricing</t>
+          <t>https://tcbmag.com/minnetonka-based-e-commerce-firm-digital-river-to-shut-down/, https://ohn.haendlerbund.de/themen/unternehmen-maerkte/digital-river-pleite-mycommerce-dienste-voruebergehend-eingestellt, https://www.theregister.com/software/2024/10/15/digital-river-delays-sales-payments-to-vendors-since-july/1464508, https://en.wikipedia.org/wiki/Digital_River, https://web.archive.org/web/20210118205758/https://www.digitalriver.com/legal-other/prohibited-good-services/, https://www.digitalriver.com/, https://intellizence.com/insights/bankruptcy/leading-companies-filing-for-bankruptcy/, https://www.startribune.com/digital-river-barry-kasoff-fraud-lawsuit-kaspersky-lab/601846300</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>verotel</t>
+          <t>gumroad</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Verotel (Yoursafe B.V.)</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>High-risk эквайринг</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Не подтверждено: в Merchant Services Agreement VPN, proxy и circumvention не упоминаются</t>
+          <t>нет (де-факто): слова «VPN» в списке нет, но п.47 запрещает услуги как класс — «services (including, but not limited to, "get rich quick" schemes, business opportunities, investment opportunities, mortgage consulting, real estate purchases, mortgage reduction services and credit repair and protection)», а VPN-подписка это длящаяся услуга, а не цифровой файл. Плюс отсутствует канал выплат в РФ.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Любое юрлицо; РФ не подтверждено</t>
+          <t>Продавать может продавец-физлицо из большинства стран, но выплаты ограничены. В официальной таблице банковских выплат России НЕТ; при этом прямо сказано: "Where we also do not support bank payouts — Zambia, Syria, Russia, Iraq and a number of others — there is currently no way for us to pay out to a creator in that country unless their PayPal account is registered elsewhere". PayPal, зарегистрированный в РФ, переводы принимать не может. Поддерживаются (с локальными минимумами): Армения (AMD, min 12 100), Азербайджан (AZN, min 50), Казахстан (KZT, стандартный порог $100), Молдова (MDL, min 500), Узбекистан (UZS, min 343 000), ОАЭ — только для Business-аккаунтов (AED). То есть для российской прописки канала выплат фактически нет; для юрлица в Казахстане/Армении — есть, но банковский счёт обязан быть в стране регистрации бизнеса.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Карты, FlexPay, рекуррент</t>
+          <t>Оплата покупателем картой, через PayPal и локальные методы (например UPI в Индии) — зависит от страны покупателя; выплата продавцу — банковский перевод или PayPal. Другие способы (Payoneer, Wise, чек, wire) не поддерживаются.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>BASIC 15,5% за non-recurring + EUR 25/нед при обороте менее EUR 1000/нед; PREMIUM — по объёму</t>
+          <t>10% + $0.50 за транзакцию при прямых продажах (профиль/прямые ссылки) плюс отдельно обработка карты 2.9% + $0.30, итого ориентировочно 12,9% + $0,80. Продажи через витрину Discover — плоские 30% (включая обработку). При обороте свыше $20 000 оплаченных продаж за календарный месяц ставка на новые прямые продажи в этом месяце снижается до 5% + $0.50. Месячной платы нет. Комиссия за chargeback отдельно не публикуется. Выплата на PayPal — дополнительно 2% processing fee. Instant payouts (только США) — 3%.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Annual registration fee EUR 500 (продление при обороте &gt;= EUR 100/нед)</t>
+          <t>отсутствует (не публикуется как отдельный платёж за подключение)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Не раскрыт</t>
+          <t>по запросу (не публикуется). Публично описаны только удержание баланса минимум 7 дней на расписаниях weekly/monthly/quarterly, минимум $100 на балансе и возможность придержать баланс при открытом review/подозрении в fraud ("it stays held until that is resolved")</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>BASIC без требования по обороту; PREMIUM — от EUR 100/нед; валюта EUR, счёт в Нидерландах</t>
+          <t>Ежедневно (только США), еженедельно, ежемесячно или ежеквартально; свой порог, но не ниже применимого минимума (обычно $100). Банковские выплаты уходят по вторникам/средам/четвергам, обработка банком 2–7 рабочих дней, PayPal — 1–3 рабочих дня. Для РФ канала выплат нет. Нужны government-issued photo ID и подтверждение адреса; для бизнеса банковский счёт должен быть в стране регистрации бизнеса; для США требуется SSN.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Любое юрлицо; PREMIUM требует 6 месяцев выписок</t>
+          <t>Юрлицо не обязательно — продавать можно как individual; для верификации нужны фото ID, подтверждение адреса (Stripe KYC, P.O. Box не принимается). VAT/GST номер от продавца не требуется: с 1 января 2025 Gumroad сам является Merchant of Record и собирает/перечисляет налоги по всему миру ("Since January 1, 2025, Gumroad handles ALL your tax obligations"). Проверка аккаунта занимает 1–3 недели, обычно 3–4 продажи с балансом более $100. Покупка собственного товара для ускорения проверки расценивается как fraud.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Подписки и memberships поддерживаются ("Can I use Gumroad for memberships? Yes! Whether it's for a podcast, online course, or SaaS subscriptions..."), но только в рамках разрешённых категорий цифровых продуктов.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>FlexPay, hosted-страница, публичная спецификация API; сложность 3/5</t>
+          <t>Хостед-чекаут + публичный API (gumroad.com/api), webhooks (Gumroad Ping), реферальная программа, встроенные ссылки на оплату. Бот может генерировать ссылки на оплату, но Gumroad остаётся продавцом и требует, чтобы продавался цифровой продукт, а не длящийся сервис; чисто «backend-only» магазин без витрины Gumroad не предусмотрен. Сложность интеграции: 2 — есть API, webhooks и простые checkout-ссылки, но модель диктует свою витрину и не подходит как «невидимый» эквайер под Telegram-бота.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Единственный публичный прайс в категории, но 15,5% + EUR 500/год — дорого для чеков 199-1590 руб</t>
+          <t>Ключевой риск — несовпадение продукта с правилами: услуги запрещены (п.47), предмет сделки ограничен цифровыми продуктами (п.1.1 ToS). Второй риск — выплаты: для РФ нет ни банковского канала, ни работоспособного PayPal. Третий — Gumroad как MoR контролирует и витрину, и деньги, поэтому блокировка затрагивает и баланс; в Terms прямо закреплено право "terminate or suspend your access to all or part of the Services for any or no reason". ПРАКТИКА: Gumroad работает как MoR и платит по расписанию; отдельной платы за онбординг нет, проверка аккаунта занимает 1–3 недели. Случаи блокировок с задержкой выплат широко обсуждаются в комьюнити; сторонний обзор (Latuos, обновлён 14.09.2026) прямо оговаривает, что упоминания VPN в контексте блокировок — это рассказы продавцов, а не подтверждённая политика Gumroad. Собственного «порога входа» по обороту нет.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>https://www.verotel.com/en/productchoice.html, https://www.verotel.com/en/merchantagreement.html</t>
+          <t>https://gumroad.com/prohibited, https://gumroad.com/pricing, https://gumroad.com/terms, https://gumroad.com/help/article/13-getting-paid, https://gumroad.com/help/article/66-gumroads-fees, https://quasa.io/ru/media/gumroad-platit-v-tenge-dramah-i-sumah-dlya-rossii-vyvoda-net, https://latuos.com/gumroad-account-suspended/, https://gumroad.com/api</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>payop</t>
+          <t>sellfy</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Payop</t>
+          <t>Sellfy</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>PSP</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>НЕТ: VPN прямо не назван, но РФ в Prohibited Countries и есть запрет Items which facilitate illegal activities</t>
+          <t>MoR/SaaS-биллинг</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>серая зона (де-факто нет): VPN прямо не назван, но Sellfy — площадка цифровых ФАЙЛОВ, а не сервисов, и она прямо запрещает «No selling of services that advertise access to video and/or audio broadcasts, channels, or apps» (пункт IPTV). Дополнительно: цифровые товары нельзя продавать на бесплатном плане, а аккаунт блокируется навсегда без возврата подписки.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>РФ прямо запрещена</t>
+          <t>Формально Sellfy декларирует глобальную гибкость ("Global flexibility — you can operate as a business from anywhere in the world"), но деньги идут только через PayPal и Stripe, и других процессоров нет. Значит принимающая сторона ограничена странами PayPal/Stripe: российский резидент или российское юрлицо подключиться не сможет (PayPal не открывает новые счета в РФ, Stripe Россию не обслуживает). Для Казахстана/Армении/Грузии/Кыргызстана Stripe не поддерживается (Sellfy отдельно оговаривает только ограничение по Индии), а PayPal в этих странах работает, но для подписок требуется PayPal Business.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Карты, локальные методы, крипта</t>
+          <t>Только PayPal и Stripe (карты, Apple Pay, Google Pay). Другие способы недоступны: "Can I use another payment method other than Stripe or PayPal? No".</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>Платная подписка с 14-дневным триалом (в триале чекаут отключён): Starter $39/мес ($348/год), Business $79/мес ($708/год), Premium $159/мес ($1428/год). Транзакционной комиссии Sellfy нет: "There are no transaction fees from Sellfy". Годовой лимит выручки по тарифам: $10K / $50K / $200K, при превышении возможна overage-плата 2%. Комиссии процессоров: PayPal 2.9% + $0.30 в США и в среднем 3.4% + $0.30 по миру, Stripe 2.9% + $0.30. Комиссия за chargeback отдельно не публикуется. Месячного минимума нет.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>отсутствует; вместо него обязательна платная подписка (без неё продавать нельзя, чекаут включается только после оплаты тарифа)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>нет. "Sellfy does not hold your funds or payments from customers. It's not our money; it's yours!" Единственная оговорка — PayPal может придержать первые транзакции нового аккаунта: "if your PayPal account is brand new, PayPal may slow the deposit of the very first transactions"</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Публично не раскрыты</t>
+          <t>Мгновенно: деньги поступают напрямую в ваш PayPal/Stripe сразу после покупки, отдельного графика выплат от Sellfy нет. Дальнейший вывод — по правилам PayPal/Stripe.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Юрлицо; оператор Transferop Payment Gateway Ltd (Канада)</t>
+          <t>Регистрация юрлица не требуется (Sellfy: "you don't need a registered business entity (like an LLC or Corporation) to use Stripe"), но для продажи подписок PayPal требует Business-аккаунт. Налоги — ваша ответственность: Sellfy не является MoR, есть только инструменты (расчёт EU VAT, отчёты, возможность ограничить продажи в EU/UK). Требований к VAT/GST номеру платформа не выставляет. Глубина KYC — на стороне PayPal/Stripe.</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Да, но в виде файловой подписки: интервалы weekly/monthly/annual, автоплатёж и рассылка новых ссылок, купоны применяются к каждому платежу, отмена моментально лишает доступа к файлам, срок фиксированной длительности недоступен ("each subscription will continue indefinitely, or until the customer cancels"), dunning и tokenisation публично не документированы.</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>API-first, документация на GitHub; сложность 3/5</t>
+          <t>Хостед-магазин и чекаут, кастомизация чекаута, вебхуки (docs sellfy article 127), license keys с API и вебхуками, Zapier, встраиваемая корзина на свой сайт, приложение для Wix. Для Telegram-бота без сайта: можно давать ссылки, но доступ выдаётся к файлам в Sellfy, а не к внешнему VPN-сервису. Сложность интеграции: 3 — техника простая (вебхуки, license keys), но продуктовая модель «выдача файла» ломает сценарий VPN-подписки.</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>РФ-резидент не подходит по юрисдикции</t>
+          <t>Первый риск — несоответствие продукта (нет категории услуг, запрет IPTV/сервисов доступа к контенту, подписка = файл). Второй — полная зависимость от PayPal/Stripe, что закрывает РФ и делает невозможным онбординг без поддерживаемой юрисдикции. Третий — нарушение правил ведёт к постоянной блокировке без возврата предоплаченного времени: "Account suspension is permanent. If your account has been suspended after violating Sellfy's rules, you will not receive a refund for any prepaid subscription time". ПРАКТИКА: Онбординга по обороту нет — достаточно оплатить тариф, что удобно для малого бизнеса без истории. Средства не удерживаются. Но: в триале продавать нельзя, аккаунт можно потерять вместе с оплаченным периодом, а спорные категории модерируются вручную.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>https://payop.com/acceptable-use-policy/, https://github.com/Payop/payop-api-doc</t>
+          <t>https://docs.sellfy.com/article/24-product-guidelines, https://docs.sellfy.com/article/366-merchant-of-record, https://docs.sellfy.com/article/211-how-much-does-sellfy-cost, https://docs.sellfy.com/article/42-how-to-receive-payments-from-customers, https://docs.sellfy.com/article/158-subscription-products, https://docs.sellfy.com/article/405-receiving-payments-with-stripe, https://sellfy.com/terms/</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -4693,323 +4693,323 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>unlimit</t>
+          <t>payhip</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Unlimit (ex-Cardpay)</t>
+          <t>Payhip</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>PSP / EMI</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: страницы AUP и prohibited-businesses отдают 404, restricted-список на онбординге</t>
+          <t>MoR/SaaS-биллинг (фактически storefront, не полный MoR)</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>серая зона. VPN в списке запрещённых продуктов не назван; запрещены get-rich-quick, порнография, файлохостинг, азартные игры, виртуальные карты, card sharing и т.п. Но Payhip прямо обязывает соблюдать правила платёжных провайдеров: "In addition to our terms, you will need to comply with the terms of our payment providers" (PayPal AUP и Stripe restricted businesses), а также запрещает "Products that violate laws to which you are subject". Поскольку VPN-сервис формально не запрещён самой Payhip, но полностью зависит от Stripe/PayPal, итог — серая зона, которая на практике закрывается для РФ из-за отсутствия платёжного плеча.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>UK/Cyprus юрлицо; РФ не подтверждено</t>
+          <t>Аккаунт можно открыть из большинства стран, но получить деньги — только через один из 13 процессоров (PayPal, Stripe, Mollie, Square, Mercado Pago, Flutterwave, Paystack, Xendit, Midtrans, PayU, Razorpay, Iyzico, PayTabs). Stripe по версии Payhip доступен в 40+ странах: Австрия, Австралия, Бельгия, Бразилия, Болгария, Канада, Хорватия, Кипр, Чехия, Дания, Эстония, Финляндия, Франция, Германия, Гибралтар, Греция, Гонконг, Венгрия, Ирландия, Италия, Япония, Латвия, Лихтенштейн, Литва, Люксембург, Малайзия, Мальта, Мексика, Нидерланды, Новая Зеландия, Норвегия, Польша, Португалия, Румыния, Сингапур, Словения, Словакия, Испания, Швеция, Швейцария, Таиланд, ОАЭ, Великобритания, США. России в списке нет, Казахстана, Армении, Грузии и Кыргызстана тоже. Вывод: российский резидент или российское юрлицо не сможет получать выплаты; для Казахстана/Армении потребуется отдельно проверять PayU/PayTabs/PayPal (PayPal для приёма платежей в этих странах возможен, но комиссии и правила — на стороне PayPal).</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Карты, локальные методы, подписки</t>
+          <t>Зависит от подключённого процессора: PayPal и Stripe (карты, Apple Pay, Google Pay, локальные методы вроде iDEAL, Klarna, Afterpay, Alipay в зависимости от страны Stripe-аккаунта), а также Mollie, Square, Mercado Pago, Paystack, Flutterwave, Xendit, Midtrans, PayU, Razorpay, Iyzico, PayTabs. Обычно можно подключить PayPal плюс один процессор для карт.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>Free Forever — 5% с транзакций; Plus $29/мес — 2%; Pro $99/мес — 0% от Payhip. Процессорные комиссии сверху (Stripe стандартно 2.9% + $0.30). Комиссия за chargeback и месячный минимум отдельно не публикуются.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>отсутствует</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>нет. Деньги уходят напрямую в PayPal/Stripe продавца в момент покупки; холдов на стороне Payhip не заявлено (холд возможен только на стороне процессора — первая транзакция Stripe висит несколько дней на approval)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Публично не раскрыты</t>
+          <t>Платформа не платит: "the payment is processed and sent directly to your connected payment processor at the time of purchase". Выплаты — по графику процессора: Stripe по умолчанию ежедневно на подключённый банковский счёт, первая транзакция может задержаться на несколько дней; PayPal — по его правилам.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>UK/EU юрлицо (Terms governed by Cyprus law), в ряде вертикалей лицензия</t>
+          <t>Юрлицо не требуется, регистрация не упоминается; обязателен аккаунт PayPal и/или Stripe на ваше имя. Подписки технически работают только через Stripe: "Each instalment of the subscription is deposited to your Stripe account". Налоги: Payhip автоматически считает и удерживает EU VAT и UK VAT (можно отключить), есть разделы про US и Canada sales tax; полноценным MoR платформа себя при этом не называет.</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Да: отдельный тип продукта «subscriptions/memberships», рекуррент через Stripe, управление биллингом в личном кабинете покупателя, вебхуки subscription.created и subscription.deleted. Свободных триалов и MIT-токенизации в документации нет — это уровень Stripe.</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>REST API, hosted checkout, подписочный продукт; сложность 3/5</t>
+          <t>Хостед-чекаут, страницы продуктов, memberships-кабинет покупателя, вебхуки с 4 событиями (paid, refunded, subscription.created, subscription.deleted), подпись запроса hash('sha256', apiKey), license keys API, Zapier, реферальная программа. Для Telegram-бота это один из самых удобных вариантов: бот получает webhook paid/subscription.created и выдаёт доступ сам, без сайта. Сложность интеграции: 2 — хостед-чекаут + понятные вебхуки с подписью, магазин без сайта допустим и не требует отдельной витрины.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Условия по VPN не опубликованы: узнаются только в процессе онбординга</t>
+          <t>Первый риск — платёжное плечо: без PayPal/Stripe аккаунта в поддерживаемой стране продавать невозможно, а РФ и большинство стран Центральной Азии в Stripe-списке Payhip отсутствуют. Второй — VPN-сервис формально не запрещён, но подпадает под обязанность соблюдать Stripe restricted businesses и локальные законы. Третий — за нарушение правил: "you risk getting your Payhip account permanently deleted without prior notice". ПРАКТИКА: Порога по обороту нет, мини-бизнес без истории подключают: достаточно зарегистрироваться и подключить процессор, деньги приходят напрямую, платформа не удерживает и не резервирует средства. Жалобы на заморозку средств на стороне Payhip не обнаружены — риски сосредоточены в процессоре.</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>https://www.unlimit.com/legal/, https://www.unlimit.com/payment-processing/</t>
+          <t>https://help.payhip.com/article/205-what-products-are-not-allowed-on-payhip, https://help.payhip.com/article/102-billing-and-upgrading, https://help.payhip.com/article/173-how-do-i-get-paid, https://help.payhip.com/article/65-connecting-your-stripe-account, https://help.payhip.com/article/132-how-payhip-works, https://help.payhip.com/article/115-webhooks, https://help.payhip.com/article/127-digital-eu-vat, https://foxreload.com/en/library/marketplaces/payhip-sell-from-russia</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>tailoredpay</t>
+          <t>kofi</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>TailoredPay</t>
+          <t>Ko-fi</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Брокер high-risk эквайринга</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>ДА, заявляет: профильная страница VPN Merchant Account (тело страницы за Cloudflare не читается)</t>
+          <t>MoR/SaaS-биллинг (фактически платформа донатов/магазина; не PSP и не MoR)</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>серая зона со склонностью к «нет». VPN прямо не упомянут. Ko-fi запрещает использовать сервис для всего, что запрещено PayPal и Stripe: "creators can't use Ko-fi in ways that go against PayPal's acceptable use policy or Stripe's prohibited businesses". Магазин Ko-fi заточен под товары, а не услуги: "Creators can sell digital and physical products in a Ko-fi Shop" (файлы, шаблоны, софт, мерч), а услуги существуют только как Commissions. Длящаяся VPN-подписка в эти категории не помещается; дополнительно Ko-fi оставляет за собой право запросить объяснение по членствам с офсайт-доставкой: "If we have reason to believe that prohibited content is being provided offsite but through Ko-fi (e.g. being offered via Memberships), we may need to verify this with you".</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Подбирает банк под мерчанта; РФ не подтверждено</t>
+          <t>Юридически Ko-fi — британская компания Ko-fi Labs Limited (Англия и Уэльс, компания 11087704, VAT 318563687), но деньги проводит не она. Выплаты возможны только на ваш PayPal или Stripe: Stripe доступен в 40+ странах, иначе остаётся только PayPal. Россия не обслуживается ни Stripe, ни PayPal (PayPal не открывает новые личные и корпоративные счета в РФ), поэтому российский резидент/юрлицо не сможет принимать деньги. Аккаунт обязан быть 18+.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Зависит от подобранного эквайера</t>
+          <t>Только PayPal и Stripe: "Right now, Stripe and PayPal are our only payment options". Все платежи идут напрямую на ваш аккаунт PayPal/Stripe, Ko-fi их не процессит.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>Ko-fi Free: 0% с разовых чаевых, 5% со всего остального (shop, memberships, monthly tips, commissions). Standard (тоже $0/мес): 5% со всех типов, включая разовые чаевые. Ko-fi Gold — платная подписка, её цена в справке не указана. Сверху — обычные комиссии процессора, обычно около 3% + $0.30. Комиссия за chargeback и месячный минимум не публикуются.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>По запросу (зависит от банка)</t>
+          <t>отсутствует</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>нет. "payments are immediate. When a sale happens, funds land straight in the creator's PayPal or Stripe account... no confusing hold periods, no waiting on scheduled payout days". Холд возможен только со стороны PayPal (справка отдельно объясняет, почему средства могут быть on hold)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Определяет эквайер</t>
+          <t>Мгновенно на ваш PayPal/Stripe; Ko-fi не держит и не выплачивает деньги сам ("do not process or hold payments"). Сроки зачисления дальше — по правилам процессора: у Stripe выплаты обычно в течение 7–14 дней после первого успешного платежа, далее по расписанию дашборда Stripe.</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Типично юрлицо (US/EU/offshore) и KYC; определяет принимающий банк</t>
+          <t>Юрлицо не требуется; обязателен аккаунт PayPal и/или Stripe на ваше имя. Требуется статус 18+ ("You must be 18 years old or older to use Ko-fi and create an Account"; для аккаунтов младше 18 — анпаблиш до подтверждения возраста по документу). VAT/GST номер не запрашивается; налоги — ваша ответственность ("Taxes are your responsibility, we don't collect or pay taxes on your behalf"). KYC — на стороне PayPal/Stripe. Дополнительно Ko-fi запрашивает местоположение и может проводить verification check.</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Зависит от эквайера</t>
+          <t>Memberships (месячные тиры) поддерживаются, комиссия 5%; вебхук приходит только на факт платежа: "Our API is currently limited to when a payment is made... a webhook can notify you when you receive a membership payment but cannot inform you if the membership has ended". То есть статус отмены подписки нужно отслеживать в PayPal/Stripe.</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Отдельного продукта нет: посредничество и согласование; сложность 4/5</t>
+          <t>Хостед-страница, Shop, Memberships, Commissions, webhook только на платежи (HTTP POST, повтор при не-200), zapier, Discord-бот, виджет и кнопка для сайта. Для Telegram-бота подходит технически (webhook → выдача доступа), но продавать придётся «товар/членство», а не VPN-сервис. Сложность интеграции: 2 — вебхук на оплату и простые ссылки на страницу/магазин; сложность не в технике, а в том, что VPN-подписка не вписывается в продуктовую модель.</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Это брокер, а не процессинг: итоговые условия и риск зависят от выбранного банка</t>
+          <t>Первый риск — модерация по правилам PayPal/Stripe и по понятию "unsuitable use": за это аккаунт анпаблишат, при трёх страйках — навсегда. Второй риск — блокировка за то, что контент/услуга предоставляется офсайт (в том числе через Memberships). Третий — Россия вне платёжного покрытия. Четвёртый — вебхук не сообщает об окончании членства, риск не отключить доступ вовремя. ПРАКТИКА: Онбординга по обороту нет, возрастных ограничений по бизнесу нет (кроме 18+ на аккаунт), деньги не удерживаются. Обратная сторона — активная ручная модерация и трёхстрайковая система, плюс практика анпаблиша страницы «для проверки, откуда приходят деньги».</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>https://tailoredpay.com/vpn-merchant-account/</t>
+          <t>https://more.ko-fi.com/terms, https://help.ko-fi.com/hc/en-us/articles/360007937553-Ko-fi-Content-Guidelines, https://help.ko-fi.com/hc/en-us/articles/360002506494-Does-Ko-fi-take-a-fee, https://help.ko-fi.com/hc/en-us/articles/360009265834-Can-I-use-Stripe-in-my-country, https://help.ko-fi.com/hc/en-us/articles/360009712917-Ko-fi-Shop, https://help.ko-fi.com/hc/en-us/articles/360004162298-Does-Ko-fi-have-an-API-or-webhook</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>patreon</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Telegram Stars (Bot Payments)</t>
+          <t>Patreon</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Telegram-нативный</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Не регламентировано: модерации тематики нет, но цифровые товары в Telegram обязаны продаваться за Stars</t>
+          <t>серая зона. VPN прямо не упомянут, но у Patreon двухуровневая система правил: Community Guidelines для всего контента и отдельные Commerce Guidelines именно для бенефитов и офферов. Terms of Use фиксирует: "You may only post material to Patreon that is permissible under our Community Guidelines. And creators may only provide membership benefits and offerings that are also permissible under our Commerce Guidelines". Сводка правил: "we don't allow: illegal material or benefits; material or benefits that are abusive towards other people; material or benefits that are misleading or deceptive; material or benefits that use others' intellectual property...". VPN-доступ как бенефит членства под эти формулировки прямо не подпадает, но и не разрешён явно; отдельно требуется категоризация бенефитов для налоговых целей.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Глобально; поддержка зависит от флага stars_purchase_blocked в конфиге Telegram (в дефолте true)</t>
+          <t>Аккаунт создаётся из большинства стран (13+ для аккаунта, 18+ или с разрешения родителя/опекуна для страницы создателя). Отсечение по санкциям: "you must not be located, organized, or ordinarily resident in a country or territory subject to comprehensive U.S. sanctions or embargoes (currently, Cuba, Iran, North Korea, and the Crimea, so-called Donetsk People's Republic, and so-called Luhansk People's Republic regions of Ukraine)" — России в этом перечне нет, но выплаты в РФ отсутствуют: в таблицах выплат (банковский перевод через Payoneer, PayPal, Payoneer Wallet) России нет. То есть российский резидент не сможет получить деньги; для Казахстана/Армении/Грузии/Кыргызстана/ОАЭ нужно проверять наличие страны в списках банковских переводов и PayPal (ОАЭ в списке USD→local есть, Казахстана и Армении в таблицах нет).</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Stars (XTR); пополнение звёзд картой или через Fragment</t>
+          <t>Оплата участниками — карты, Apple Pay, PayPal/Venmo (для США), плюс iOS in-app purchase. Выплаты создателю — банковский перевод (Payoneer), PayPal или Payoneer Wallet.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Спред Telegram 7,8%: покупка 1000 Stars = 1,41 USD, вывод 1000 Stars = 1,30 USD</t>
+          <t>Платформенная комиссия 10% для страниц, опубликованных после 4 августа 2025 (легаси-создатели сохраняют прежние условия). Процессинг: карты/Apple Pay и PayPal/Venmo США — 2.9% + $0.30; PayPal/Venmo вне США — 3.9% + $0.30; для не-USD выплат 3.0–3.9% + фикс. Комиссия за конвертацию валюты 2.5% с платежа в валюте, отличной от вашей валюты выплат. Разовые покупки — платформенная комиссия 5–12%. Комиссия выплат: банковский перевод Payoneer $0.50 (локальная валюта) или $0.25 + 1.55% (USD→локальная валюта), PayPal 1% (min $0.25, max $20), Payoneer Wallet $1.00; минимумы $10 (PayPal/банк) и $25 (Payoneer Wallet). Комиссия за chargeback отдельно не публикуется. iOS IAP — 30% сверху (кроме США).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>отсутствует</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>21 день удержания каждой звезды - данные вторичного источника, в офиц. документации не зафиксировано</t>
+          <t>по запросу (не публикуется). Terms допускают удержание: "different levels and types of Patreon service may have different timelines associated with funds becoming accessible to you and/or may require that reserves of funds are withheld" и "We may also block or withhold access to these funds for violations of our Terms or policies or for compliance reasons". Отдельно есть 5-дневный холд при добавлении нового способа выплат</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Fragment, только TON-кошелёк; минимум 1000 Stars; максимум 25000000 Stars за операцию</t>
+          <t>Банковский перевод через Payoneer (локальная валюта или USD→локальная с конвертацией), PayPal (обычно доступен в большинстве стран), Payoneer Wallet; заявку можно подавать раз в 24 часа, минимум $10 (PayPal, банк) / $25 (Payoneer Wallet), фиксированного верхнего лимита нет. Для России ни один из каналов не указан.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Только Telegram-аккаунт владельца бота и 2FA-пароль; документы, ИП, ООО, самозанятость не требуются</t>
+          <t>Юрлицо не требуется; аккаунт создателя — 18+ или с разрешения родителя/опекуна (важно для 15-летнего основателя: формально страница возможна с согласия родителя). Нужны налоговые данные (Patreon отчитывается перед налоговыми органами и может удерживать налог при неполных данных), платёжные реквизиты, а также проверка страницы перед запуском ("Why is my account under review?"). VAT/GST номер не требуется — Patreon сам собирает и перечисляет transaction taxes. Требуется независимая категоризация бенефитов по налоговым категориям.</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Да, Star Subscriptions (stars_subscription_amount_max = 10000 Stars)</t>
+          <t>Да, это ядро продукта: месячные и годовые автоспродлеваемые подписки, бесплатные триалы, gifted access, апгрейды/даунгрейды, billing с восстановлением неудачных платежей (в состав payment processing fee входит "recurring billing, recovering declined payments, and fighting fraud"), Dynamic pricing/скидки. Токенизация карт скрыта внутри Patreon.</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Bot API sendInvoice currency=XTR + successful_payment; сложность 1 из 5</t>
+          <t>Хостед-страница создателя, Patreon API, вебхуки, RSS, Patreon app, Patreon embeds. Для Telegram-бота плохо подходит: покупатель платит за членство на Patreon, а доступ к VPN пришлось бы выдавать по вебхуку, при этом Patreon остаётся витриной и биллинговой сущностью. Сложность интеграции: 3 — API и вебхуки есть, но продукт заточен под контент и членство на своей витрине, а не под внешний сервис.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Возвраты и refund понижают рейтинг аккаунта Telegram; флаг stars_purchase_blocked может быть переключён; долгий путь денег TON - биржа - рубли</t>
+          <t>Первый риск — правила бенефитов: VPN-доступ должен проходить по Commerce Guidelines, полный текст которых недоступен для проверки (Cloudflare), значит предсказуемость низкая. Второй — выплаты: РФ отсутствует в каналах выплат, а санкционный скрининг применяется строго. Третий — Patreon может удерживать средства и блокировать аккаунт по своему усмотрению; возвратов по умолчанию нет. Четвёртый — 30% Apple IAP на мобильные покупки. ПРАКТИКА: Patreon проверяет страницы перед запуском и оставляет за собой право удерживать баланс; порогов по обороту для онбординга нет, но для несовершеннолетних основателей нужна родительская авторизация. Массовые жалобы на заморозку средств — это, скорее, общий риск политики ("Funds withheld for violations or compliance"), а не системная практика по малым аккаунтам.</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>https://core.telegram.org/api/stars, https://core.telegram.org/api/config, https://isales.ai/fr/blog/sell-content-telegram-stars-usdt</t>
+          <t>https://support.patreon.com/hc/en-us/articles/36426991446797-A-standard-platform-fee-for-new-creators-effective-after-August-4-2025, https://support.patreon.com/hc/en-us/articles/39694936541965-Payouts-guide-for-creators-outside-of-the-US, https://support.patreon.com/hc/en-us/articles/207553303-What-are-Patreon-s-Community-Guidelines, https://www.patreon.com/policy/guidelines, https://www.patreon.com/policy/benefits, https://conductatlas.com/platform/patreon/patreon-terms-of-use/provision/CA-P-031025/creator-offerings-must-comply-with-commerce-guidelines/, https://conductatlas.com/platform/patreon/patreon-terms-of-use/provision/CA-P-031026/prohibited-content-categories-on-platform/, https://tostracker.app/document/patreon</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>segpay</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Telegram Payments через провайдеров BotFather</t>
+          <t>SegPay (Toccata, Inc. / Segregated Payments Limited (UK) / Segregated Payments (Ireland) Limited / Segregated Payments (Australia) Pty Ltd)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Telegram-нативный</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Определяется провайдером, а не Telegram; BotFather тематику продавца не проверяет</t>
+          <t>High-risk эквайринг/PSP (IPSP + Payment Facilitator под мастер-аккаунтами банков-партнёров). НЕ Merchant of Record: по потребительским Terms &amp; Conditions Segpay лишь процессит платёж, а товар/услугу поставляет Client Website, т.е. продавцом перед покупателем остаётся мерчант.</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>да. VPN прямо и дважды назван в списке поддерживаемых вертикалей на официальном сайте: сначала в меню ("Digital goods payment processing includes streaming subscriptions, software, educational seminars, VPNs and more"), затем в основном тексте страницы digital-content. Кроме того, в блоге SegPay (август 2026) прямо заявлено, что VPN-трафик покупателя не является для них основанием для отказа в транзакции. Это самый явный VPN-friendly сигнал из четырёх провайдеров. Важная оговорка: заявления относятся к VPN как к цифровому товару и к VPN-пользователям-плательщикам, а не к отдельному VPN-андеррайтингу; финальное решение всё равно принимает compliance по конкретному сайту.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Список провайдеров отдаётся в BotFather динамически, публично не индексируется</t>
+          <t>Мерчанты: только США, Великобритания и Европа — в официальном FAQ дословно: "Segpay can process for merchants located in the United States, United Kingdom, and Europe". Россия, Казахстан, Армения, Грузия, Кыргызстан, ОАЭ в список не входят. Российский резидент/российское ИП/ООО и самозанятый НЕ принимаются (даже при родителе-заявителе — критерий привязки к юрисдикции мерчанта, а не к гражданству). Потребители — по всему миру, кроме стран, ограниченных правительством США. У SegPay есть локальные юрлица-лицензиаты в США, UK (FCA 584599), Ирландии (CBI C193896) и Австралии (AUSTRAC), поэтому австралийское направление реально существует, хотя страница FAQ с формулировкой про US/UK/Europe датирована 2021 годом и может быть не обновлена.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Зависит от провайдера: карты РФ, СБП, кошельки</t>
+          <t>Visa, MasterCard, Maestro, JCB, Discover, PayPal, SEPA Direct Debit (официальный FAQ); есть отдельная страница решения по крипте. Авторизация в 15 валютах: AUD, CZK, USD, EUR, CAD, CHF, DKK, GBP, HKD, ILS, INR, JPY, MXN, NOK, SEK.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Комиссия провайдера; отдельная комиссия Telegram не подтверждена</t>
+          <t>по запросу (не публикуется). Дословно из FAQ: "Fees vary by merchant business model and volume, please contact sales@segpay.com for a quote". Ни процент, ни транзакционный сбор, ни chargeback fee на сайте не опубликованы. Сторонний справочник PaymentProviders.io указывает диапазон "4-15% (high-risk)" и settlement 7 business days, но это неофициальная оценка и не подтверждено самой SegPay.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Зависит от провайдера</t>
+          <t>Отдельного setup fee не публикуется (по запросу). Публично указан только ежегодный регистрационный сбор кард-брендов для части high-risk: "If you are a high-risk merchant, there is an annual Visa registration fee of $950 and MasterCard registration fee of $500. High-risk registration fees apply to merchants in the adult, dating, and nutraceutical space." То есть для VPN/цифрового сервиса вне adult/dating/nutraceutical этот сбор, судя по формулировке, может не применяться — это надо подтверждать у sales письменно.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Зависит от провайдера</t>
+          <t>5% на 6 месяцев. FAQ: "Yes, Segpay will take a 5% 6-month rolling reserve". Документация уточняет механику: "During the first 6 months Segpay processes your payments, up to 5% of your revenues are held in reserve to cover refunds and fees incurred for chargebacks. Beginning in your 7th month with Segpay, reserves are returned to you in each weekly payout." В Merchant Portal поле Reserve Rate задаётся индивидуально, т.е. фактический процент может отличаться от 5%.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Зависит от провайдера</t>
+          <t>В FAQ две модели: "If you are a Segpay Payment Facilitator merchant, you are paid each Wednesday, two weeks in arrears" и "If you are a Segpay PSP merchant, your funds will be settled directly to your bank account by the acquiring bank. Settlements are usually 3 days in arrears and will not occur on Sundays and Mondays." В документации для мерчантов написано иначе: "Segpay sends payouts every Tuesday", плюс обязательный минимальный порог баланса — в Payout Configuration поле "When my balance reaches" требует значение 125 или выше (т.е. минимум ~$125). Резервы с 7-го месяца возвращаются с каждым недельным пейаутом. Банк для выплат верифицируется 3-5 рабочих дней (IBAN/SWIFT для международных счетов).</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Договор с провайдером; почти всегда ИП, ООО или самозанятость</t>
+          <t>Полный KYC-файл: (1) корпоративные документы (certificate of incorporation, operating agreement, документы акционеров); (2) водительские права/паспорт всех директоров и бенефициаров с долей более 20%; (3) банковская выписка или voided check для расчётов; (4) Tax ID/VAT number; (5) подтверждение владения доменом, если домен приватный. Плюс обязательный Website Compliance Checklist: подтверждённое владение доменом, доступ к закрытым разделам, обязательные диcклоузуры (Terms, Refund/Cancellation policy, контакты), запрещённый контент, правила рекламы. Approval — "up to a week once we have a complete Know Your Customer (KYC) file". Юрлицо обязательно в поддерживаемом регионе; вариант "физлицо/самозанятый" на публичных страницах не описан, KYC-требования перечислены в корпоративной логике. VAT/Tax ID обязателен.</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Зависит от провайдера</t>
+          <t>Да, полноценно: "The Segpay system supports recurring billing: 1. Free Trial to monthly membership 2. Limited Trials to monthly membership 3. Monthly memberships 4. Quarterly memberships". Поддерживается one-click checkout для повторных покупок. Есть отдельные страницы/FAQ по Dispute Alerts, RDR (recovery of declined rebills), Stand-In Processing. В блоге прямо описан network tokenization как инструмент сохранения авторизаций у подписчиков, меняющих VPN-локацию между биллингами — это релевантно именно для VPN-аудитории.</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Bot API sendInvoice с валютой RUB, pre_checkout_query, successful_payment; сложность 2 из 5</t>
+          <t>Есть API и hosted pay pages: техническая документация на gethelp.segpay.com и sphelpdesk.com, postbacks, Merchant Portal (сайты, price points, postback, packages), Gateway Docs. Готовые интеграции/партнёры: NATS, MPA Affiliate Software, WordPress/WooCommerce, Magic Members. НО: чистый Telegram-бот без сайта не подойдёт — обязательны подтверждённое владение доменом и прохождение Website Compliance Checklist (диcклоузуры, доступ к контенту, реклама). Минимально нужен лендинг с офертой, рефанд-политикой и контактами. Сложность интеграции: 3. Технически просто (hosted pay page + postback, есть готовые модули и понятная документация), но обязательны живой комплаентный сайт с доменом, полный KYC-пакет и до недели на апрув — для Telegram-бота это главный барьер, а не код..</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Риск отказа комплаенса по тематике VPN; список и условия провайдеров меняются</t>
+          <t>1) Проценты и все транзакционные сборы не публикуются — экономика проекта непредсказуема до переговоров. 2) 5% six-month rolling reserve + удержание выплат "two weeks in arrears" — кассовый разрыв на старте. 3) Для adult/dating/nutraceutical обязателен ежегодный регистрационный сбор Visa $950 + MC $500; для VPN-вертикали это надо уточнять (формулировка FAQ оставляет лазейку). 4) Россия/СНГ как юрисдикция мерчанта исключены. 5) Reserve rate в договоре — индивидуальный, "up to 5%" может быть выше. 6) Противоречие в документации по дню выплат (Tuesday в одном месте, Wednesday в другом) — уточнять в договоре. 7) Расхождение публичных страниц: FAQ датирован 2021, блог — август 2026. ПРАКТИКА: Да, малый бизнес берут: в FAQ прямой вопрос "Does Segpay work with Start-Ups?" — ответ "Yes, Segpay can process for new and small businesses as well as enterprise operations". Требования к processing history на публичных страницах не заявлены, наоборот FAQ для SegPay Premium-аналогов такого условия не содержит. Апрув до недели при полном KYC. Честная оговорка: я НЕ нашёл проверяемого публичного массива жалоб мерчантов на заморозку средств именно по SegPay, поэтому по этому пункту уверенности мало; потребительские жалобы и резервы — стандартный high-risk набор.</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>https://core.telegram.org/api/payments, https://spbnews78.ru/society/2026/04/20/235181.html, https://vibecoderz.ru/blog/kak-podklyuchit-oplatu-k-telegram-botu-v-2026-yukassa-stars-</t>
+          <t>https://segpay.com/verticals/, https://segpay.com/verticals/digital-content/, https://segpay.com/csfaq/, https://segpay.com/terms-conditions/, https://segpay.com/blog/age-verification-managing-payments-in-the-age-of-vpns/, https://gethelp.segpay.com/docs/Content/MPDocs/FinancialDetails/MP-FinancialDetails-Report-Reserves.htm, https://gethelp.segpay.com/docs/Content/MPDocs/MP-ViewEditMerchantInfo.htm, https://gethelp.segpay.com/docs/Content/ComplianceDocs/WebsiteComplianceRequirements.htm, https://gethelp.segpay.com/docs/Content/ComplianceDocs/ProhibitedContent.htm, https://gethelp.segpay.com/docs/Content/GettingStarted/GettingPaid.htm, https://paymentproviders.io/compare/segpay-vs-paxum?focus=method</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -5021,77 +5021,77 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>ccbill</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Tribute</t>
+          <t>CCBill (CCBill LLC, США; CCBill UK Limited, FCA 936980; CCBill IE Limited, Central Bank of Ireland C569018)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Telegram-нативный посредник</t>
+          <t>High-risk эквайринг/PSP. Два продукта: PSP (суб-мерчант под мастер-аккаунтом CCBill, ISO/MSP и PSP/Payment Facilitator банка Esquire Bank NA) и ISO (свой MID). НЕ Merchant of Record: в Merchant Terms and Conditions прямо сказано "Merchant acknowledges its responsibility as the consumer facing entity".</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Серая зона: VPN, прокси и анонимайзеры в списке запрещённых категорий отсутствуют, но товар проходит ручную модерацию со статусами pending/approved/rejected</t>
+          <t>серая зона: слова VPN/proxy/anonymizer нет ни в Merchant Acceptable Use Policy (v.15, июль 2026), ни в EU-версии AUP, ни в Merchant Terms and Conditions (v.21, июль 2026). Ключевой риск — не политика, а формулировки о деньгах и о правилах карточных сетей.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>РФ и СНГ; выплаты в рублях, долларах, евро и USDT</t>
+          <t>Только регионы Visa/MC: США, Канада, EU, UK. Полный опубликованный список стран (док. "Full List of Countries Designated for any Visa and MasterCard Processing via CCBill"): Andorra, Austria, Bear Island, Belgium, Bulgaria, Canada, Channel Islands, Cyprus, Croatia, Czech Republic, Denmark, Estonia, Faroe Islands, Finland, France, Germany, Gibraltar, Greece, Greenland, Hungary, Iceland, Isle of Man, Ireland, Italy, Latvia, Liechtenstein, Lithuania, Luxembourg, Malta, Monaco, Netherlands, Norway, Poland, Portugal, Romania, San Marino, Slovakia, Slovenia, Spain, Sweden, Switzerland, United Kingdom, United States, Vatican City. России в списке НЕТ; Казахстана, Армении, Грузии, Кыргызстана, ОАЭ — тоже НЕТ. Условия: "Be incorporated in and have a principal in the same country within the supported regions", "Business bank account must be in country of incorporation of your business", "Have a registered company or operate as a sole proprietor in one of the supported regions" (т.е. sole proprietor допустим, но только в поддерживаемой стране).</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Карты (RUB, USD, EUR), СБП, Telegram Stars, TON, USDT, BTC, Telegram Wallet</t>
+          <t>Visa, MasterCard, кредитные/дебетовые/подарочные карты, электронный чек (ACH), SEPA EU Direct Debit, DirectPayEU (36 европейских стран, включая iDEAL и Giropay), Apple Pay/Android Pay, локальные методы биллинга. Флагманский PSP-продукт — CCBill Pay (сохранённые способы оплаты, до 25 методов на покупателя).</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>10% с каждой успешной транзакции, включая комиссию сервиса и платёжных провайдеров, плюс динамический сервисный сбор (размер зависит от суммы платежа, точные значения не опубликованы)</t>
+          <t>Проценты на собственном сайте CCBill НЕ публикуются — на странице /pricing описаны только типы сборов (interchange, card brand assessments, processor markup) и 4 модели ценообразования (Flat Rate для PSP; Interchange Plus / Tiered / Discount Plus для ISO) без цифр. Опубликовано: "High-risk merchants are required to pay annual VISA and mastercard registration fees ... Visa $950 / Mastercard $1000" и "Flat Rate ... No monthly fees". Сторонние источники (Merchant Machine, январь 2026; GuidingDecisions, март 2026): Standard 3.9% + $0.55 за транзакцию; High-risk ("Blue") 5.9% + $0.55; Adult 10.8%-14.5%; для транзакций дешевле $10 — surcharge 3%; на большинстве планов рефанды и chargeback fee не взимаются; annual registration fee $500 для dating и $1,000 для остальных high-risk категорий, setup fee и monthly fee отсутствуют.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Setup/application fee отсутствует и публично не взимается (сторонние обзоры подтверждают "no setup fees and no monthly account fees"). Публично подтверждён только ежегодный регистрационный сбор кард-брендов: на странице /pricing — Visa $950 и Mastercard $1000, в базе знаний — "CCBill collects the annual card brand fees for Mastercard ($1000) and Visa ($950) as part of our service. We then submit the payments to the card brands on your behalf at no additional cost." Дополнительно есть раздел "Annual High-Risk Registration", применяется только к определённым MCC.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Явно не заявлен; роль холда выполняет расчётный период до 15 дней плюс срок доставки</t>
+          <t>Процент НЕ публикуется — по запросу (не публикуется). Определение из Merchant Terms and Conditions: "Security Deposit: A percentage of the value of each transaction that is withheld from your gross amount as determined by CCBill and/or the Acquiring Bank. The amount of security deposit will vary from time to time and payment form to payment form as will the period of time the security deposit is held for as dictated by risk at the sole discretion of CCBill." Публично зафиксирована только ДЛИТЕЛЬНОСТЬ: "CCBill shall hold a security deposit for a default minimum of six months" и "Upon cancellation/termination of your account, CCBill will hold all funds due to you for a minimum of six months as reserve for possible refunds, returned checks and chargebacks." В AUP отдельно: при приостановке за unacceptable conduct или подозрение в мошенничестве все ребиллы могут быть отменены, а средства удержаны на 6 месяцев - 1 год.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Минимум 3000 RUB / 100 USD / 100 EUR / 100 USDT; авто 10 и 25 числа, по заявке 2-5 рабочих дней, максимум 2 заявки в месяц; на карту или Telegram Wallet</t>
+          <t>Каждую неделю по понедельникам. Механика: биллинговый цикл Sunday-Saturday, во вторник CCBill проверяет транзакции, выплата уходит в следующий понедельник (кроме US-праздников); ACH Express — к пятнице. Порог выплаты задаётся "Break Amount": time payouts (каждые X недель) или money payouts (по достижении суммы). Минимумы: ACH $25, ACH Express $100, SEPA $50 (до конвертации в EUR), USPS/почтовый чек $25, FedEx $50. Сборы: ACH Transfer $5.00, SEPA $10.00, US Mail $0.78, Canada/Mexico $1.70, international mail $1.70, FedEx 2-day $15.00, Priority Overnight $22.00, International Priority (Canada) $30.00. Stop payment/перевыпуск чека $30.00. ACH только на US-счёт в US-банке; выплаты сплитуются (до 10 сплитов на субаккаунт).</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Регистрация через @tribute в Telegram; документы и статус не требуются; для выплат есть страница новых требований к данным, содержимое не проверено</t>
+          <t>Юрлицо ИЛИ sole proprietor в поддерживаемой стране; принципал должен быть в той же стране; бизнес-банк-счёт обязательно в стране инкорпорации; деятельность должна попадать в поддерживаемые индустрии и AUP; обязателен живой работающий сайт: "Fully functional, live website / Listed products / services / Clearly displayed pricing / Clearly displayed contact information / Specified Terms &amp; Conditions / Defined Privacy Policy / Temporary access to restricted/members only areas". VAT/Tax ID в явном виде не описан, но 1099-K FAQ и налоговый раздел T&amp;C предполагают налоговую отчётность. По сторонним данным большинство заявок без кредитного чека.</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Для подписок Tribute да, но автопродление внешней VPN-подписки требует своей логики</t>
+          <t>Очень сильно: триалы/limited trials, rebilling с merchant-defined интервалом, многоуровневые цены, loyalty-скидки, win-back офферы для отменяющих, автоматические ретраи по расписанию мерчанта, email-уведомления по событиям подписки, CCBill Pay (токенизация до 25 способов оплаты), 3DS 2.0/SCA и MIT для card-on-file. Дефолтные лимиты цены: минимум $2.95, максимум $99.99 за транзакцию (исключения — только письменным согласованием).</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Платёжная ссылка + API + вебхук new_digital_product с HMAC-SHA256 в заголовке trbt-signature, ретраи 5 мин / 15 мин / 30 мин / 1 час / 10 часов; сложность 2 из 5</t>
+          <t>RESTful Transaction API (payment tokens, 3DS/non-3DS, deferred charges), legacy API, Advanced Widget API, Webhooks (overview + user guide), FlexForms hosted checkout с A/B тестами и CSS-кастомизацией, GitHub-репозитории, готовые модули WooCommerce 3.0 (октябрь 2025, + патч январь 2026), osCommerce, X-Cart, DatingPro, NATS4. Чистый Telegram-бот БЕЗ сайта не пройдёт: обязательны "Fully functional, live website", явные цены, контакты, Terms и Privacy Policy. Дополнительно есть ограничение выгрузки данных: Data Link Extract отдаёт CSV окнами максимум 24 часа и не чаще одного раза в 60 минут. Сложность интеграции: 3. API/webhooks/FlexForms документированы хорошо и есть готовые модули, но обязателен живой сайт с полным набором юридических страниц, плюс неочевидные вещи вроде дефолтного минимума цены $2.95 и лимитов выгрузки данных..</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Возможен rejected при модерации товара; приём идёт через СБП, и провайдер может изменить политику по VPN; возврат через API доступен только для платежей Stars; лимит цифрового товара 100000 RUB за разовую транзакцию</t>
+          <t>1) Резерв: при расторжении CCBill держит все средства минимум 6 месяцев, при приостановке за нарушение — 6-12 месяцев (деньги замораживаются в самый неудобный момент). 2) Запрет на обход: "for a period of one year following such cancellation you will not attempt to circumvent CCBill by utilizing any of CCBill's acquirers or service providers" — год нельзя перейти к тем же эквайерам. 3) Дефолтный минимум $2.95 за транзакцию: тариф 199 RUB/мес — это примерно $2.1, что НИЖЕ минимума; придётся либо поднимать минимальный тариф, либо письменно согласовывать исключение. 4) Российское юрлицо невозможно, банк обязан быть в стране инкорпорации. 5) Процент резерва не публикуется вообще. 6) Профиль бренда adult-центричный — дескриптор может вызывать вопросы у плательщиков. 7) Сильно отрицательные пользовательские отзывы (Trustpilot 1.8/5, Sitejabber 1.2/5 по данным Merchant Machine) — в основном потребительские, про биллинг и блокировки аккаунтов. ПРАКТИКА: Да, малый бизнес и стартапы берут: "No Min or Max Volumes", "All Merchant Sizes ... For startups, mid-sized companies, or enterprises alike", по сторонним данным большинство заявок без кредитного чека. Дополнительно подтверждено, что non-adult digital services с recurring billing относятся к среднему риску и в списке low risk прямо названы "Non-adult digital products, such as music, video, or non-adult subscription services" — это аргумент, что для VPN с подпиской можно просить medium, а не adult-прайс. Но: конкретно processing history в требованиях не упоминается, зато упоминаются MCC, TMF/MATCH blacklist и плохая кредитная история гарантора как факторы риска.</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>https://wiki.tribute.tg/ru/for-content-creators/content-restrictions.md, https://wiki.tribute.tg/ru/for-content-creators/fees-limits-currencies.md, https://wiki.tribute.tg/ru/for-content-creators/payouts.md, https://wiki.tribute.tg/ru/for-content-creators/digital-product/api-integration.md</t>
+          <t>https://ccbill.com/cs/client/policies/ccbill/acceptable_use.html, https://ccbill.com/cs/client/policies/cceu/acceptable_use-eu.html, https://ccbill.com/cs/client/policies/ccbill/terms_and_conditions_cc.html, https://ccbill.com/pricing, https://ccbill.com/merchants, https://ccbill.com/doc/list-of-countries-for-visa-and-mastercard-processing, https://ccbill.com/doc/risk-difference-between-low-risk-and-high-risk-accounts, https://ccbill.com/doc/merchant-accounting-faqs, https://ccbill.com/industries/high-risk-business, https://merchantmachine.co.uk/high-risk/ccbill/, https://www.guidingdecisions.com/ccbill-review-adult-credit-card-processing-built-for-the-business-everyone-else-declines</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -5103,159 +5103,159 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>verotel</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Boosty</t>
+          <t>Verotel (торговая марка Yoursafe B.V., Нидерланды, KvK 34180575; ранее Payment Institution, с 2019 — Electronic Money Institution)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Донат-платформа</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: официальные правила отдаются только JavaScript-рендерингом, текст не извлекается</t>
+          <t>High-risk эквайринг/PSP (IPSP + Payment Facilitator Visa/MasterCard/JCB/Discover/Diners; деньги держатся в эскроу Stichting Geldbeheer Verotel). НЕ Merchant of Record: договор называет продавцом Merchant ("the individual or business entity listed under Merchant Company Name"), Verotel лишь процессит и выдаёт Subscription Code.</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>серая зона. Ни на одной публичной странице Verotel (главная, pricechart, productchoice, integration, paymentprocessing, contactus, merchantagreement) нет слов VPN, proxy, anonymizer, circumvention или privacy tools. Более того, content policy вообще НЕ публикуется: в Merchant Agreement сказано "Merchant is fully responsible for the contents of Merchant's Web site and follow the content policy of Company. The content policy of Company will be sent on request and is published on www.verotel.com" — но на сайте её нет (проверены все разумные URL, все 404). Позиционирование строго adult/entertainment: "Process credit cards for your entertainment website", "Solutions for Webmasters selling Online Entertainment", "Adult? No problem!", "perfect solution for cam sites". Сторонний обзор перечисляет обслуживаемые индустрии (Adult, CBD &amp; Hemp, Cigars &amp; Tobacco, Dating, Electronics, Gaming, Gas Station, Hosting, Marijuana/Cannabis, SAAS, SEO &amp; SEM, Smoking Accessories, Travel, Web Design) — VPN там отсутствует, но есть близкие Hosting и SAAS.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>РФ и СНГ; выплаты заявлены в долларах или евро на банковские карты</t>
+          <t>Формально — "Accepted merchants | Worldwide" (графа в официальном Price and comparison chart), и "High risk accepted: Yes". Никакого опубликованного списка стран нет, поэтому Россия/СНГ формально не исключены текстом, но: (а) Verotel — нидерландская EMI (Yoursafe B.V.), на которую распространяются санкционные и AML-правила EU/Wwft; (б) в Merchant Agreement есть прямая оговорка "High Risk Countries: Company shall have the right, in its sole discretion, to block certain high risk countries from transaction processing, without the need to compensate Merchant for any damages that might result from such action". Прямого подтверждения, что принимают или не принимают мерчанта-резидента РФ/юрлицо из СНГ, найти не удалось — по этому пункту честная оценка: не подтверждено, низкая уверенность, нужно письмо в sales. Ни Казахстан, ни Армения, ни Грузия, ни Кыргызстан, ни ОАЭ в публичных материалах не упомянуты.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Банковские карты (по правилам платежей), внутренние подписки</t>
+          <t>Кредитные и дебетовые карты: Visa, MasterCard (Payment Facilitator), JCB, Discover, Diners Club; Verotel US-Check (чек по банковским реквизитам для США); Verotel Direct Debit Europe — доступен в Германии, Австрии, Швейцарии, Бельгии, Франции, Нидерландах, Италии, Испании и Словакии. Приём в USD, CAD, AUD, EUR, GBP, NOK, DKK, SEK, CHF; расчёты с мерчантом в USD, EUR или GBP. Мультивалютность — только на PREMIUM.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>11,7% агентского вознаграждения при оплате банковскими картами с 20.02.2026</t>
+          <t>Полностью публично. BASIC: EUR 500/год регистрация (для Visa/MC registration и compliance monitoring) + фиксированные 15,5% с транзакции независимо от объёма. PREMIUM: EUR 0/год, ступенчато по среднему недельному обороту: 1-1.000 EUR = 14,0%; 1.001-2.000 = 13,9%; 2.001-3.000 = 13,8%; 3.001-4.000 = 13,7%; 4.001-5.000 = 13,6%; 5.001-7.000 = 13,5%; 7.001-10.000 = 13,4%; 10.001-17.500 = 13,3%; 17.501-25.000 = 13,2%; 25.001-40.000 = 13,1%; 40.000+ = 13,0%. Обязательный недельный минимум для PREMIUM: EUR 100/нед; если недельный оборот менее EUR 1.000 — доп. сбор EUR 25/нед. Наценка на рекуррентные транзакции +1,5% (не применяется к первой транзакции подписки). Chargeback fees — нет, refund fees — нет. Но: "If the number of transactions in the last four weeks, with a two-week lag period, exceeds 50 transactions ... If this ratio is 1.0% or more, a surcharge of 2.5% will apply to the base rate." Verotel US-Check и Direct Debit Europe: 15,5% (Basic) / 14,0% (Premium).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Setup fee отсутствует: "We provide free technical setup of your account - you supply the website and the content" (сторонний обзор подтверждает Setup Fee $0, Monthly Fee $0, Early Termination Fee $0, month-to-month без контракта). Вместо setup — годовой регистрационный платёж BASIC EUR 500,00, причём "Annual renewal fees for Verotel BASIC accounts will be waived if the transaction volume is at least EUR 100 per week on the renewal date."</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>10% на 6 месяцев (26 недель). Прайс: "All accounts have a 10% 6-month rolling reserve" (сказано дважды, и для BASIC, и для PREMIUM). Договор: "Company shall also hold a 10% of Customer Charges for a period of 26 weeks against potential charge backs ("Holdback"). This Holdback is kept by an escrow agent, appointed by Company. Until further notice this escrow agent is Escrow Stichting. Company shall have the right, in its sole discretion, to adjust the amount held as is deemed necessary as security against future charge backs after notification to the Merchant." При отмене аккаунта: "Any Customer Charges or retained Holdback that has not been invoiced on date of cancellation will be paid out to Merchant 6 months after the last Merchant invoice." При приостановке аккаунта: "Suspended holdback and reserves are available to Merchant 30 weeks after the suspension of a Merchant's account in the form of a TBC-Payment" и их надо востребовать в течение 12 недель, иначе сгорают. По сторонним данным именно 10% резерв — главная причина жалоб мерчантов.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Вывод в долларах или евро на банковские карты; фиксированный сбор 1 USD или 1 EUR за операцию; лимит 1500 за разовую транзакцию; суточные, недельные и месячные лимиты зависят от Visa или MasterCard</t>
+          <t>Публично заявлены ежедневные выплаты: "Daily payouts: Verotel has never missed a payment", "Daily deposit of funds — All Verotel accounts come with a Yoursafe Business Account", услуга "Free of charge". При этом Merchant Agreement описывает недельную модель: "Merchant will receive an invoice on a weekly basis, every Monday ... The balance of any invoice, if positive, will be paid 14 days after the issuing date of the invoice. If the balance of any invoice is negative, payment is due within 14 days." Это расхождение (ежедневный депозит на Yoursafe-счёт vs оплата счёта через 14 дней) нужно уточнять в договоре. Сборы за вывод с Yoursafe Business Account: SEPA IBAN в EUR — EUR 7,50; счёт в UK — GBP 15,00; любой другой международный wire — USD 30,00; US Check на US-бенефициара — USD 2,50; International Check для не-US бенефициара — USD 0,00; ACH только для US-бенефициаров — USD 0,00.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Юрлицо НЕ обязательно — в договоре "Merchant" определён как "the individual or business entity listed under Merchant Company Name", а на странице About сказано: "Our account offerings are specifically tailored to all payment processing needs: from the sole proprietor with a small website to larger merchants with a portfolio of online properties." То есть sole proprietor/ИП концептуально возможен. Обязателен собственный сайт и контент ("you supply the website and the content"), сайт должен соответствовать content policy (не публикуется, выдаётся по запросу). Регистрация Visa/MC и compliance monitoring включены в годовой платёж. KYC/AML по нидерландским Wwft и Wft: "The Merchant is obliged to actively supply the Company at all times with necessary information or documents which the Company or its affiliates need to comply with relevant Dutch laws and regulations and more specifically by virtue of the Wwft and/or Wft." Для adult-контента может запрашиваться документация по 18 U.S.C. §2257 ("Failure to comply ... may result in immediate suspension of processing"). PREMIUM требует 6 месяцев процесссинговых стейтментов — то есть фактически processing history обязательна для дешёвого тарифа; BASIC истории не требует. VAT/налоговый номер явно не требуется в тексте, но налоги — на мерчанте.</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Да (подписки - суть платформы)</t>
+          <t>Да, ядро продукта: "The Basic Account includes a turn-key subscription management system", VerotelRUM (Remote User Manager) для добавления/изменения/удаления подписчиков через postback, FlexPay API с поддержкой подписок, Control Center API для отмены будущих биллингов/даунгрейдов/рефандов. Рекуррентные транзакции +1,5% к базовой ставке. Dunning/ретраи как отдельный продукт публично не описаны — не подтверждено.</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Отдельная страница платформы, интеграции с ботом нет; сложность 3 из 5</t>
+          <t>Hosted order pages (мультиязычные, кастомизируемые логотипом/цветом), VerotelRUM — скрипт на сервере мерчанта (библиотеки ASP v1.0 и Perl v1.0, документация PDF), Verotel может установить RUM бесплатно; Verotel FlexPay API v3.x (любая сумма и описание, one-click, upgrade, подписки) + PDF-документация; Control Center API (https://controlcenter.verotel.com/api-doc/index.html); OpenAffiliate. Чистый Telegram-бот без сайта не подойдёт: RUM работает через postback на сервер мерчанта, а сам Verotel требует "you supply the website and the content". Сложность интеграции: 3. Hosted-страницы и postback технически несложные, документация и библиотеки открыты, но обязательны собственный сайт и (для RUM) серверный скрипт с postback; плюс для PREMIUM нужны 6 месяцев стейтментов, а для BASIC — EUR 500/год и ставка 15,5%..</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Вывод в валюте при рублёвой выручке даёт конвертацию и валютные вопросы; при статусе Неактивного автора списывается 1 единица валюты в день, соглашение расторгается; VPN-политика неизвестна</t>
+          <t>1) 10%/26 недель holdback — самый обсуждаемый минус, по сторонним данным именно он основной источник жалоб мерчантов. 2) Ставка дорогая: 15,5% на BASIC и 13,0-14,0% на PREMIUM плюс 1,5% на рекуррент — для чеков 199-1590 RUB это очень много. 3) Content policy не опубликована — нельзя заранее проверить, разрешён ли VPN; ответ только письмом. 4) Расхождение daily payouts (сайт) vs оплата счёта через 14 дней (договор). 5) При приостановке аккаунта резервы выдаются через 30 недель и сгорают, если не востребовать за 12 недель. 6) Нет chargeback fee, но при CB-ratio &gt;=1,0% (при &gt;50 транзакциях за 4 недели) ставка растёт на 2,5% — а VPN/подписки как раз склонны к CB. 7) Формулировка "High Risk Countries" даёт Verotel право в одностороннем порядке блокировать транзакции из целых стран без компенсации. 8) Позиционирование adult/entertainment, не SaaS/VPN. 9) Маркетинговые страницы в футере помечены "© 2023 - Verotel Merchant Services" — часть контента может быть не обновлена. ПРАКТИКА: Да, малый бизнес и одиночек берут: BASIC создан именно под это — "The Verotel Basic account is perfect for new online businesses", "No minimum", "No history needed", "from the sole proprietor with a small website to larger merchants". Нет setup fee, нет monthly fee, нет early termination fee, договор month-to-month. Жалобы есть, но в основном (а) потребительские — Trustpilot по verotel.com 1,9/5, и (б) мерчантские — про удержание 10% резерва; наёмных судебных исков/федеральных жалоб сторонний обзор не нашёл.</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>https://www.playground.ru/misc/news/platforma_boosty_vvodit_edinuyu_komissiyu_dlya_avtorov-1825946, https://boosty.to/boosty/posts/de1e6f32-3a80-4824-95bd-a264ff1b00aa</t>
+          <t>http://verotel.cc/en/pricechart.html, http://verotel.cc/en/merchantagreement.html, https://www.verotel.com/en/productchoice.html, https://www.verotel.com/en/paymentprocessing.html, http://verotel.cc/en/integration.html, https://www.verotel.com/en/contactus.html, https://www.verotel.com/en/index.html?lang=en, https://merchantalternatives.com/reviews/verotel/, https://wifitalents.com/service/high-risk-payment-processing/</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>epoch</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DonationAlerts</t>
+          <t>Epoch (Epoch Payment Solutions; юрлицо по Modern Slavery Statement: Summit Building, 3415 North Pines Way, Suite 206, Wilson, Wyoming 83014, USA; потребительский офис в Santa Monica, CA)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Донат-платформа</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Формально не запрещено: пункта VPN, прокси или анонимайзер в правилах нет, но запрещён контент, нарушающий закон; юридически это платформа донатов, а не продаж</t>
+          <t>High-risk эквайринг/PSP (сам себя называет "full service Payment Facilitator", одобренный Visa и MasterCard Payment Facilitator, PCI-DSS Level 1 с 2002 года). НЕ Merchant of Record: обрабатывает платежи и хранит карточные данные, но продавцом остаётся мерчант; в разделе про digital content прямо указано, что мерчанты из US/EU должны платить регистрационный сбор Visa/MasterCard.</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>серая зона, ближе к "не подтверждено". У Epoch вообще нет публичной Acceptable Use Policy: на сайте есть только Privacy Policy, Copyright Infringement Policy, Legal (Modern Slavery Statement) и Accessibility Statement — проверены все варианты URL (/legal_docs/acceptable_use, /aup, /terms, /merchant_agreement, /legal_terms) — 404. Слова VPN, proxy, anonymizer в публичных материалах Epoch не встречаются. Позиционирование — платежи для digital content вообще и adult-индустрии в частности: сторонний обзор 2026 года описывает Epoch как "Established payment processor for adult entertainment and high-risk digital goods". Acceptance VPN-сервиса публично не подтверждён и не опровергнут — нужен прямой запрос в sales.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>СНГ; оператор Zaya Solutions Limited (Гонконг)</t>
+          <t>Только США и Европа. Дословно из FAQ на business_services: "Payment Facilitators must remain compliant with processing regions established by the card associations. Epoch processes for consumers worldwide, however merchants must be within either the US or EU region. If your business is a non US entity, it must be incorporated in the European region and at least one of the principals must also reside in the European region. If you are a sole proprietor, you must reside in the European region." Опубликованный список "Qualifying EU Region Countries": Andorra, Austria, Belgium, Bulgaria, Channel Islands, Croatia, Cyprus, Czechia, Denmark, Estonia, Faroe Islands, Finland, France, Germany, Gibraltar, Greece, Greenland, Hungary, Iceland, Ireland, Isle Of Man, Israel, Italy, Latvia, Liechtenstein, Lithuania, Luxembourg, Malta, Monaco, Netherlands, Norway, Poland, Portugal, Romania, San Marino, Slovakia, Slovenia, Spain, Sweden, Switzerland, Türkiye, United Kingdom, Vatican City. Выпадающий список "COUNTRY OF BUSINESS" в форме регистрации совпадает: United States + Andorra...United Kingdom (включая Türkiye и Israel). России, Казахстана, Армении, Грузии, Кыргызстана, ОАЭ там НЕТ. Российский резидент/самозанятый не подходит.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Банковские карты (RUB, EUR, USD), YooMoney, VKPay, мобильный счёт, крипта в USDT</t>
+          <t>Один из самых широких наборов: Visa, Mastercard, Maestro, JCB, Discover, Diners Card, PayPal, BLIK, iDEAL, Bancontact, Multibanco, Przelewy 24, PIX, Boleto Bancario, Khipu, Pago Efectivo, SPEI, PaySafeCard, PaySera, EPS, Euteller, ePay, Direct Debit, Bank Cash-ins / Bank Transfer-ins / Pay Via Bank, Pay with Mobile. Поддержка австралийского, канадского, европейских и латиноамериканских валют, ~60+ валют, автоподстановка валюты и языка по IP/браузеру (18 языков, включая русский).</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>12% при обороте до 1 млн RUB за предыдущий месяц, 9% свыше; первый месяц всегда 12%; за перечисление на карту РФ 1,9% плюс 20 RUB; конвертация с удержанием 10% от курса OER</t>
+          <t>Опубликованы полностью, модель flat % по среднему недельному объёму: Tier 1 (0-$5.000) = 15,00%; Tier 2 ($5.001-$7.000) = 14,75%; Tier 3 ($7.001-$9.000) = 14,50%; Tier 4 ($9.001-$12.000) = 14,25%; Tier 5 ($12.001-$15.000) = 14,00%; Tier 6 ($15.001-$20.000) = 13,75%; Tier 7 ($20.001-$25.000) = 13,50%; Tier 8 ($25.001-$35.000) = 13,25%; Tier 9 ($35.001-$45.000) = 13,25%; Tier 10 ($45.001+) = по запросу (Contact Us). Отдельно: "We do not charge a transaction fee, nor a decline fee, maintenance fee, monthly fee, or annual fee. Our full suite of services, features, customer and technical support, merchant services, and international billing are included in a flat fee which is a percentage of your sales. New accounts without an established volume of sales start at 15%. Your rate is periodically adjusted based on sales figures." Сбор за кредит/рефанд — $1. Chargeback fee — $12,50.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Setup fee отсутствует, но есть обязательный регистрационный сбор кард-брендов. Дословно: "We do not charge a fee to set up an account. However, merchants selling digital content from a US and EU based company are required to pay the Visa and MasterCard registration fee. The initial fee and annual renewal is $1,950. You will pay this fee during the contract initiation and we then pay the card associations on your behalf." То есть $1.950 при подключении и столько же ежегодно — это существенно выше, чем у SegPay (Visa $950 + MC $500 только для adult/dating/nutraceutical) и у CCBill (Visa $950 + MC $1000).</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Investigation Period до 90 дней: выплата может быть задержана или отменена для оценки риска</t>
+          <t>Резерва НЕТ по публичному заявлению: "Is there a security deposit or reserve withholding? — We do not require a security deposit nor do we withhold a reserve. Most, if not all banks and/or processors require either a rolling reserve (of up to 6 months) or a security deposit based on a percentage (5-10%) of your gross sales. We do not require either. This means you receive more of your money faster than you would with other solutions." Это самое выгодное условие из четырёх провайдеров, но это заявление самого Epoch (публичного договора с условиями резерва на сайте нет), поэтому его обязательно надо фиксировать в контракте — для high-risk эквайринга отсутствие резерва нетипично.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Ежедневно по мере возможности, но гарантии нет; лимиты по карте РФ 50 транзакций в день и 50 в месяц, минимум 150 RUB, максимум 2500000 RUB</t>
+          <t>по запросу (не публикуется). На публичных страницах Epoch нет ни периодичности выплат, ни порогов, ни комиссий за wire/ACH — только маркетинговое "This means you receive more of your money faster than you would with other solutions". Никаких цифр (сроки arrears, минимальный баланс, стоимость перевода) не опубликовано, поэтому здесь честная оценка — не подтверждено.</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>KYC обязателен до вывода средств; требования к статусу физлицо или самозанятый не подтверждены</t>
+          <t>Жёстко: юрлицо инкорпорировано в US или в Europe region, минимум один из принципалов должен там же проживать; если sole proprietor и бизнес не US — он обязан проживать в European region. В форме регистрации страна бизнеса выбирается только из US + европейского списка. Обязательны собственные платёжные формы/сайт с продуктом и ценами (Epoch предоставляет hosted secure payment forms и сам держит карточные данные). PCI-DSS Level 1 у провайдера; поддержка 3DS/VBV и MasterCard SecureCode. API-документация выдаётся ТОЛЬКО после начала регистрации: "In order for us to send you the APIs, you need to start the sign up process. Once you are assigned a sales representative, they will be happy to assist you." VAT/налоговый номер в публичных требованиях не описан — не подтверждено.</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено (донатная модель)</t>
+          <t>Да, широко: "Recurring Billing — You can offer your customers the ability to purchase a subscription that bills automatically until the customer cancels"; Per Unit Billing (токены/кредиты/блоки времени); One-Time Billing; One-Click Billing (повторные покупки без ввода данных, т.к. Epoch хранит карту). Управление отменами и billing support 24/7/365 на стороне Epoch. Триалы/dunning как отдельные продукты публично не описаны — не подтверждено.</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>API (apidoc) + виджеты + страница DALink; связка донат - выдача VPN-доступа нештатная, сложность 3 из 5</t>
+          <t>Feature-rich API + hosted secure payment forms; автоматическая локализация (язык по браузеру, валюта по IP); "developer-friendly"; свои data structures/object classes/variables. Documentation/API выдаются после старта регистрации. Отдельной публичной библиотеки интеграций/плагинов (как у CCBill/SegPay) не найдено. Telegram-бот без сайта: формально требуется только страна бизнеса и продукт, но платёжные формы Epoch hosted, а требования к сайту/оферте в публичных материалах не детализированы — риск, что чисто-ботовый магазин без сайта не примут, оцениваю как высокий. Сложность интеграции: 3. Регистрация открытая (онлайн-форма, ответ в течение 24 часов), hosted payment forms и API снимают большую часть работы, но API-доки дают только после подписания, география ограничена US/EU, обязателен сбор $1.950 и неясны требования к сайту..</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Переквалификация донатов в выручку даёт налоговые вопросы; блокировка аккаунта за нарушение правил; заморозка до 90 дней; отсутствие гарантии ежедневных выплат</t>
+          <t>1) $1.950 при подключении и ежегодно — самый дорогой вход из четырёх, при этом для чеков 199-1590 RUB это критично. 2) Ставка 15,00% на старте (Tier 1, объём до $5.000/нед) — самая высокая стартовая ставка в подборке. 3) Публичной AUP нет, VPN-политика неизвестна — риск отказа после оплаты $1.950. 4) Российское юрлицо/резидент невозможен. 5) Обещание "we do not withhold any reserve" не подтверждено договором — обязательна фиксация в контракте. 6) Периодичность и стоимость выплат не публикуются. 7) Профиль adult-биллинга (Epoch исторически ассоциируется с adult), что влияет на репутацию и на дескриптор. 8) Публичные страницы не раскрывают пороги, штрафы и условия терминации. ПРАКТИКА: Малый бизнес формально берут: "Our services can meet the needs of companies ranging from internet start-ups to large multi-national organizations" и "New accounts without an established volume of sales start at 15%", обработка истории для входа не требуется (наоборот, ставка для новых аккаунтов стартует с базовой 15%). Практика: по данным сайта решение по заявке за 24 часа (обещание "We'll be in touch within 24 hours"). Честная оговорка: проверяемых публичных данных о заморозках средств у мерчантов Epoch я получить не смог — BBB-профиль Epoch отдаёт 403 (Cloudflare), отчёт investigations.org также 403, поэтому по риску заморозки уверенность низкая. У Epoch есть отдельный публичный массив потребительских жалоб (BBB, Sikayetvar, ProConsumer), но это потребительская сторона, а не мерчантская.</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>https://www.donationalerts.com/terms-of-service/payments?cis=1, https://www.donationalerts.com/terms-of-service/broadcasters</t>
+          <t>https://epoch.com/, https://epoch.com/business_services, https://epoch.com/business_services/contract_initiation.html, https://epoch.com/legal_docs/legal.html, https://epoch.com/legal_docs/privacy_policy.html, https://epoch.com/legal_docs/copyright.html, https://wifitalents.com/service/high-risk-payment-processing/</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
@@ -5267,241 +5267,241 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>payop</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>VK Donut</t>
+          <t>Payop (юрлицо: Transferop Payment Gateway Ltd., Ванкувер, Канада)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Донат-платформа</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: страница правил не отдаётся для машинного чтения</t>
+          <t>High-risk эквайринг/PSP — фактически платёжный шлюз/агрегатор, а не прямой банк-эквайер и не MoR</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>серая зона. VPN, proxy, anonymizer, circumvention, «privacy tools» и «unblocking» не упомянуты ни разу ни в списке Prohibited Industries в Acceptable use policy, ни в FAQ-списке моделей, с которыми Payop «не работает». При этом смежные ниши прямо запрещены: в FAQ указаны «IPTV - Internet television» и «Video hosting». Практического значения это не имеет: Payop полностью закрывает Россию и как юрисдикцию мерчанта, и как юрисдикцию плательщика, поэтому для Kometa в текущей конфигурации политика по VPN второстепенна — отказ придёт по гео.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>РФ, внутри ВКонтакте</t>
+          <t>Заявлено 170+ стран, но есть жёсткий стоп-лист. В FAQ прямо сказано: "we do not provide our services to the legal entities and private entrepreneurs, which registered and/or residing in the following countries" — и в списке есть "Russia (the Russian Federation)", а также Belarus, United States of America, Taiwan, Afghanistan и др. Отдельно оговорено: "if the Ultimate Beneficial Owner (UBO) of a legal entity or its corporate business structure is registered and/or residing in the banned countries, we reserve the right to refuse service without requesting the UBO's proof of address". Acceptable use policy добавляет: "You may not use our services in case you or your payers are situated in certain countries and jurisdictions" — Россия в том же списке. Итог: ИП/самозанятый/юрлицо из РФ не принимаются, и плательщики из РФ тоже запрещены. Юрлицо в Казахстане/Армении/Грузии/Кыргызстане/ОАЭ в стоп-лист формально не входит, но при UBO-резиденте РФ Payop оставляет за собой право отказать без объяснений.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Внутри VK (VK Pay и др.), детали не подтверждены</t>
+          <t>Международные и локальные карты, банковские переводы, интернет-банкинг, e-wallets, предоплата, мобильные платежи, наличные, Pay by Bank (open banking, SCA/PSD2, вендор заявляет "no chargebacks"); 100+ валют, 170+ стран. Вывод: SEPA/SWIFT, e-wallet PayDo, крипта, Payoneer.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>по запросу (не публикуется). Публичной страницы тарифов нет (payop.com/pricing отдаёт 404), ни в FAQ, ни в Legal-разделе нет ни процента, ни фиксированной ставки, ни chargeback-фи, ни месячного минимума. Единственная публичная цифра по удержаниям — rolling reserve 5–10%.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Опубликовано: "The Rolling Reserve refers to a percentage (5-10%) of the transactions received that is held for three months. It is a standard practice in payment processing used to cover possible chargebacks/refunds or fraudulent activities." Дополнительно существует Pending balance: срок удержания "depends on the type of account verification, project history, turnover, industry, risk level" — конкретные сроки не публикуются.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Внутри VK, детали не подтверждены</t>
+          <t>Опубликованы типы и частота. Settlement — вывод на счета, оформленные на имя компании или на pooled-счета, требует предварительной верификации реципиента (Bank statement или Bank Confirmation Letter). Payout — вывод на внешние счета без предварительной верификации владельца, в т.ч. массовые выплаты через API. Scheduled settlements: bi-weekly (дважды в неделю, понедельник и среда), weekly (фиксированный день), monthly. Сроки зачисления и минимальные суммы — по запросу (не публикуется).</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Принимаются и компания, и individual entrepreneur: "You can create and verify a merchant account for a company or an individual entrepreneur." Для ИП: официальный документ о госрегистрации ИП, подтверждение налоговой регистрации, паспорт/ID, proof of residence. Для компании: Certificate of Incorporation, реестры директоров и акционеров, паспорта и proof of residence директоров и UBO, Memorandum &amp; Articles of Association, Certificate of Good Standing/Extract (если компании больше 2 лет). Для Betting/Gambling/Crypto/Forex — лицензия на деятельность и Payment Agent Agreement. Все документы на английском или с заверенным переводом, proof of residence — не старше 3 месяцев. Обязателен сайт: логотипы платёжных систем, Contact us, данные компании (название, адрес, страна регистрации), условия доставки, подробное описание товаров и услуг, Privacy Policy, Return &amp; Cancellation Policy, SSL. Требование VAT/GST-номера не упоминается — не подтверждено. Pre-check ≤ 2 рабочих дня, далее верификация через платформу KYCB.</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>не подтверждено: публичной документации Payop по подпискам, токенизации, free trials и MIT/CIT (в FAQ, на странице Merchant Services и в GitHub-репозитории API) обнаружить не удалось; описаны только checkout/invoice, статусы транзакций, балансы и выплаты.</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Внутри ВКонтакте, вне Telegram; ломает воронку бота; сложность 4 из 5</t>
+          <t>REST API (документация: github.com/Payop/payop-api-doc), hosted checkout page, плагины/CMS, отчёты, массовые выплаты через API, merchant panel с проектами и ключами (public/secret key на проект). Storefront-бот в Telegram без сайта не подойдёт: у Payop "a project is your website used to make sales", а верификация проекта требует сайта с полным набором политик. Сложность интеграции: 3 — стандартный REST API + hosted checkout и понятная документация, но обязательны полноценный сайт с политиками, KYCB с документами на ИП/юрлицо и риск-проверка; плюс критичный блокер по РФ..</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Полное отсутствие проверяемых данных по правилам, комиссии и выплатам; работа вне Telegram</t>
+          <t>1) Российская Федерация в стоп-листе — для мерчантов, для UBO и для плательщиков: это делает Payop неприменимым для Kometa в текущей конфигурации. 2) Rolling reserve 5–10% на 3 месяца плюс неопределённый pending-hold. 3) Нет публичных тарифов и chargeback-фи — экономику нельзя посчитать заранее. 4) Payop — агрегатор: часть методов идёт через партнёров, возможны отказы на стороне апстрима. 5) Юрлицо — канадский MSB (FINTRAC M22769088), то есть не банк и не прямой договор с Visa/Mastercard. ПРАКТИКА: Публично Payop позиционирует "fast onboarding", "no paperwork, no delays" и отдельную страницу Digital goods с блоком "Built for high-risk businesses — Reliable payments even in industries underserved by traditional providers", т.е. работа с малым бизнесом заявляется. Независимого подтверждения онбординга без истории процессинга и жалоб на заморозку средств найти не удалось; Trustpilot по payop.com — около 3.0–3.8/5 в разных локалях. Оценивать как не подтверждено.</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>https://vk.ru/@donut-pravila, https://calculory.com/ru/calculators/vk-donut-revenue-calculator</t>
+          <t>https://payop.com/acceptable-use-policy/, https://payop.com/faq-category/start-work/, https://payop.com/faq-category/account-verification/, https://payop.com/faq-category/transactions-balances-reporting/, https://payop.com/faq-category/settlements-and-payouts/, https://payop.com/merchant-services, https://payop.com/digital-goods, https://payop.com/pricing/, https://github.com/Payop/payop-api-doc</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>unlimit</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>FunPay</t>
+          <t>Unlimit (ранее Unlimint, ранее Cardpay); в документах и отзывах фигурируют UNLIMINT EU LTD (Кипр) и UNLIMINT PSP FZ-LLC (ОАЭ)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Площадка цифровых товаров</t>
+          <t>High-risk эквайринг/PSP — глобальный acquiring PSP + BaaS + crypto on/off-ramp; НЕ MoR</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Серая зона: прямого запрета VPN нет, но п. 2.2.5 запрещает подписки на сервисы без спецраздела, а п. 2.1.12 запрещает размещать объявления на других площадках под угрозой отказа в выплатах</t>
+          <t>серая зона. Единого глобального Acceptable Use / Banned Category List на unlimit.com нет: сайт публикует только Website Terms of Use (last updated 24.04.2024), где отраслевых ограничений нет вообще, а раздел "Prohibited use" относится к использованию самого сайта, а не к деятельности мерчанта. Публичный Banned Category List существует только у индийской структуры группы (in.unlimit.com) — и в нём VPN, proxy, anonymizer и circumvention НЕ упомянуты. Запрещены смежные «обходные» категории (modification chips, cable descramblers/black boxes, hacking and cracking materials), плюс очень широкая формулировка про бизнесы, работающие в юридически неоднозначной зоне. Явного разрешения VPN нет, явного запрета тоже нет.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>РФ и СНГ</t>
+          <t>Группа работает в EU/UK (Кипр, Великобритания), Латинской Америке, APAC, Африке, Индии, ОАЭ. Публичного списка принимаемых и непринимаемых юрисдикций мерчантов на unlimit.com нет — не подтверждено. Явного упоминания России или запрета для резидентов РФ в публичных документах группы также нет; при этом для лицензированных EU/UK-структур группы приём резидентов РФ де-факто крайне маловероятен по санкционным причинам — но это оценка, а не опубликованный факт, уверенность низкая. Онбординг начинается со страницы acquiring-onboarding с обязательными полями о типе бизнеса и сайте.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Внутренние методы площадки, детали не подтверждены</t>
+          <t>Карты (credit/debit, Visa/Mastercard), Apple Pay, Google Pay, SEPA Direct Debit, bank transfer, Boleto, Pix, digital wallets, локальные методы LATAM/APAC/Африки; отдельно crypto on-ramp/off-ramp (crypto.unlimit.com, stable.com). По стороннему справочнику paymentproviders.io регионы покрытия — Азия, Европа, Латинская Америка (Северная Америка и Океания не указаны).</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено: три слоя (сбор с продажи, сбор за вывод, стоимость платёжного метода), ставки не опубликованы</t>
+          <t>по запросу (не публикуется). На unlimit.com нет ни процентов, ни фиксированной ставки, ни chargeback-фи, ни месячного минимума. Сторонний справочник paymentproviders.io указывает модель "Custom" (цена по запросу) и ставок не приводит.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>При блокировке по категорийным нарушениям выплата только после идентификации, 30 или 60 дней</t>
+          <t>по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>При блокировке по ряду пунктов выплаты не производятся вовсе</t>
+          <t>Продукт Payouts есть (unlimit.com/payouts). Сторонний справочник paymentproviders.io указывает срок расчётов "1–3 business days". Официально сроки, минимальные суммы и валюты расчётов Unlimit не публикует — по запросу (не публикуется).</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Физлицо, регистрация свободная; документы для вывода не подтверждены</t>
+          <t>Публичных требований к онбордингу группа не публикует: страница acquiring-onboarding на глобальном домене отдаёт 404, списка документов KYC/KYB нет, требований к сайту нет. Практически речь о юрлице (в отзывах фигурируют корпоративные структуры группы), но подтверждения возможности ИП/самозанятого, требований к VAT/GST и к сайту найти не удалось — не подтверждено.</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Да, подтверждено официальной документацией. Раздел "Recurring Types" описывает credentials-on-file (COF): "A recurring payment is a credentials-on-file (COF) transaction that allows the Merchant to charge a Customer's debit or credit card for goods or services on a regular schedule or on-demand". Поддерживаются one-click payments и scheduled payments (scheduled by Acquirer / scheduled by Merchant), схемы CIT и MIT; интервал между транзакциями при расписании не может превышать 1 год. Оговорка: "Recurring operation can be used with BANKCARD payment method only." Режимы интеграции: payment page, gateway, server-to-server. Картхолдер автоматически уведомляется о создании подписки и о каждом успешном/неуспешном списании. Публичного описания retry/dunning-логики не найдено — не подтверждено.</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Ручная или автоматическая выдача; автовыдача прямо запрещена для товаров, требующих общения или доп. услуг; сложность 2 из 5</t>
+          <t>REST API + SDK (публичный iOS SDK: github.com/cardpay/unlimit-ios-sdk), hosted payment page, gateway mode, server-to-server, sandbox/demo (demo.unlimit.com/ma-new), документация integration.unlimit.com, webhooks (подтверждается сторонними справочниками и Gr4vy-коннектором). Данных о приёме магазина-бота в Telegram без сайта нет — не подтверждено; процесс онбординга предполагает наличие сайта/продукта. Сложность интеграции: 4 — технически всё стандартно (API/SDK/hosted page/sandbox), но это крупный enterprise-эквайер: KYB, отсутствие публичных тарифов и публичного AUP, непрозрачная политика по РФ и высокорисковым нишам. Для нового мелкого VPN-проекта без истории процессинга шансы не подтверждены и, скорее, низкие..</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Блокировка и отказ в выплатах за размещение объявлений на других площадках (п. 2.1.12) и за передачу контактов, включая Telegram (п. 1.1); риск трактовки п. 2.2.5 против VPN-подписок</t>
+          <t>1) На глобальном сайте полностью отсутствует публичная политика по VPN и высокорисковым нишам — решение принимается индивидуально и может быть отозвано. 2) Нет публичных тарифов, резервов и сроков выплат: экономику нельзя оценить заранее. 3) Репутационный риск: Trustpilot по unlimit.com — 1.6/5 ("Bad"), сотни жалоб 2025–2026 о непоставленной крипте, зависших SEPA-переводах и неотвечающей поддержке; большая часть жалоб относится к потребительскому crypto-сервису, а не к мерчант-эквайрингу, но это одна и та же группа. 4) Не подтверждено, принимаются ли резиденты РФ и структуры с российским UBO. 5) Единственный публичный banned-лист — индийский, он формально может не совпадать с политикой европейских структур группы. ПРАКТИКА: Не подтверждено: публичных данных, что Unlimit онбордит мелкий бизнес без истории процессинга, нет; при отсутствии тарифов и AUP это выглядит как enterprise-онбординг по запросу. Массовые жалобы в Trustpilot касаются потребительского крипто-направления (невозвраты, незачисленные переводы) — для мерчанта это сигнал о качестве операционки и поддержки, а не о мерчант-политике.</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>https://funpay.com/trade/info, https://foxreload.com/ru/library/marketplaces/funpay-seller-commission-fees</t>
+          <t>https://www.in.unlimit.com/banned-category-list/, https://www.in.unlimit.com/general-terms-and-conditions-for-unlimit-services/, https://www.unlimit.com/website-terms-of-use/, https://www.unlimit.com/payment-processing/, https://www.unlimit.com/sitemap-global-pages.xml, https://www.unlimit.com/sitemap-global.xml, https://integration.unlimit.com/, https://integration.unlimit.com/doc-guides/r59ahoj0tkvzk-a-recurring-types, https://www.trustpilot.com/review/www.unlimit.com, https://paymentproviders.io/compare/unlimit-vs-2checkout?focus=licensing, https://docs.gr4vy.com/connections/payments/unlimit-card</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>praxiscashier</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PayMaster</t>
+          <t>Praxis Cashier (Praxis Tech Ltd., Лимасол, Кипр)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
+          <t>НЕ эквайринг и НЕ PSP: платёжный оркестратор / hosted cashier. Дословно: "we do not process or settle transactions, nor do we handle client funds."</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Серая зона: оферта молчит, требование общее - товары не должны входить в список запрещённых к продаже; VPN прямо не назван</t>
+          <t>серая зона (скорее нет). В Client Acceptance Policy перечислены только три допустимые отрасли — iGaming, Trading / Forex, E-commerce — плюс требование быть лицензированным зарегистрированным бизнесом; VPN не назван ни в разрешённых, ни в запрещённых. В запретах есть "Malware or cybercrime tools", к чему VPN формально не относится, но также сказано, что клиенты в ограниченных и санкционных юрисдикциях, "including the United States", не допускаются. Практически важнее другое: даже при успешном онбординге Praxis не решает задачу приёма денег — свой эквайер/PSP всё равно нужен отдельно.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>РФ, есть отдельное направление для нерезидентов</t>
+          <t>"Praxis works with licensed, reputable businesses operating in approved jurisdictions and industries, including: iGaming, Trading / Forex, E-commerce". Клиенты в ограниченных и санкционных юрисдикциях, "including the United States", не допускаются. Публичный список принимаемых лицензий: Forex — FCA (UK), CySEC (Кипр), BaFin, Consob, FMA, ASIC, FSCA, IOMFSA, CBCG (Черногория), FSA (Сейшелы), BVFSC, CIMA, FINTRAC, VFSC, Labuan FSA; Gaming — MGA (Мальта), GGC (Гибралтар), CGC (Кюрасао), UK GC, Cyprus National Betting Authority. Россия и СНГ в публичном списке не упомянуты; требование "legally registered and verifiable business" плюс лицензия означает, что для российского ИП/самозанятого путь закрыт (прямого запрета нет — не подтверждено, но следует из требований).</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Карты, электронные деньги, мобильные платежи, терминалы, банковские переводы, СБП</t>
+          <t>Своих методов приёма нет: Praxis — оркестратор, который подключает PSP и финансовых провайдеров мерчанта (по сторонним обзорам — сотни коннекторов). Реальные методы оплаты определяются выбранными PSP.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2-5% с каждой успешной транзакции в зависимости от вида платежа; ежемесячных и скрытых платежей нет</t>
+          <t>по запросу (не публикуется). Страницы тарифов нет (praxis.tech/pricing отдаёт 404). Единственная публичная цифра — не подтверждённое компанией утверждение клиента в отзыве Trustpilot от 16.06.2024: "We trusted Praxis Tech, believing they had four PSPs ready for us after paying $2200". Это отзыв, а не тариф.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0: подключение бесплатное</t>
+          <t>по запросу (не публикуется); в отзывах Trustpilot фигурирует разовая сумма $2200 за подключение PSP — не подтверждено компанией</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не применимо: Praxis не процессит и не держит средства клиентов ("we do not process or settle transactions, nor do we handle client funds") — резервы и hold формируются вашими PSP/эквайерами, а не Praxis.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено: сроки, минимальная сумма и куда перечисляют, не найдены</t>
+          <t>Не применимо: Praxis не проводит расчёты и не выплачивает средства; расчёты идут напрямую от подключённых PSP/эквайеров. У Praxis есть отдельный модуль Withdrawal Management для управления выплатами через подключённых провайдеров.</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Есть публичный вход для физлиц (кнопка У меня нет юр. лица) и отдельный для юрлиц и ИП; нужен готовый ресурс с товарами, ценами и офертой; заявленный срок подключения 2 дня</t>
+          <t>Только зарегистрированный и проверяемый бизнес: "Operate a legally registered and verifiable business", "Hold valid and relevant licenses or regulatory registrations (when applicable)", "Have a transparent corporate structure with identifiable beneficial owners". Физлицо и самозанятый не подходят. KYB-проверка обязательна, обработка данных по GDPR, есть DPO. Для работы нужна точка входа для checkout (hosted page/iframe). Требование VAT/GST-номера не упоминается — не подтверждено.</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Да, есть страница рекуррентных платежей и автоплатежей</t>
+          <t>Да. В документации есть раздел MIT &amp; Subscriptions и страница "Zero Amount Authorization": "Allows the merchant to securely store card details for future or recurring payments (Subsequent Merchant-Initiated Transactions)". Есть также отдельный Subscription API (create subscription plan). Автоматические ретраи и decline recovery работают только в режиме Hosted Cashier ("Automated cascade &amp; retries"); при прямой интеграции retry — на стороне мерчанта.</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>API, платёжный виджет, модули CMS, Payment notification POST-вебхук с MD5-подписью, защита от дублей, тестовый режим, подключение к Telegram; сложность 2 из 5</t>
+          <t>Hosted Payment Page (Cashier) с redirect или iframe, Hosted Payment Fields (JS SDK, PCI-нагрузка на Praxis), Server-to-Server REST API (требует PCI Level 1 у мерчанта), Google Pay и Apple Pay, sandbox и тестирование, документация docs.praxis.tech, есть даже MCP-сервер; webhooks и return URLs/dynamic redirects. Для Telegram-бота без сайта неудобно: hosted cashier предполагает веб-страницу и redirect; прямой поддержки «витрины-бота» в документации нет — не подтверждено. Сложность интеграции: 4 — сама интеграция (hosted cashier) простая, но Praxis не даёт эквайринг: нужно самостоятельно получить PSP/эквайеров, готовых работать с VPN, а Praxis онбордит преимущественно лицензированные iGaming/Forex/E-commerce компании. Для маленького VPN без лицензии и без сайта — высокий риск отказа..</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Отказ комплаенса по непубличному списку запрещённых товаров; неизвестные условия холда и выплат; риск отказа по тематике VPN</t>
+          <t>1) Главный риск — мисматч ожиданий: Praxis не эквайер и не держит средства, поэтому задачу приёма карт для VPN он сам не решает. 2) Допустимые отрасли ограничены iGaming/Forex/E-commerce плюс требование лицензий. 3) США и санкционные юрисдикции исключены. 4) Нет публичных тарифов — экономику нельзя оценить. 5) Репутационные риски: Trustpilot 3.4/5 в en-US, но 2.7–2.8/5 в других локалях; есть жалобы о $2200 без запуска и обвинения в обслуживании нелицензированных казино. ПРАКТИКА: Не подтверждено. Публично Praxis ориентируется на midsize business; в отзывах есть положительные кейсы трёхлетнего сотрудничества и жалобы на уплату $2200 без результата и на недоступность менеджера. Онбординг мелкого бизнеса без истории процессинга публично не подтверждён; ключевое — Praxis сам не выдаёт MID.</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>https://info.paymaster.ru/blog/process-podklyucheniya-k-paymaster/, https://info.paymaster.ru/blog/rekurrentnye-platezhi/, https://info.paymaster.ru/oplata-v-telegram/</t>
+          <t>https://praxis.tech/client-acceptance-policy, https://docs.praxis.tech/docs/get-started, https://docs.praxis.tech/docs/zero-amount-authorization, https://doc.praxiscashier.com/integration_docs/latest/subscription_api/create_subscription_plan, https://www.trustpilot.com/review/praxis.tech, https://ca.trustpilot.com/review/praxis.tech, https://praxis.tech/pricing, https://praxis.tech/industries</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -5513,77 +5513,77 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>ikajo</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>RollyPay</t>
+          <t>Ikajo International (Ikajo International BV, Амстердам; Ikajo Asia, Гонконг; Ikajo Brazil, Сан-Паулу; MYPAY, Рига)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Серая зона: в оферте и на сайте VPN, прокси и анонимайзеры не упомянуты, тематика решается менеджером после проверки проекта</t>
+          <t>High-risk эквайринг/PSP — merchant account provider (MSP) через сеть банков-эквайеров; НЕ MoR</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>да. VPN — отдельная открыто поддерживаемая вертикаль: у Ikajo есть выделенная страница "VPN Merchant Account", где VPN разбирается как high-risk бизнес (высокий уровень chargeback и fraud), перечисляются потребности VPN-мерчантов (recurring billing, fraud/chargeback prevention, PCI DSS, много методов оплаты) и предлагается онбординг.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>РФ и другие страны; выплаты на карты РФ или в USDT</t>
+          <t>Заявлено 130+ стран, 14 000+ проектов, 16+ лет работы. Офисы: Ikajo International BV (Kingsfordweg 151, 1043 GR Амстердам, Нидерланды), Ikajo Asia (Tung Ning Building, Гонконг), Ikajo Brazil (Сан-Паулу), MYPAY Latvia (Рига, LV-1024). Эквайринговая сеть (по данным сайта и стороннего обзора): 10 банков EU, 15 банков CIS, 5 китайских банков, 30 прочих — присутствие в СНГ заявлено. Валюты процессинга включают RUB и UAH, но валюты расчётов (settlement) только USD и EUR. Прямого заявления «принимаем/не принимаем резидентов РФ» нет — не подтверждено; с учётом CIS-банков и поддержки RUB это одна из немногих реалистичных опций для СНГ, но требует подтверждения у менеджера.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>СБП QR, карты Visa, Mastercard, Мир, крипта USDT, BTC, ETH, TON, CryptoBot, xRocket, ЕРИП</t>
+          <t>100+ методов и 100+ валют: Visa, Mastercard, American Express, JCB, UnionPay, SEPA, Klarna, Przelewy24, iDEAL, POLi, Sofort, Trustly, Multibanco, Teleingreso, GiroPay, EPS, Paysafecard, QIWI, FasterPay, Alibaba и другие. Выплаты только на корпоративные счета юрлиц, но возможны выплаты и на карты: "Yes, our clients can receive payouts to their cards."</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Крипта от 1%; по данным представителя сервиса СБП QR от 5% и карты РФ от 5% - это заявление в неофициальном канале, а не текст оферты</t>
+          <t>Частично опубликовано: на странице Solutions указаны стартовые ставки по отраслям — "Online dating. Rates starting at 2,5%", "Gambling. Rates starting at 3%", "CBD. Rates starting at 2%", "Advertising. Rates starting at 2%". Для VPN ставка не публикуется — по запросу (не публикуется). Chargeback-фи и месячный минимум не публикуются, страницы тарифов нет (ikajo.com/pricing отдаёт 404). Сторонний обзор Merchant Machine (обновлён 08.01.2026) подтверждает: "Ikajo International doesn't have prices listed on its website."</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено: оферта в машиночитаемом виде не получена</t>
+          <t>по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено; заявлены автоматические выводы</t>
+          <t>по запросу (не публикуется). Rolling reserve используется как стандартный инструмент (есть отдельная статья в глоссарии ikajo.com/glossary/rolling-reserve), но конкретные проценты и сроки не публикуются.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>На карты российских банков или в USDT; лимиты и комиссии согласуются при подключении; минимум и сроки не подтверждены</t>
+          <t>Опубликовано в FAQ: "How often do you release payouts? The frequency depends on the type of business, merchant's turnover, company's registration country, and the acquiring bank." То есть сроки индивидуальны и не публикуются. Выплаты только на корпоративные счета юрлиц ("We sign contracts with legal persons only"), плюс возможны выплаты на карты. Валюты расчётов: USD, EUR.</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Подключение доступно физлицам, самозанятым, ИП и компаниям после проверки проекта; публичной оферты с перечнем запретов нет</t>
+          <t>Только юрлицо: "Do you offer payouts to a personal account? No, we don't. We sign contracts with legal persons only." ИП и самозанятый не подойдут. Требования к сайту опубликованы отдельно на странице Compliance: подробное и ясное описание товаров/услуг, все ссылки рабочие, страницы Terms &amp; Conditions и Privacy Policy, Cancellation Policy — обязательна при продаже цифровых товаров или по подписке, Shipping and Return&amp;Refund Policy — для физических товаров, Deposit/withdrawal, AML и KYC Policy — для gambling/forex/crypto, Risk disclaimer — для gambling/forex/crypto/adult; Contact page минимум с двумя способами связи, один из которых телефон; форма регистрации/покупки с чекбоксом T&amp;C и Privacy Policy. Сроки онбординга: "Depending on the setup type, you can have your account opened with us within one day. However, some businesses need to wait for up to 31 days", в маркетинге — до 2 рабочих дней. Требование VAT/GST-номера не упоминается — не подтверждено.</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Да, рекуррентные платежи заявлены</t>
+          <t>Да, подтверждено: "Recurring billing — Ikajo International has solutions for subscription-based businesses. From now on, enjoy free recurring billing to fit all of your business needs thanks to: multiple retry options; hassle-free transaction flow." (ikajo.com/solutions). На VPN-странице также указано "Free recurring billing". Ретраи дают базовую dunning-логику. Отдельных публичных данных о free trials и о схеме токенизации/MIT нет — не подтверждено.</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>REST API, вебхуки, SDK на Node.js, PHP, Python, готовые модули и платёжные ссылки, тестовый режим; сложность 2 из 5</t>
+          <t>API (REST/SOAP) с захватом карточных данных на странице мерчанта, Hosted Payment Page (HPP), Virtual Terminal для MO/TO, плагины и CMS: WooCommerce, WHMCS, Magento, OpenCart, PrestaShop, CS-Cart, Drupal/UberCart, Ecwid, osCommerce, VirtueMart, X-Cart, ZenCart и другие. Есть antifraud (Standard — ограничения по картам/email/IP, Premium — MaxMind и Sift Science), smart routing и выбор 3DS/non-3DS. Магазин-бот в Telegram без сайта не пройдёт: страница Compliance прямо требует "adjust your website" до онлайн-заявки, а форма заявки запрашивает Website URL. Сложность интеграции: 3 — типовой API/HPP плюс готовые плагины, VPN открыто приветствуется, но обязательны юрлицо-контрагент, полноценный сайт с политиками и телефоном и банковский андеррайтинг (до 31 дня)..</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Комиссия 5% по СБП и картам вдвое дороже обычного эквайринга; оферта и запреты недоступны для проверки; схема без ИП и юрлица создаёт налоговые и банковские риски для коммерческой выручки; серая зона закрывается первой при смене политики</t>
+          <t>1) Нет публичных тарифов по VPN, резерва и сроков выплат — торговая позиция непрозрачна. 2) Контракт только с юрлицом: российский самозанятый или ИП как контрагент не подходит, нужна компания в KZ/AM/GE/KG/UAE. 3) Зависимость от 60+ банков-партнёров: MID может быть закрыт конкретным банком, отсюда риск внезапного отключения. 4) Ikajo — MSP, а не банк: реальный эквайер — один из партнёрских банков, и его требования к VPN могут отличаться. 5) Мало отзывов (Trustpilot ~4.2/5, около 28 отзывов) — статистически слабая выборка. ПРАКТИКА: Публично Ikajo заявляет готовность работать с новичками: "Whether you are a new and want to obtain your first merchant account or a business guru looking for more affordable solutions, we are here to help" (ikajo.com/industries), а также "Fast approvals and easy onboarding". Есть отдельная VPN-вертикаль и встроенный antifraud, то есть компания системно работает с высоким риском. Независимых жалоб на заморозку средств именно у Ikajo в ходе проверки найти не удалось; онбординг без истории процессинга — не подтверждено.</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>https://rollypay.io/, https://overtonfx.ru/threads/rollypay-io-servis-priyem-platezhei-cherez-sbp-karty-i-kriptovalyutu-bez-yurlitsa.14127/, https://docs.rollypay.io</t>
+          <t>https://ikajo.com/industries/vpn-merchant-account, https://ikajo.com/industries, https://ikajo.com/solutions, https://ikajo.com/faq, https://ikajo.com/compliance, https://ikajo.com/about-us, https://ikajo.com/terms-conditions, https://ikajo.com/pricing, https://merchantmachine.co.uk/high-risk/ikajo-international/, https://uk.trustpilot.com/review/ikajo.com</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
@@ -5595,323 +5595,323 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>zotapay</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Tranzzo</t>
+          <t>Zota (ранее Zotapay)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Запрещено: п. 11 запрещает объекты для снятия защиты авторских прав или региональных ограничений, п. 14 запрещает деятельность с репутационными рисками для провайдера и платёжных систем</t>
+          <t>High-risk эквайринг/PSP (маркетплейс платёжных методов + шлюз MetaGate; не прямой эквайер, работает «alongside acquiring banks» и через сеть провайдеров)</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>серая зона (склоняется к «нет»): Zota публикует два явных списка вертикалей: разрешённые (Digital Goods: Software (SAAS), Online subscriptions, File sharing &amp; online backup services, Internet hosting &amp; domain registry, Telecom VoIP и др.) и запрещённые (Digital Goods: Hacking materials, Malware and vulnerabilities, CyberLock services, File sharing services, Technical support, PC repair и др.). VPN/прокси/анонимайзеры/«circumvention» не упомянуты НИ В ОДНОМ из списков, поэтому vpn_quote = «не подтверждено». В Terms of Use запрет сформулирован только общо («Illegal Actions», «Restricted Territories» — юрисдикции, блокируемые Zota по своему усмотрению), отраслевого запрета VPN там нет. Практический вывод: VPN-вертикаль не заявлена как поддерживаемая, решение по ней принимает риск-команда в ручном режиме.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Международно; TRANZZO LTD (UK), суды в Великобритании</t>
+          <t>Формально работает в 150+ странах и 8 регионах (SEA, South Asia, East Asia, China, Africa, MENA, LATAM, CIS, Europe, Turkey — регионы перечислены в форме онбординга). В CIS у Zota подключены только методы приёма для Казахстана/Kyrgyzstan/Uzbekistan (Kaspi, Halyk, Jusan, Freedom, Forte, BCC, MBANK, Uzcard, Humo, P2P/QR) — это покрытие платёжных методов для покупателей, а НЕ признание РФ юрисдикцией мерчанта. Приём российского юрлица/резидента РФ явно не подтверждён: «Restricted Territories» — jurisdictions blocked by Zota at its sole discretion; требуется tax identification number и URL бизнеса. Юрлица Zota: Zota Technology Ltd (UK) и Zota Technologies Systems Pte. Ltd. (Сингапур, лицензия MAS Major Payment Institution), головной офис основан в Тель-Авиве (2015). Российская юрисдикция мерчанта: не подтверждено, высокая вероятность отказа.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Карты, СБП, QR, платёжные ссылки, подписки, холдирование</t>
+          <t>1 000+ локальных и альтернативных методов: карты (Visa/Mastercard/локальные схемы), eWallets, QR-платежи, mobile money, cash payments, instant bank wire, P2P/P2C, ATM online/offline, криптовалютные кошельки, локальные банковские переводы. Отдельного SBP для РФ в публичном покрытии не найдено.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено: публичного тарифа нет</t>
+          <t>по запросу (не публикуется). На странице тарифов прямо: «Zota doesn't have one fixed price. Our team of payment experts provides you with a fully customized and transparent pricing plan». Ставки зависят от отрасли, региона, уровня риска, срока существования бизнеса и целевых рынков. Никаких публичных % и per-transaction fee нет; интернет-обзор (YesPress) подтверждает: «It earns transaction and gateway fees, with rates shaped by geography, currency, method, volume and risk».</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>по запросу (не публикуется). Публично упомянута только программа «Startup club» — поддержка бизнесов «from day one» и помощь с заявкой в топовые банки после 3 месяцев надёжного процессинга; конкретных сумм нет.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Холд и роллинг-резерв на усмотрение сервиса; при расторжении после превышения лимита чарджбеков средства удерживаются 540 дней</t>
+          <t>по запросу (не публикуется). Rolling reserve/deposit в публичных документах Zota не раскрыт; в Terms of Use только указано, что Zota вправе устанавливать «minimum thresholds to be maintained on an Account and other restrictions».</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Ограничение вывода возможно в зависимости от местоположения, проданных товаров, запроса полиции и жалоб; чарджбеки ограничены 1% транзакций за месяц</t>
+          <t>по запросу (не публикуется). Есть отдельный продукт Payouts и «settlement currencies» (ежедневные/недельные/месячные расчёты в выбранной валюте), но конкретные сроки выплат публично не указаны.</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Только 18+, обязателен KYC; приём только с согласованного ресурса, иначе расторжение; требования к статусу не подтверждены</t>
+          <t>Только бизнесы, включая sole proprietors (ИП-аналоги) — но НЕ физлица: «only businesses (including sole proprietors) ... are eligible to open an Account». На онбординге обязательны business/trade name, физический адрес, email, телефон, tax identification number, URL сайта, характер деятельности; сбор personal information о beneficial owners и принципалах (KYC/KYB). Обязательны Merchant Services Agreement, price proposal и compliance review, затем underwriting. Жёсткое ограничение: «Our Services are not available to persons under the age of 18» — сам 15-летний основатель оформить аккаунт не сможет, только родитель. Отдельного требования VAT/GST-номера в публичных материалах не найдено — есть требование tax identification number. Telegram-бот без сайта: требование URL бизнеса делает чистый бот-сторфронт проблемным, нужен хотя бы лендинг.</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Да, отдельный продукт платежей по подписке</t>
+          <t>Прямого публичного описания подписок/dunning у Zota не найдено (проверено: страницы pricing, payment-methods, developers portal, terms of use). Есть карточные платежи и токенизация через PCI-hosted cashier, S2S, HTTP API, SDK, то есть технический фундамент для рекуррентов есть, но MIT/free trials/dunning в публичных материалах не заявлены как функция — уточнять у провайдера.</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>API (guide.tranzzo.com), CMS-модули, мобильное SDK, платёжные ссылки, QR; сложность 4 из 5</t>
+          <t>MetaGate gateway: hosted PCI cashier page (определяет страну покупателя, показывает локальные методы/валюту/язык, кастомизируется под бренд), server-to-server (только для PCI-валидированных мерчантов), HTTP REST API + Swagger, SDK для PHP, Python, Node.js, Go, C#, плагины WooCommerce и PrestaShop, публичный GitHub (github.com/zota) и портал developers.zota.com. Есть API access request. Telegram-бот без сайта: официально не описан; hosted cashier можно открыть из бота, но требование URL бизнеса при онбординге сохраняется. Сложность интеграции: 2 — публичные SDK на 5 языках, Swagger и готовые плагины; основной барьер не технический, а комплаенс/underwriting, а не разработка..</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Штраф до 50000 USD за запрещённую деятельность; удержание средств до 540 дней; холд и роллинг-резерв по усмотрению сервиса; VPN прямо попадает под п. 11 и п. 14</t>
+          <t>1) Отраслевой политики по VPN нет — риск отказа или закрытия после онбординга; 2) онбординг многоступенчатый (expert review -&gt; форма -&gt; price proposal &amp; compliance review -&gt; underwriting), сроки не публикуются; 3) «Restricted Territories» определяются единолично Zota, то есть аккаунт может быть закрыт без объяснения причин; 4) ключевой риск путаницы: существует НЕЗАВИСИМОЕ Android-приложение «Zota VPN» (com.zota.vpn.piepre.tech), не связанное с платёжной Zota — при переписке с провайдером это нужно явно разграничивать, чтобы вас не заподозрили в попытке мимикрии под собственный бренд провайдера; 5) нет публичных данных о работе с российскими мерчантами; 6) штрафов/регуляторных санкций против Zota не найдено (в отличие от Nexpay). ПРАКТИКА: Ведёт ли Zota малый бизнес без истории процессинга: да, есть явная программа «Startup club» («We support businesses from day one», «Our unique merchant accounts allow you to start generating a processing portfolio, or future processing history», «After three months of reliable processing, we can help businesses apply to top-tier banks»). Это редкость и прямо релевантно проекту без истории. Жалоб на замороженные средства в проверенных источниках не найдено. Масштаб: company-reported $3B+ транзакций за 2025, 1 000+ методов, 150 стран, ~191-210 сотрудников.</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>https://www.tranzzo.com/ru/prohibited-categories, https://www.tranzzo.com/ru/terms-and-conditions</t>
+          <t>https://zota.com/pricing/, https://zota.com/industries/, https://zota.com/terms-of-use/, https://zota.com/get-started/, https://zota.com/region/cis/, https://developers.zota.com/, https://developers.zota.com/introduction-to-payments/, https://zota.com/payment-methods/, https://yespress.io/zota, https://www.citiumtech.com/resources/psd2-register/institutions/lt-lt-bl-304708124-lt</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>corepay</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Ecommpay</t>
+          <t>Corepay</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
+          <t>High-risk эквайринг/PSP (позиционирует себя как full-service processor и «direct acquirer», но фактически является registered ISO/MSP — то есть посредником/брокером, а не банком-эквайером)</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Не подтверждено: страница Business Risk Appetite не читается роботом (пустой ответ)</t>
+          <t>не подтверждено (вероятно «нет» для РФ-сценария) — на всём сайте corepay.net (проверены: pricing, merchant-accounts, subscription-management, payment-processing, about, apply, partner-with-us, digital goods, integrations/payment-methods, terms-conditions, contact) слова VPN, «virtual private network», proxy, anonymizer нет ни в списке поддерживаемых, ни в списке запрещённых вертикалей. Заявленные специализации: healthcare, telehealth, online pharmacy, medspa, CBD/hemp, nutraceuticals, iGaming, travel, subscription/recurring, fantasy sports, adult entertainment, dating, digital goods &amp; services. VPN-вертикаль не заявлена.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Юрлица: US Office — 1133 Louisiana Avenue, Suite 212, Winter Park, FL 32789, США; UK Office — 53 Davies Street, London W1K 5JH. Заявлены «direct acquiring in the US, EU, UK, and Australia» и «banking relationships spanning the US, UK, and EU», процессинг в 30+ странах, принятие в 180+ странах и 135+ валютах через эквайеров. Российский резидент/российское юрлицо: прямо НЕ поддержано. В форме заявки на партнёрство в списке стран есть Russia, но в поле «Country of Incorporation» на странице /apply/ Россия и Беларусь отсутствуют (есть Казахстан, Кыргызстан, Армения, Грузия, Узбекистан, Азербайджан, Украина). То есть компания из КЗ/АРМ/ГЕО/КГЗ формально может подать заявку, а из РФ — нет.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Карты Visa/Mastercard/Amex/Discover, Apple Pay, Google Pay, PayPal, Venmo, Cash App, ACH, SEPA Direct, Bancontact, Blik, iDEAL, EPS, Swish, Wero, PIX, SPEI, OXXO, PSE, M-PESA, bKash, gCash, QRIS, FPX, UPI, WeChat Pay, China UnionPay, JCB, Crypto. Для РФ-специфичных методов (СБП/карты МИР) публичных подтверждений нет.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Частично публично. Публичная опорная точка для low-risk: $99/месяц + $0,05 за транзакцию + interchange (со страницы /pricing/: «no setup fees, no monthly minimums»). Для high-risk заявлено «as low as 2.95% blended» (по независимому обзору GuidingDecisions, март 2026). Точные ставки — только по индивидуальному quote: «Your business deserves tailored pricing based on your volume, industry, and processing needs». Chargeback fee, gateway fee, PCI-программа и annual high-risk registration fee публично НЕ раскрыты — по запросу.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Публично заявлено отсутствие: «no setup fees», «No application fee, ever», «No hidden fees or monthly minimums». Отдельно упоминается annual high-risk registration fee, требуемый карточными сетями, — Corepay на него ссылается, но НЕ публикует сумму.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Прямо на сайте Corepay процент резерва НЕ публикуется (есть только интерактивный Reserve Estimator без открытых цифр). Независимый обзор GuidingDecisions (март 2026) со ссылкой на «Corepay's own published guidance» указывает: типичный резерв 5–15% от ежедневно заселлённых транзакций, удерживаемый 90–180 дней до возврата. Это сторонний источник, поэтому трактовать как ориентир, а не как официальные условия; Corepay заявляет, что готов «work with acquiring banks to negotiate lower reserves as your chargeback ratios improve».</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>по запросу (не публикуется). Публично заявлены «faster settlement», «next-day funding» для domestic US и multi-currency settlement, но конкретные сроки выплат (T+? для high-risk) не раскрыты.</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Нужно юрлицо. Подача заявки требует First/Last Name, Email, Business Name, Industry и Country of Incorporation. Для физлица/самозанятого публичных подтверждений нет — модель ISO/MSP по умолчанию предполагает бизнес-сущность и банковский счёт. KYC/KYB глубокий: in-house underwriting, проверка бизнес-модели, processing history и compliance posture, упоминается LegitScript enterprise partnership для регулируемых категорий, запрашиваются business license, bank statements, processing history. VAT/GST-номер как обязательное требование публично не заявлен. Требования к сайту публично не формализованы, но андеррайтинг построен вокруг e-commerce-мерчанта; Telegram-бот без сайта прямо не поддержан.</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Сильная сторона: automated billing cycles (от daily до annual), smart retry logic по типу decline, dunning management, Card Account Updater, trials/proration/upgrades/usage-based billing, Customer Vault (токенизация), Network Tokens. Отдельно указана поддержка recurring для specialty-категорий. Токены живут в собственном шлюзе NetValve — по независимой оценке переносимость токенов при уходе к другому провайдеру под вопросом.</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Собственный шлюз NetValve: smart BIN routing, tokenization, payment orchestration, REST API, hosted checkout, antifraud, chargeback representment через sister-brand CB-ALERT/Dispu, 3-D Secure 2.1, Level II/III data. Готовые интеграции: Shopify, WooCommerce, Magento, BigCommerce, Wix, Salesforce, NetSuite, Microsoft 365. Публичная техническая документация по API на сайте слабо представлена (нет открытого developer-портала уровня RocketGate/Zota). Telegram-бот без сайта: не заявлен как поддерживаемый сценарий. Сложность интеграции: 2 — REST API и готовые плагины для основных e-commerce платформ упрощают разработку, но высокий комплаенс-барьер и отсутствие открытой dev-документации сдвигают сложность на онбординг..</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Нет проверяемых данных: ни VPN-политика, ни комиссия, ни требования к подключающему</t>
+          <t>1) Формально это ISO/MSP («Corepay is a registered ISO/MSP of North American Banking Company, Roseville, MN»), при этом маркетинг утверждает «As a direct acquirer, we control more of that chain than most processors» — то есть заявление о прямом эквайринге не соответствует регистрационному статусу, и это надо проверять в договоре; 2) VPN-вертикаль не заявлена, отраслевого разрешения нет; 3) РФ-юрлицо не поддержано, в форме происхождения РФ отсутствует; 4) rolling reserve 5–15% на 90–180 дней (по стороннему источнику) — при обороте 40 000 $/мес и 10% на 180 дней блокируется порядка 24 000 $; 5) отсутствие публичных rate card и публичной практики по малым мерчантам: «Corepay's public footprint is thin relative to the role it plays in your business. Independent merchant feedback is limited»; 6) токены не переносимы, что критично для подписочной модели; 7) специализация на telehealth/medspa/фарме может означать, что цифровые подписки вне медицины получат другой риск-профиль. ПРАКТИКА: Малый бизнес без истории процессинга: публично декларируется приём мерчантов, которых отклонили другие, «streamlined approvals», решения «within one to three business days» и «24 to 72 hours», отдельно указано, что компания «underwrites and manages risk itself rather than relying on a bank's automated system». Независимый обзор, однако, отмечает крайне тонкий публичный след и ограниченную обратную связь от реальных мерчантов. На странице отзывов — только верифицированные через Google отзывы (4,8 рейтинг по Google Maps), попытка загрузить Trustpilot (au.trustpilot.com/review/corepay.net) вернула 403 (анти-бот), то есть независимую проверку жалоб на заморозку средств через Trustpilot провести не удалось. Публичных сообщений о замороженных средствах в проверенных источниках не найдено — но это отсутствие данных, а не подтверждение безопасности.</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>https://ecommpay.com/compliance/business-risk-appetite/</t>
+          <t>https://corepay.net/solutions/high-risk-merchant-accounts/, https://corepay.net/pricing/, https://corepay.net/about/, https://corepay.net/contact/, https://corepay.net/apply/, https://corepay.net/terms-conditions/, https://corepay.net/solutions/subscription-management/, https://corepay.net/solutions/payment-processing/, https://corepay.net/industries/best-digital-goods-services-merchant-accounts/, https://corepay.net/integrations/payment-methods/, https://www.guidingdecisions.com/corepay-review-custom-e-commerce-credit-card-processing-for-high-risk-merchants</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>rocketgate</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Telegram Gifts и перепродажа звёзд</t>
+          <t>RocketGate</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Telegram-нативный серый</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Нарушение правил Telegram и экономически невозможно легально: покупка 1000 Stars стоит 1,41 USD, вывод даёт 1,30 USD</t>
+          <t>High-risk эквайринг/PSP (фактически ШЛЮЗ + оркестрация поверх 200+ эквайеров; НЕ эквайер и не MoR)</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>не подтверждено — на rocketgate.com (проверены: главная, /solutions, /resources, privacy-policy, help-центр, developer docs) есть только макро-формулировки: «High-risk &amp; complex businesses — Specialized routing and expertise for complex verticals other platforms turn away», «High-Risk» в навигации. Слов VPN, virtual private network, proxy, anonymizer, circumvention ни в одном публичном документе RocketGate не найдено. По отраслевой репутации RocketGate исторически работает с adult-вертикалью и подписочными high-risk моделями, поэтому VPN как «circumvention/anonymity tool» — зона ручного решения риск-команды.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Глобально</t>
+          <t>Юрлицо: RocketGate PR, LLC — 425 Carr. 693, PMB 260, Dorado, PR 00646, Пуэрто-Рико (по Privacy Policy, обновлена 12 июня 2025). Заявлено покрытие 190+ стран с локальным эквайрингом в Северной Америке, Европе и Latam через сеть 200+ эквайеров, плюс «Plus local cards and bank transfers on request». Российский резидент/РФ-юрлицо: явно не подтверждён. Мерчант должен иметь собственный merchant account у эквайера-партнёра RocketGate, а не у самой RocketGate.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Подарки за Stars, конвертация подарка обратно в Stars</t>
+          <t>Visa, Mastercard, American Express, Discover, JCB, Carte Bancaire, Apple Pay, Google Pay, PIX, плюс локальные карты и банковские переводы «on request». eChecks и mCommerce упоминаются в сторонних обзорах.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Скидка посредника 20-40% от официальной цены означает краденые или возвратные звёзды</t>
+          <t>по запросу (не публикуется). Публичного прайс-листа нет: сайт ведёт только через «Contact us» / «Talk to our payments engineering team»; в футере нет страницы Pricing. Сторонний обзор Centurion (июль 2026) прямо указывает, что выбор между шлюзами — «a stack decision, not a rate decision: gateway fees are a rounding error next to the authorization-rate, retention, and dispute-ratio differences». Конкретных %, per-transaction fee, chargeback fee и monthly minimum в публичных источниках нет.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Не применимо</t>
+          <t>по запросу (не публикуется).</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Не применимо</t>
+          <t>по запросу (не публикуется). Reserve устанавливает не RocketGate, а эквайер-партнёр под конкретный MID; в публичных материалах RocketGate условий резерва нет. В стороннем обзоре есть только общее предупреждение рынка: «confirm portability terms in writing with either before boarding, because vault portability is your future leverage».</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Не применимо</t>
+          <t>по запросу (не публикуется). Settlement происходит на стороне эквайера-партнёра; публичных сроков выплат RocketGate не раскрывает.</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Не применимо</t>
+          <t>Нужен собственный merchant account (MID) у одного из 200+ эквайеров-партнёров; RocketGate сам мерчантов не андеррайтит и не борется за них. Практически это означает, что предприниматель должен сначала пройти онбординг у эквайера (обычно high-risk банк/PSP), а RocketGate подключается как шлюз поверх. Физлицо/самозанятый: не подтверждено, но модель (merchant account + MID) подразумевает юрлицо. Публичной формы онлайн-заявки на сайте нет — только контактная форма. Требований к сайту/VAT публично не заявлено.</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Не применимо</t>
+          <t>Сильно: «SaaS &amp; Subscription — Protect MRR with subscription-aware retries, smart dunning, and account updater», cross-sells, lifecycle-aware recovery, subscription telemetry. Сторонние обзоры подтверждают гибкие рекурренты: free trials, paid trials, step-down billing, произвольные циклы (daily/weekly/monthly), управление апгрейдами и отменами через API и веб-админку. Есть PCI-compliant tokenization и network tokenization, Account Updater, снижение involuntary churn.</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Схема с посредником; технически возможно, но недопустимо</t>
+          <t>Несколько моделей: RocketGate-hosted payment page, hosted form (данные собираются на сайте мерчанта и передаются в RocketGate), iFrame/redirect и полная API-интеграция с примерами кода на нескольких языках. Возможности: multi-MID cascading (повтор decline-ов на разных эквайерах), velocity/BIN-правила, device fingerprinting, scoring, scrubbing, negative database, RDR/Ethoca/CDRN, 3-D Secure 2. Поддержка Apple Pay через Gateway API документирована в help-центре. Telegram-бот без сайта: официально не заявлен; hosted page технически можно открыть из бота. Сложность интеграции: 4 — API есть и документация для мерчантов доступна, но онбординг двухступенчатый (сначала эквайер + MID, потом шлюз), публичной документации и заявки в открытом доступе почти нет, а продукт позиционируется под команды с in-house engineering и объёмами от ~$100k/мес..</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Отзыв звёзд по флагу refund; понижение рейтинга аккаунта Telegram при рефандах и конвертации подарков; convert_stars всегда меньше цены покупки; конвертация подарка возможна только 7 дней (604800 секунд); риск мошенничества у посредника</t>
+          <t>1) RocketGate НЕ эквайер: она не выдаёт merchant account и не решает вопрос VPN-политики — это решает эквайер, поэтому вся риск-работа по VPN ложится на вас и на посредника; 2) продукт ориентирован на масштаб: сторонний обзор прямо говорит, что routing depth RocketGate оправдан для бизнеса с «six figures of monthly volume», а при «Single MID, under ~$100k/month» рекомендуют другой вариант; 3) публичной цены, reserve и сроков выплат нет; 4) историческая специализация на adult-индустрии (обзоры называют RocketGate одним из «two long-standing specialists» для adult internet) означает, что банк-партнёр может быть чувствителен к VPN-трафику как к circumvention-инструменту; 5) токены в vault не переносимы — критично для подписок; 6) отсутствие онлайн-заявки и публичных требований затрудняет оценку шансов для малого бизнеса из СНГ. ПРАКТИКА: Малый бизнес без истории процессинга: публично НЕ подтверждено. RocketGate позиционируется как платформа производительности для команд, у которых уже есть мерчант-аккаунты и объёмы; отдельной программы для стартапов, аналогичной «Startup club» у Zota, не найдено. Жалоб на замороженные средства в проверенных источниках не найдено. Компания активно присутствует в индустрии: указана как exhibitor на отраслевой конференции i-Con (adult/payments), имеет help-центр на Freshdesk и публичный developer-раздел.</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>https://core.telegram.org/api/gifts, https://core.telegram.org/api/stars, https://core.telegram.org/api/config, https://tehnoobzor.com/tg-stars-com-moshennik/</t>
+          <t>https://www.rocketgate.com/, https://www.rocketgate.com/solutions, https://www.rocketgate.com/resources, https://www.rocketgate.com/resources/privacy-policy.php, https://help.rocketgate.com/support/home, https://help.rocketgate.com/support/solutions, https://help.checkoutchamp.com/crm/gateway-setup/gateway-integrations/rocketgate, https://centurionpaymentservices.com/blog/netbilling-vs-rocketgate, https://bilixe.com/listing/rocketgate-payment-gateway/</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>nexpay</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Digiseller (digiseller.market)</t>
+          <t>Nexpay (UAB "NexPay", Литва; сайт paynexpay.com)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Платформа цифровых товаров и витрин (движок для GGsel и др.)</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Серая зона: VPN в запретах не упомянут; запрещены товары, нарушающие законодательство, и абстрактные/неописанные товары (п.1.2.4)</t>
+          <t>High-risk эквайринг/PSP (на деле — EMI, то есть электронные деньги и платёжные счёта/SEPA/SWIFT, а НЕ эквайер и НЕ MoR; карточная авторизация PS_03C есть в лицензии, но публичный продукт — бизнес-счёт, а не merchant acquiring)</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>нет — Nexpay прямо запрещает такие активности. В официальном списке запрещённых отраслей указано «Circumvention devices» без дополнительных пояснений, и это размещено в списке, который начинается словами: «The companies who do business in these industries, or undertake any of these activities won't be able to open an account with Nexpay». Формулировка «circumvention devices» (устройства/средства обхода) — это тот же класс, к которому сети и банки относят VPN/прокси/анонимайзеры, и она отделена от «high-risk»-списка, куда попадают IT services и Marketing services (то есть даже обычный IT-сервис для них лишь high-risk, а обходные средства — прямой запрет). Публичного развёрнутого разъяснения, что именно входит в «Circumvention devices», Nexpay не даёт, поэтому VPN-интерпретация — это строгое чтение общего правила, но риск отказа очень высок.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Международный, расчёты в WM-титулах</t>
+          <t>Юрлицо: UAB "NexPay", Литва; лицензия EMI Банка Литвы (национальная ссылка LB000428, entity code LT_LT_BL_304708124), первая авторизация 10 октября 2017, последняя верификация реестра 22 июля 2026; паспортизация в 29 дополнительных стран EEA. Принимаемые юрисдикции юрлиц (публичный список): Европа — Андорра, Австрия, Бельгия, Болгария, Хорватия, Кипр, Чехия, Дания, Эстония, Финляндия, Франция, Грузия, Германия, Греция, Guernsey, Венгрия, Исландия, Ирландия, Isle of Man, Израиль, Италия, Jersey, Латвия, Лихтенштейн, Литва, Люксембург, Madeira, Мальта, Молдова, Монако, Черногория, Нидерланды, Северная Македония, Норвегия, Польша, Португалия, Румыния, Сан-Марино, Сербия, Словакия, Словения, Испания, Швеция, Швейцария, Украина, Великобритания, Ватикан; Азия — Австралия, Бутан, Китай, Гонконг, Индия, Япония, Казахстан, Макао, Малайзия, Непал, Новая Зеландия, Папуа-Новая Гвинея, Сингапур, Соломоновы о-ва, Южная Корея, Тайвань, Тимор-Лешти, Туркменистан, Тувалу; Америка — Бермуды, Бразилия, Канада, Чили, Кюрасао, Гренада, Гондурас, Перу, Sint Maarten, St. Lucia, St. Vincent, Суринам, Saint Pierre and Miquelon, Turks and Caicos, США, Уругвай; Африка — Мадагаскар, Нигер, Сан-Томе, ЮАР, Эсватини, Того, Замбия; Ближний Восток — Кувейт, Саудовская Аравия, Тунис. ВАЖНО: России, Беларуси, Армении, Кыргызстана, Узбекистана и ОАЭ в списке НЕТ; есть Казахстан и Грузия. Российский резидент/российское юрлицо — не принимается. Сам сайт добавляет: «we can only work with companies from certain countries» и «The fact that a country is mentioned on this list doesn't guarantee account opening».</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>WebMoney, банковские карты, СБП через внешних интеграторов (есть отдельная инструкция по подключению СБП)</t>
+          <t>По лицензии EMI: выпуск электронных денег (ES_010), кредитовые переводы (PS_03A), прямые дебеты (PS_03B), карточные платежи (PS_03C), денежные переводы (PS_05A), конвертация валют (PS_05B). Публичный продуктовый набор — бизнес-счёт: выделенные IBAN, SWIFT, SEPA и SEPA Instant, REST API с sandbox, массовые платежи, Multilogin, Multisig. Мерчант-эквайринг (приём карт от покупателей) как продукт на сайте НЕ представлен.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Комиссия DS 1,5-6% в зависимости от тематики, но не менее 0,02 WM; сверху комиссия платёжного метода и стоимость вывода</t>
+          <t>Публично раскрыты тарифные пакеты (это редкость и реальная ценность): Basic+ — €200–400/мес, Premium — €1 250–1 450/мес, Enterprise — custom. Разовые: document processing €500 во всех пакетах; account opening €1 000 (в Premium указано €1 000 со звёздочкой). Account balance fee — бесплатно. Входящие/исходящие SEPA и SEPA Instant: Basic+ — 0,15% + €1,5 за операцию, Premium — бесплатно (со сносками **), Enterprise — custom. Перевод между счетами Nexpay — бесплатно. Priority support: нет в Basic+, бесплатно в Premium и Enterprise. Процентов за эквайринг карт, chargeback fee и monthly minimum по оборотам в публичных тарифах НЕТ — по запросу.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>Публично: account opening fee €1 000 (во всех пакетах) плюс document processing €500. Это фактически плата за онбординг; отдельного «setup fee» сверх этого в тарифах не заявлено.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Вывод доступен не ранее чем через 72 часа после продажи (для Plati); для отдельных разделов задержка больше</t>
+          <t>по запросу (не публикуется). Rolling reserve/депозит в публичных тарифах Nexpay не раскрыт; продуктовый набор — платёжный счёт, а не merchant acquiring, поэтому классического chargeback-резерва в прайсе нет.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Вывод в WM-кошелёк/на карту; в РФ обслуживание через филиал DigiCore Solutions LTD (ИНН 9909773220)</t>
+          <t>по запросу (не публикуется). Публично заявлены SWIFT и SEPA/SEPA Instant переводы и «bulk payments», но сроки расчётов (settlement/payout terms) не раскрыты.</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>П.1.2.1: клиентом DS может стать только лицо, прошедшее идентификацию в системе WebMoney; регистрация как физлицо возможна</t>
+          <t>Только юрлица: «Legal entities incorporated in these jurisdictions are able to open an account with Nexpay» — физлицо/самозанятый не подходит. Обязательны строгий KYC/KYB и оценка по нескольким критериям, при этом «The fact that an industry isn't mentioned on this list, doesn't guarantee account opening. This is only one of the criteria which we need to assess when we are evaluating potential clients». Отраслевой фильтр очень широкий: запрещены, среди прочего, любые незалицензированные онлайн-гэмблинг/ставки, донаты/благотворительность, MLM, финансовые пирамиды, коллекторство, нелицензированный форекс/бинарные опционы; high-risk (возможно открытие) — крипто-активности, лицензированный гэмблинг, дайтинг, онлайн-игры, IT-услуги, маркетинг, юридические/бухгалтерские услуги, туризм, транспорт и др. VAT/GST-номер в публичных требованиях не заявлен; Telegram-бот без сайта не поддержан (продукт — счёт для digital-бизнеса, требуется юрлицо и комплаенс-профиль).</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Рекуррент не поддерживается платформой; продление — новый заказ</t>
+          <t>Подписки/dunning/free trials как продукт НЕ заявлены: Nexpay продаёт платёжный счёт (IBAN/SWIFT/SEPA), а не рекуррентный биллинг. REST API с sandbox есть, но токенизации карт и MIT-схем для подписок в публичном описании платформы нет.</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Есть API Digiseller для автоматической выдачи ключей и внешних витрин</t>
+          <t>REST API с sandbox, платформа с мобильным интерфейсом, Multilogin/Multisig, массовые платежи. Это API банковского типа (платежи, счета, переводы), а не checkout-шлюз: hosted payment page, плагинов для e-commerce и карточного checkout в публичном продукте нет. Для Telegram-бота с подписками это означает необходимость строить собственный биллинг поверх обычных SEPA-переводов, что для российской аудитории неприменимо. Сложность интеграции: 4 — API технически понятен (REST + sandbox), но это банковский API платёжного счёта, а не платёжный шлюз: нет hosted checkout, нет карточного acquiring-продукта, нет рекуррентов, и онбординг стоит €1 500 (€1 000 + €500) с полным KYB только для юрлиц из белого списка стран..</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Зависимость от WebMoney-инфраструктуры, риск блокировки при несоответствии описания, возвраты списываются со счёта продавца</t>
+          <t>1) ПРЯМОЙ ЗАПРЕТ: «Circumvention devices» в списке отраслей, с которыми Nexpay не работает, — VPN попадает в зону высокого риска отказа; 2) РФ и Беларусь не входят в список принимаемых юрисдикций, а Казахстан и Грузия — входят; 3) РЕГУЛЯТОРНЫЙ ИНЦИДЕНТ: Банк Литвы в конце декабря 2023 оштрафовал NexPay на €50 000 за нарушение правил предоставления отчётов об операционных и security-инцидентах; компания оспорила это в суде, затем заключила мировое соглашение, и штраф был снижен до €30 000 (подтверждено Региональным административным судом, сообщение от 30 января 2026); 4) продукт не является мерчант-эквайрингом: нет приёма карт от покупателей как сервиса, нет подписок и checkout-страницы; 5) входной билет €1 500 несгораемо даже при отказе в дальнейшем обслуживании; 6) очень широкий список запрещённых отраслей и дискреция «факт отсутствия отрасли в списке не гарантирует открытие счёта»; 7) домен nexpay.eu (указанный в задании) НЕ принадлежит компании — это припаркованный домен на продажу через Nameshift, а nexpay.com — вообще американский payroll-сервис; это создаёт риск фишинга/ошибки при поиске провайдера. ПРАКТИКА: Малый бизнес без истории: публично не подтверждено и маловероятно — модель построена на юрлицах с полным KYB и ежемесячной платой €200–1 450, что для микробизнеса экономически невыгодно. Целевая аудитория по интервью основателя: digital assets, крипто-биржи, платёжные провайдеры, юрфирмы, форекс-брокеры — то есть не микропредприниматели. Жалоб на замороженные средства в проверенных источниках не найдено, но есть подтверждённый факт штрафа регулятора за нарушения в отчётности об инцидентах. Отдельно: собственный список high-risk включает «Cryptocurrency related activities (crypto ATM services, cryptocurrency exchange services, cryptocurrency custody services, cryptocurrency trading, crypto-mixers etc.)».</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>https://digiseller.com/agreement, https://plati.market/sellerinfo/</t>
+          <t>https://paynexpay.com/, https://paynexpay.com/blog/list-of-prohibited-and-high-risk, https://paynexpay.com/blog/list-of-accepted-jurisdictions-for, https://www.citiumtech.com/resources/psd2-register/institutions/lt-lt-bl-304708124-lt, https://subjektid.fi.ee/view/19074/PROVIDERS_OF_CROSS_BORDER_E_MONEY_SERVICES?lang=et, https://en.ain.ua/2024/05/10/startup-of-the-day-nexpay/, https://www.delfi.lt/verslas/naujienos/lb-sudare-taikos-sutartis-su-phoenix-payments-ir-nexpay-sumazino-skirtas-baudas-120205510, https://nexpay.eu/en-gb, https://www.nexpay.com/</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
@@ -5923,77 +5923,77 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>paydo</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Plati.Market</t>
+          <t>PayDo (бренд Ecommerce Technologies LTD; лицензии FCA (UK) и FINTRAC (Канада))</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Маркетплейс цифровых товаров (та же экосистема, что Digiseller)</t>
+          <t>High-risk эквайринг/PSP (не MoR: это EMI + платёжный чекаут/эквайринг, а не Merchant of Record)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Серая зона: в Приложении 1 (перечень запрещённых товаров) VPN не упомянут; прямо разрешены к продаже сервисы подписки</t>
+          <t>серая зона. VPN как вид деятельности прямо не запрещён и не разрешён: в Schedule 2 запрещённых/ограниченных категорий VPN нет, но близкая категория «Computer Network / Information Services / Cyberlockers and similar remote digital file-sharing services» (MCC 4816) отнесена к деятельности, запрещённой без предварительного письменного одобрения PayDo. Отдельно PayDo прямо обязывает мерчанта выявлять использование VPN клиентами как попытку обхода гео-/KYC-контроля, то есть VPN-трафик плательщиков трактуется как риск-флаг. Практический блокер для проекта не в VPN, а в географии: Российская Федерация — в списке запрещённых юрисдикций и для компании/UBO/директоров, и для места отправки средств/локации плательщика.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>РФ, СНГ, международный</t>
+          <t>PayDo лицензирован в Великобритании (FCA) и Канаде (FINTRAC), головной офис — Saffron Walden, Essex, UK; бренд принадлежит Ecommerce Technologies LTD, также SWIFT Direct Participant и Mastercard Principal Member. Обслуживает клиентов по всему миру, КРОМЕ списка prohibited jurisdictions: Afghanistan, Belarus, Burundi, CAR, DR Congo, Cuba, Guinea, Guinea-Bissau, Haiti, Iran, Iraq, North Korea, Lebanon, Libya, Mali, Myanmar, Nicaragua, Palestine, Russian Federation, Somalia, South Sudan, Sudan, Syria, Taiwan*, USA*, Venezuela, Western Sahara, Yemen, Zimbabwe (* — по умолчанию недоступны для инкорпорации компании и UBO, но переводы принимать/отправлять можно). Отдельно указано, что prohibited jurisdictions применяются «to where funds originate and/or where a payer is geographically located» — то есть платежи из России будут отклонены. ВЫВОД: российский резидент/российское юрлицо НЕ принимаются; юрлица Казахстана, Армении, Грузии, Кыргызстана и ОАЭ в запретном списке не значатся, то есть теоретически доступны.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Карты, СБП, WebMoney, электронные кошельки</t>
+          <t>PayDo Checkout — более 350 локальных и международных методов: банковские переводы, карты (Cards International / Cards through PayDo wallet top-up), eWallet, мобильные переводы, препеид-кэш; плюс мультивалютные IBAN (GB, CH, DE, DK), SEPA/SEPA Instant/Faster Payments/SWIFT/TARGET2/Fedwire/CHAPS/BACS/Kronos, выпуск физических и виртуальных карт Visa/Mastercard, массовые выплаты (mass payouts).</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Комиссия от 3% от суммы платежа (заявлено на странице для продавцов)</t>
+          <t>Опубликованы тарифы бизнес-счёта (минимальные котировки на странице без заполнения анкеты о компании): setup fee 1500 EUR + 200 EUR/мес; другие показанные тарифы — 300 EUR setup + 125 EUR/мес и бесплатный setup + 100 EUR/мес. Карточные транзакции по счёту внутри EEA 1–4%, вне EEA 2–4%; SEPA исходящие 0.2–0.75% (min 3–15 EUR); cross-border 0.3–1% + 15–35 EUR; конвертация 1%; вывод в ATM и прочее по тарифу. По Checkout опубликованы только локальные методы: «0.2 USD + 3%…5.5%» за транзакцию (примеры: PayDo Wallet Bank transfer South Africa 0.2 USD + 5.5%, Mobile Money Ghana 0.2 USD + 4.7%, Oxxo Mexico 0.2 USD + 5.4%), refund fee «–». Ставка эквайринга по международным картам на странице не публикуется (таблица с карточными строками формируется только после ввода данных о компании) — по запросу (не публикуется). Chargeback fee и monthly minimum для эквайринга — по запросу (не публикуется).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0 руб; регистрация не требует документов или технических знаний</t>
+          <t>Для бизнес-счёта — 1500 EUR (базовая котировка), в других тарифных планах 300 EUR или бесплатно; отдельный onboarding/setup fee для эквайринга на сайте не публикуется — по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Вывод не ранее чем через 72 часа с момента продажи; для отдельных разделов/товаров/продавцов задержка увеличена</t>
+          <t>по запросу (не публикуется) — rolling reserve в публичных тарифах и Merchant Services Terms не указан</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Вывод на кошелёк/карту; для расширенных возможностей нужен формальный или персональный аттестат WebMoney</t>
+          <t>Расчёт на собственный счёт PayDo (settlement); конкретный срок/период выплат на сайте не публикуется — по запросу (не публикуется). В Terms есть право PayDo приостанавливать выплаты по подозрительным транзакциям до завершения проверки.</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Физлицо без документов; при отрицательном отзыве без аттестата возможна блокировка счёта и продаж</t>
+          <t>Только юридическое лицо: в Merchant Services Terms UK прямо сказано: «"Client" means any legal entity that has executed Annex 1 (Fees and Terms)» — индивидуальный предприниматель/самозанятый не подходит. KYC/KYB: документ о госрегистрации компании и документ о владении, ID + proof of address + CV или ссылки на соцсети для каждого UBO/директора/топ-менеджера; для бенефициаров вне EEA дополнительно proof of funds (например, банковская выписка). Проверка UBO с фото и совпадением лица, срок открытия счёта — до ~3 недель. Для чекаута требуется «merchant's website(s) and application(s)» — то есть сайт/приложение, а не только Telegram-бот. Требуется соответствие Card Scheme Rules: чёткие условия подписки, отмена, refund policy.</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Рекуррент нет; продажа подписки как разового цифрового товара</t>
+          <t>Да, поддержка подписок описана детально (отдельный Schedule по Recurring Transactions): определения Continuity Program, Free Trial, Introductory Offer, Negative Option Billing, Recurring Transaction, Standing Instruction, Subscription; обязательные флаги Card-on-File (COF) и Merchant-Initiated Transactions (MIT) с Transaction Initiator, Initial/Subsequent indicator и Network Transaction ID; мерчанты с подписками и free trial отнесены к Tier 3 High Integrity Risk по Visa Integrity Risk Program (VIRP) — усиленные требования регистрации и мониторинга; запрещены предустановленные («pre-checked») галочки согласия, правил раскрытия условий free trial и отмены. Токенизация — только в контролируемой среде PayDo: привлекать сторонних tokenisation-провайдеров без письменного согласия PayDo нельзя.</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>API и автовыдача уникальных кодов (автоматически создаваемые уникальные коды)</t>
+          <t>Есть hosted payment page + SDK/API, документация docs.paydo.com/overview, вебхуки и «Payment page, SDK, API» в терминах. Telegram-бот без сайта — рискованно: Terms описывают приём платежей через «website(s) and application(s)» мерчанта, а проверка сайта (контакты, refund/cancellation policy, privacy policy) — часть онбординга. Сложность интеграции: 3 — техническая интеграция стандартная (hosted page/API/docs), но высокая комплаенс-нагрузка: только юрлицо, письменное одобрение MCC 4816, GEO-блокировки, а главное — Россия в запрещённых юрисдикциях..</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Риск блокировки товаров при отрицательном отзыве, запрет HTML в описании, запрет рекламы сторонних ресурсов в товаре</t>
+          <t>1) Россия прямо запрещена и как юрисдикция компании/UBO/директора, и как география плательщика/источника средств — приём платежей из РФ невозможен. 2) VPN-деятельность не одобрена явно: MCC 4816 «Computer Network / Information Services» требует письменного согласия PayDo. 3) Ставки по международным картам не публикуются. 4) Индивидуалы/самозанятые не обслуживаются — нужен родитель как юрлицо или иностранная структура. 5) Старый справочный центр PayDo на Zendesk закрыт («Help Center Closed»), часть статей, находимых поиском, мертва — качество поддержки/документации нестабильно. ПРАКТИКА: Публично PayDo позиционируется как «High-risk friendly» и заявляет «No minimums. No hidden fees», приём платежей до 3 млн EUR (это заявления самой компании в каталоге TheBanks.eu; оценка каталога — 4.73 «Outstanding», оценка от 5 сентября 2026, #4 EMI в Великобритании). Onboarding полностью удалённый: онлайн-заявка, документы UBO и компании, счёт до ~3 недель. Сведений о массовых заморозках средств в проверенных источниках не найдено — не подтверждено. Требование processing history как формального условия не публикуется.</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/sellerinfo/, https://plati.market/asp/soglas_add1.asp</t>
+          <t>https://paydo.com/merchant-services-terms-uk/, https://paydo.com/terms-of-use-uk/, https://paydo.com/prohibited-jurisdictions/, https://paydo.com/business/pricing-iban/, https://paydo.com/business/pricing-merchant/, https://paydo.com/business/merchant/, https://paydo.zendesk.com/hc/en-us/articles/11772533053725-What-industries-are-not-supported, https://thebanks.eu/emis/ecommerce-technologies-355193</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -6005,405 +6005,405 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>zen</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>GGsel</t>
+          <t>ZEN.COM (UAB ZEN.COM, Литва; услуги эквайринга — ZEN-UK Limited, Великобритания)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Витрина цифровых товаров на бэкенде Digiseller</t>
+          <t>High-risk эквайринг/PSP (EMI + карточный эквайер; не MoR)</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Серая зона: наследует правила Digiseller; VPN отдельно не упомянут</t>
+          <t>серая зона. Прямого упоминания VPN нет НИ в «List of Prohibited Activities» (опубликован 14.11.2024), НИ в Schedule I «List of Prohibited Items» британских E-Commerce Terms (версия 1.01 от 05.11.2025) — VPN, proxy, anonymizer, «unblocking» и IP-masking там не названы. Запрещены только смежные вещи: «Cable descramblers and black boxes… devices and applications, intended to obtain and share internet TV signals – IPTV» и «copyright unlocking devices or other devices designed to circumvent copyright protection» — это про обход авторских прав/платного ТВ, а не про VPN. Отсутствие запрета ≠ разрешение: финальное решение принимает риск-подразделение ZEN, а «Merchant must not be … involved in any activity provided in the prohibited activities list». Отдельный блокер — география: Россия и Беларусь в prohibited jurisdictions, а Казахстан/Армения/Грузия/Кыргызстан/ОАЭ отсутствуют в списке разрешённых для онбординга юрисдикций.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>РФ, СНГ</t>
+          <t>Эквайринг предоставляет ZEN-UK Limited (344-354 Gray's Inn Road, London, компания 13953648) — Authorised Electronic Money Institution с лицензией FCA, firm reference number 1000019, выдана 09.08.2024; именно ZEN выступает Acquirer для мерчанта («Unless otherwise mentioned, ZEN acts as an Acquirer for the Merchant»). Групповые структуры: UAB ZEN.COM (Литва, рег. № 304749651) и ZEN Technology B.V. Onboarding permitted jurisdictions (документ от 29 июня 2023, v1.1) — Åland, Guernsey, New Zealand, Austria, Hong Kong, Norway, Australia, Hungary, Poland, Belgium, Iceland, Portugal, Bulgaria, India, Réunion, Canada, Ireland, Romania, Cayman Islands, Isle of Man, Saint Martin (French part), Israel, Singapore, Croatia, Italy, Slovakia, Cyprus, Japan, Slovenia, Czech Republic, Jersey, South Africa, Denmark, Latvia, United States, South Korea, Greece, Estonia, Monaco, Liechtenstein, Spain, Finland, Lithuania, Sweden, France, Luxembourg, Switzerland, French Guiana, Malta, Taiwan, Germany, Martinique, United Kingdom, Gibraltar, Mayotte, Guadeloupe, Netherlands. Prohibited Jurisdictions List (14.11.2024) прямо включает: Russia (#16), Belarus, Crimea/Donetsk/Kherson/Luhansk/Zaporizhzhia, Afghanistan, Iran, North Korea и др. ИТОГ: российский резидент/юрлицо — НЕТ; юрлица Казахстана, Армении, Грузии, Кыргызстана и ОАЭ в permitted-списке 2023 года ОТСУТСТВУЮТ, то есть открыть бизнес-счёт по этому документу нельзя (список может быть устаревшим — требует проверки у ZEN напрямую).</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Карты, СБП, кошельки</t>
+          <t>Карточный эквайринг Visa и Mastercard, Apple Pay и Google Pay, BLIK, iDEAL, Bancontact, Trustly, Sofort, PayByLinks (Польша), Skrill (+Skrill Rapid Transfer), Neteller, Paysafecard, Paysafecash, Neosurf, WeChat, UnionPay, Twisto; отдельный блок BoaCompra для Латинской Америки (Visa/Mastercard BR и CL, Pix, Boleto, PSE, Redcompra, MultiBanco, Pagoefectivo, Efecty, PayPal BR); собственный кошелёк ZEN Pay.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Сбор площадки зависит от раздела и условий продавца; публичной ставки нет; расчёты идут через Digiseller, плюс стоимость платёжного метода и вывода</t>
+          <t>Опубликованы в ZEN Business pricing (effective 7 января 2025) и на ценовой странице. Эквайринг: Visa и Mastercard — IF++ 0.89% + 0.30 EUR; Apple Pay/Google Pay — IF++ 0.89% + 0.30 EUR; BLIK/iDEAL/Bancontact/Trustly/Sofort/Polish PayByLinks — 0.89% + 0.30 EUR; Skrill (свыше 4 EUR) 4.20% + 0.30 EUR, Skrill micro (до 4 EUR) 7.20%, Skrill Rapid 2.20% + 0.30 EUR; Neteller 4.20% + 0.30 EUR; Paysafecard 10.20% + 0.30 EUR; Paysafecash 5.20% + 0.30 EUR; WeChat 2.20% + 0.30 EUR; UnionPay 2.20% + 0.30 EUR; Twisto 2.40% + 0.30 EUR; Neosurf 10.20% + 0.30 EUR. Refund 2.50 EUR. Chargeback fee — 35 EUR (при chargeback rate 0.00–0.30%), 40 EUR (0.30–0.50%), 45 EUR (0.50–0.70%), 50 EUR (0.70–1.00%), 60 EUR (&gt;1.00%); representment 10.00 EUR. Fraud Prevention Service: 0.00% + 0.07 EUR за транзакцию при низком fraud rate, до 2.00% + 0.07 EUR для high-risk merchant, плюс 200 EUR/мес в отдельных случаях. Обслуживание счёта: Smart 25.00 EUR/мес (спец. предложение — бесплатно), Enterprise 100.00 EUR/мес. ZEN Pay processing 0.35% + 0.10 EUR. Обязательный минимум оборота не публикуется.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0 руб, регистрация бесплатна</t>
+          <t>Отдельный setup fee для эквайринга не публикуется; открытие счёта бесплатно (Smart/Enterprise) — по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Возврат списывается со счёта продавца; комиссии при возврате полностью не возвращаются</t>
+          <t>по запросу (не публикуется): Security Deposit — ZEN вправе запросить его единой суммой или на rolling-основе, размер определяется на усмотрение ZEN (риск-профиль, Delivery Pending Amount, финансы мерчанта) и фиксируется в Merchant Agreement; ZEN может увеличить депозит в любой момент письмом. Период удержания после расторжения (Security Deposit Release Period) определяется ZEN по своему усмотрению.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Баланс и заявки на вывод — в кабинете Digiseller</t>
+          <t>Settlements на счёт мерчанта в ZEN (создаются 4 счёта: GBP, EUR, USD, PLN); срок — Settlement Period, указанный в Annex A к Merchant Agreement, то есть по запросу (не публикуется). ZEN вправе удерживать settlement по подозрительным/потенциально chargeback-транзакциям до конца расследования и вправе отказать в выплате.</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Требуется идентификация WebMoney (наследуется от Digiseller)</t>
+          <t>Мерчант должен быть «a legal person or a sole trader (or equivalent) registered in a jurisdiction that is not included in the Prohibited Jurisdictions List» — то есть ИП/самозанятый или аналог формально допустимы, но только из разрешённой юрисдикции (РФ — нет). KYC: подтверждение личности акционеров, директоров и UBO — фото ID/паспорта/водительских прав/ВНЖ + сравнение с фото лица, дополнительные документы по запросу; ZEN может отказать в регистрации без объяснения причин. Для карточных CNP-транзакций на сайте обязательны: юридическое имя мерчанта, полное описание товаров/услуг, return/refund/delivery policy, контакты поддержки (e-mail/телефон), физический адрес ведения деятельности, политика защиты данных покупателя; обязательна интеграция антифрод-инструмента docs.zen.com/payments/api-integration/fraud-collector; обрабатывать транзакции можно только по URL, явно одобренным ZEN (новые URL — по письменному согласованию, «The Merchant may only process Transactions through URLs explicitly approved by ZEN»).</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да: отдельный раздел 8 «Recurring Transactions» в UK E-Commerce Terms v1.01 (05.11.2025) — рекуррентная транзакция определена как транзакция с stored credential; требуется явное согласие держателя карты в момент оформления заказа, в том числе согласие на хранение карточных данных; мерчант обязан обеспечить возможность отмены и подтвердить отмену в течение 2 рабочих дней; при изменении условий или если прошло более 6 месяцев с предыдущего списания — уведомить клиента минимум за 7 дней; интервал между рекуррентными списаниями не может превышать 1 год. Есть раздел «Платёж по инициативе мерчанта/MIT» в отраслевых условиях. Dunning-логика (авто-ретраи) в публичных условиях не описана — не подтверждено.</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Автовыдача мгновенных кодов; API наследуется от Digiseller</t>
+          <t>REST API + хостед-страница/редирект (Pages: «an Account Holder is redirected from the Merchant's website»), документация docs.zen.com, обязательная интеграция fraud-collector, вебхуки/нотификации в личном кабинете. Telegram-бот как единственная витрина — проблема: контракт требует одобренного URL/сайта с полным набором данных мерчанта, а Telegram-бот не является сайтом по правилам карточных схем. Сложность интеграции: 4 — API и хостед-страница стандартные, но объём требований большой (43-страничный договор, обязательный fraud collector, одобрение URL, KYC/UBO, Security Deposit по усмотрению ZEN) и по каждому пункту ZEN оставляет свободу отказа..</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Три слоя сборов плюс возвраты; двойной набор правил (витрина + платформа); непрозрачные тарифы</t>
+          <t>1) Россия и Беларусь — запрещённые юрисдикции, а KZ/AM/GE/KG/UAE отсутствуют в списке разрешённых для онбординга. 2) ZEN прямо сохраняет право отказать в регистрации и «not obliged to reveal the merchant the reasons» — непрозрачный отказ. 3) Security Deposit вправе запрашиваться и увеличиваться по усмотрению ZEN, release period тоже на его усмотрение. 4) Mandatory fraud collector и одобрение URL усложняют схему «только Telegram-бот». 5) Условия фиксируют, что ZEN не отвечает за задержки settlement из-за эквайеров/провайдеров и может отказать в settlement по подозрению. ПРАКТИКА: ZEN начинал как retail-необанк и лишь в 2024 получил британскую EMI-лицензию под ZEN-UK Limited (09.08.2024) — то есть эквайринговое направление молодое, публичной статистики по онбордингу малого бизнеса без processing history нет — не подтверждено. Публичная политика допускает sole trader, что для «родитель как ИП» теоретически удобнее, чем PayDo, но только в разрешённой юрисдикции. Сведений о массовой заморозке средств мерчантов в проверенных источниках не найдено — не подтверждено. Внешние обзоры ZEN.COM в потребительском сегменте встречаются критические, но их содержание я не проверял.</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://foxreload.com/ru/library/marketplaces/ggsel-commissions-payouts, https://ggsel.net/en/selleragreement.pdf</t>
+          <t>https://www.zen.com/files/terms-and-conditions/UK/UK_ecommerce_terms.pdf, https://www.zen.com/files/terms-and-conditions/prohibited_activities.pdf, https://www.zen.com/files/terms-and-conditions/prohibited_jurisdictions.pdf, https://www.zen.com/files/terms-and-conditions/onboarding_permitted_jurisdictions.pdf, https://www.zen.com/files/tc/business_pricing.pdf, https://www.zen.com/files/terms-and-conditions/Terms_and_Conditions_Business.pdf, https://www.zen.com/files/terms-and-conditions/ZEN_LT_Terms_for_Business_Users_v1.13.pdf, https://ask.zen.com/hc/en-us/articles/14525243260188-How-to-apply-for-a-ZEN-Payment-Gateway-for-your-e-commerce-store</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>connectum</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Playerok</t>
+          <t>Connectum (Connectum Limited, Великобритания)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Маркетплейс игровых товаров и цифровых услуг</t>
+          <t>High-risk эквайринг/PSP (реальный британский эквайер/PSP; фактически деятельность остановлена регулятором)</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Не подтверждено: текст оферты отдаётся только JS-рендером, явного запрета или разрешения VPN найти не удалось</t>
+          <t>нет — не из-за политики по VPN, а из-за полной остановки деятельности: VPN отдельно не упомянут нигде в публичных документах Connectum (ни в Terms of Use, ни в прайсе, ни на страницах сайта) — «не подтверждено»; при этом с 22 мая 2024 компания приняла добровольное обязательство перед FCA: не оказывать регулируемые платёжные услуги (включая процессинг платежей и payout-счета), прекратить онбординг новых клиентов и вернуть средства клиентам. То есть подключиться к Connectum в 2026 году нельзя, независимо от того, разрешён ли был бы VPN.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Connectum Limited, 63 St. Mary Axe, London EC3A 8AA, Великобритания; регистрационный номер 8941525; Authorised Payment Institution, регистрация в FCA № 624117; SWIFT CNNNGB21; PCI DSS Level 1 Service Provider; сайт заявляет работу с 2014 года. Язык сайта — английский (русская версия отключена в разметке). Публично заявлены «3000+ мерчантов», глобальный процессинг Mastercard/UnionPay/Visa, мультивалютность. Ограничений по странам мерчантов на сайте не опубликовано; из-за остановки онбординга география неприменима. Российский резидент/юрлицо формально не описан ни как запрещённый, ни как разрешённый — в 2024–2026 это уже неактуально, приём клиентов закрыт.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Карты РФ, СБП</t>
+          <t>Процессинг карт Mastercard, UnionPay, Visa; мультивалютный процессинг; выплаты на карты (Original Credit Transactions и MoneySend); card-to-card (P2P); настройка рекуррентных списаний; токены (one-click payments); 3-D Secure; e-Invoicing; динамический дескриптор; платёжная страница с шаблонами; интернет-банк (ib.connectum.eu) и SEPA/SWIFT-переводы по счёту.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Многослойная: ставка зависит от типа товара плюс стоимость вывода; конкретные проценты не подтверждены</t>
+          <t>Прайс опубликован на сайте и в PDF (ставки действуют с 21 июня 2021 и могут меняться). Эквайринг: onboarding fee за MID — от 50 EUR; monthly monitoring fee за MID — от 10 EUR; acquiring fee за транзакцию — «Set individually», то есть по запросу (не публикуется); refund/reversal — 0.50 EUR; chargeback processing — от 30 EUR; rolling reserve — 0–10% месячного оборота на 180 дней; payout hold — «Set individually»; application review — бесплатно. Счёт: открытие мерчант-счёта бесплатно, обслуживание 25 EUR/мес, закрытие счёта 100 EUR, account balance fee 0.6% годовых; входящий SEPA 5 EUR / non-SEPA 10 EUR; исходящий SEPA 20 EUR / non-SEPA 60 EUR; FX 0.35% (min 5 EUR); settlement SEPA 30 EUR / non-SEPA 60 EUR. Отдельный минимальный месячный оборот не публикуется.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>Onboarding fee за MID — от 50 EUR; открытие мерчант-счёта — бесплатно (прайс 2021 года; сейчас онбординг остановлен, поэтому fee неприменим)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Эскроу: деньги удерживаются до подтверждения сделки</t>
+          <t>Rolling reserve — 0–10% месячного оборота, удержание 180 дней; payout hold (число дней удержания до settlement) — устанавливается индивидуально</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Вывод на карту РФ; сроки и минимум не подтверждены</t>
+          <t>На сайте заявлено зачисление на банковский счёт в течение 24 часов и settlement через SEPA (30 EUR) или non-SEPA (60 EUR), но payout hold определяется индивидуально; в связи с обязательством перед FCA выплаты по payout-счетам остановлены, средства клиентов возвращаются.</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>KYC низкий/средний; физлицо</t>
+          <t>Юридическое лицо; анкета клиента (Connectum Customer Questionnaire, PDF) + пакет документов; удалённое открытие счёта заявлено за 48 часов при срочном варианте; обязательные требования к сайту: контакты мерчанта (название, рег. номер, адрес, e-mail, телефон) для переписки с держателем карты, полное описание товаров/услуг, цен и сроков действия, Terms and Conditions, Return/Refund Policy, Cancellation Policy, Consumer Data Privacy Policy; PCI DSS Level 1. Допустимость вида деятельности проверяется через форму pre-check на сайте. Нужен ли сайт именно как витрина (Telegram-бот не подойдёт) — прямо не сказано, но требования к контенту сайта сформулированы как обязательные.</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да, заявлены «Recurring charges set-up» и «Tokens (one-click payments)» — то есть техническая поддержка подписок и токенизации карт присутствовала; детальных правил (dunning, MIT-флаги, требования к free trial) в публичных документах нет — не подтверждено.</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Частичная автовыдача (коды мгновенно, аккаунты/валюта — вручную)</t>
+          <t>Платёжный шлюз с хостед-платёжной страницей (настраиваемый дизайн: логотип, шрифты, цвета), личный кабинет с аналитикой и мониторингом транзакций, заявлена техническая интеграция «от 2 часов». Документация API публично не найдена — не подтверждено. Сложность интеграции: 5 — фактически подключение невозможно: с 22 мая 2024 компания не оказывает регулируемые платёжные услуги и не подключает новых клиентов..</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Массовые блокировки товаров в отдельных разделах; правила арбитража закрыты; тарифы непубличны</t>
+          <t>1) Ключевой риск реализован: добровольное обязательство перед FCA от 22 мая 2024 — остановка процессинга, прекращение онбординга, возврат средств клиентов (баннер на главной странице connectum.eu). 2) В СМИ и профильных изданиях публиковались материалы о расследовании FCA и подозрениях в отмывании миллиардов, связанных с Connectum (заголовки на investigations.org, rima.media, compliancecorylated.com); содержание статей я подтвердить не смог (403/усечённый ответ), поэтому это только указание на наличие публикаций, а не подтверждённый факт. 3) Публичный прайс датирован 2021 годом и часть ставок «set individually» — непрозрачно. 4) Наличие средств клиентов в компании в момент остановки означало задержки возвратов. ПРАКТИКА: Connectum исторически работал с высокорисковыми нишами и СНГ-рынком (сайт с 2014, заявлено 3000+ мерчантов, PCI DSS L1, «remote application review»), но с мая 2024 новых клиентов не берёт и средства возвращает. Независимая оценка Trustpilot — 3.2/5 («Average»), что указывает на смешанный клиентский опыт, однако страницу отзывов я не смог прочитать напрямую (Cloudflare 403). Требование processing history не публиковалось.</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://playerok.com/terms-of-sale, https://foxreload.com/ru/library/compare/funpay-vs-playerok</t>
+          <t>https://connectum.eu/, https://connectum.eu/pricelist/, https://connectum.co.uk/wp-content/uploads/2021/06/connectum_merchant_account_fees.pdf, https://connectum.eu/account-opening/, https://connectum.eu/opportunities/, https://connectum.eu/wp-content/themes/connectum/file/Terms_of_Use_en.pdf?202206, https://www.investigations.org/news/edgars-lasmanis-connectum-fca-requirement, https://www.compliancecorylated.com/news/uk-regulator-yet-to-shut-pep-owned-payments-firm/</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>valyuz</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Z2U</t>
+          <t>Valyuz (Valyuz UAB, Литва)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Маркетплейс игровой валюты, аккаунтов и ключей</t>
+          <t>НЕ эквайринг и не MoR — это EMI (электронные деньги) с IBAN-счетами, массовыми выплатами и картами; мерчант-чекаута/приёма карточных платежей как продукта нет</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Не подтверждено: явной политики по VPN в публичных правилах найти не удалось</t>
+          <t>нет. В официальном списке запрещённых индустрий есть прямая строка «Circumvention devices» (устройства/средства обхода), что с высокой вероятностью покрывает VPN и аналогичные privacy-инструменты. Дополнительно в restricted industries отнесены «B2C/C2B activities» — то есть продажа цифровой услуги конечным потребителям (как раз модель VPN-подписки) ограничена, и «Direct cryptocurrency related activities». Плюс Россия в списке запрещённых стран для переводов.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Международный</t>
+          <t>Valyuz UAB — литовская электронная денежная организация (EMI) с лицензией Банка Литвы (Bank of Lithuania, www.lb.lt), код юрлица 304782929, зарегистрированный адрес Gedimino ave. 44A-201, Vilnius, корреспондентский — Saltoniskiu Str. 2, Vilnius. НЕ Мальта — в отличие от формулировки задания, все официальные документы и футер сайта указывают Литву. В реестре EBA EUCLID/PIR у Valyuz UAB открыты услуги, в том числе через паспорт в Бельгии: ES_010 выпуск электронных денег, PS_02 cash withdrawals, PS_03A direct debits, PS_03B платежи по картам, PS_03C credit transfers, PS_05A выпуск платёжных инструментов, PS_05B acquiring of payment transactions (авторизация с 29.03.2018). Restricted countries (нельзя получать/отправлять средства): Afghanistan, American Samoa, Anguilla, Belarus, Burundi, CAR, Chad, DR Congo, Congo, Cuba, Djibouti, Eritrea, Palestine, Guam, Guinea-Bissau, Haiti, Iran, Iraq, North Korea, Kosovo, Laos, Lebanon, Liberia, Libya, Maldives, Mali, Mozambique, Myanmar, Netherlands Antilles, Nicaragua, Pakistan, Palau, Panama, RUSSIA, Somalia, Sudan, South Sudan, Syria, Turks and Caicos, Vanuatu, Venezuela, Vietnam, US Virgin Islands, Western Sahara, Yemen. ИТОГ: российский резидент/юрлицо — НЕТ (Россия в restricted list); Казахстан, Армения, Грузия, Кыргызстан, ОАЭ в запретном списке не указаны, но продажа B2C и «circumvention devices» всё равно запрещены.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Карты, электронные кошельки, крипта</t>
+          <t>Банковские переводы SEPA, SEPA Instant, SWIFT, локальные схемы; мультивалютные и выделенные IBAN (EUR, USD, GBP, ILS, ZAR, SEK и др.); массовые выплаты (mass/bulk payments); FX по рыночным курсам; предоплаченные дебетовые карты; Open API для интеграции с SAP/CRM/бухгалтерией. Платёжного шлюза, хостед-страницы и приёма карточных платежей от покупателей как продукта НЕТ.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Ставка комиссии публично не раскрыта; типовой стек: сбор площадки + стоимость вывода</t>
+          <t>по запросу (не публикуется): тарифы фиксируются в индивидуальном fee schedule («You will be asked to conclude a separate fee schedule before starting to use our Services»), и в Terms прямо сказано, что комиссии определяются на усмотрение Valyuz и различаются по клиентам в зависимости от страны регистрации и вида деятельности. Единственная публичная цифра — плата за онбординг/рассмотрение заявки не взимается.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>0 EUR — опубликовано: «No, there is no application processing fee, and no charges or upfront payments are required until your account is fully operational»</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Эскроу, холд до подтверждения сделки</t>
+          <t>не применимо — эквайринга нет; резервы/депозиты в публичных документах не описаны, по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Международные рельсы (карта/кошелёк/крипта); выплаты на карту РФ не подтверждены</t>
+          <t>Исходящие SEPA/SWIFT-переводы со счёта, массовые выплаты файлами, лимиты зависят от страны, статуса верификации и усмотрения Valyuz; конкретные сроки и лимиты — по запросу (не публикуется). Средства клиентов сегрегированы на защищённом счету (safeguarding), но НЕ покрываются литовской системой страхования вкладов.</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Регистрация продавца; KYC не подтверждён</t>
+          <t>Поддерживаемые юридические формы: Private Limited Company, Public Limited Company, Partnership, Foundation. Специализация — B2B-счета («Valyuz specializes in providing B2B (Business-to-Business) accounts»); физлицо может открыть только личный счёт и не вправе использовать его для бизнеса («As an individual you will not be entitled to use your private Valyuz Account for business purposes»). Минимальный возраст — 18 лет. KYC/KYB: заявка онлайн или офлайн, верификация e-mail и телефона, идентификация по AML-требованиям, документы компании и UBO, доказательство адреса; для бизнес-счёта до 4 подписантов. Крипто-деятельность и B2C/C2B — restricted. Требований к сайту/чекауту нет, поскольку эквайринга нет.</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Приёма карточных подписок нет, поэтому рекуррентный биллинг для VPN-подписки невозможен. Есть только «reoccurring payments» — сохранённые шаблоны повторяющихся ИСХОДЯЩИХ платежей (например, зарплаты, подписки самого клиента), а также автоматические переводы. Токенизация карт покупателей и MIT/dunning — не применимо.</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Есть автоматическая выдача кодов</t>
+          <t>Open API для подключения SAP/бухгалтерии/CRM, загрузка файлов массовых платежей, нотификации по запланированным транзакциям и входящим платежам; мобильное приложение + Token App для 2FA. Хостед-чекаута и платёжной страницы нет, поэтому Telegram-бот как витрина технически не может принимать платежи через Valyuz — можно только получать переводы на IBAN. Сложность интеграции: 5 — нет платёжного шлюза/чекаута; приём денег возможен только банковским переводом на IBAN, что для подписок в Telegram-боте нерабочая модель. Плюс прямой запрет «Circumvention devices» и ограничение B2C..</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Высокий порог доверия у покупателей, споры, отсутствие русскоязычной поддержки выплат</t>
+          <t>1) «Circumvention devices» в списке запрещённых индустрий — риск закрытия счёта и удержания средств при описании деятельности как VPN/proxy. 2) B2C/C2B activities — restricted, а проект продаёт конечным потребителям. 3) Россия — в списке стран, куда/откуда запрещены переводы. 4) EMI: средства не застрахованы системой страхования вкладов; ответственность Valyuz ограничена суммой комиссий за 3 месяца. 5) Право расторгнуть договор, если клиент «no longer meet our Client's profile», и блокировать платёж при подозрении. 6) Тарифы непубличны и определяются индивидуально. ПРАКТИКА: Valyuz публично нацелен на корпоративных клиентов с KYB-аудитом; отдельного требования processing history нет — не подтверждено. Есть отдельная статья «What is required to proceed with the audit of the company? Is there an audit fee?» — то есть аудит компании является частью процесса. Сведений о массовых жалобах на заморозку средств в проверенных источниках не найдено — не подтверждено. База знаний активно обновляется (например, статья о Beneficiary Name Verification от 5 октября 2025), Terms of Use пересмотрены 23 февраля 2026 — сервис живой и развивается.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>https://foxreload.com/en/library/marketplaces/sell-digital-goods-z2u</t>
+          <t>https://www.valyuz.com/knowledge-base/which-industries-are-prohibited, https://www.valyuz.com/knowledge-base/are-there-any-countries-that-are-restricted-for-payments, https://www.valyuz.com/knowledge-base/what-are-supported-business-legal-entities, https://www.valyuz.com/knowledge-base/what-account-type-i-can-open-with-valyuz-b2b-b2c-c2c, https://www.valyuz.com/knowledge-base/is-there-application-processing-fee-for-onboarding, https://www.valyuz.com/utility-pages/terms-conditions, https://www.valyuz.com/payment-capabilities/, https://www.valyuz.com/dedicated-ibans/, https://paymentinstitutionsregister.eu/services/be/card-payments/valyuz-uab-1343</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>wallester</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>G2G</t>
+          <t>Wallester AS (Wallester Business / White-Label)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Международный маркетплейс игровых товаров</t>
+          <t>НЕ эквайер и не MoR — карточный эмитент / BaaS / BIN-спонсор (корпоративные Visa-карты и IBAN-счета)</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Ограничение: продавать можно только подписки сроком не более одного месяца (п.1 правил для Software &amp; App), что несовместимо с длинными тарифами 3/6/12 мес. Для GiftCard прямо запрещено просить покупателя использовать внешний софт или VPN</t>
+          <t>нет (вопрос не применим) — Wallester вообще не оказывает услуги эквайринга и не подключает мерчантов к приёму платежей: продукт — выпуск Visa Business карт и IBAN-счетов для расходов компании. VPN в документах не упоминается ни разу, но даже положительный ответ ничего не даёт: принять оплату подписки от клиента через Wallester технически невозможно.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Международный, приоритет ЮВА</t>
+          <t>FAQ: "Any legal entity registered in the European Economic Area and United Kingdom can join the program". Help Center (Boarding Process): "Our services are accessible to businesses from the European Economic Area, as well as the United Kingdom and Switzerland. However, we extend our services to companies from other countries as well. In such cases, we carry out a thorough due diligence process and conduct a comprehensive business case review before onboarding the company." Требуется выписка из торгового реестра. Россия: нет — клиент проходит проверки Sanctions (разд. 10 соглашения), Wallester вправе отказать по своему AML/CFT risk appetite, а материнская структура обязана быть в ЕЭЗ/UK/Швейцарии.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Карты, электронные кошельки, локальные методы</t>
+          <t>Не применимо — Wallester не принимает платежи от покупателей. Наоборот: клиент пополняет свой IBAN-счёт (банковский перевод в EUR бесплатно; пополнение картой Visa/Mastercard/Maestro/Apple Pay — 1.20%; стейблкоин USDC), а затем тратит средства выпущенными картами.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Ставка комиссии публично не раскрыта; сайт обещает удержание платежей продавцу при нарушениях</t>
+          <t>Тарифы опубликованы: Free — €0/мес (300 виртуальных карт включено); Premium — €199.00/мес (3 000 карт); Platinum — €999.00/мес (18 000 карт); Enterprise Suite — по запросу. Дополнительная виртуальная карта: €0.35 / €0.20 / €0.10 в месяц по тарифам. Доставка физической карты: €5.00 standard, €20.00 express. ATM: Европа 2.00% (мин €2.00), международные €2.00 + 2.00%, запрос баланса €0.50. Конвертация валют 2.00% + курс Visa. Пополнение переводом в EUR — €0.00, в другой валюте — €15.00 за пополнение; пополнение картой 1.20%. Диспут €20, справка о счёте €15, закрытие счёта €25 за валюту. Эквайрингового процента с оборота не существует, потому что услуга не оказывается. Также есть "Industry Fee" — надбавка для отдельных рискованных отраслей, размер не публикуется.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>€0 — "Free to start. No setup fees."</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>При офсайт-торговле — заморозка доступного баланса на 6 месяцев</t>
+          <t>не применимо / по запросу (не публикуется) — эквайринговых резервов у Wallester нет.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Вывод на международные рельсы; карта РФ не подтверждена</t>
+          <t>не применимо — расчётов с мерчантом не существует. Средства клиента хранятся на сегрегированном банковском счёте, процент на остаток 0%. Зачисление пополнения: "Generally, it takes anywhere from several minutes to 1-3 business days".</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Уровень аккаунта продавца не ниже 30 для категории Software &amp; Apps</t>
+          <t>Только юрлицо (либо sole proprietor) ЕЭЗ/UK/Швейцарии; "Incorporation details", "Corporate document extract from the business register", KYC акционеров и директоров, описание бизнеса и географии, примерный оборот по картам, подтверждение адреса. KYB-проверка около 48 часов. Потребители не принимаются: "In addition to legal entities, only such natural persons are accepted as clients who conduct business as sole proprietors and use the Service exclusively for that purpose". Сервис строго B2B.</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Максимум 1 месяц на подписку</t>
+          <t>не применимо к приёму платежей. Токенизация, 3D Secure и Apple/Google Pay у Wallester относятся к расходным операциям по выпущенным картам, а не к рекуррентному списанию с карт подписчиков.</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Есть система загрузки данных заказа, автовыдача частичная</t>
+          <t>REST API для выпуска карт и управления счетами (api-doc.wallester.com), открытый пример интеграции на GitHub, Help Center, мобильное приложение, White-Label BIN-спонсирование. Платёжного шлюза для приёма оплаты нет, поэтому для Telegram-бота без сайта не подходит в принципе. Сложность интеграции: 5 — интеграция бессмысленна: продукт про выпуск карт и BaaS, а не про приём платежей..</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Жёсткая модерация, постоянный бан за офсайт-торговлю, ограничение срока подписки убивает годовые тарифы</t>
+          <t>Главный риск — принять Wallester за PSP и потерять время: компания не подключает мерчантов к эквайрингу. Дополнительно: обязательное юрлицо в ЕЭЗ/UK, жёсткий AML/sanctions-контроль, запрет на личные расходы и перепродажу сервиса третьим лицам (п. 4.1.2.2 соглашения: "reselling the Service to third parties, e.g., the Client makes the Cards available to third parties"). ПРАКТИКА: Малый бизнес онбордит (бесплатный тариф, KYB ~48 ч), но исключительно на стороне расходов компании. Для приёма платежей за VPN-подписки нерелевантен.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>https://support.g2g.com/support/solutions/articles/5000001405, https://support.g2g.com/support/solutions/articles/5000888791</t>
+          <t>https://wallester.com/, https://wallester.com/white-label, https://wallester.com/card-payment-platform/payment-processing, https://wallester.com/card-solutions/ecommerce-marketplaces, https://wallester.com/business/pricing, https://wallester.com/faq, https://wallester.com/business-account-card-agreement, https://wallester.com/legal-notice, https://helpcenter.wallester.com/en/articles/120226-boarding-process, https://helpcenter.wallester.com/en/articles/120225-wallester-service-fees</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>paymentcloud</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Eldorado.gg</t>
+          <t>PaymentCloud (PaymentCloud, Inc. / PaymentCloud LLC)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Международный маркетплейс игровых товаров</t>
+          <t>High-risk эквайринг/PSP — фактически registered ISO/MSP и брокер между мерчантом и банками-эквайерами</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Не подтверждено: отдельной политики по VPN нет; площадка заточена под игровые категории</t>
+          <t>серая зона (не подтверждено) — ни в списке отраслей, ни в блоге, ни во внутреннем поиске по сайту VPN не упоминается (поиск ?s=VPN не даёт результатов). Принимаются смежные вертикали Digital Downloads, SaaS Companies, Tech Support, Continuity &amp; Subscription. Прямого запрета нет, но и подтверждения приёма VPN нет — решение принимает банк-партнёр в индивидуальном порядке.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Международный</t>
+          <t>США-центричный провайдер: в требованиях фигурируют business license и Employer Identification Number (EIN), voided check или bank letter от банка. Merchant Maverick (обзор обновлён 03.03.2026) прямо указывает в минусах: "No offshore accounts". Российское юрлицо/резидент: нет — офшорных схем нет, а расчётный счёт и EIN должны быть американскими. FAQ допускает sole proprietorship (для ИП в чеке должно быть напечатано полное имя владельца), но не "самозанятого" из РФ. В списке стран на сайте (PaymentCloud vs Mexico и т.п.) есть отзывы "No disponible en México" — то есть обслуживание вне США фактически отсутствует.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Карты, крипта через выплатные рельсы</t>
+          <t>Карты Visa/Mastercard/AmEx/Discover (e-commerce card-not-present, MOTO, virtual terminal, POS), ACH и eCheck, криптовалюта, интеграции с 20+ банками и сторонними платёжными шлюзами (Authorize.Net и др.).</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Sales fee 5% для валюты, 0% для пополнений и гифткарт, 10% для предметов/аккаунтов/бустинга; у части игр свои ставки</t>
+          <t>Собственная ставка не публикуется — только по запросу. Публикуются ориентиры high-risk рынка: processing rate 3.49%–3.95%, per-transaction fee ~$0.25, monthly account fee $10–$50 (плюс $25–$60 за PCI/gateway/statement), chargeback ~$20 за диспут (плюс $5–$15 за запрос документов), rolling reserve 5%–10% (для повышенного риска до 15%+). Модель ценообразования: tiered, а interchange-plus — при наличии обширной истории процессинга. Merchant Maverick: "No publicly disclosed pricing".</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>$0 — в статье о комиссиях: "PaymentCloud doesn't charge a startup fee"; на странице /high-risk/: "Competitive, low rates with no setup fees". Merchant Maverick перечисляет отсутствующие сборы: application fee, account setup fee, gateway setup fee, annual fee, monthly minimum, PCI compliance fee, statement fee.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Эскроу до завершения заказа</t>
+          <t>Публикуются типовые условия: rolling reserve 5%–10% оборота (для аккаунтов с повышенным риском 15%+), удержание 90–180 дней. Возможны также capped reserve (удержание до достижения порога) и up-front reserve — единовременный депозит, равный 1–3 месяцам ожидаемого оборота. Конкретный процент и срок для VPN-мерчанта — по запросу (не публикуется).</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Payoneer (мин. 10-50 USD, комиссия 4% + 2 USD), Skrill (мин. 10 USD, 5%), SEPA, BTC, USDC; вывод в рублях на карту РФ отсутствует</t>
+          <t>по запросу (не публикуется) — конкретный график выплат в открытых источниках не публикуется; в статье о комиссиях упоминаются "funding holds or payout delays" при скачке chargeback или резком росте объёма. Срок одобрения: "Full underwriting typically takes 2 to 5 business days; difficult files or complex verticals can run up to two weeks".</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Физлицо-продавец, регистрация; верификация для выплат через Payoneer/Skrill</t>
+          <t>Business license и Employer Identification Number (EIN), government-issued photo identification, подписанная merchant application, voided check или bank letter, 3 месяца банковских стейтментов (для новой компании допускаются 3 месяца личных), 3 месяца processing statements, подробное описание бизнеса и продуктов, работающий сайт с описанием продуктов и политик. Underwriting 2–5 рабочих дней. Самозанятый/физлицо вне США не подходит.</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да: есть отдельная вертикаль "Continuity &amp; Subscription", заявлены recurring billing, invoicing, automatic receipts. Dunning и токенизация/MIT зависят от выбранного шлюза (например, Authorize.Net с открытым API), а не от самого PaymentCloud.</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Выдача через страницу заказа</t>
+          <t>Платёжный шлюз + virtual terminal + hosted checkout, интеграции с корзинами и CRM, open API через Authorize.Net developer toolbox, embedded payments; webhooks зависят от конкретного шлюза. Telegram-бот без сайта: нет — работающий сайт с продуктами и политиками обязателен по требованиям андеррайтинга. Сложность интеграции: 3 — технически стандартный шлюз и большой каталог интеграций, но всё упирается в американское юрлицо и наличие сайта, а не в API..</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Фиксированный сбор 2 USD при чеке ~2,4 USD (199 руб) съедает почти всю выручку; нет выплат в РФ</t>
+          <t>Брокерская модель: финальное решение и условия (резерв, ставка, лимиты) определяет сторонний банк/процессор, PaymentCloud — посредник. Подтверждённый риск по резервам: отзыв на Trustpilot от 15.04.2026 — "After resolving chargeback issues, we requested a full reserve release... nearly a year of delays... The funds are still being held", и ответ компании подтверждает, что резерв оставлен. Нет публичных тарифов. Нет офшорных счетов. В январе 2024 PaymentCloud приобретён Electronic Merchant Services (EMS) — правила и аппетит к риску могут меняться. ПРАКТИКА: Со стартапами работает: FAQ допускает 3 месяца личных выписок вместо корпоративных, /high-risk/ заявляет "Over a 98% approval rate with multiple acquiring bank options". Trustpilot 4.3/5 "Excellent", много благодарностей менеджерам; но есть жалобы на затянутый онбординг (сентябрь 2026: "It has been 13 days of repetitive back and forth", при обещанных 2–3 днях) и на невозврат резерва. Подтверждения онбординга именно VPN-проекта нет.</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>https://support.eldorado.gg/en/articles/8409025-seller-fees, https://support.eldorado.gg/en/articles/8409026-seller-withdrawal-methods</t>
+          <t>https://paymentcloudinc.com/, https://paymentcloudinc.com/industries/, https://paymentcloudinc.com/industries/continuity-subscription/, https://paymentcloudinc.com/high-risk/, https://paymentcloudinc.com/faq/, https://paymentcloudinc.com/terms/, https://paymentcloudinc.com/blog/high-risk-merchant-account-fees/, https://paymentcloudinc.com/blog/merchant-account-reserve/, https://paymentcloudinc.com/blog/domestic-high-risk-merchant-account/, https://paymentcloudinc.com/?s=VPN, https://www.trustpilot.com/review/paymentcloudinc.com, https://www.merchantmaverick.com/reviews/paymentcloud-review/</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
@@ -6415,241 +6415,241 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>durango</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PlayerAuctions</t>
+          <t>Durango Merchant Services, LLC</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Международный маркетплейс игровых аккаунтов и валюты</t>
+          <t>High-risk эквайринг/PSP — фактически registered ISO и брокер для Fifth Third Bank, N.A. и других банков</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Не подтверждено: специализируется на игровых активах, категории цифровых подписок и VPN в правилах не описаны</t>
+          <t>серая зона (не подтверждено) — VPN нигде не упоминается: внутренний поиск (?s=VPN) выдаёт только две нерелевантные статьи о фроде, а в тематических материалах (Digital Downloads, SaaS, Annual Membership &amp; Subscription) слов VPN/proxy/anonymizer нет. Вертикали цифровых товаров и подписок принимаются, прямого запрета VPN нет, но и подтверждения нет — решение принимает банк-партнёр.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Международный</t>
+          <t>FAQ: "Do you provide services for non-USA clients? Yes! We can place merchants from virtually any country in the world. The only countries we cannot accept merchants from are countries known for heavy chargebacks, fraud, or on the OFAC list." НО в официальном списке запрещённых стран прямо указаны: "Russian Federation", "Belarus", "Ukraine", "Georgia", а также Albania, Croatia, Romania, Malaysia, Indonesia, India, Egypt и др. Фактически: российское юрлицо/резидент — нет; Грузия (рассматриваемая как будущая юрисдикция) — тоже нет; Армения, Кыргызстан, Казахстан, ОАЭ в списке отсутствуют, но проходят индивидуальный андеррайтинг. Минимум оборота: "$5,000 minimum for US accounts, $50,000 if you are located in the EU or United Kingdom". Заявлено покрытие 100+ стран.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Карты, PayPal, крипта</t>
+          <t>Visa, MasterCard, Discover, American Express, Diners Club, China UnionPay, JCB, Google Pay и Apple Pay; ACH/eCheck, криптопроцессинг, MOTO, POS/EMV и contactless, мультивалютный эквайринг.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Комиссия продавца публично не подтверждена</t>
+          <t>Опубликованы ориентиры. International merchant account: "Credit card Discount rates that range between 1.95% and 4.95%", "Authorization fees ranging from: $0.15 to $0.25", "Monthly installments: rates ranging from $15.00 per month to $60.00 per month". High-risk guide: "Expect discount rates in the 1.9 – 5 % range and per-item fees above the standard 10–15 ¢". Chargeback fee — по запросу (не публикуется). Минимальный оборот: $5,000/мес (US), $50,000/мес (EU/UK). Точная ставка только по запросу: "We work with several banks and processors worldwide, and pricing varies widely by country".</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>$0 — "Application Cost: 0 USD"; также "Free Application Processing" в разделе типовых условий.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Эскроу, длительный холд по спорам</t>
+          <t>Опубликовано: "Rolling reserve requirements that range from: 0% to 10%"; в high-risk guide — "Most high-risk agreements hold back 5 – 10 % of daily sales for 90–180 days"; также описаны capped reserve (обычно 5–15% до достижения порога, равного половине–полному месячному обороту) и upfront reserve (эквивалент 1–3 месяцев оборота деньгами или через letter of credit). Точный процент по конкретной заявке — по запросу.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>PayPal/банковский перевод; карта РФ не подтверждена</t>
+          <t>Опубликовано: "Funding: Typically 1–3 business days", "Settlement currencies: USD or local (your choice)", "Reserves (if high-risk): Rolling reserve with clear release schedules", отчётность batch-level, FX-логи. Сроки одобрения: пре-андеррайтинг от нескольких часов до 24 ч, полное одобрение 1–3 рабочих дня (сложные и международные кейсы 3–5 дней), в FAQ — 4–6 рабочих дней.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Верификация личности продавца, история аккаунта</t>
+          <t>Government-issued ID владельца, бизнес-регистрация (articles of incorporation/organization — "sole proprietors do not require any of the above"), EIN letter, voided business check или bank letter, 3–6 месяцев банковских стейтментов, предыдущие processing statements, письменный chargeback-mitigation plan (3-D Secure 2, Ethoca/Verifi, device fingerprinting), финансовая отчётность и/или proof of launch capital, 12-месячный прогноз выручки для нового бизнеса, и обязательный сайт: "Before you apply, make sure your site displays full pricing, currency, refund policy, privacy policy, and real contact details above the Pay button".</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да: recurring billing APIs и subscription tools, отдельные материалы по annual membership и subscription merchant account, разбор FTC click-to-cancel для подписок, 3-D Secure 2.0, токенизация и шифрование, chargeback alerts.</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Ручная выдача, API не подтверждён</t>
+          <t>Собственный Durango E-Commerce Gateway (Fluid Pay), 175+ интеграций с корзинами, pre-built plugins, hosted checkout pages, recurring billing API, mobile SDK для iOS/Android, batch file и virtual terminal, инструкции по интеграции шлюза. Telegram-бот без сайта: нет — сайт обязателен по требованиям андеррайтинга. Сложность интеграции: 3 — шлюз, плагины и API есть, но интеграция упирается не в технику, а в обязательный сайт, андеррайтинг и минимальный оборот..</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Нецелевой канал для VPN, отсутствие выплат в РФ, высокий порог входа</t>
+          <t>Trustpilot 1.7/5 при 36 отзывах ("Bad"), включая прямые отказы малым оборотам: "They decided not to accept my business because they said I don't make enough volume or money" (07.09.2022) и инцидент с хамством и сбросом звонка (03.06.2026). Жёсткие минимумы оборота ($5,000/мес для US, $50,000/мес для EU/UK) отсекают проект на ранней стадии (199–1590 ₽ за подписку). РФ, Беларусь, Украина и Грузия — в запрещённом списке. Модель ISO/брокера: реальные условия задаёт банк. ПРАКТИКА: Со стартапами формально работает: "Can my startup/ brand new business be approved? The short answer is YES!" и "Average Approval Time: 3 days". Но отзывы фиксируют отказы небольшим оборотам, а минимум $5,000/мес (и $50,000/мес для ЕС/UK) практически исключает Kometa на текущем этапе. Отдельно: список запрещённых стран выглядит устаревшим, но именно он опубликован на сайте.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>https://www.playerauctions.com/guide/other/mmorpg/how-to-sell-game-accounts/</t>
+          <t>https://durangomerchantservices.com/, https://durangomerchantservices.com/frequently-asked-questions-for-high-risk-credit-card-processing/, https://durangomerchantservices.com/high-risk-merchant-account/, https://durangomerchantservices.com/international-merchant-account/, https://durangomerchantservices.com/list-of-prohibited-countries-for-international-merchant-accounts/, https://durangomerchantservices.com/reserves-why-many-high-risk-merchant-accounts-require-them/, https://durangomerchantservices.com/digital-downloads-merchant-account/, https://durangomerchantservices.com/subscription-billing-streamlining-recurring-payments/, https://durangomerchantservices.com/?s=VPN, https://www.trustpilot.com/review/durangomerchantservices.com</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>instabill</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Kwork</t>
+          <t>Instabill (Instabill Corporation, США / Instabill Limited, Мальта)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Фриланс-маркетплейс услуг</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>ПРЯМОЙ ЗАПРЕТ: п.1.2.5 Неподдерживаемых услуг — запрещены услуги, связанные с обходом блокировок запрещённых сервисов, в т.ч. использование VPN-сервисов</t>
+          <t>High-risk эквайринг/PSP — фактически брокер/ISO, подбирающий банк-эквайер (domestic, international, offshore)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>серая зона (не подтверждено) — VPN не упоминается ни в списке поддерживаемых индустрий, ни в блоге, ни во внутреннем поиске по сайту ("Sorry, but nothing matched your search terms" на ?s=VPN). Есть смежные вертикали Multimedia Streaming, Membership Sites, Continuity (free trials), Tech Support, Mobile Apps, но VPN среди них нет и в запрещённом списке его тоже нет — то есть прямого запрета не опубликовано, подтверждения приёма тоже.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Международный/офшорный фокус: банки-партнёры принимают более 160 валют, пейауты в 18 основных валютах, платёжный шлюз работает "From the United States, UK, and Australia to Hong Kong, India and Panama". По юрлицу требуется Incorporation/Registration Certificate; для ЕС Instabill прямо предупреждает, что мерчанту нужно зарегистрировать компанию в стране/регионе банка-эквайера с физическим присутствием (директор, офисный телефон, счёт в банке ЕС). Российский резидент/юрлицо: подтверждения приёма нет — РФ присутствует лишь как пункт в выпадающем списке стран формы, что не является политикой; с учётом санкций и требований банков рассчитывать на РФ нельзя.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Карты РФ, СБП, кошелёк Kwork</t>
+          <t>Visa, MasterCard, AmericanExpress, Discover, UnionPay, JCB, UK Maestro, Diners Club; ACH/eCheck (NACHA), Bitcoin, epin; POS/EMV и contactless; MOTO и virtual terminal.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Комиссия площадки с заказа (точная ставка не проверялась)</t>
+          <t>по запросу (не публикуется). Сайт прямо пишет: "every merchant is different, and an exact dollar amount cannot be determined until we can learn about your business"; перечислены только категории (Merchant Account Fee, Transaction Fee, Discount Rate, Merchant Account Registration Fee, Monthly Statement Fee, Chargeback Fee, Refund Fee). Сторонний обзор Merchant Alternatives (данные старые, требуют перепроверки) указывает swiped/keyed 1.00%–4.99%+, Monthly Fee — Undisclosed, Monthly Minimum — Undisclosed, PCI fee — Undisclosed.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>$0 — на главной в списке преимуществ: "No Merchant Account Set Up Fees"; есть отдельная статья "We Don't Charge Merchant Account Application Fees, and Neither Should You".</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Эскроу: оплата резервируется до сдачи заказа</t>
+          <t>Опубликовано прямо: "The reserve is a fixed percentage amount based on your weekly sales volume, usually between 5-10%. Your acquiring bank will place the money into a rolling reserve fund, and six months later, you'll receive a payout of these funds." С оговоркой: "the rolling reserve fund only applies to high risk, international and third party merchant accounts" — большинство банков США резерв не требуют, многие офшорные требуют.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Вывод на карту РФ/кошелёк</t>
+          <t>Опубликовано: "Daily, three days in arrears; Weekly, one week in arrears; Weekly, two weeks in arrears" — график определяет банк-эквайер. Выплаты wire transfer на выбранный банк, доступны в 18 основных валютах. Срок одобрения: "you may be able to start accepting payments in as little as 5-7 business days".</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Физлицо; верификация для вывода</t>
+          <t>Application form, Valid Passport/Photo ID бенефициаров и подписанта, Personal Utility Bill не старше 3 месяцев, Personal &amp; Company Bank Statements не старше 3 месяцев, Incorporation/Registration Certificate, Articles of Association или Memorandum of Association, Register of Shareholder(s) &amp; Director(s). При обороте свыше USD 100k в месяц все KYC-документы должны быть нотариально заверены. Расчёты только на бизнес-счёт: "Settlement proceeds are only wired to business bank account, no personal account". Сайт обязателен — "our acquiring banking partners... will link your website with its secure payment gateway". Самозанятый/физлицо без зарегистрированной компании по этой схеме не проходит.</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Нет (только разовые кворки)</t>
+          <t>Да, заявлены: Continuity (free trials), Membership Sites, Recurring/Subscription Billing, Dunning Management, Online Invoicing, Contingency Billing (по данным стороннего каталога Merchant Alternatives; на самом сайте подтверждены только Continuity и Membership Sites).</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Автовыдача не предусмотрена: услуга оказывается вручную через чат</t>
+          <t>PCI-совместимый платёжный шлюз (US, UK, Australia, Hong Kong, India, Panama), бесплатный virtual terminal для MOTO, привязка сайта к шлюзу банка, shopping cart options, альтернативные способы оплаты. Telegram-бот без сайта: нет — связка идёт через сайт и шлюз банка. Сложность интеграции: 3 — стандартный шлюз и virtual terminal, но интеграция идёт через шлюз конкретного банка-партнёра, единого API нет, а сайт обязателен..</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Прямой бан услуги и аккаунта за VPN; реклама обхода блокировок = нарушение ФЗ о рекламе</t>
+          <t>Публичный контент сайта устарел: последний пост блога — 15.01.2021, page-sitemap.xml имеет lastmod 21.10.2020, в текстах "more than 15 years experience" и "For more than a decade", при этом копирайт в футере автоматически показывает 2026 — то есть дата на сайте не доказывает актуальность. Trustpilot 2.6/5 "Poor" (всего 4 отзыва), в том числе от 01.02.2026: "Scam mails. They want me to pay 4500€". Жалобы на отказ после сбора KYC-документов (11.03.2025, adult/dating: "after 2 weeks of waiting... they informed me that they are unable to assist with a merchant account as the risk is too high for the bank") и на отказ стартапу без истории процессинга (19.11.2024). Merchant Alternatives фиксирует 25+ жалоб и отсутствие публичных тарифов. Сам сайт признаёт: "Instabill declines about 15 percent of the merchant account inquiries". ПРАКТИКА: Смешанно. Формально есть статья "We Do Startups! Need a Merchant Account" и приём стартапов с bank reference letter, но отзыв от ноября 2024 описывает прямой отказ проекту без processing history, а отзыв от марта 2025 — отказ после полного сбора документов. Для нового VPN-проекта без истории платежей шансы невысоки и без подачи заявки непроверяемы.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>https://kwork.ru/prohibited_services</t>
+          <t>https://instabill.com/, https://instabill.com/ecommerce-industries/, https://instabill.com/merchant-services/fees/, https://instabill.com/merchant-services/merchant-accounts/high-risk/, https://instabill.com/merchant-services/merchant-accounts/offshore/, https://instabill.com/kyc-compliance-documents-we-require/, https://instabill.com/about-us/company/, https://instabill.com/articles/why-we-decline-merchant-accounts/, https://instabill.com/news/, https://instabill.com/?s=VPN, https://www.trustpilot.com/review/instabill.com, https://merchantalternatives.com/reviews/instabill/</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>emerchantbroker</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Avito</t>
+          <t>eMerchantBroker (EMB), Emerchantbroker, LLC</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Классифайд, с 30.04.2026 есть онлайн-оплата цифровых товаров (Авито Доставка)</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>ПРЯМОЙ ЗАПРЕТ по заявлению пресс-службы (2022): Запрещено размещение объявлений по установке сервисов для обхода блокировок регуляторов и обеспечению доступа к запрещённым на территории РФ ресурсам. Подобные объявления при обнаружении оперативно блокируются. Отдельной категории для VPN нет</t>
+          <t>High-risk эквайринг/PSP — фактически брокер-ISO, а не эквайер и не MoR</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>серая зона. VPN нигде явно не упомянут: ни в списке отраслей (online gaming, CBD, adult, e-cigarettes, nutraceuticals, collections, tech support, software &amp; e-books, VOIP/telecom), ни в Terms and Conditions (раздел Prohibited uses не содержит списка запрещённых индустрий — только общие формулировки про unlawful purpose и circumvention of security features). EMB позиционируется как высокорисковый брокер, который «берет» hard-to-place вертикали и цифровые товары, поэтому VPN теоретически может быть размещён через их банк-партнёр, но подтверждения нет: решение принимает sponsor bank (BMO Harris) в рамках underwriting.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Юрлицо US (Thousand Oaks, CA) + офис в UK (London). Программа International перечисляет ~35 стран: Австралия, Австрия, Бельгия, Болгария, Хорватия, Кипр, Чехия, Дания, Эстония, Финляндия, Франция, Германия, Гибралтар, Греция, Гонконг, Венгрия, Исландия, Ирландия, Италия, Латвия, Лихтенштейн, Литва, Люксембург, Мальта, Нидерланды, Норвегия, Польша, Португалия, Румыния, Сингапур, Словакия, Словения, Испания, Швеция, UK. России в списке нет; Казахстана, Армении, Грузии, Кыргызстана, ОАЭ — тоже. Пакет документов требует SSN или EIN, банковское письмо/voided check и 3 месяца банковских выписок — то есть практически US-резидент/юрлицо. Вывод: для российского физлица/самозанятого и для российской компании — не подтверждено (де-факто нет); для юрлица в EAЭС/ОАЭ — не подтверждено, нужно спрашивать.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Карты РФ, СБП, Авито Доставка (деньги продавцу только после подтверждения получения)</t>
+          <t>Visa, Mastercard, American Express, Discover; ACH/e-check (включая recurring), бумажные чеки и check-by-web; криптоприём (отдельная страница Accept cryptocurrency payments); собственный шлюз Bankful.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>7% за продажу цифрового продукта на тарифе с оплатой за успешную сделку</t>
+          <t>по запросу (не публикуется). На сайте нет ни ставок, ни тарифных планов: «Pricing varies depending on the merchant's industry, past credit card processing history...». Сторонний обзор CardFellow фиксирует, что EMB на своём сайте заявляет «high-risk merchant account rates may start as low as 2.99%», но без указания, к каким типам бизнеса и транзакций это относится. Chargeback fee, monthly minimum, PCI-плата и gateway-плата — не публикуются.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>0 руб; нужен тариф с оплатой за успешную сделку</t>
+          <t>$0 заявлено: «$0 application fee, $0 start up fee» и «No hidden fees... without the hassle of upfront costs or hidden set up fees». При этом отдельные платы (PCI, statement, gateway) на сайте не раскрыты.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Эскроу: продавец обязан отправить ключ в течение 24 часов, иначе заказ отменяется; деньги приходят после подтверждения покупателем</t>
+          <t>по запросу (не публикуется). Ни размер, ни срок rolling reserve на сайте не указаны; в кейсе BBB-жалобы упоминается удержание $2000 (см. practice).</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Вывод на карту РФ по графику выплат Авито</t>
+          <t>не подтверждено (сроки зачисления по картам не публикуются). Публично указано только: ACH-переводы — «electronic transfer of funds occurs within 7 business days» (по данным CardFellow), и общая заявка «Quick business funding in 5-7 days» (это про business funding/advance, не про settlements).</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Физлицо может размещать объявления; для регулярной коммерческой деятельности нужен статус ИП/самозанятого (не подтверждено для этой категории)</t>
+          <t>Для заявки: government-issued ID (паспорт/права), bank letter или pre-printed voided check, «A secure, working website», 3 месяца банковских выписок, 3 месяца processing statements (если есть), SSN или EIN, chargeback ratio ниже 2%. Отдельно заявлено, что работают с мерчантами без processing history, с плохим кредитом и с ранее закрытыми аккаунтами. Наличие работающего сайта обязательно — Telegram-бот без сайта не подойдёт.</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>не подтверждено. Публично заявлена поддержка subscriptions/medium-risk вертикали и ACH «one-time or recurring transactions» (CardFellow), но описания dunning, free trials, tokenisation/MIT и card-on-file на сайте нет.</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Нет автовыдачи: ключ отправляется вручную в чат в течение 24 часов; API не предусмотрен</t>
+          <t>Собственный шлюз Bankful + hosted checkout/виртуальный терминал; интеграции с Shopify, Wix, WooCommerce, BigCommerce, OpenCart, Shift4Shop, QuickBooks; Apple Pay. Публичной открытой API-документации на сайте EMB нет (только страница Payment gateways). Telegram-бот без сайта: нет — обязателен «secure, working website». Сложность интеграции: 4 — нет публичной документации API и тестового контура; интеграция идёт через сторонний шлюз Bankful и требует полноценного сайта с чекаутом, плюс ручной онбординг под hard-to-place вертикаль..</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Блокировка объявлений за VPN (подтверждено практикой 2022 г.), мисс-категория, ручная выдача, споры</t>
+          <t>Модель брокера/ISO: реальное решение об approval, reserve и удержаниях принимает банк-спонсор (BMO Harris) и процессор, а не EMB. Условия резервов и платы не публикуются. Известен кейс жалобы в BBB о фальсификации данных по аккаунту и удержании ~$2000 (со ссылкой на BBB в обзоре CardFellow). CardFellow также отмечает агрессивный sales-стиль: сайт даёт минимум информации и подталкивает к немедленной заявке. Для VPN + российского происхождения платежей добавляется санкционный/банковский риск — не подтверждено. ПРАКТИКА: Заявляют approval 99% (для digital-вертикали — 95%) и онбординг 24–48 часов; работают с бизнесами без processing history, плохим кредитом и с потерянными ранее merchant account. BBB-аккредитация с 2012, рейтинг A+; по данным CardFellow за 3 года всего 2 жалобы в BBB, одна — про удержанные $2000 (EMB вернул деньги, но отказался продолжать работу). Массовых публичных жалоб на заморозку средств не видно.</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>https://www.dp.ru/a/2022/03/17/Avito_blokiruet_objavle, https://78.ru/news/2026-04-30/na-avito-poyavilas-funkciya-onlainoplati-podpisok-i-cifrovih-klyuchei, https://foxreload.com/en/library/marketplaces/avito-digital-section</t>
+          <t>https://emerchantbroker.com/, https://emerchantbroker.com/high-risk-merchant-accounts/, https://emerchantbroker.com/ebooks-software-merchant-accounts/, https://emerchantbroker.com/international/, https://emerchantbroker.com/terms-and-conditions/, https://www.cardfellow.com/credit-card-processors/emerchant-broker</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
@@ -6661,77 +6661,77 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>smbglobal</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Ozon (цифровые товары)</t>
+          <t>SMB Global (SMB Global Payments LLC)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Ритейл-маркетплейс, отдельные категории цифровых товаров</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: VPN прямо не запрещён в опубликованном договоре, но модерация цифровых товаров строгая и требует подтверждения источника товара</t>
+          <t>High-risk эквайринг/PSP — фактически посредник (intermediary) между мерчантом и банками, не прямой процессор</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>серая зона. VPN не упомянут ни в списке отраслей на сайте (Dropshipping, Telemedicine, Firearms &amp; Tobacco, Nutraceuticals, Online Gaming, Adult &amp; Dating, Digital Marketing, Coaching Products, MLM &amp; Direct Sales, eCommerce, Travel &amp; Tourism), ни в описаниях решений. Публичного Acceptable Use / списка запрещённых индустрий у них нет вовсе; при этом компания заявляет, что «actively place accounts» для hard-to-place индустрий и работает через 20+ банков, поэтому цифровой сервис вроде VPN может быть рассмотрен — но подтверждения нет.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Компания US (South Jordan, Utah), основана в 2016; ориентирована на мерчантов, продающих в США, но имеет отдельное направление International &amp; Offshore: «The SMB Global Network uses both international and offshore banking relationships to help entrepreneurs from around the world secure a credit card processing solution». Для offshore-аккаунта нужно минимум $50 000/мес оборота или сильная финансовая история. России и постсоветских юрисдикций в публичных материалах нет; приём российского резидента/российской компании — не подтверждено (высокий риск отказа).</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Карты, СБП, рассрочка</t>
+          <t>Карты Visa/Mastercard/Amex/Discover через банки-партнёры, ACH и e-check, мультивалютный процессинг с dynamic currency conversion на offshore-аккаунтах; шлюзы NMI, Authorize.net, USA ePay.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Комиссия зависит от категории, плюс эквайринг и продвижение; точные ставки — в тарифах Ozon Seller</t>
+          <t>по запросу (не публикуется). Ни ставок, ни тарифной сетки, ни примеров на сайте нет — только «Transparent pricing... No surprise reserves» без цифр; сторонние обзоры (GuidingDecisions, 2026; Merchant Maverick, 2024) подтверждают полное отсутствие раскрытия цен. Ориентиры по рынку, а не по SMB Global: high-risk типично 2,5–4% эффективной ставки — это оценка обозревателя, не публикация компании.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>по запросу (не публикуется). По данным GuidingDecisions (март 2026), SMB Global заявляет отсутствие application fee, cancellation fee и фиксированного срока контракта; Merchant Maverick (2024) фиксирует «Account Setup Fee — Not disclosed». В текущей версии сайта (Webflow, 2026) этих условий в явном виде нет.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Выплаты по графику Ozon после закрытия периода</t>
+          <t>противоречие, требует письменного подтверждения. На главной странице заявлено: «No Rolling Reserves — 100% of your funds. Available immediately.» Однако GuidingDecisions предупреждает, что реальный merchant agreement заключается с банком-партнёром SMB Global, и если банк потребует rolling reserve (типичный отраслевой диапазон 5–10% на 180 дней), то сроки возврата определяет банк, а не SMB Global. Размер и срок резерва самой SMB Global не публикуются.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Вывод только на реквизиты ИП/юрлица</t>
+          <t>не подтверждено (график settlements/funding не публикуется). Компания заявляет «Same Day Approvals. Get approved and processing within 24 hours» — это про approval, а не про выплаты; в отзывах клиентов упоминается «unlimited processing» без деталей.</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Нужен статус ИП или юридического лица, договор и документы на источник товара</t>
+          <t>Публичного перечня требований нет (не подтверждено). Известно из сторонних источников: аккредитация/андеррайтинг идёт через банк-партнёр, в ToS компании предусмотрен запрос в Experian по FCRA (GuidingDecisions, 2026), для offshore — минимум $50 000/мес оборота либо сильная финансовая история. Наличие юрлица, VAT/GST, требований к сайту компания не публикует.</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>не подтверждено как продукт с описанием. Косвенно: шлюзы NMI/Authorize.net поддерживают recurring billing/MIT, ACH-платформа — recurring and automated billing, а система chargeback-аналитики умеет разбивать спорные транзакции по «subscription cycle» (описания SMB Global/Shark Processing). Публичного описания dunning и free trials нет.</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Отгрузка цифрового кода/электронного товара</t>
+          <t>Payment API, Mobile SDK, EMV SDK, hosted checkout (Collect Checkout), 175+ интеграций с корзинами, шлюзы NMI / Authorize.net / USA ePay. Документация слабая: интеграционный портал ведёт на общие ресурсы NMI, а не на гайды SMB Global (GuidingDecisions, 2026). Требование сайта для онбординга не публикуется, поэтому приемлемость Telegram-бота без сайта — не подтверждено. Сложность интеграции: 4 — отдельных фирменных документов и sandbox нет, интеграция сводится к сторонним шлюзам, а политика (резервы, лимиты, требования к сайту) полностью определяется банком-партнёром; для цифрового продукта без сайта ясности нет..</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Недоступен физлицу и 15-летнему основателю; требования к источнику товара; блокировки региональных кодов</t>
+          <t>Не процессор: договор с банком-партнёром, и именно банк устанавливает reserve, holds и termination — маркетинговое «no rolling reserves» не гарантирует условий банка. Полная непрозрачность цен до подачи заявки. Согласие на запрос в Experian при подаче (риск hard pull при параллельных заявках). Мало проверяемых публичных отзывов, нет профиля BBB. Для российского продавца добавляется геополитический риск и отсутствие какой-либо публичной политики по РФ. ПРАКТИКА: Компания небольшая, основана в 2016, команда маленькая; не аккредитована BBB и не имеет там профиля, жалоб на Ripoff Report не найдено (Merchant Maverick, 2024). Отзывы клиентов на сайте и в обзорах хвалят скорость одобрения, отсутствие резервов и «unlimited processing», но объём независимых отзывов невелик. GuidingDecisions даёт 6,5/10 именно за непрозрачность цен. Публичных жалоб на заморозку средств не найдено.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>https://seller-edu.ozon.ru/libra/contract-for-sellers/contract-digital-goods/digital-product-seller-agreement, https://foxreload.com/ru/library/marketplaces/sell-digital-goods-ozon</t>
+          <t>https://www.smbglobalpayments.com/, https://www.smbglobalpayments.com/industries, https://www.smbglobalpayments.com/apply-now, https://www.guidingdecisions.com/smb-global-review-high-risk-offshore-processing-for-hard-to-place-merchants, https://www.merchantmaverick.com/reviews/smb-global-review/, https://sharkprocessing.com/smb-global-overview/, https://smbglobal.com/</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -6743,323 +6743,323 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>soarpayments</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Wildberries (цифровые товары)</t>
+          <t>Soar Payments / SoarPay (Soar Payments LLC, DBA AltruPay LLC)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Ритейл-маркетплейс</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: отдельная площадка WB Digital закрыта, правила переноса цифровых товаров на основную платформу по VPN не раскрыты</t>
+          <t>High-risk эквайринг/PSP — фактически брокер-ISO, не эквайер и не MoR</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>серая зона с практическим «нет» для проекта. VPN нигде не упомянут: ни в списке из 50+ индустрий (SaaS, digital streaming, subscription/continuity, credit repair, nutraceuticals, firearms и т.д.), ни в списке запрещённых. Но у Soar есть жёсткие ограничения по мерчанту: сервис только для US-бизнесов с SSN владельца, а «offshore merchants and businesses headquartered outside the United States» прямо запрещены. То есть сама VPN-вертикаль не запрещена, но российский продавец (физлицо/самозанятый/РФ-юрлицо) не может быть онборднут.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>Только США. Дословно: “SoarPay only provides merchant accounts for US-based businesses whose owners hold a valid US Social Security Number. We cannot serve any business headquartered or primarily operating outside the United States, and we cannot process applications where the business owner does not have a valid SSN and US-issued government photo ID. An EIN alone is not sufficient.” Дополнительно в списке запрещённых: “Offshore merchants and businesses headquartered outside the United States”. Российский резидент/юрлицо — нет. Юрлицо в Казахстане/Армении/Грузии/Кыргызстане/ОАЭ — тоже нет, пока бизнес не US-based.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Карты, СБП, WB Кошелёк</t>
+          <t>Visa, Mastercard и ATM debit у всех; Amex/Discover — для квалифицированных мерчантов; ACH/e-check (settlement 1–3 рабочих дня); шлюзы Authorize.net, NMI, FluidPay, AcceptBlue.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Комиссия зависит от категории (не подтверждено для цифры)</t>
+          <t>по запросу (не публикуется). Модель — interchange-plus («Your processing fee is the interchange rate set by the card networks plus a fixed markup from SoarPay»), но конкретные ставки только в персональном письменном предложении. Отдельно не публикуются: chargeback fee, monthly minimum, PCI-плата, ACH-ставки. Сторонний обзор GuidingDecisions (март 2026) указывает типичные ориентиры: gateway от $15/мес, tiered 2,5–4,0% для mid/high-risk, и что ETF на mid/high-risk контрактах высокий.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>заявлено отсутствие: по данным GuidingDecisions (2026) — «Soar doesn't charge application or setup fees». На собственном сайте отдельной страницы с ценами нет, прямая формулировка про $0 setup в публичных материалах SoarPay не найдена — считать «0 (по стороннему источнику) / на сайте не опубликовано».</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Выплаты по графику WB</t>
+          <t>5–10% от объёма процессинга, пока аккаунт «не созреет». Дословно из их FAQ: “A reserve is a cash deposit held by the acquiring bank in a non-interest bearing escrow account as security against potential chargebacks. Typically 5 to 10% of your processing volume is held while your account matures.” Пересмотр — обычно каждые 60–90 дней. Не для всех: «Not every merchant requires one». Плюс заявлено, что у Soar «rolling reserves have predetermined caps» и срок релиза короче рынка (GuidingDecisions, 2026). Важно: превышение одобренного месячного лимита удерживается минимум 90 дней (“Any volume processed above your approved limit will typically be held by the acquiring bank for a minimum of 90 days”).</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Вывод на расчётный счёт ИП/юрлица</t>
+          <t>48–72 часа с момента закрытия батча: “SoarPay typically processes settlements within 48 to 72 hours of a transaction batch closing.” ACH-сеттлменты — 1–3 рабочих дня. Точный график фиксируется в merchant agreement.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>ИП или юрлицо</t>
+          <t>Только US: бизнес в США + владелец с действующим SSN и US-issued photo ID (EIN недостаточен); обязателен бизнес-счёт для LLC/корпорации (личный счёт нельзя); документы: 3 месяца банковских выписок (для стартапов — личные выписки владельца), voided business check или bank letter, фото-ID, 3 месяца processing statements (если есть), proof of inventory для товарных бизнесов, sample customer contract/terms of sale, FFL для оружия, ARC/surety bond для travel. Кредитная проверка обязательна и не может быть отменена (hard или soft pull — зависит от банка). Сайт: “If you sell online, you need a functioning website with products and pricing” — то есть Telegram-бот без сайта не подойдёт. Запрещены: adult, cannabis/THC, peptides/SARMs/research chemicals, forex и нерегулируемые фининструменты, kratom, misleading tech support, offshore/не-US бизнесы, онлайн-казино и нелицензированный гэмблинг, payday loans, MATCH-listed мерчанты, hate speech.</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>да. Есть отдельная вертикаль Continuity/Subscription Products; recurring billing поддерживается шлюзами (Authorize.net/NMI), ACH рекомендован для subscription billing. Free trials — серая зона: “Free trials are in a gray area no matter what type of product or service your business is offering... if you're selling a nutraceutical product, free trials are simply not accepted by any banks Soar Payments currently works with”, для остальных — case by case. Auto-opt-in («auto opt-in as part of their sales funnel») не поддерживается вообще. Про dunning/retries публичного описания нет.</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Цифровые коды на основной платформе</t>
+          <t>Merchant account + сторонние шлюзы: Authorize.net (нативный для WooCommerce, Shopify, BigCommerce, Magento), NMI (3-D Secure 2.0, multi-processor routing), FluidPay, AcceptBlue; virtual terminal, recurring billing, ACH, Shopify-гайд (через Authorize.net alternative payment provider). Своего API нет — интеграция идёт через шлюз партнёра. Storefront в Telegram без сайта: нет (нужен работающий сайт с ценами). Сложность интеграции: 4 — технически подписки и шлюзы стандартные, но требуется US-юрлицо + SSN владельца + бизнес-счёт + сайт с ценами, а также обязательный кредитный чек; для Telegram-бота с российским основателем это блокирующие условия..</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>WB Digital закрыт 01.12.2025, заявки на вывод после 27.12.2025 обрабатывались только с 12.01.2026 — риск заморозки средств на переходном периоде</t>
+          <t>Брокер: «Soar isn't your processor. They're the broker who places you with an acquiring bank, and that bank is the entity that actually holds your funds, sets your reserve requirements» (GuidingDecisions, 2026) — при флаге банк может удерживать средства, брокер не может это отменить. Отсутствие публичных цен, multi-year контракты с дорогим ETF для mid/high-risk. Есть негативные отзывы (Google/BBB-агрегация Birdeye, 4–5 лет назад) с обвинениями в угрозах отключения аккаунта и невозврате CDRN/Ethoca alert — единичные и непроверенные, но фиксируют паттерн риска. Противоречие в источниках: FAQ запрещает MATCH-listed мерчантов, а GuidingDecisions пишет, что Soar помогает MATCH-listed бизнесам сниматься из списка. ПРАКТИКА: Со стартапами работает: «new businesses and startups can be approved... provide the owner's personal bank statements in place of business bank statements»; плохой кредит допустим, но при отсутствии кредитной истории, недавнем банкротстве или скоре ниже 600 одобрение маловероятно. Средний рейтинг по агрегатору Birdeye — 4,3 из 5 при 41 отзыве (Google 27, BBB 7, Birdeye 5, Facebook 2), внутри есть резко негативные отзывы о попытках закрыть аккаунт. Публичных массовых жалоб на заморозку средств не найдено.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>https://oborot.ru/news/pochemu-wildberries-zakryvaet-svoyu-platformu-cifrovyh-tovarov-i-chto-dalshe-i259021.html</t>
+          <t>https://www.soarpay.com/, https://www.soarpay.com/high-risk-merchant-accounts/, https://www.soarpay.com/faq/, https://www.soarpay.com/terms/, https://www.soarpay.com/industry/continuity-subscription-boxes/, https://www.guidingdecisions.com/soar-payments-review-high-risk-credit-card-processing-for-hard-to-place-merchants, https://reviews.birdeye.com/soar-payments-159470028283084</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>maverick</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>WATA Telegram-stars</t>
+          <t>Maverick Payments (Maverick Bankcard, Inc.)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Легальный оптовый поставщик звёзд без депозита</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Разрешено: продукт WATA для продажи Telegram-звёзд с встроенным эквайрингом; WATA заявляет отказ только от гемблинга, беттинга и адалта</t>
+          <t>High-risk эквайринг/PSP — процессинговая платформа с собственным шлюзом и сетью банков-партнёров; продажи в основном через ISO/ISV-партнёров, не MoR</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>серая зона. VPN/прокси нигде не упомянут. Раздел Specialty markets / High-risk перечисляет вертикали: Travel &amp; leisure, Health products, Education &amp; coaching, Dating &amp; social networks, E-commerce &amp; subscriptions, Tobacco &amp; vape, Financial &amp; lending, Firearms &amp; ammo, Gaming &amp; gambling — плюс, по сторонним обзорам, vapes/e-cig, nutraceuticals, direct response, MLM, lenders. Цифровые сервисы и подписки заявлены («Streamlined solutions for e-commerce and subscription models»), но VPN отдельно не назван и публичного Acceptable Use со списком запрещённых индустрий нет (Terms of use на сайте — только условия использования сайта).</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Клиенты из РФ, международный бизнес</t>
+          <t>Компания US (Calabasas, CA), работает с 2000 года. Публичного списка стран нет; на сайте есть только дисклеймер Global Availability («Maverick makes no representation that materials, products or services depicted in the site are appropriate or available in all locations»), а онбординг идёт через партнёров (ISOs/agents/ISVs) и demo-заявку. России, Казахстана, Армении, Грузии, Кыргызстана, ОАЭ в публичных материалах нет. Приём российского резидента/юрлица — не подтверждено (практически маловероятно, учитывая US-банки-партнёры).</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Карты РФ (МИР), зарубежные карты, СБП QR</t>
+          <t>Visa, Mastercard, Amex, Discover, debit/EBT, ACH (in-house), digital wallets, gift &amp; loyalty cards, POS/терминалы, surcharging/cash discount.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Доход мерчанта — разница между установленной им ценой и закупкой у WATA; отдельная комиссия за конвертацию не взимается (по заявлению WATA)</t>
+          <t>по запросу (не публикуется). Своей тарифной страницы нет: «As is common for the industry, Maverick Payments does not list its rates for high-risk merchant accounts on its website. You must contact them for a quote» (Shark Processing). CardFellow: «Maverick doesn't publish pricing... Some fees that may apply include the transaction fee, PIN debit fee, AVS fee, statement fee, and internet gateway fee.» Ставки, chargeback fee, monthly minimum — не публикуются.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Депозит не нужен (WATA держит его за мерчанта)</t>
+          <t>по запросу (не публикуется)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Заморозки средств нет по заявлению WATA; курсовой риск берёт на себя WATA</t>
+          <t>по запросу (не публикуется). В публичном дашборде-описании фигурирует отчётность по reserves, что подтверждает их наличие как механики, но размер/срок не раскрыты. Отдельно: жалоба на Ripoff Report (22.11.2024) утверждает удержание резерва более $60 000 при chargebacks менее $3 000 и трёхмесячную задержку возврата — это непубличное, непроверенное утверждение одной стороны.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Выплаты в рублях и в цифровой валюте через модуль автовыплат</t>
+          <t>same-day или next-day funding (Shark Processing, 2021); на странице для разработчиков упоминается real-time reporting по batches, chargebacks и reserves. Точный график выплат на публичных страницах 2025–2026 не раскрыт.</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Мерчант WATA; требования к статусу не раскрыты публично — уточнять при подключении</t>
+          <t>Публично не раскрыто (не подтверждено): ни перечня документов, ни требований к юрлицу/индивидуальному предпринимательству, ни требований к сайту. Косвенно: онбординг идёт через партнёров (ISOs/agents) и Onboarding API, что подразумевает стандартный US-KYB (EIN, банковский счёт, owner ID). Приемлемость Telegram-бота без сайта — не подтверждено.</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>да. Recurring billing и payment plans, account updater для обновления карт, tokenisation, электронное инвойсирование, batch upload, hosted forms, fraud/chargeback-инструменты (Shark Processing; CardFellow). Публичного описания dunning/retry-логики и free trials нет.</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Ускоренная интеграция через API, заявленный запуск за 1 час</t>
+          <t>Собственный (proprietary) шлюз для карт и ACH, direct API, hosted forms, virtual terminal, Connect для сертифицированных решений, Onboarding API, white-label dashboard, документация для разработчиков на developers.maverickpayments.com, sandbox и API-документация (Shark Processing). Интеграции с CRM и корзинами; большой набор POS/Poynt/Vital. Telegram-бот как витрина: технически оплата возможна через API/hosted form, но политика по storefront без сайта не публикуется — не подтверждено. Сложность интеграции: 3 — есть нормальная API/developer-инфраструктура и hosted forms, но нет публичных тарифов и правил андеррайтинга, онбординг только через demo/партнёра, а VPN и бот-витрина не подтверждены..</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Зависимость от одного контрагента; условия подключения и ставки не опубликованы публично</t>
+          <t>Непрозрачные цены и условия резервов; продажи через ISO/агентов (риск некачественного раскрытия условий). Жалобы в Ripoff Report (в т.ч. от 22.11.2024): «deceptive fees, unjustified reserve holds, and poor customer service», удержание $60k+ резерва; CardFellow фиксирует жалобы на сложности с высвобождением средств, заморозку аккаунтов и «deceptive practices» (4 жалобы на то время). Часть Google-отзывов негативная; компания отрицала как минимум один такой кейс. Для российского продавца — дополнительный риск отсутствия публичной политики по не-US юрисдикциям. ПРАКТИКА: Работает с 2000 года, по собственным заявлениям обслужила десятки тысяч мерчантов (CardFellow упоминает заявку «over 80,000 businesses»); андеррайтинг, комплаенс и risk-менеджмент делает in-house. Берёт высокорисковые вертикали, включая те, что банки не берут. При этом независимых отзывов мало, а негативные касаются именно удержаний и релиза средств, поэтому «без истории процессинга и без рисков» — не подтверждено.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://wata.pro/prodazhatelegramzvezd, https://wata.pro/faq</t>
+          <t>https://maverickpayments.com/, https://maverickpayments.com/high-risk, https://maverickpayments.com/payment-processing, https://maverickpayments.com/terms, https://maverickpayments.com/developers, https://sharkprocessing.com/maverick-payments-review/, https://www.cardfellow.com/credit-card-processors/maverick-bankcard, https://www.ripoffreport.com/report/maverick-bank-card-calabasas/ca-payments-engages-unethical-1535040</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>hostmerchantservices</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Серые посредники по звёздам</t>
+          <t>Host Merchant Services (HMS)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Перепродажа Telegram Stars дешевле официальной цены</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Нарушение правил Telegram по существу: схема строится на возврате платежа (chargeback) через банк или магазин приложений</t>
+          <t>High-risk эквайринг/PSP — ISO (не прямой эквайер, не MoR); high-risk направление через «alternate partners»</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>серая зона. VPN нигде не упомянут, хотя у HMS очень широкий high-risk каталог: adult, airlines/jet charter, auto warranty, bail bonds, CBD, coins, content downloads &amp; digital goods, continuity/subscription, credit repair, debt collection, document prep, vape/e-cig, gambling/casinos, firearms, insurance, MLM, nutraceuticals, offshore businesses, online dating, online pharmacy, pawn shops, self-defense, SEO/SEM, sports betting, tech support, telemedicine, timeshares, travel, web design, web hosting, weight loss. Цифровые товары и подписки прямо поддержаны, но VPN/прокси/анонимайзеры не названы нигде, и публичного Acceptable Use со списком запрещённых вертикалей нет.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>РФ и СНГ, телеграм-каналы и боты</t>
+          <t>Юрлицо US (Newark, Delaware + Naples, Florida). Базовый рынок — США и Канада: «thousands of merchants across the U. S. and Canada placed their trust in us». При этом есть отдельная программа Offshore Businesses: «We work with a network of trusted offshore acquiring banks, allowing us to match your business with the most suitable banking partner», с FAQ «Incorporation can be done in days, with a banking setup right after» и документами «your proof of address, passport, and basic details». То есть не-US юрлицо (в т.ч. потенциально Казахстан/Армения/Грузия/Кыргызстан/ОАЭ) теоретически возможно через offshore-направление, но Россия отдельно не упомянута — не подтверждено; для российского резидента/РФ-юрлица — не подтверждено (высокий риск из-за банков-партнёров и санкционного комплаенса).</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Оплата продавцу картой/СБП/криптой</t>
+          <t>Visa, Mastercard, Amex, Discover, Apple Pay/Android Pay, PayPal (заявлено в прайс-таблице), ACH/eCheck, gift &amp; loyalty; в offshore-программе — 50+ валют, dynamic currency conversion, settlement локально или на offshore-счёт, валюты USD/EUR/GBP/CAD/AUD.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Формально дешевле официальной цены; экономика держится на краденых картах, региональном арбитраже или фарме звёзд</t>
+          <t>Публикуются для стандартных программ (интерчейндж + марка): retail — interchange + 0,25% + $0,10 за транзакцию; рестораны — +0,20% + $0,09; e-commerce — +0,35% + $0,10; offshore — «interchange-plus pricing with low markups starting at 0.20%-0.35% + $0.09-$0.10 per transaction». Прочие платы (прайс-лист): gateway $14,99/мес, monthly fee $14,99/мес, PCI compliance $0,75, batch fee $0,75, PIN debit $0,20/батч, annual 1099 reporting $24/год, voice authorization $5,00/мес (опционально), AVS $0,00, closure fee $0,00. Для high-risk — custom quote: «High-risk merchants receive custom pricing through HMS's arrangement with Electronic Merchant Systems, and those rates require a direct conversation» (GuidingDecisions, 2026). Chargeback fee — не публикуется.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>$0 заявлено для стандартных аккаунтов: «No Setup Fees», «No PCI Compliance Fees», «No Hidden Markups or Surprise Increases», «Month-to-Month Agreements», «No Long-Term Contracts», «Free Equipment for Qualified Merchants». Для high-risk-аккаунта условия могут отличаться (см. риски) — отдельная публикация отсутствует.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Нет резерва у продавца, но есть риск аннулирования звёзд постфактум</t>
+          <t>по запросу (не публикуется). Сама HMS резервы не раскрывает. Сторонний обзор предупреждает: стандартное соглашение HMS — month-to-month без ETF, но high-risk-аккаунты обслуживаются через партнёра (EMS) и «high-risk merchant agreements through EMS may include different contract durations, reserve requirements, and processing restrictions»; отраслевой ориентир, приведённый там же — rolling reserve 5–10% на 90–180 дней (это общая практика рынка, а не опубликованное условие HMS).</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Выплат как таковых нет</t>
+          <t>next-day funding заявлен: «Keep your cash flowing with funds deposited as soon as next business day», для digital goods — «Earn faster with next-day deposits», для offshore — «Next-day worldwide payouts». Есть отдельная страница Next Day Funding Times. Конкретные cutoff-времена нужно смотреть на этой странице/в договоре.</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Анонимный продавец без документов</t>
+          <t>Для стандартного онбординга: обычные бизнес-документы, 24–72 часа на одобрение (digital goods — 1–3 дня). Для high-risk: «We work with specialized acquiring banks and a team experienced in high risk industries» — конкретный список документов и требований не публикуется (не подтверждено); по данным GuidingDecisions 2026, андеррайтинг и условия идут через EMS. Для offshore: proof of address, passport и базовые данные; возможна помощь с инкорпорацией. Требования к сайту для цифрового сервиса не публикуются — приемлемость Telegram-бота без сайта не подтверждена.</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>да, полноценно: «Tokenized Recurring Billing for Subscriptions and Memberships», «Custom Subscription Plans», «Automate renewals, recurring billing, and reminders to save time and cut on declined payments» (то есть dunning/retry заявлены), recurring billing в HMS Pay, поддержка подписок в offshore- и digital-программах. Free trials отдельно не описаны — не подтверждено.</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Продажа через ботов-панели</t>
+          <t>Собственный шлюз HMS Pay (карты + ACH, virtual terminal, batch, multi-location), API-driven gateway, hosted checkout/payment links/payment buttons, mobile SDK, QR, плагины для корзин, интеграции с QuickBooks/ERP/CRM; поддерживаются также Authorize.Net и NMI. Документация по API публично в открытом виде не выложена (страница Payment integration), поэтому Telegram-бот без сайта — не подтверждено. Сложность интеграции: 3 — есть hosted checkout, API, tokenised recurring и поддержка подписок, но high-risk-онбординг ручной и идёт через партнёрские банки, публичной API-документации и правил для storefront без сайта нет..</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Схема: продавец покупает звёзды официально (часто украденной картой), передаёт покупателю, затем инициирует возврат; Telegram отслеживает возвраты и автоматически аннулирует покупки, звёзды списываются с баланса бота и он может уйти в минус. Риски: бан аккаунта и бота, потеря выручки, вовлечение в чужое мошенничество (ст.159 УК РФ), вопросы по 115-ФЗ при потоке чужих средств</t>
+          <t>HMS — ISO, а не прямой процессор: спонсоры — PNC Bank, Pinnacle Bank (dba Synovus) и Wells Fargo; high-risk — «provided through alternate partners» (в стороннем обзоре — Electronic Merchant Systems). Решение об удержаниях/резервах принимает backend-процессор, а не аккаунт-менеджер. Условия high-risk (срок, ETF, reserve) могут отличаться от рекламируемых month-to-month без ETF — нужно требовать оба договора в письменном виде. Для проекта добавляется вопрос приёма российского продавца: публично не подтверждено. ПРАКТИКА: Компания с 2009 года (основатель Lou Honick), BBB-аккредитация с 2011, репутация с очень малым числом жалоб для своего размера, dedicated account manager, больше support-агентов, чем продавцов, отсутствие early termination fee на стандартных аккаунтах. High-risk не автоматизируется: «HMS, through the EMS partnership, engages these businesses rather than automating a decline». Отзывы клиентов о много­летнем процессинге положительные; массовых публичных жалоб на заморозку средств не найдено.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://donatov.blog/post/pochemu-otnimayut-zvyozdy-i-podarki-v-telegrame-posle-pokupki-cherez-posrednikov, https://www.likeni.ru/events/telegram-annuliruet-zvezdy-podarki-i-premium-poluchennye-obmannym-putem/</t>
+          <t>https://hostmerchantservices.com/pricing/, https://hostmerchantservices.com/high-risk-merchants/, https://hostmerchantservices.com/merchant-account-for-content-downloads/, https://hostmerchantservices.com/offshore-businesses/, https://hostmerchantservices.com/terms-of-service/, https://hostmerchantservices.com/articles/high-risk-merchant-accounts/, https://www.guidingdecisions.com/host-merchant-services-review-interchange-plus-pricing-with-a-personal-touch</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Google Play (In-App Purchase)</t>
+          <t>Telegram Stars (Bot Payments)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Магазин приложений Google, продажа подписок через биллинг</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено с декларацией: приложение с VPN обязано использовать VpnService, пройти декларацию в Play Console, документировать использование в листинге и показывать prominent disclosure</t>
+          <t>Telegram-нативный</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Не регламентировано: модерации тематики нет, но цифровые товары в Telegram обязаны продаваться за Stars</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Глобально; РФ-разработчикам монетизация закрыта</t>
+          <t>Глобально; поддержка зависит от флага stars_purchase_blocked в конфиге Telegram (в дефолте true)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Google Play Billing (для РФ-аккаунтов не работает с 26.12.2024)</t>
+          <t>Stars (XTR); пополнение звёзд картой или через Fragment</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Стандартная шкала: 15% для первых 1 млн USD в год и 30% свыше; для автопродлеваемых подписок 15% независимо от выручки; в ряде рынков новая схема 10-25% плюс 5% billing fee</t>
+          <t>Спред Telegram 7,8%: покупка 1000 Stars = 1,41 USD, вывод 1000 Stars = 1,30 USD</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Регистрация разработчика: разовый сбор (не подтверждено в этой проверке)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Google удерживает выручку до выплаты по порогу</t>
+          <t>21 день удержания каждой звезды - данные вторичного источника, в офиц. документации не зафиксировано</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Для разработчиков с расчётным счётом в РФ: с 26.12.2024 продажи приостановлены бессрочно, последняя выплата 15.01.2025; выплат после этой даты не будет</t>
+          <t>Fragment, только TON-кошелёк; минимум 1000 Stars; максимум 25000000 Stars за операцию</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Аккаунт разработчика Google Play; для организации нужен D-U-N-S; минимальный возраст — 18 лет (не подтверждено отдельным документом в этой проверке)</t>
+          <t>Только Telegram-аккаунт владельца бота и 2FA-пароль; документы, ИП, ООО, самозанятость не требуются</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Да: автопродлеваемые подписки нативно</t>
+          <t>Да, Star Subscriptions (stars_subscription_amount_max = 10000 Stars)</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Google Play Developer API, server-side проверка покупок</t>
+          <t>Bot API sendInvoice currency=XTR + successful_payment; сложность 1 из 5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Канал мёртв для РФ: невозможность монетизации и получения выплат при российском расчётном счёте</t>
+          <t>Возвраты и refund понижают рейтинг аккаунта Telegram; флаг stars_purchase_blocked может быть переключён; долгий путь денег TON - биржа - рубли</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>https://support.google.com/googleplay/android-developer/answer/15685001, https://support.google.com/googleplay/android-developer/answer/112622, https://support.google.com/googleplay/android-developer/answer/12564964</t>
+          <t>https://core.telegram.org/api/stars, https://core.telegram.org/api/config, https://isales.ai/fr/blog/sell-content-telegram-stars-usdt</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
@@ -7071,201 +7071,201 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Apple App Store</t>
+          <t>Telegram Payments через провайдеров BotFather</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Магазин приложений Apple, продажа подписок через IAP</t>
+          <t>Telegram-нативный</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>ЖЁСТКОЕ ОГРАНИЧЕНИЕ п.5.4: приложения с VPN обязаны использовать NEVPNManager API и могут размещаться только разработчиками, зарегистрированными как организация (enrolled as an organization). Физлицо опубликовать VPN-приложение не может. Требуется декларация о собираемых данных до покупки и обязательство не передавать данные третьим лицам</t>
+          <t>Определяется провайдером, а не Telegram; BotFather тематику продавца не проверяет</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Глобально (кроме РФ-специфики)</t>
+          <t>Список провайдеров отдаётся в BotFather динамически, публично не индексируется</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Apple In-App Purchase; собственные платёжные механизмы для разблокировки функциональности запрещены п.3.1.1</t>
+          <t>Зависит от провайдера: карты РФ, СБП, кошельки</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Стандарт 30%, 15% для малого бизнеса (до 1 млн USD) и для подписок после первого года; точные условия программы не перепроверялись в этой сессии</t>
+          <t>Комиссия провайдера; отдельная комиссия Telegram не подтверждена</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Apple Developer Program: 99 USD в год</t>
+          <t>Зависит от провайдера</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Apple удерживает выручку до выплаты по порогу</t>
+          <t>Зависит от провайдера</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Выплаты на банковский счёт; для российских разработчиков статус выплат в 2026 не подтверждён</t>
+          <t>Зависит от провайдера</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Только организация (юрлицо) для VPN-приложения; нужен D-U-N-S; минимальный возраст для enrollment — 18 лет</t>
+          <t>Договор с провайдером; почти всегда ИП, ООО или самозанятость</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Да: нативные подписки</t>
+          <t>Зависит от провайдера</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>App Store Server API / verifyReceipt для проверки чеков</t>
+          <t>Bot API sendInvoice с валютой RUB, pre_checkout_query, successful_payment; сложность 2 из 5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>VPN-приложение физически недоступно физлицу из-за п.5.4; плюс санкционные сложности с выплатами; п.3.1.1 запрещает продавать подписку в обход IAP</t>
+          <t>Риск отказа комплаенса по тематике VPN; список и условия провайдеров меняются</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>https://developer.apple.com/app-store/review/guidelines/, https://developer.apple.com/programs/enroll/</t>
+          <t>https://core.telegram.org/api/payments, https://spbnews78.ru/society/2026/04/20/235181.html, https://vibecoderz.ru/blog/kak-podklyuchit-oplatu-k-telegram-botu-v-2026-yukassa-stars-</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>RuStore</t>
+          <t>Tribute</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Российский магазин приложений для Android</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>Не подтверждено: явного запрета VPN в изученных документах нет, но в 2023-2024 гг. в СМИ обсуждалась инициатива Совфеда ограничить скачивание VPN из RuStore — актуальный статус модерации VPN не подтверждён</t>
+          <t>Telegram-нативный посредник</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Серая зона: VPN, прокси и анонимайзеры в списке запрещённых категорий отсутствуют, но товар проходит ручную модерацию со статусами pending/approved/rejected</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>РФ</t>
+          <t>РФ и СНГ; выплаты в рублях, долларах, евро и USDT</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Карты РФ, СБП, баланс мобильного</t>
+          <t>Карты (RUB, USD, EUR), СБП, Telegram Stars, TON, USDT, BTC, Telegram Wallet</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>По условиям приёма платежей размер вознаграждения определяется п.6.1 соглашения о распространении; по данным 2023 г. — от 0,9% до 3,35% при обороте менее 1 млн руб, далее до 10% в категории Медиа и до 15% в остальных</t>
+          <t>10% с каждой успешной транзакции, включая комиссию сервиса и платёжных провайдеров, плюс динамический сервисный сбор (размер зависит от суммы платежа, точные значения не опубликованы)</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0 руб</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Мошеннические платежи удерживаются, но не более 3% дохода за период; возвраты списываются с дохода разработчика</t>
+          <t>Явно не заявлен; роль холда выполняет расчётный период до 15 дней плюс срок доставки</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Доход перечисляется на расчётный счёт в течение 15 рабочих дней после окончания отчётного месяца (отчётный период — календарный месяц), только в рублях</t>
+          <t>Минимум 3000 RUB / 100 USD / 100 EUR / 100 USDT; авто 10 и 25 числа, по заявке 2-5 рабочих дней, максимум 2 заявки в месяц; на карту или Telegram Wallet</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>ПРЯМОЕ ОГРАНИЧЕНИЕ: условия приёма платежей заключаются только с зарегистрированным в РФ юридическим лицом или ИП. Условия не применяются и не могут быть приняты физическим лицом. Программа для самозанятых существовала в 2023 г. (выплаты через VK Pay самозанятые, минимум 5000 руб) — действует ли она сейчас, не подтверждено</t>
+          <t>Регистрация через @tribute в Telegram; документы и статус не требуются; для выплат есть страница новых требований к данным, содержимое не проверено</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Да: п.4.2 регулирует автоплатежи, не более чем за 8 часов до истечения оплаченного периода</t>
+          <t>Для подписок Tribute да, но автопродление внешней VPN-подписки требует своей логики</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>RuStore API и система приёма платежей, серверные колбэки</t>
+          <t>Платёжная ссылка + API + вебхук new_digital_product с HMAC-SHA256 в заголовке trbt-signature, ретраи 5 мин / 15 мин / 30 мин / 1 час / 10 часов; сложность 2 из 5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Нужен ИП или юрлицо — 15-летний основатель не подходит; самозанятый родитель тоже не подходит по букве условий приёма платежей</t>
+          <t>Возможен rejected при модерации товара; приём идёт через СБП, и провайдер может изменить политику по VPN; возврат через API доступен только для платежей Stars; лимит цифрового товара 100000 RUB за разовую транзакцию</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>https://www.rustore.ru/help/legal/devs/developers-offer, https://www.comnews.ru/content/226667/2023-06-08/2023-w23/magazin-prilozheniy-rustore-razreshil-zarabatyvat-fizicheskim-licam</t>
+          <t>https://wiki.tribute.tg/ru/for-content-creators/content-restrictions.md, https://wiki.tribute.tg/ru/for-content-creators/fees-limits-currencies.md, https://wiki.tribute.tg/ru/for-content-creators/payouts.md, https://wiki.tribute.tg/ru/for-content-creators/digital-product/api-integration.md</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Huawei AppGallery</t>
+          <t>Boosty</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Магазин приложений Huawei</t>
+          <t>Донат-платформа</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Не подтверждено: официальные страницы политики и расчётов отдаются только JS-рендером; явной политики по VPN получить не удалось</t>
+          <t>Не подтверждено: официальные правила отдаются только JavaScript-рендерингом, текст не извлекается</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Глобально, фокус на РФ и СНГ</t>
+          <t>РФ и СНГ; выплаты заявлены в долларах или евро на банковские карты</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Huawei In-App Purchase</t>
+          <t>Банковские карты (по правилам платежей), внутренние подписки</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено: официальную ставку комиссии получить не удалось</t>
+          <t>11,7% агентского вознаграждения при оплате банковскими картами с 20.02.2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Есть отдельный раздел расчётов для РФ на developer.huawei.com, содержание не получено</t>
+          <t>Вывод в долларах или евро на банковские карты; фиксированный сбор 1 USD или 1 EUR за операцию; лимит 1500 за разовую транзакцию; суточные, недельные и месячные лимиты зависят от Visa или MasterCard</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -7290,22 +7290,22 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Да (IAP-подписки)</t>
+          <t>Да (подписки - суть платформы)</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Huawei IAP server-side verification</t>
+          <t>Отдельная страница платформы, интеграции с ботом нет; сложность 3 из 5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено из-за недоступности документов; риск строить расчёт на непроверенных данных</t>
+          <t>Вывод в валюте при рублёвой выручке даёт конвертацию и валютные вопросы; при статусе Неактивного автора списывается 1 единица валюты в день, соглашение расторгается; VPN-политика неизвестна</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>https://developer.huawei.com/consumer/ru/doc/help/settlement-0000001052983076</t>
+          <t>https://www.playground.ru/misc/news/platforma_boosty_vvodit_edinuyu_komissiyu_dlya_avtorov-1825946, https://boosty.to/boosty/posts/de1e6f32-3a80-4824-95bd-a264ff1b00aa</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
@@ -7317,77 +7317,77 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Amnezia Premium (партнёрка)</t>
+          <t>DonationAlerts</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено: провайдер сам продаёт обфусцированный VPN и принимает партнёров</t>
+          <t>Донат-платформа</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Формально не запрещено: пункта VPN, прокси или анонимайзер в правилах нет, но запрещён контент, нарушающий закон; юридически это платформа донатов, а не продаж</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Глобально; русскоязычная аудитория целевая</t>
+          <t>СНГ; оператор Zaya Solutions Limited (Гонконг)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Оплата провайдеру; партнёр получает вознаграждение</t>
+          <t>Банковские карты (RUB, EUR, USD), YooMoney, VKPay, мобильный счёт, крипта в USDT</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>До 40% с продажи Amnezia Premium и 30% с каждого продления (по данным партнёрской страницы); пример: 100 полугодовых продаж = 1000 USD, 100 годовых = 1720 USD сразу плюс 30% с продлений</t>
+          <t>12% при обороте до 1 млн RUB за предыдущий месяц, 9% свыше; первый месяц всегда 12%; за перечисление на карту РФ 1,9% плюс 20 RUB; конвертация с удержанием 10% от курса OER</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>0 руб, подача заявки через форму или Telegram @amnezia_affiliate</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено: сроки холда на странице не указаны</t>
+          <t>Investigation Period до 90 дней: выплата может быть задержана или отменена для оценки риска</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Выплаты партнёру; рельсы (карта РФ/СБП/крипта) не подтверждены</t>
+          <t>Ежедневно по мере возможности, но гарантии нет; лимиты по карте РФ 50 транзакций в день и 50 в месяц, минимум 150 RUB, максимум 2500000 RUB</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Заявка физлица возможна (форма + Telegram/email); требование юрлица не заявлено</t>
+          <t>KYC обязателен до вывода средств; требования к статусу физлицо или самозанятый не подтверждены</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Да: 30% с каждого продления — рекуррентный доход</t>
+          <t>Не подтверждено (донатная модель)</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская ссылка и личный кабинет; API автовыдачи доступа не заявлен</t>
+          <t>API (apidoc) + виджеты + страница DALink; связка донат - выдача VPN-доступа нештатная, сложность 3 из 5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Зависимость от провайдера; отсутствие публичных условий по выплатам в РФ; VPN-сервис может быть заблокирован в РФ</t>
+          <t>Переквалификация донатов в выручку даёт налоговые вопросы; блокировка аккаунта за нарушение правил; заморозка до 90 дней; отсутствие гарантии ежедневных выплат</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>https://amnezia.org/en/partners</t>
+          <t>https://www.donationalerts.com/terms-of-service/payments?cis=1, https://www.donationalerts.com/terms-of-service/broadcasters</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
@@ -7399,42 +7399,42 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>HideMy.name (партнёрка)</t>
+          <t>VK Donut</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено: провайдер сам продаёт VPN и приглашает партнёров</t>
+          <t>Донат-платформа</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: страница правил не отдаётся для машинного чтения</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Глобально; русскоязычный сервис</t>
+          <t>РФ, внутри ВКонтакте</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Оплата провайдеру</t>
+          <t>Внутри VK (VK Pay и др.), детали не подтверждены</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>До 50% с привлечённых покупок и 25% со всех продлений без ограничения по времени</t>
+          <t>Не подтверждено</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0 руб, после регистрации выдаётся реферальная ссылка</t>
+          <t>Не подтверждено</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -7444,74 +7444,74 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Выплаты партнёру; рельсы и минимум не подтверждены</t>
+          <t>Внутри VK, детали не подтверждены</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Регистрация партнёра; требование юрлица не заявлено</t>
+          <t>Не подтверждено</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Да: 25% с продлений без ограничения срока</t>
+          <t>Не подтверждено</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Реферальная ссылка; API автовыдачи не заявлен</t>
+          <t>Внутри ВКонтакте, вне Telegram; ломает воронку бота; сложность 4 из 5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Условия выплат не опубликованы; зависимость от провайдера; репутационные и юридические риски продажи VPN в РФ</t>
+          <t>Полное отсутствие проверяемых данных по правилам, комиссии и выплатам; работа вне Telegram</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>https://hide.mn/en/faq/general-questions/cooperation-with-us/for-partners/</t>
+          <t>https://vk.ru/@donut-pravila, https://calculory.com/ru/calculators/vk-donut-revenue-calculator</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>низкая</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>AdGuard VPN (партнёрка)</t>
+          <t>FunPay</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено: провайдер продвигает партнёрскую программу</t>
+          <t>Площадка цифровых товаров</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Серая зона: прямого запрета VPN нет, но п. 2.2.5 запрещает подписки на сервисы без спецраздела, а п. 2.1.12 запрещает размещать объявления на других площадках под угрозой отказа в выплатах</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Глобально</t>
+          <t>РФ и СНГ</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Оплата провайдеру</t>
+          <t>Внутренние методы площадки, детали не подтверждены</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Ставка на странице программы не извлечена (страница отдаётся JS-рендером) — не подтверждено</t>
+          <t>Не подтверждено: три слоя (сбор с продажи, сбор за вывод, стоимость платёжного метода), ставки не опубликованы</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -7521,17 +7521,17 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>При блокировке по категорийным нарушениям выплата только после идентификации, 30 или 60 дней</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>При блокировке по ряду пунктов выплаты не производятся вовсе</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Физлицо, регистрация свободная; документы для вывода не подтверждены</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -7541,64 +7541,64 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская ссылка</t>
+          <t>Ручная или автоматическая выдача; автовыдача прямо запрещена для товаров, требующих общения или доп. услуг; сложность 2 из 5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Проверить условия и доступность выплат для РФ-партнёра напрямую</t>
+          <t>Блокировка и отказ в выплатах за размещение объявлений на других площадках (п. 2.1.12) и за передачу контактов, включая Telegram (п. 1.1); риск трактовки п. 2.2.5 против VPN-подписок</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>https://adguard-vpn.com/en/vpn-affiliate-program.html</t>
+          <t>https://funpay.com/trade/info, https://foxreload.com/ru/library/marketplaces/funpay-seller-commission-fees</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>KeepSolid VPN Unlimited (partners)</t>
+          <t>PayMaster</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская/реселлерская программа VPN-провайдера</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено: у провайдера есть раздел partnership для партнёров и партнёрская программа</t>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Серая зона: оферта молчит, требование общее - товары не должны входить в список запрещённых к продаже; VPN прямо не назван</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Глобально; русскоязычный интерфейс и сайт</t>
+          <t>РФ, есть отдельное направление для нерезидентов</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Оплата провайдеру</t>
+          <t>Карты, электронные деньги, мобильные платежи, терминалы, банковские переводы, СБП</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Ставка не извлечена (страница отдаётся JS-рендером) — не подтверждено</t>
+          <t>2-5% с каждой успешной транзакции в зависимости от вида платежа; ежемесячных и скрытых платежей нет</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>0: подключение бесплатное</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -7608,156 +7608,156 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не подтверждено: сроки, минимальная сумма и куда перечисляют, не найдены</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Есть публичный вход для физлиц (кнопка У меня нет юр. лица) и отдельный для юрлиц и ИП; нужен готовый ресурс с товарами, ценами и офертой; заявленный срок подключения 2 дня</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Да, есть страница рекуррентных платежей и автоплатежей</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Отдельно упоминается Telegram-бот VPN Unlimited</t>
+          <t>API, платёжный виджет, модули CMS, Payment notification POST-вебхук с MD5-подписью, защита от дублей, тестовый режим, подключение к Telegram; сложность 2 из 5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Условия и выплаты для РФ-партнёра не подтверждены</t>
+          <t>Отказ комплаенса по непубличному списку запрещённых товаров; неизвестные условия холда и выплат; риск отказа по тематике VPN</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpnunlimited.com/partnership/affiliates</t>
+          <t>https://info.paymaster.ru/blog/process-podklyucheniya-k-paymaster/, https://info.paymaster.ru/blog/rekurrentnye-platezhi/, https://info.paymaster.ru/oplata-v-telegram/</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>NordVPN (партнёрка/white label)</t>
+          <t>RollyPay</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено провайдером; критично проверить ограничения по странам и санкциям для партнёра из РФ</t>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Серая зона: в оферте и на сайте VPN, прокси и анонимайзеры не упомянуты, тематика решается менеджером после проверки проекта</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Глобально</t>
+          <t>РФ и другие страны; выплаты на карты РФ или в USDT</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Оплата провайдеру</t>
+          <t>СБП QR, карты Visa, Mastercard, Мир, крипта USDT, BTC, ETH, TON, CryptoBot, xRocket, ЕРИП</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Ставка не подтверждена в этой проверке</t>
+          <t>Крипта от 1%; по данным представителя сервиса СБП QR от 5% и карты РФ от 5% - это заявление в неофициальном канале, а не текст оферты</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не подтверждено: оферта в машиночитаемом виде не получена</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не подтверждено; заявлены автоматические выводы</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено; программы такого класса обычно платят через PayPal или банковский перевод, что неприменимо для физлица из РФ</t>
+          <t>На карты российских банков или в USDT; лимиты и комиссии согласуются при подключении; минимум и сроки не подтверждены</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Обычно требуется партнёрская сеть (Admitad/Awin) и подтверждение личности; доступность для РФ не подтверждена</t>
+          <t>Подключение доступно физлицам, самозанятым, ИП и компаниям после проверки проекта; публичной оферты с перечнем запретов нет</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Да, рекуррентные платежи заявлены</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Партнёрские ссылки/промокоды</t>
+          <t>REST API, вебхуки, SDK на Node.js, PHP, Python, готовые модули и платёжные ссылки, тестовый режим; сложность 2 из 5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Высокий риск отказа в выплатах партнёру-резиденту РФ; санкционные ограничения</t>
+          <t>Комиссия 5% по СБП и картам вдвое дороже обычного эквайринга; оферта и запреты недоступны для проверки; схема без ИП и юрлица создаёт налоговые и банковские риски для коммерческой выручки; серая зона закрывается первой при смене политики</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>https://www.admitad.com/cz/store/offers/nordvpn-ww/</t>
+          <t>https://rollypay.io/, https://overtonfx.ru/threads/rollypay-io-servis-priyem-platezhei-cherez-sbp-karty-i-kriptovalyutu-bez-yurlitsa.14127/, https://docs.rollypay.io</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Proton VPN (партнёрка)</t>
+          <t>Tranzzo</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено провайдером; доступность для РФ-партнёра не подтверждена</t>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Запрещено: п. 11 запрещает объекты для снятия защиты авторских прав или региональных ограничений, п. 14 запрещает деятельность с репутационными рисками для провайдера и платёжных систем</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Глобально</t>
+          <t>Международно; TRANZZO LTD (UK), суды в Великобритании</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Оплата провайдеру</t>
+          <t>Карты, СБП, QR, платёжные ссылки, подписки, холдирование</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Ставка не подтверждена</t>
+          <t>Не подтверждено: публичного тарифа нет</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7767,79 +7767,79 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Холд и роллинг-резерв на усмотрение сервиса; при расторжении после превышения лимита чарджбеков средства удерживаются 540 дней</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Через партнёрские сети (например Indoleads); рельсы для РФ не подтверждены</t>
+          <t>Ограничение вывода возможно в зависимости от местоположения, проданных товаров, запроса полиции и жалоб; чарджбеки ограничены 1% транзакций за месяц</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Регистрация в партнёрской сети; доступность РФ не подтверждена</t>
+          <t>Только 18+, обязателен KYC; приём только с согласованного ресурса, иначе расторжение; требования к статусу не подтверждены</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Да, отдельный продукт платежей по подписке</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Партнёрские ссылки</t>
+          <t>API (guide.tranzzo.com), CMS-модули, мобильное SDK, платёжные ссылки, QR; сложность 4 из 5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Санкционные и платёжные ограничения для РФ-партнёра</t>
+          <t>Штраф до 50000 USD за запрещённую деятельность; удержание средств до 540 дней; холд и роллинг-резерв по усмотрению сервиса; VPN прямо попадает под п. 11 и п. 14</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>https://indoleads.com/blog/new-offer-launched-proton-vpn-mail-drive-pass-webapp-affiliate-program/</t>
+          <t>https://www.tranzzo.com/ru/prohibited-categories, https://www.tranzzo.com/ru/terms-and-conditions</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Ivacy VPN (white label)</t>
+          <t>Ecommpay</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>White-label VPN</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено: у провайдера исторически есть white-label/affiliate предложение</t>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: страница Business Risk Appetite не читается роботом (пустой ответ)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Глобально</t>
+          <t>Не подтверждено</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Оплата провайдеру</t>
+          <t>Не подтверждено</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Ставка не подтверждена в этой проверке</t>
+          <t>Не подтверждено</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7869,17 +7869,17 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>White-label панель (не подтверждено)</t>
+          <t>Не подтверждено</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Условия и доступность для РФ не подтверждены</t>
+          <t>Нет проверяемых данных: ни VPN-политика, ни комиссия, ни требования к подключающему</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>https://www.postaffiliatepro.sk/adresar/ivacy-affiliate-program/</t>
+          <t>https://ecommpay.com/compliance/business-risk-appetite/</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
@@ -7891,22 +7891,22 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>OrbVPN (reseller)</t>
+          <t>Telegram Gifts и перепродажа звёзд</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Реселлерская программа VPN-провайдера</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Разрешено: у провайдера есть отдельная документация для реселлеров</t>
+          <t>Telegram-нативный серый</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Нарушение правил Telegram и экономически невозможно легально: покупка 1000 Stars стоит 1,41 USD, вывод даёт 1,30 USD</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7916,226 +7916,2358 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Оплата через реселлерскую панель</t>
+          <t>Подарки за Stars, конвертация подарка обратно в Stars</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Скидка посредника 20-40% от официальной цены означает краденые или возвратные звёзды</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не применимо</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не применимо</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не применимо</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не применимо</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Не применимо</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Есть документация для реселлеров на docs.orbvpn.com</t>
+          <t>Схема с посредником; технически возможно, но недопустимо</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Нишевый провайдер, условия и выплаты для РФ не подтверждены</t>
+          <t>Отзыв звёзд по флагу refund; понижение рейтинга аккаунта Telegram при рефандах и конвертации подарков; convert_stars всегда меньше цены покупки; конвертация подарка возможна только 7 дней (604800 секунд); риск мошенничества у посредника</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://docs.orbvpn.com/en/reseller</t>
+          <t>https://core.telegram.org/api/gifts, https://core.telegram.org/api/stars, https://core.telegram.org/api/config, https://tehnoobzor.com/tg-stars-com-moshennik/</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Instant-delivery шопы (типовой магазин автовыдачи)</t>
+          <t>Digiseller (digiseller.market)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Собственная витрина с автовыдачей, часто на бэкенде Digiseller</t>
+          <t>Платформа цифровых товаров и витрин (движок для GGsel и др.)</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Серая зона: правила задаёт владелец шопа, а не площадка; для приёма денег нужен собственный эквайринг или подключение к чужой кассе</t>
+          <t>Серая зона: VPN в запретах не упомянут; запрещены товары, нарушающие законодательство, и абстрактные/неописанные товары (п.1.2.4)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>СНГ</t>
+          <t>Международный, расчёты в WM-титулах</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Карты, СБП, крипта — зависит от владельца шопа</t>
+          <t>WebMoney, банковские карты, СБП через внешних интеграторов (есть отдельная инструкция по подключению СБП)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Комиссия платформы-бэкенда (Digiseller 1,5-6%) плюс комиссия эквайринга; плюс доля владельца шопа, если продаёте через него</t>
+          <t>Комиссия DS 1,5-6% в зависимости от тематики, но не менее 0,02 WM; сверху комиссия платёжного метода и стоимость вывода</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Зависит от бэкенда</t>
+          <t>0 руб</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Зависит от бэкенда</t>
+          <t>Вывод доступен не ранее чем через 72 часа после продажи (для Plati); для отдельных разделов задержка больше</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Выплаты через владельца шопа; юридически это доход физлица без договора</t>
+          <t>Вывод в WM-кошелёк/на карту; в РФ обслуживание через филиал DigiCore Solutions LTD (ИНН 9909773220)</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Чаще всего достаточно регистрации; договор с продавцом часто отсутствует</t>
+          <t>П.1.2.1: клиентом DS может стать только лицо, прошедшее идентификацию в системе WebMoney; регистрация как физлицо возможна</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Зависит от реализации</t>
+          <t>Рекуррент не поддерживается платформой; продление — новый заказ</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Обычно есть API автовыдачи ключей</t>
+          <t>Есть API Digiseller для автоматической выдачи ключей и внешних витрин</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Нет договора и защиты сделки; владелец шопа может исчезнуть с деньгами; репутация площадки не защищает продавца</t>
+          <t>Зависимость от WebMoney-инфраструктуры, риск блокировки при несоответствии описания, возвраты списываются со счёта продавца</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>https://digiseller.com/agreement, https://foxreload.com/ru/library/marketplaces/ggsel-commissions-payouts</t>
+          <t>https://digiseller.com/agreement, https://plati.market/sellerinfo/</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Plati.Market</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Маркетплейс цифровых товаров (та же экосистема, что Digiseller)</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Серая зона: в Приложении 1 (перечень запрещённых товаров) VPN не упомянут; прямо разрешены к продаже сервисы подписки</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>РФ, СНГ, международный</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Карты, СБП, WebMoney, электронные кошельки</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Комиссия от 3% от суммы платежа (заявлено на странице для продавцов)</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>0 руб; регистрация не требует документов или технических знаний</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Вывод не ранее чем через 72 часа с момента продажи; для отдельных разделов/товаров/продавцов задержка увеличена</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Вывод на кошелёк/карту; для расширенных возможностей нужен формальный или персональный аттестат WebMoney</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Физлицо без документов; при отрицательном отзыве без аттестата возможна блокировка счёта и продаж</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Рекуррент нет; продажа подписки как разового цифрового товара</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>API и автовыдача уникальных кодов (автоматически создаваемые уникальные коды)</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Риск блокировки товаров при отрицательном отзыве, запрет HTML в описании, запрет рекламы сторонних ресурсов в товаре</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>https://plati.market/sellerinfo/, https://plati.market/asp/soglas_add1.asp</t>
+        </is>
+      </c>
+      <c r="P93" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>GGsel</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Витрина цифровых товаров на бэкенде Digiseller</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Серая зона: наследует правила Digiseller; VPN отдельно не упомянут</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>РФ, СНГ</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Карты, СБП, кошельки</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Сбор площадки зависит от раздела и условий продавца; публичной ставки нет; расчёты идут через Digiseller, плюс стоимость платёжного метода и вывода</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>0 руб, регистрация бесплатна</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Возврат списывается со счёта продавца; комиссии при возврате полностью не возвращаются</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Баланс и заявки на вывод — в кабинете Digiseller</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Требуется идентификация WebMoney (наследуется от Digiseller)</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Автовыдача мгновенных кодов; API наследуется от Digiseller</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Три слоя сборов плюс возвраты; двойной набор правил (витрина + платформа); непрозрачные тарифы</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>https://foxreload.com/ru/library/marketplaces/ggsel-commissions-payouts, https://ggsel.net/en/selleragreement.pdf</t>
+        </is>
+      </c>
+      <c r="P94" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Playerok</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Маркетплейс игровых товаров и цифровых услуг</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: текст оферты отдаётся только JS-рендером, явного запрета или разрешения VPN найти не удалось</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Карты РФ, СБП</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Многослойная: ставка зависит от типа товара плюс стоимость вывода; конкретные проценты не подтверждены</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Эскроу: деньги удерживаются до подтверждения сделки</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Вывод на карту РФ; сроки и минимум не подтверждены</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>KYC низкий/средний; физлицо</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Частичная автовыдача (коды мгновенно, аккаунты/валюта — вручную)</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Массовые блокировки товаров в отдельных разделах; правила арбитража закрыты; тарифы непубличны</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>https://playerok.com/terms-of-sale, https://foxreload.com/ru/library/compare/funpay-vs-playerok</t>
+        </is>
+      </c>
+      <c r="P95" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Z2U</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Маркетплейс игровой валюты, аккаунтов и ключей</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: явной политики по VPN в публичных правилах найти не удалось</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Международный</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Карты, электронные кошельки, крипта</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Ставка комиссии публично не раскрыта; типовой стек: сбор площадки + стоимость вывода</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Эскроу, холд до подтверждения сделки</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Международные рельсы (карта/кошелёк/крипта); выплаты на карту РФ не подтверждены</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация продавца; KYC не подтверждён</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Есть автоматическая выдача кодов</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Высокий порог доверия у покупателей, споры, отсутствие русскоязычной поддержки выплат</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>https://foxreload.com/en/library/marketplaces/sell-digital-goods-z2u</t>
+        </is>
+      </c>
+      <c r="P96" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>G2G</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Международный маркетплейс игровых товаров</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Ограничение: продавать можно только подписки сроком не более одного месяца (п.1 правил для Software &amp; App), что несовместимо с длинными тарифами 3/6/12 мес. Для GiftCard прямо запрещено просить покупателя использовать внешний софт или VPN</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Международный, приоритет ЮВА</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Карты, электронные кошельки, локальные методы</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Ставка комиссии публично не раскрыта; сайт обещает удержание платежей продавцу при нарушениях</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>При офсайт-торговле — заморозка доступного баланса на 6 месяцев</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Вывод на международные рельсы; карта РФ не подтверждена</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Уровень аккаунта продавца не ниже 30 для категории Software &amp; Apps</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Максимум 1 месяц на подписку</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>Есть система загрузки данных заказа, автовыдача частичная</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Жёсткая модерация, постоянный бан за офсайт-торговлю, ограничение срока подписки убивает годовые тарифы</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>https://support.g2g.com/support/solutions/articles/5000001405, https://support.g2g.com/support/solutions/articles/5000888791</t>
+        </is>
+      </c>
+      <c r="P97" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Eldorado.gg</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Международный маркетплейс игровых товаров</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: отдельной политики по VPN нет; площадка заточена под игровые категории</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Международный</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Карты, крипта через выплатные рельсы</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Sales fee 5% для валюты, 0% для пополнений и гифткарт, 10% для предметов/аккаунтов/бустинга; у части игр свои ставки</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Эскроу до завершения заказа</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Payoneer (мин. 10-50 USD, комиссия 4% + 2 USD), Skrill (мин. 10 USD, 5%), SEPA, BTC, USDC; вывод в рублях на карту РФ отсутствует</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Физлицо-продавец, регистрация; верификация для выплат через Payoneer/Skrill</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Выдача через страницу заказа</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Фиксированный сбор 2 USD при чеке ~2,4 USD (199 руб) съедает почти всю выручку; нет выплат в РФ</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>https://support.eldorado.gg/en/articles/8409025-seller-fees, https://support.eldorado.gg/en/articles/8409026-seller-withdrawal-methods</t>
+        </is>
+      </c>
+      <c r="P98" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>PlayerAuctions</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Международный маркетплейс игровых аккаунтов и валюты</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: специализируется на игровых активах, категории цифровых подписок и VPN в правилах не описаны</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Международный</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Карты, PayPal, крипта</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Комиссия продавца публично не подтверждена</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Эскроу, длительный холд по спорам</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>PayPal/банковский перевод; карта РФ не подтверждена</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Верификация личности продавца, история аккаунта</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Ручная выдача, API не подтверждён</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Нецелевой канал для VPN, отсутствие выплат в РФ, высокий порог входа</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.playerauctions.com/guide/other/mmorpg/how-to-sell-game-accounts/</t>
+        </is>
+      </c>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Kwork</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Фриланс-маркетплейс услуг</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>ПРЯМОЙ ЗАПРЕТ: п.1.2.5 Неподдерживаемых услуг — запрещены услуги, связанные с обходом блокировок запрещённых сервисов, в т.ч. использование VPN-сервисов</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Карты РФ, СБП, кошелёк Kwork</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Комиссия площадки с заказа (точная ставка не проверялась)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Эскроу: оплата резервируется до сдачи заказа</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Вывод на карту РФ/кошелёк</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Физлицо; верификация для вывода</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Нет (только разовые кворки)</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Автовыдача не предусмотрена: услуга оказывается вручную через чат</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Прямой бан услуги и аккаунта за VPN; реклама обхода блокировок = нарушение ФЗ о рекламе</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>https://kwork.ru/prohibited_services</t>
+        </is>
+      </c>
+      <c r="P100" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Avito</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Классифайд, с 30.04.2026 есть онлайн-оплата цифровых товаров (Авито Доставка)</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>ПРЯМОЙ ЗАПРЕТ по заявлению пресс-службы (2022): Запрещено размещение объявлений по установке сервисов для обхода блокировок регуляторов и обеспечению доступа к запрещённым на территории РФ ресурсам. Подобные объявления при обнаружении оперативно блокируются. Отдельной категории для VPN нет</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Карты РФ, СБП, Авито Доставка (деньги продавцу только после подтверждения получения)</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>7% за продажу цифрового продукта на тарифе с оплатой за успешную сделку</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>0 руб; нужен тариф с оплатой за успешную сделку</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Эскроу: продавец обязан отправить ключ в течение 24 часов, иначе заказ отменяется; деньги приходят после подтверждения покупателем</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Вывод на карту РФ по графику выплат Авито</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Физлицо может размещать объявления; для регулярной коммерческой деятельности нужен статус ИП/самозанятого (не подтверждено для этой категории)</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>Нет автовыдачи: ключ отправляется вручную в чат в течение 24 часов; API не предусмотрен</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Блокировка объявлений за VPN (подтверждено практикой 2022 г.), мисс-категория, ручная выдача, споры</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dp.ru/a/2022/03/17/Avito_blokiruet_objavle, https://78.ru/news/2026-04-30/na-avito-poyavilas-funkciya-onlainoplati-podpisok-i-cifrovih-klyuchei, https://foxreload.com/en/library/marketplaces/avito-digital-section</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Ozon (цифровые товары)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Ритейл-маркетплейс, отдельные категории цифровых товаров</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: VPN прямо не запрещён в опубликованном договоре, но модерация цифровых товаров строгая и требует подтверждения источника товара</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Карты, СБП, рассрочка</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Комиссия зависит от категории, плюс эквайринг и продвижение; точные ставки — в тарифах Ozon Seller</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Выплаты по графику Ozon после закрытия периода</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Вывод только на реквизиты ИП/юрлица</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Нужен статус ИП или юридического лица, договор и документы на источник товара</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>Отгрузка цифрового кода/электронного товара</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Недоступен физлицу и 15-летнему основателю; требования к источнику товара; блокировки региональных кодов</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>https://seller-edu.ozon.ru/libra/contract-for-sellers/contract-digital-goods/digital-product-seller-agreement, https://foxreload.com/ru/library/marketplaces/sell-digital-goods-ozon</t>
+        </is>
+      </c>
+      <c r="P102" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Wildberries (цифровые товары)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Ритейл-маркетплейс</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: отдельная площадка WB Digital закрыта, правила переноса цифровых товаров на основную платформу по VPN не раскрыты</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Карты, СБП, WB Кошелёк</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Комиссия зависит от категории (не подтверждено для цифры)</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Выплаты по графику WB</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Вывод на расчётный счёт ИП/юрлица</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>ИП или юрлицо</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>Цифровые коды на основной платформе</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>WB Digital закрыт 01.12.2025, заявки на вывод после 27.12.2025 обрабатывались только с 12.01.2026 — риск заморозки средств на переходном периоде</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>https://oborot.ru/news/pochemu-wildberries-zakryvaet-svoyu-platformu-cifrovyh-tovarov-i-chto-dalshe-i259021.html</t>
+        </is>
+      </c>
+      <c r="P103" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>WATA Telegram-stars</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Легальный оптовый поставщик звёзд без депозита</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Разрешено: продукт WATA для продажи Telegram-звёзд с встроенным эквайрингом; WATA заявляет отказ только от гемблинга, беттинга и адалта</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Клиенты из РФ, международный бизнес</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Карты РФ (МИР), зарубежные карты, СБП QR</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Доход мерчанта — разница между установленной им ценой и закупкой у WATA; отдельная комиссия за конвертацию не взимается (по заявлению WATA)</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Депозит не нужен (WATA держит его за мерчанта)</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Заморозки средств нет по заявлению WATA; курсовой риск берёт на себя WATA</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Выплаты в рублях и в цифровой валюте через модуль автовыплат</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Мерчант WATA; требования к статусу не раскрыты публично — уточнять при подключении</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>Ускоренная интеграция через API, заявленный запуск за 1 час</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Зависимость от одного контрагента; условия подключения и ставки не опубликованы публично</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>https://wata.pro/prodazhatelegramzvezd, https://wata.pro/faq</t>
+        </is>
+      </c>
+      <c r="P104" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Серые посредники по звёздам</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Перепродажа Telegram Stars дешевле официальной цены</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Нарушение правил Telegram по существу: схема строится на возврате платежа (chargeback) через банк или магазин приложений</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>РФ и СНГ, телеграм-каналы и боты</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Оплата продавцу картой/СБП/криптой</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Формально дешевле официальной цены; экономика держится на краденых картах, региональном арбитраже или фарме звёзд</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Нет резерва у продавца, но есть риск аннулирования звёзд постфактум</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Выплат как таковых нет</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Анонимный продавец без документов</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Продажа через ботов-панели</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Схема: продавец покупает звёзды официально (часто украденной картой), передаёт покупателю, затем инициирует возврат; Telegram отслеживает возвраты и автоматически аннулирует покупки, звёзды списываются с баланса бота и он может уйти в минус. Риски: бан аккаунта и бота, потеря выручки, вовлечение в чужое мошенничество (ст.159 УК РФ), вопросы по 115-ФЗ при потоке чужих средств</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>https://donatov.blog/post/pochemu-otnimayut-zvyozdy-i-podarki-v-telegrame-posle-pokupki-cherez-posrednikov, https://www.likeni.ru/events/telegram-annuliruet-zvezdy-podarki-i-premium-poluchennye-obmannym-putem/</t>
+        </is>
+      </c>
+      <c r="P105" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Google Play (In-App Purchase)</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Магазин приложений Google, продажа подписок через биллинг</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено с декларацией: приложение с VPN обязано использовать VpnService, пройти декларацию в Play Console, документировать использование в листинге и показывать prominent disclosure</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Глобально; РФ-разработчикам монетизация закрыта</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Google Play Billing (для РФ-аккаунтов не работает с 26.12.2024)</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Стандартная шкала: 15% для первых 1 млн USD в год и 30% свыше; для автопродлеваемых подписок 15% независимо от выручки; в ряде рынков новая схема 10-25% плюс 5% billing fee</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация разработчика: разовый сбор (не подтверждено в этой проверке)</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Google удерживает выручку до выплаты по порогу</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Для разработчиков с расчётным счётом в РФ: с 26.12.2024 продажи приостановлены бессрочно, последняя выплата 15.01.2025; выплат после этой даты не будет</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Аккаунт разработчика Google Play; для организации нужен D-U-N-S; минимальный возраст — 18 лет (не подтверждено отдельным документом в этой проверке)</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Да: автопродлеваемые подписки нативно</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Google Play Developer API, server-side проверка покупок</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Канал мёртв для РФ: невозможность монетизации и получения выплат при российском расчётном счёте</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>https://support.google.com/googleplay/android-developer/answer/15685001, https://support.google.com/googleplay/android-developer/answer/112622, https://support.google.com/googleplay/android-developer/answer/12564964</t>
+        </is>
+      </c>
+      <c r="P106" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Apple App Store</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Магазин приложений Apple, продажа подписок через IAP</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>ЖЁСТКОЕ ОГРАНИЧЕНИЕ п.5.4: приложения с VPN обязаны использовать NEVPNManager API и могут размещаться только разработчиками, зарегистрированными как организация (enrolled as an organization). Физлицо опубликовать VPN-приложение не может. Требуется декларация о собираемых данных до покупки и обязательство не передавать данные третьим лицам</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Глобально (кроме РФ-специфики)</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Apple In-App Purchase; собственные платёжные механизмы для разблокировки функциональности запрещены п.3.1.1</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Стандарт 30%, 15% для малого бизнеса (до 1 млн USD) и для подписок после первого года; точные условия программы не перепроверялись в этой сессии</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Apple Developer Program: 99 USD в год</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Apple удерживает выручку до выплаты по порогу</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Выплаты на банковский счёт; для российских разработчиков статус выплат в 2026 не подтверждён</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Только организация (юрлицо) для VPN-приложения; нужен D-U-N-S; минимальный возраст для enrollment — 18 лет</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Да: нативные подписки</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>App Store Server API / verifyReceipt для проверки чеков</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>VPN-приложение физически недоступно физлицу из-за п.5.4; плюс санкционные сложности с выплатами; п.3.1.1 запрещает продавать подписку в обход IAP</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.apple.com/app-store/review/guidelines/, https://developer.apple.com/programs/enroll/</t>
+        </is>
+      </c>
+      <c r="P107" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>RuStore</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Российский магазин приложений для Android</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: явного запрета VPN в изученных документах нет, но в 2023-2024 гг. в СМИ обсуждалась инициатива Совфеда ограничить скачивание VPN из RuStore — актуальный статус модерации VPN не подтверждён</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Карты РФ, СБП, баланс мобильного</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>По условиям приёма платежей размер вознаграждения определяется п.6.1 соглашения о распространении; по данным 2023 г. — от 0,9% до 3,35% при обороте менее 1 млн руб, далее до 10% в категории Медиа и до 15% в остальных</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>0 руб</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Мошеннические платежи удерживаются, но не более 3% дохода за период; возвраты списываются с дохода разработчика</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Доход перечисляется на расчётный счёт в течение 15 рабочих дней после окончания отчётного месяца (отчётный период — календарный месяц), только в рублях</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>ПРЯМОЕ ОГРАНИЧЕНИЕ: условия приёма платежей заключаются только с зарегистрированным в РФ юридическим лицом или ИП. Условия не применяются и не могут быть приняты физическим лицом. Программа для самозанятых существовала в 2023 г. (выплаты через VK Pay самозанятые, минимум 5000 руб) — действует ли она сейчас, не подтверждено</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Да: п.4.2 регулирует автоплатежи, не более чем за 8 часов до истечения оплаченного периода</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>RuStore API и система приёма платежей, серверные колбэки</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Нужен ИП или юрлицо — 15-летний основатель не подходит; самозанятый родитель тоже не подходит по букве условий приёма платежей</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rustore.ru/help/legal/devs/developers-offer, https://www.comnews.ru/content/226667/2023-06-08/2023-w23/magazin-prilozheniy-rustore-razreshil-zarabatyvat-fizicheskim-licam</t>
+        </is>
+      </c>
+      <c r="P108" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Huawei AppGallery</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Магазин приложений Huawei</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Не подтверждено: официальные страницы политики и расчётов отдаются только JS-рендером; явной политики по VPN получить не удалось</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Глобально, фокус на РФ и СНГ</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Huawei In-App Purchase</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено: официальную ставку комиссии получить не удалось</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Есть отдельный раздел расчётов для РФ на developer.huawei.com, содержание не получено</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Да (IAP-подписки)</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>Huawei IAP server-side verification</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено из-за недоступности документов; риск строить расчёт на непроверенных данных</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.huawei.com/consumer/ru/doc/help/settlement-0000001052983076</t>
+        </is>
+      </c>
+      <c r="P109" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Amnezia Premium (партнёрка)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено: провайдер сам продаёт обфусцированный VPN и принимает партнёров</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Глобально; русскоязычная аудитория целевая</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Оплата провайдеру; партнёр получает вознаграждение</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>До 40% с продажи Amnezia Premium и 30% с каждого продления (по данным партнёрской страницы); пример: 100 полугодовых продаж = 1000 USD, 100 годовых = 1720 USD сразу плюс 30% с продлений</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>0 руб, подача заявки через форму или Telegram @amnezia_affiliate</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено: сроки холда на странице не указаны</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Выплаты партнёру; рельсы (карта РФ/СБП/крипта) не подтверждены</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Заявка физлица возможна (форма + Telegram/email); требование юрлица не заявлено</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Да: 30% с каждого продления — рекуррентный доход</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская ссылка и личный кабинет; API автовыдачи доступа не заявлен</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Зависимость от провайдера; отсутствие публичных условий по выплатам в РФ; VPN-сервис может быть заблокирован в РФ</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>https://amnezia.org/en/partners</t>
+        </is>
+      </c>
+      <c r="P110" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>HideMy.name (партнёрка)</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено: провайдер сам продаёт VPN и приглашает партнёров</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Глобально; русскоязычный сервис</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Оплата провайдеру</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>До 50% с привлечённых покупок и 25% со всех продлений без ограничения по времени</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>0 руб, после регистрации выдаётся реферальная ссылка</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Выплаты партнёру; рельсы и минимум не подтверждены</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация партнёра; требование юрлица не заявлено</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Да: 25% с продлений без ограничения срока</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>Реферальная ссылка; API автовыдачи не заявлен</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Условия выплат не опубликованы; зависимость от провайдера; репутационные и юридические риски продажи VPN в РФ</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>https://hide.mn/en/faq/general-questions/cooperation-with-us/for-partners/</t>
+        </is>
+      </c>
+      <c r="P111" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>AdGuard VPN (партнёрка)</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено: провайдер продвигает партнёрскую программу</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Глобально</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Оплата провайдеру</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Ставка на странице программы не извлечена (страница отдаётся JS-рендером) — не подтверждено</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская ссылка</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Проверить условия и доступность выплат для РФ-партнёра напрямую</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>https://adguard-vpn.com/en/vpn-affiliate-program.html</t>
+        </is>
+      </c>
+      <c r="P112" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>KeepSolid VPN Unlimited (partners)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская/реселлерская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено: у провайдера есть раздел partnership для партнёров и партнёрская программа</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Глобально; русскоязычный интерфейс и сайт</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Оплата провайдеру</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Ставка не извлечена (страница отдаётся JS-рендером) — не подтверждено</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>Отдельно упоминается Telegram-бот VPN Unlimited</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Условия и выплаты для РФ-партнёра не подтверждены</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vpnunlimited.com/partnership/affiliates</t>
+        </is>
+      </c>
+      <c r="P113" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>NordVPN (партнёрка/white label)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено провайдером; критично проверить ограничения по странам и санкциям для партнёра из РФ</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Глобально</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Оплата провайдеру</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Ставка не подтверждена в этой проверке</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено; программы такого класса обычно платят через PayPal или банковский перевод, что неприменимо для физлица из РФ</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Обычно требуется партнёрская сеть (Admitad/Awin) и подтверждение личности; доступность для РФ не подтверждена</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрские ссылки/промокоды</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Высокий риск отказа в выплатах партнёру-резиденту РФ; санкционные ограничения</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.admitad.com/cz/store/offers/nordvpn-ww/</t>
+        </is>
+      </c>
+      <c r="P114" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Proton VPN (партнёрка)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено провайдером; доступность для РФ-партнёра не подтверждена</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Глобально</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Оплата провайдеру</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Ставка не подтверждена</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Через партнёрские сети (например Indoleads); рельсы для РФ не подтверждены</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация в партнёрской сети; доступность РФ не подтверждена</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрские ссылки</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Санкционные и платёжные ограничения для РФ-партнёра</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>https://indoleads.com/blog/new-offer-launched-proton-vpn-mail-drive-pass-webapp-affiliate-program/</t>
+        </is>
+      </c>
+      <c r="P115" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Ivacy VPN (white label)</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>White-label VPN</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено: у провайдера исторически есть white-label/affiliate предложение</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Глобально</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Оплата провайдеру</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Ставка не подтверждена в этой проверке</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>White-label панель (не подтверждено)</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Условия и доступность для РФ не подтверждены</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.postaffiliatepro.sk/adresar/ivacy-affiliate-program/</t>
+        </is>
+      </c>
+      <c r="P116" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>OrbVPN (reseller)</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Реселлерская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Разрешено: у провайдера есть отдельная документация для реселлеров</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Глобально</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Оплата через реселлерскую панель</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>Есть документация для реселлеров на docs.orbvpn.com</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Нишевый провайдер, условия и выплаты для РФ не подтверждены</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.orbvpn.com/en/reseller</t>
+        </is>
+      </c>
+      <c r="P117" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Instant-delivery шопы (типовой магазин автовыдачи)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Собственная витрина с автовыдачей, часто на бэкенде Digiseller</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Серая зона: правила задаёт владелец шопа, а не площадка; для приёма денег нужен собственный эквайринг или подключение к чужой кассе</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>СНГ</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Карты, СБП, крипта — зависит от владельца шопа</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Комиссия платформы-бэкенда (Digiseller 1,5-6%) плюс комиссия эквайринга; плюс доля владельца шопа, если продаёте через него</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Зависит от бэкенда</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Зависит от бэкенда</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Выплаты через владельца шопа; юридически это доход физлица без договора</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Чаще всего достаточно регистрации; договор с продавцом часто отсутствует</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>Зависит от реализации</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>Обычно есть API автовыдачи ключей</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Нет договора и защиты сделки; владелец шопа может исчезнуть с деньгами; репутация площадки не защищает продавца</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>https://digiseller.com/agreement, https://foxreload.com/ru/library/marketplaces/ggsel-commissions-payouts</t>
+        </is>
+      </c>
+      <c r="P118" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Telegram-боты-реселлеры (чужая касса)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Сторонний бот принимает деньги и передаёт вам заказ</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>Серая зона: правила задаёт владелец бота; часто это перепродажа чужих цифровых товаров без документов</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>РФ, СНГ</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Stars, карты, СБП, крипта</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>Реселлер обычно забирает 10-30% маржи; точная ставка определяется договорённостью и не подтверждена</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>0 руб</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>Зависит от владельца бота; гарантий нет</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>Расчёт между физлицами (перевод на карту), без договора и без закрывающих документов</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>Физлицо; верификации нет</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="L119" s="2" t="inlineStr">
         <is>
           <t>Зависит от реализации</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="M119" s="2" t="inlineStr">
         <is>
           <t>Автовыдача через API партнёра, если он его даёт</t>
         </is>
       </c>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="N119" s="2" t="inlineStr">
         <is>
           <t>Нет юридической защиты, риск неоплаты, риск быть крайним при претензиях покупателей и при проверке на дробление бизнеса/115-ФЗ</t>
         </is>
       </c>
-      <c r="O93" s="2" t="inlineStr">
+      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>https://core.telegram.org/bots/payments-stars, https://donatov.blog/post/pochemu-otnimayut-zvyozdy-i-podarki-v-telegrame-posle-pokupki-cherez-posrednikov</t>
         </is>
       </c>
-      <c r="P93" s="4" t="inlineStr">
+      <c r="P119" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P93"/>
+  <autoFilter ref="A1:P119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8146,7 +10278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8576,709 +10708,1317 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Paddle</t>
+          <t>Paddle (Paddle.com Market Ltd / Paddle Payments Ltd / Paddle.com Inc.)</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>MoR (merchant of record)</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: VPN and Proxies — Restricted Category, нужен enhanced due diligence</t>
+          <t>серая зона: VPN и прокси прямо названы в п.19 списка Prohibited Categories, но с пометкой «(Restricted Category)» — продавать можно только после усиленного due diligence и одобрения Paddle. Формально это не бан, но и не разрешение: заявка рассматривается вручную, отказ возможен на этапе Domain Review по AUP.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>5% + $0.50 за транзакцию; резерв и chargeback fee не раскрыты</t>
+          <t>Pay-as-you-go: 5% + $0.50 за транзакцию Paddle Checkout (подтверждено на https://www.paddle.com/pricing, проверено 2026-10-05); Paddle Invoicing с оплатой банковским переводом — 3.5%; Checkout Recovery — 10% от успешно восстановленной корзины; FX-маржа 2% (USD/EUR/GBP), 2.5% (CZK/DKK/NOK/THB), 3% (прочие валюты), плюс до 1.5% при выплате в валюте, отличной от Payment Currency; $15/€15/£15 за международный банковский перевод; chargeback/Pre-Chargeback Alert — до 20 GBP/USD/EUR или 40 AUD/CAD. Месячной платы нет — «No monthly fees, migration fees, or hidden extras». При среднем чеке ниже $10 — только индивидуальные условия.</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Юрлицо в поддерживаемой юрисдикции; РФ в unsupported countries -&gt; нет; VAT-номер не нужен</t>
+          <t>Юрлицо ИЛИ физлицо/ИП (sole trader) — для individuals/sole traders бизнес-верификация не требуется. KYC/KYB: обязательный Domain Review + Identity Verification + Business Identification (регистрационные документы и владельцы с долей &gt;25%) через сторонний сервис, плюс Supplier Information (финстатус, акционеры, UBO) по запросу. Обязателен живой сайт на HTTPS с описанием продукта, ценами, T&amp;C, Refund Policy, Privacy Policy и именем компании (для самозанятого — «legal name preferred»); продавать можно только через одобренные Supplier URLs, продажи вне одобренных доменов прямо запрещены. VAT/налоговый номер: требуется информировать Paddle при VAT-регистрации в ЕС и при её изменении. История процессинга не обязательна: «Processing statement ... If you don't have this due to being a new business, we'll take that into account during our review».</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Hosted checkout, REST API, вебхуки; сложность 2/5</t>
+          <t>API Paddle Billing, hosted checkout, overlay и inline checkout, webhooks, sandbox, отдельный домен для checkout; документация лучшая в группе (developer.paddle.com, есть .md-версии каждой страницы, Docs MCP, Postman-коллекция). Telegram-бот без сайта НЕ подходит: обязателен одобренный домен и запрет продаж вне одобренных Supplier URLs; checkout можно открывать только с согласованных домена/поддомена. Сложность интеграции: 2 — drop-in hosted checkout + webhooks, код простой; реальная сложность не в интеграции, а в прохождении Domain Review/AUP..</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>CCBill</t>
+          <t>Lemon Squeezy (Sold through Link, LLC f/k/a Lemon Squeezy LLC — Stripe company)</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>High-risk эквайринг</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: VPN в AUP не запрещён, но запрещены shell accounts и поддержка ботов</t>
+          <t>серая зона: VPN, прокси и обход блокировок нигде не названы — ни в Prohibited Products, ни в Appendix A ToS, ни в списке Stripe (обновление 22.09.2026). Но под запрет попадают «Services of any kind», а VPN-подписка — это услуга, а не цифровой товар, плюс действует общий пункт «Any products restricted by our payment processing partners». Риск отказа/suspension высокий, но формального бана по слову «VPN» нет.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>По запросу; публично только структура издержек (interchange, brand assessments, processor markup)</t>
+          <t>5% + 50¢ за транзакцию; +1.5% за международные (вне США) платежи; +1.5% за PayPal; +0.5% за подписочные платежи (итого для Kometa-кейса ~7%+ на международных подписках). Chargeback — $15 dispute fee. Payout fees: банк вне США 1% за выплату, PayPal $0.50 (США) / 3% (максимум $30) вне США. Маркетинговые сборы: +5% за восстановленные корзины, +3%/+2% affiliate. Месячной платы нет; для чеков ниже $10 — custom pricing.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Юрлицо, KYB, сайт с раскрытием условий подписки и триалов</t>
+          <t>Юрлицо не требуется — регистрация возможна как физлицо, но обязательна возможность получать выплаты на банк/PayPal в поддерживаемой стране; при подключении банковских выплат возможна проверка личности («you may be asked to verify your identity for fraud prevention»). VAT/налоговый номер не обязателен — LS как MoR сам считает и платит налоги; налоговые данные можно добавить в payout invoice. Сайт: ToS 3.4(d) разрешает использовать сервис только для продажи собственных продуктов «through the website» — модель «только Telegram-бот» не предусмотрена, нужен стор/сайт (LS даёт hosted storefront и checkout-ссылки).</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Hosted payment page, REST API, вебхуки; сложность 3/5</t>
+          <t>REST API + webhooks + hosted checkout, overlay checkout, hosted storefront, custom domain; документация хорошая (docs.lemonsqueezy.com, отдельные API-доки, официальный Laravel-пакет). Telegram-бот без сайта: checkout-ссылку технически можно отправить в бота, но LS ожидает собственный сайт/стор, а покупатели из РФ заблокированы на уровне платформы. Сложность интеграции: 2 — hosted checkout + API/webhooks, интеграция простая; сложность в модерации стора и в гео-ограничениях..</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>TailoredPay</t>
+          <t>FastSpring (Bright Market, LLC dba FastSpring; FastSpring B.V.; SalesRight Technologies ULC)</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Брокер high-risk эквайринга</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>ДА, заявляет: профильная страница VPN Merchant Account (тело страницы за Cloudflare не читается)</t>
+          <t>серая зона: VPN, прокси, «circumvention» и privacy-инструменты не упомянуты ни в Vendor ToS (§4.5), ни в Digital Retailer Terms (§6.2), ни в Restricted Countries. Запрещены только adult, tobacco, pharma, gambling, hate/violence, third-party processing и «any form of unlawful activity»; есть широкая формулировка про продукты, которые «do not contain devices which are intended to be used to perform illegal activities». Явного разрешения нет — решение принимает ручной underwriting.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>По запросу</t>
+          <t>по запросу (не публикуется) — pricing-страница перешла на «Build A Custom Quote»: единая flat-rate ставка зависит от GTV, числа транзакций и географии, публичных процентов больше нет (прежние публичные 5.9% + 95¢ не подтверждаются текущим сайтом). Опубликованы только дополнительные сборы: $20 за chargeback, $20 за chargeback prevention alert, FX-конвертация 3.5% (AUD/CAD/CHF/DKK/EUR/GBP/HKD/JPY/NZD/SEK/SGD/USD/ZAR) и 5.5% (прочие), $10 за возврат чеком и $30 за ручной банковский перевод, $15 за return SEPA/ACH, $20/мес за Abandoned Account, комиссии Hyperwallet по тарифам провайдера.</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Типично юрлицо (US/EU/offshore) и KYC; определяет принимающий банк</t>
+          <t>Требуется бизнес-регистрация: Vendor ToS §4.1 прямо перечисляет «personal information of Vendor's beneficial owners, business registration information, tax identification number, and bank account information»; заполняется Tax Questionnaire (W-8/W-9) для налогового статуса; онбординг и underwriting — на усмотрение FastSpring, при отказе причины не сообщаются. Наличие сайта подразумевается (в форме квоты поле «Website» обязательно). Возможность онбординга физлица/самозанятого и требования к VAT/GST-номеру публично не описаны — не подтверждено.</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Отдельного продукта нет: посредничество и согласование; сложность 4/5</t>
+          <t>REST API, webhooks, Store Builder Library, hosted и embedded/branded checkout, тестовая среда, подробная документация (developer.fastspring.com, есть llms.txt-индекс и code samples). Продажа возможна только через продукты, зарегистрированные в дашборде FastSpring; Telegram-бот без сайта — не подтверждено (сайт ожидается при онбординге/квоте). Сложность интеграции: 3 — API и Store Builder Library мощные, но онбординг sales-led (квота), underwriting и настройка стора требуют времени..</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Telegram Stars (Bot Payments)</t>
+          <t>Cleverbridge</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Telegram-нативный</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Не регламентировано: модерации тематики нет, но цифровые товары в Telegram обязаны продаваться за Stars</t>
+          <t>да (с оговоркой). В письменной Acceptable Conduct Policy слова VPN/proxy/anonymizer НЕТ — список запретов общий и прямо назван неисчерпывающим, формально это «серая зона» текста. Но фактически VPN принимается: у Cleverbridge есть отдельная вертикаль Cybersecurity, и VPN-провайдер CyberGhost обслуживается через чекаут cleverbridge.com (живой поддомен cyberghostvpn-s.cleverbridge.com, ссылка на чекаут CyberGhost Premium на cleverbridge.com/848/). Для Kometa это означает: VPN не запрещён, но решение принимается на KYC/due-diligence по продукту и рынкам.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Спред Telegram 7,8%: покупка 1000 Stars = 1,41 USD, вывод 1000 Stars = 1,30 USD</t>
+          <t>по запросу (не публикуется). Официальная страница https://grow.cleverbridge.com/pricing не содержит тарифов: «Get custom pricing»/«Get a Quote». В MoR-термс (п.7.1) Resale Fee = процент из Fees Table × Total Cart Value + фиксированная сумма, где и процент, и фикс заданы в индивидуальном Subscription Schedule; там же — FX-надбавка за конвертацию. Сторонний бенчмарк (Vendr, обновлено февраль 2026, НЕ официальные данные): 3,5–8% от GMV, медиана сделки $3,482/год; начальные котировки мид-маркет 5–7%, согласованные 4–6%; enterprise 2,5–5% + платформенная плата $50k–200k/год; сквозные платёжные издержки 2–3%; FX 1–2% сверх спота; заявлено, что TCO на 20–40% выше заявленной ставки.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Только Telegram-аккаунт владельца бота и 2FA-пароль; документы, ИП, ООО, самозанятость не требуются</t>
+          <t>Нужно юрлицо/компания: онбординг-чеклист требует company-register extract, учредительные документы, подтверждение зарегистрированного/операционного адреса, ownership structure chart, ID документы, proof of authority to represent. Возможность оформления на физлицо/самозанятого: не подтверждено (все формулировки — «your company»/«the business, its owners and representatives»; отдельного individual-пути, в отличие от 2Checkout, в документации нет). KYC/KYB: полноценный — идентичность компании, ownership/control/authority, санкционные и PEP-проверки, проверка продуктов/клиентского пути/целевых рынков, платёжные, fraud, кредитные, налоговые, юридические и репутационные факторы; возможен исход «Not approved» или «Approved with conditions». Обязателен полноценный сайт: product pages, прозрачные цены и условия подписки, checkout URLs/скриншоты, fulfillment, post-purchase письма, доступная поддержка, refund/cancellation policy, ToS, privacy notice. Экспорт-контроль: требуется предоставить ECCN/EAR99-классификацию продукта. Налоговый номер: VAT ID компании нужен для контрактного лица (у самой Cleverbridge GmbH VAT DE244822460); требование VAT/GST именно от клиента прямо не сформулировано — не подтверждено.</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Bot API sendInvoice currency=XTR + successful_payment; сложность 1 из 5</t>
+          <t>Хостед-чекаут Online Store + Commerce Assistant (CA)/Subscription Commerce Manager (SCM) для управления продуктами, REST API (dev.cleverbridge.com), вебхуки (PaidOrderNotification), готовые интеграции с CRM/ERP/бухгалтерией/аналитикой, SFTP-выгрузка клиринг-файлов. Telegram-бот без сайта: скорее всего не подойдёт — онбординг прямо требует product pages, product/checkout URLs, скриншоты чекаута, ToS, privacy notice и refund policy; в разделе «Restrictions and special requirements» отдельно запрашивают информацию о категориях, которые платёжные провайдеры и карточные сети считают повышенно рискованными. Приемлемость bot-only витрины без сайта не подтверждена — не подтверждено. Сложность интеграции: 4 — хостед-чекаут снижает объём кода, но вход энтерпрайзный: обязательный sales-процесс, KYC/due diligence с исходом «Not approved», обязательный сайт и кастомная имплементация (по сторонним оценкам — недели-месяцы)..</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Tribute</t>
+          <t>MyCommerce (Digital River MyCommerce / Share-It)</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Telegram-нативный посредник</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: VPN, прокси и анонимайзеры в списке запрещённых категорий отсутствуют, но товар проходит ручную модерацию со статусами pending/approved/rejected</t>
+          <t>серая зона, но вопрос практический смысла не имеет: в 2026 г. действующей политики нет, потому что сервиса нет. Платформа MyCommerce — это торговая марка германского юрлица Digital River GmbH (оно же Share-It), которое ушло в неплатёжеспособность; домен mycommerce.com теперь занят не связанным с платежами испаноязычным классифайдом («Compra y Vende de Todo, a Todos», © 2026 MyCommerce). VPN отдельно не запрещался и не разрешался; MoR исторически продавал софт и антивирусы (EnigmaSoft SpyHunter), но онбординг новых мерчантов прекращён.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>10% с каждой успешной транзакции, включая комиссию сервиса и платёжных провайдеров, плюс динамический сервисный сбор (размер зависит от суммы платежа, точные значения не опубликованы)</t>
+          <t>по запросу (не публикуется). MSA п.5(a): DR Margin — «the revenue share percentage and/or flat fee that you select upon registration», то есть индивидуальная ставка, публичного тарифа нет. Показательно для оценки: по сообщениям мерчантов на Hacker News (октябрь 2024) маржа MyCommerce составляла «between 5 and 10%, depending on order size and how much of currency exchange they take». Chargeback fee также не публиковался: «in an amount agreed between the parties and/or further described in the Administration Interface».</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Регистрация через @tribute в Telegram; документы и статус не требуются; для выплат есть страница новых требований к данным, содержимое не проверено</t>
+          <t>Юрлицо: MSA адресован «you» и «Company»; п.9(b) требует от клиента гарантий прав на продукты; п.14(c) обязывает предоставить экспортные классификации (ECL, USML, HTS) и назначить ответственного за экспорт-контроль. Возможность оформления на физлицо/самозанятого: не подтверждено. Налоги: клиент сам отвечает за сбор и перечисление sales/GST/VAT по продаже продуктов Digital River и по запросу выдаёт валидный tax invoice на VAT. KYC: в 2024 г. Digital River массово разослал требования пройти новые KYC-формы («Digital River emailed out of the blue a few months back saying we need to do new Know-Your-Customer paperwork. The forms are painful... it seems to take a week or more for any response to a ticket»). Требования к сайту — не подтверждено.</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Платёжная ссылка + API + вебхук new_digital_product с HMAC-SHA256 в заголовке trbt-signature, ретраи 5 мин / 15 мин / 30 мин / 1 час / 10 часов; сложность 2 из 5</t>
+          <t>не подтверждено для 2026 г. Исторически: hosted checkout («Checkout Solution»), Administration Interface для управления продуктами, отчётность, email/download-фулфилмент, возможность самостоятельного фулфилмента клиентом (MSA п.4(e)), возвраты и обработка chargeback'ов в течение 2 месяцев после расторжения (п.6(c)). Telegram-бот без сайта: не подтверждено и, учитывая состояние сервиса, неактуально. Сложность интеграции: 5 — интеграция перестала иметь смысл: платформа не работает, онбординг отсутствует, деньги мерчантов не выплачены; любой новый контракт невозможен..</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>FunPay</t>
+          <t>2Checkout (Verifone) — планы 2Sell / 2Subscribe / 2Monetize / Enterprise</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Площадка цифровых товаров</t>
+          <t>MoR/SaaS-биллинг — гибрид: 2Monetize это полноценный Merchant of Record (включая global tax &amp; regulatory compliance), а 2Sell/2Subscribe — обычный PSP-шлюз. Это НЕ high-risk эквайринг.</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: прямого запрета VPN нет, но п. 2.2.5 запрещает подписки на сервисы без спецраздела, а п. 2.1.12 запрещает размещать объявления на других площадках под угрозой отказа в выплатах</t>
+          <t>серая зона (де-факто отказ): слова «VPN» в Prohibited Product List нет, но VPN попадает под п.44 «Remote Access Services, Technical Support Services», а сам список оговорён как «merely representative, but not exhaustive» и «your business practices, products and services may not be approved ... regardless of whether they appear below». Плюс полный запрет РФ и запрет приёма мерчантов из Грузии.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Не подтверждено: три слоя (сбор с продажи, сбор за вывод, стоимость платёжного метода), ставки не опубликованы</t>
+          <t>2Sell — 3.5% + $0.35 за успешную продажу; 2Subscribe — 4.5% + $0.45; 2Monetize — «Tailored pricing» (не публикуется); 4Enterprise — «Custom Pricing». Дополнительно: «In specific countries an additional 2% fee applies to accept payments from shoppers outside your own country» (список стран в Knowledge Center). Chargeback: «If your chargeback rate is less than 0.65%, the chargeback fee is $36/€31/£30. If your chargeback rate is 0.65% or more, the chargeback fee is $50/€50/£50» — то есть пороговая схема. Платёж на банковский счёт (wire) — 15 USD/GBP/EUR, только для 2Sell и 2Subscribe; PayPal — без комиссии 2Checkout; Pre-paid 2Checkout MasterCard (Payoneer) — без комиссии 2Checkout. Месячная абонплата/минимум оборота не публикуется. Минимальный порог выплаты: 50 USD/EUR/GBP (2Sell, 2Subscribe) или 100 USD/EUR/GBP (reseller на 2Monetize).</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Физлицо, регистрация свободная; документы для вывода не подтверждены</t>
+          <t>Юрлицо не обязательно: физлицо без компании допускается («Yes, this option is currently available in the application form for any type of account»). KYC для individuals: «Valid government-issued ID such as a passport or national identity card» + «Valid address proof, such as electricity bill, telephone bill (no older than two months from the date when you upload the scanned copies)» + дополнительные документы. Для компаний: «Company ownership documents (such as Articles of Incorporation or Organization, showing beneficial ownership)», налоговые документы («Europe - TIN», «US - SSN / TIN / PTIN»), «Valid government-issued ID... Include DOB, for anybody with 10% or more ownership in the company». Все документы — сканы, не просроченные. Обязательно одобрение underwriting-команды (до этого аккаунт в demo mode). Сайт: обязателен URL — buy-link вставляется «into the web page that will host the purchase button/link»; для 2Sell/2Subscribe можно несколько URL, «The request to add a new URL on the account requires risk review and approval»; для 2Monetize «this is limited to pointing towards 1 URL» и каждый новый сайт требует отдельного аккаунта. Требуются размещённые на сайте refund policy и privacy policy, полное описание продукта и сроков доставки.</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Ручная или автоматическая выдача; автовыдача прямо запрещена для товаров, требующих общения или доп. услуг; сложность 2 из 5</t>
+          <t>Способы: хостируемый checkout (ConvertPlus, InLine Checkout, Default Flows), buy-links / payment links (в т.ч. генерация ссылок из панели), REST/JSON-RPC API 6.0, legacy SOAP API 6.0, webhooks, тестовые заказы и sandbox, 120+ готовых коннекторов (WooCommerce, Shopify, Magento 2, WHMCS, Wix, Ecwid, PrestaShop и др.). Документация обширная и качественная (docs.2checkout.com с Markdown-версиями и llms.txt). Магазин без сайта: сам buy-link технически можно разместить где угодно, но аккаунт всё равно требует зарегистрированный и одобренный URL, а под 2Monetize — ровно один сайт на аккаунт; поэтому чисто Telegram-бот без сайта, скорее всего, не пройдёт underwriting. Практический обход — сделать простой сайт-витрину с refund/privacy policy и вести трафик из бота. Сложность интеграции: 3 — документация и хостируемый checkout/buy-links делают техническую часть простой, но обязателен одобренный сайт-URL, ручной underwriting и KYC; для Telegram-бота без сайта узкое место — комплаенс, а не код..</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>PayMaster</t>
+          <t>Sellfy</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: оферта молчит, требование общее - товары не должны входить в список запрещённых к продаже; VPN прямо не назван</t>
+          <t>серая зона (де-факто нет): VPN прямо не назван, но Sellfy — площадка цифровых ФАЙЛОВ, а не сервисов, и она прямо запрещает «No selling of services that advertise access to video and/or audio broadcasts, channels, or apps» (пункт IPTV). Дополнительно: цифровые товары нельзя продавать на бесплатном плане, а аккаунт блокируется навсегда без возврата подписки.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2-5% с каждой успешной транзакции в зависимости от вида платежа; ежемесячных и скрытых платежей нет</t>
+          <t>Платная подписка с 14-дневным триалом (в триале чекаут отключён): Starter $39/мес ($348/год), Business $79/мес ($708/год), Premium $159/мес ($1428/год). Транзакционной комиссии Sellfy нет: "There are no transaction fees from Sellfy". Годовой лимит выручки по тарифам: $10K / $50K / $200K, при превышении возможна overage-плата 2%. Комиссии процессоров: PayPal 2.9% + $0.30 в США и в среднем 3.4% + $0.30 по миру, Stripe 2.9% + $0.30. Комиссия за chargeback отдельно не публикуется. Месячного минимума нет.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Есть публичный вход для физлиц (кнопка У меня нет юр. лица) и отдельный для юрлиц и ИП; нужен готовый ресурс с товарами, ценами и офертой; заявленный срок подключения 2 дня</t>
+          <t>Регистрация юрлица не требуется (Sellfy: "you don't need a registered business entity (like an LLC or Corporation) to use Stripe"), но для продажи подписок PayPal требует Business-аккаунт. Налоги — ваша ответственность: Sellfy не является MoR, есть только инструменты (расчёт EU VAT, отчёты, возможность ограничить продажи в EU/UK). Требований к VAT/GST номеру платформа не выставляет. Глубина KYC — на стороне PayPal/Stripe.</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>API, платёжный виджет, модули CMS, Payment notification POST-вебхук с MD5-подписью, защита от дублей, тестовый режим, подключение к Telegram; сложность 2 из 5</t>
+          <t>Хостед-магазин и чекаут, кастомизация чекаута, вебхуки (docs sellfy article 127), license keys с API и вебхуками, Zapier, встраиваемая корзина на свой сайт, приложение для Wix. Для Telegram-бота без сайта: можно давать ссылки, но доступ выдаётся к файлам в Sellfy, а не к внешнему VPN-сервису. Сложность интеграции: 3 — техника простая (вебхуки, license keys), но продуктовая модель «выдача файла» ломает сценарий VPN-подписки.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>RollyPay</t>
+          <t>Payhip</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
+          <t>MoR/SaaS-биллинг (фактически storefront, не полный MoR)</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: в оферте и на сайте VPN, прокси и анонимайзеры не упомянуты, тематика решается менеджером после проверки проекта</t>
+          <t>серая зона. VPN в списке запрещённых продуктов не назван; запрещены get-rich-quick, порнография, файлохостинг, азартные игры, виртуальные карты, card sharing и т.п. Но Payhip прямо обязывает соблюдать правила платёжных провайдеров: "In addition to our terms, you will need to comply with the terms of our payment providers" (PayPal AUP и Stripe restricted businesses), а также запрещает "Products that violate laws to which you are subject". Поскольку VPN-сервис формально не запрещён самой Payhip, но полностью зависит от Stripe/PayPal, итог — серая зона, которая на практике закрывается для РФ из-за отсутствия платёжного плеча.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Крипта от 1%; по данным представителя сервиса СБП QR от 5% и карты РФ от 5% - это заявление в неофициальном канале, а не текст оферты</t>
+          <t>Free Forever — 5% с транзакций; Plus $29/мес — 2%; Pro $99/мес — 0% от Payhip. Процессорные комиссии сверху (Stripe стандартно 2.9% + $0.30). Комиссия за chargeback и месячный минимум отдельно не публикуются.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Подключение доступно физлицам, самозанятым, ИП и компаниям после проверки проекта; публичной оферты с перечнем запретов нет</t>
+          <t>Юрлицо не требуется, регистрация не упоминается; обязателен аккаунт PayPal и/или Stripe на ваше имя. Подписки технически работают только через Stripe: "Each instalment of the subscription is deposited to your Stripe account". Налоги: Payhip автоматически считает и удерживает EU VAT и UK VAT (можно отключить), есть разделы про US и Canada sales tax; полноценным MoR платформа себя при этом не называет.</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>REST API, вебхуки, SDK на Node.js, PHP, Python, готовые модули и платёжные ссылки, тестовый режим; сложность 2 из 5</t>
+          <t>Хостед-чекаут, страницы продуктов, memberships-кабинет покупателя, вебхуки с 4 событиями (paid, refunded, subscription.created, subscription.deleted), подпись запроса hash('sha256', apiKey), license keys API, Zapier, реферальная программа. Для Telegram-бота это один из самых удобных вариантов: бот получает webhook paid/subscription.created и выдаёт доступ сам, без сайта. Сложность интеграции: 2 — хостед-чекаут + понятные вебхуки с подписью, магазин без сайта допустим и не требует отдельной витрины.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Digiseller (digiseller.market)</t>
+          <t>Ko-fi</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Платформа цифровых товаров и витрин (движок для GGsel и др.)</t>
+          <t>MoR/SaaS-биллинг (фактически платформа донатов/магазина; не PSP и не MoR)</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: VPN в запретах не упомянут; запрещены товары, нарушающие законодательство, и абстрактные/неописанные товары (п.1.2.4)</t>
+          <t>серая зона со склонностью к «нет». VPN прямо не упомянут. Ko-fi запрещает использовать сервис для всего, что запрещено PayPal и Stripe: "creators can't use Ko-fi in ways that go against PayPal's acceptable use policy or Stripe's prohibited businesses". Магазин Ko-fi заточен под товары, а не услуги: "Creators can sell digital and physical products in a Ko-fi Shop" (файлы, шаблоны, софт, мерч), а услуги существуют только как Commissions. Длящаяся VPN-подписка в эти категории не помещается; дополнительно Ko-fi оставляет за собой право запросить объяснение по членствам с офсайт-доставкой: "If we have reason to believe that prohibited content is being provided offsite but through Ko-fi (e.g. being offered via Memberships), we may need to verify this with you".</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Комиссия DS 1,5-6% в зависимости от тематики, но не менее 0,02 WM; сверху комиссия платёжного метода и стоимость вывода</t>
+          <t>Ko-fi Free: 0% с разовых чаевых, 5% со всего остального (shop, memberships, monthly tips, commissions). Standard (тоже $0/мес): 5% со всех типов, включая разовые чаевые. Ko-fi Gold — платная подписка, её цена в справке не указана. Сверху — обычные комиссии процессора, обычно около 3% + $0.30. Комиссия за chargeback и месячный минимум не публикуются.</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>П.1.2.1: клиентом DS может стать только лицо, прошедшее идентификацию в системе WebMoney; регистрация как физлицо возможна</t>
+          <t>Юрлицо не требуется; обязателен аккаунт PayPal и/или Stripe на ваше имя. Требуется статус 18+ ("You must be 18 years old or older to use Ko-fi and create an Account"; для аккаунтов младше 18 — анпаблиш до подтверждения возраста по документу). VAT/GST номер не запрашивается; налоги — ваша ответственность ("Taxes are your responsibility, we don't collect or pay taxes on your behalf"). KYC — на стороне PayPal/Stripe. Дополнительно Ko-fi запрашивает местоположение и может проводить verification check.</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Есть API Digiseller для автоматической выдачи ключей и внешних витрин</t>
+          <t>Хостед-страница, Shop, Memberships, Commissions, webhook только на платежи (HTTP POST, повтор при не-200), zapier, Discord-бот, виджет и кнопка для сайта. Для Telegram-бота подходит технически (webhook → выдача доступа), но продавать придётся «товар/членство», а не VPN-сервис. Сложность интеграции: 2 — вебхук на оплату и простые ссылки на страницу/магазин; сложность не в технике, а в том, что VPN-подписка не вписывается в продуктовую модель.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Plati.Market</t>
+          <t>Patreon</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Маркетплейс цифровых товаров (та же экосистема, что Digiseller)</t>
+          <t>MoR/SaaS-биллинг</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: в Приложении 1 (перечень запрещённых товаров) VPN не упомянут; прямо разрешены к продаже сервисы подписки</t>
+          <t>серая зона. VPN прямо не упомянут, но у Patreon двухуровневая система правил: Community Guidelines для всего контента и отдельные Commerce Guidelines именно для бенефитов и офферов. Terms of Use фиксирует: "You may only post material to Patreon that is permissible under our Community Guidelines. And creators may only provide membership benefits and offerings that are also permissible under our Commerce Guidelines". Сводка правил: "we don't allow: illegal material or benefits; material or benefits that are abusive towards other people; material or benefits that are misleading or deceptive; material or benefits that use others' intellectual property...". VPN-доступ как бенефит членства под эти формулировки прямо не подпадает, но и не разрешён явно; отдельно требуется категоризация бенефитов для налоговых целей.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Комиссия от 3% от суммы платежа (заявлено на странице для продавцов)</t>
+          <t>Платформенная комиссия 10% для страниц, опубликованных после 4 августа 2025 (легаси-создатели сохраняют прежние условия). Процессинг: карты/Apple Pay и PayPal/Venmo США — 2.9% + $0.30; PayPal/Venmo вне США — 3.9% + $0.30; для не-USD выплат 3.0–3.9% + фикс. Комиссия за конвертацию валюты 2.5% с платежа в валюте, отличной от вашей валюты выплат. Разовые покупки — платформенная комиссия 5–12%. Комиссия выплат: банковский перевод Payoneer $0.50 (локальная валюта) или $0.25 + 1.55% (USD→локальная валюта), PayPal 1% (min $0.25, max $20), Payoneer Wallet $1.00; минимумы $10 (PayPal/банк) и $25 (Payoneer Wallet). Комиссия за chargeback отдельно не публикуется. iOS IAP — 30% сверху (кроме США).</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Физлицо без документов; при отрицательном отзыве без аттестата возможна блокировка счёта и продаж</t>
+          <t>Юрлицо не требуется; аккаунт создателя — 18+ или с разрешения родителя/опекуна (важно для 15-летнего основателя: формально страница возможна с согласия родителя). Нужны налоговые данные (Patreon отчитывается перед налоговыми органами и может удерживать налог при неполных данных), платёжные реквизиты, а также проверка страницы перед запуском ("Why is my account under review?"). VAT/GST номер не требуется — Patreon сам собирает и перечисляет transaction taxes. Требуется независимая категоризация бенефитов по налоговым категориям.</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>API и автовыдача уникальных кодов (автоматически создаваемые уникальные коды)</t>
+          <t>Хостед-страница создателя, Patreon API, вебхуки, RSS, Patreon app, Patreon embeds. Для Telegram-бота плохо подходит: покупатель платит за членство на Patreon, а доступ к VPN пришлось бы выдавать по вебхуку, при этом Patreon остаётся витриной и биллинговой сущностью. Сложность интеграции: 3 — API и вебхуки есть, но продукт заточен под контент и членство на своей витрине, а не под внешний сервис.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>GGsel</t>
+          <t>CCBill (CCBill LLC, США; CCBill UK Limited, FCA 936980; CCBill IE Limited, Central Bank of Ireland C569018)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Витрина цифровых товаров на бэкенде Digiseller</t>
+          <t>High-risk эквайринг/PSP. Два продукта: PSP (суб-мерчант под мастер-аккаунтом CCBill, ISO/MSP и PSP/Payment Facilitator банка Esquire Bank NA) и ISO (свой MID). НЕ Merchant of Record: в Merchant Terms and Conditions прямо сказано "Merchant acknowledges its responsibility as the consumer facing entity".</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: наследует правила Digiseller; VPN отдельно не упомянут</t>
+          <t>серая зона: слова VPN/proxy/anonymizer нет ни в Merchant Acceptable Use Policy (v.15, июль 2026), ни в EU-версии AUP, ни в Merchant Terms and Conditions (v.21, июль 2026). Ключевой риск — не политика, а формулировки о деньгах и о правилах карточных сетей.</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Сбор площадки зависит от раздела и условий продавца; публичной ставки нет; расчёты идут через Digiseller, плюс стоимость платёжного метода и вывода</t>
+          <t>Проценты на собственном сайте CCBill НЕ публикуются — на странице /pricing описаны только типы сборов (interchange, card brand assessments, processor markup) и 4 модели ценообразования (Flat Rate для PSP; Interchange Plus / Tiered / Discount Plus для ISO) без цифр. Опубликовано: "High-risk merchants are required to pay annual VISA and mastercard registration fees ... Visa $950 / Mastercard $1000" и "Flat Rate ... No monthly fees". Сторонние источники (Merchant Machine, январь 2026; GuidingDecisions, март 2026): Standard 3.9% + $0.55 за транзакцию; High-risk ("Blue") 5.9% + $0.55; Adult 10.8%-14.5%; для транзакций дешевле $10 — surcharge 3%; на большинстве планов рефанды и chargeback fee не взимаются; annual registration fee $500 для dating и $1,000 для остальных high-risk категорий, setup fee и monthly fee отсутствуют.</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Требуется идентификация WebMoney (наследуется от Digiseller)</t>
+          <t>Юрлицо ИЛИ sole proprietor в поддерживаемой стране; принципал должен быть в той же стране; бизнес-банк-счёт обязательно в стране инкорпорации; деятельность должна попадать в поддерживаемые индустрии и AUP; обязателен живой работающий сайт: "Fully functional, live website / Listed products / services / Clearly displayed pricing / Clearly displayed contact information / Specified Terms &amp; Conditions / Defined Privacy Policy / Temporary access to restricted/members only areas". VAT/Tax ID в явном виде не описан, но 1099-K FAQ и налоговый раздел T&amp;C предполагают налоговую отчётность. По сторонним данным большинство заявок без кредитного чека.</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Автовыдача мгновенных кодов; API наследуется от Digiseller</t>
+          <t>RESTful Transaction API (payment tokens, 3DS/non-3DS, deferred charges), legacy API, Advanced Widget API, Webhooks (overview + user guide), FlexForms hosted checkout с A/B тестами и CSS-кастомизацией, GitHub-репозитории, готовые модули WooCommerce 3.0 (октябрь 2025, + патч январь 2026), osCommerce, X-Cart, DatingPro, NATS4. Чистый Telegram-бот БЕЗ сайта не пройдёт: обязательны "Fully functional, live website", явные цены, контакты, Terms и Privacy Policy. Дополнительно есть ограничение выгрузки данных: Data Link Extract отдаёт CSV окнами максимум 24 часа и не чаще одного раза в 60 минут. Сложность интеграции: 3. API/webhooks/FlexForms документированы хорошо и есть готовые модули, но обязателен живой сайт с полным набором юридических страниц, плюс неочевидные вещи вроде дефолтного минимума цены $2.95 и лимитов выгрузки данных..</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Google Play (In-App Purchase)</t>
+          <t>Verotel (торговая марка Yoursafe B.V., Нидерланды, KvK 34180575; ранее Payment Institution, с 2019 — Electronic Money Institution)</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Магазин приложений Google, продажа подписок через биллинг</t>
+          <t>High-risk эквайринг/PSP (IPSP + Payment Facilitator Visa/MasterCard/JCB/Discover/Diners; деньги держатся в эскроу Stichting Geldbeheer Verotel). НЕ Merchant of Record: договор называет продавцом Merchant ("the individual or business entity listed under Merchant Company Name"), Verotel лишь процессит и выдаёт Subscription Code.</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Разрешено с декларацией: приложение с VPN обязано использовать VpnService, пройти декларацию в Play Console, документировать использование в листинге и показывать prominent disclosure</t>
+          <t>серая зона. Ни на одной публичной странице Verotel (главная, pricechart, productchoice, integration, paymentprocessing, contactus, merchantagreement) нет слов VPN, proxy, anonymizer, circumvention или privacy tools. Более того, content policy вообще НЕ публикуется: в Merchant Agreement сказано "Merchant is fully responsible for the contents of Merchant's Web site and follow the content policy of Company. The content policy of Company will be sent on request and is published on www.verotel.com" — но на сайте её нет (проверены все разумные URL, все 404). Позиционирование строго adult/entertainment: "Process credit cards for your entertainment website", "Solutions for Webmasters selling Online Entertainment", "Adult? No problem!", "perfect solution for cam sites". Сторонний обзор перечисляет обслуживаемые индустрии (Adult, CBD &amp; Hemp, Cigars &amp; Tobacco, Dating, Electronics, Gaming, Gas Station, Hosting, Marijuana/Cannabis, SAAS, SEO &amp; SEM, Smoking Accessories, Travel, Web Design) — VPN там отсутствует, но есть близкие Hosting и SAAS.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Стандартная шкала: 15% для первых 1 млн USD в год и 30% свыше; для автопродлеваемых подписок 15% независимо от выручки; в ряде рынков новая схема 10-25% плюс 5% billing fee</t>
+          <t>Полностью публично. BASIC: EUR 500/год регистрация (для Visa/MC registration и compliance monitoring) + фиксированные 15,5% с транзакции независимо от объёма. PREMIUM: EUR 0/год, ступенчато по среднему недельному обороту: 1-1.000 EUR = 14,0%; 1.001-2.000 = 13,9%; 2.001-3.000 = 13,8%; 3.001-4.000 = 13,7%; 4.001-5.000 = 13,6%; 5.001-7.000 = 13,5%; 7.001-10.000 = 13,4%; 10.001-17.500 = 13,3%; 17.501-25.000 = 13,2%; 25.001-40.000 = 13,1%; 40.000+ = 13,0%. Обязательный недельный минимум для PREMIUM: EUR 100/нед; если недельный оборот менее EUR 1.000 — доп. сбор EUR 25/нед. Наценка на рекуррентные транзакции +1,5% (не применяется к первой транзакции подписки). Chargeback fees — нет, refund fees — нет. Но: "If the number of transactions in the last four weeks, with a two-week lag period, exceeds 50 transactions ... If this ratio is 1.0% or more, a surcharge of 2.5% will apply to the base rate." Verotel US-Check и Direct Debit Europe: 15,5% (Basic) / 14,0% (Premium).</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Аккаунт разработчика Google Play; для организации нужен D-U-N-S; минимальный возраст — 18 лет (не подтверждено отдельным документом в этой проверке)</t>
+          <t>Юрлицо НЕ обязательно — в договоре "Merchant" определён как "the individual or business entity listed under Merchant Company Name", а на странице About сказано: "Our account offerings are specifically tailored to all payment processing needs: from the sole proprietor with a small website to larger merchants with a portfolio of online properties." То есть sole proprietor/ИП концептуально возможен. Обязателен собственный сайт и контент ("you supply the website and the content"), сайт должен соответствовать content policy (не публикуется, выдаётся по запросу). Регистрация Visa/MC и compliance monitoring включены в годовой платёж. KYC/AML по нидерландским Wwft и Wft: "The Merchant is obliged to actively supply the Company at all times with necessary information or documents which the Company or its affiliates need to comply with relevant Dutch laws and regulations and more specifically by virtue of the Wwft and/or Wft." Для adult-контента может запрашиваться документация по 18 U.S.C. §2257 ("Failure to comply ... may result in immediate suspension of processing"). PREMIUM требует 6 месяцев процесссинговых стейтментов — то есть фактически processing history обязательна для дешёвого тарифа; BASIC истории не требует. VAT/налоговый номер явно не требуется в тексте, но налоги — на мерчанте.</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Google Play Developer API, server-side проверка покупок</t>
+          <t>Hosted order pages (мультиязычные, кастомизируемые логотипом/цветом), VerotelRUM — скрипт на сервере мерчанта (библиотеки ASP v1.0 и Perl v1.0, документация PDF), Verotel может установить RUM бесплатно; Verotel FlexPay API v3.x (любая сумма и описание, one-click, upgrade, подписки) + PDF-документация; Control Center API (https://controlcenter.verotel.com/api-doc/index.html); OpenAffiliate. Чистый Telegram-бот без сайта не подойдёт: RUM работает через postback на сервер мерчанта, а сам Verotel требует "you supply the website and the content". Сложность интеграции: 3. Hosted-страницы и postback технически несложные, документация и библиотеки открыты, но обязательны собственный сайт и (для RUM) серверный скрипт с postback; плюс для PREMIUM нужны 6 месяцев стейтментов, а для BASIC — EUR 500/год и ставка 15,5%..</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Amnezia Premium (партнёрка)</t>
+          <t>Payop (юрлицо: Transferop Payment Gateway Ltd., Ванкувер, Канада)</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
+          <t>High-risk эквайринг/PSP — фактически платёжный шлюз/агрегатор, а не прямой банк-эквайер и не MoR</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Разрешено: провайдер сам продаёт обфусцированный VPN и принимает партнёров</t>
+          <t>серая зона. VPN, proxy, anonymizer, circumvention, «privacy tools» и «unblocking» не упомянуты ни разу ни в списке Prohibited Industries в Acceptable use policy, ни в FAQ-списке моделей, с которыми Payop «не работает». При этом смежные ниши прямо запрещены: в FAQ указаны «IPTV - Internet television» и «Video hosting». Практического значения это не имеет: Payop полностью закрывает Россию и как юрисдикцию мерчанта, и как юрисдикцию плательщика, поэтому для Kometa в текущей конфигурации политика по VPN второстепенна — отказ придёт по гео.</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>До 40% с продажи Amnezia Premium и 30% с каждого продления (по данным партнёрской страницы); пример: 100 полугодовых продаж = 1000 USD, 100 годовых = 1720 USD сразу плюс 30% с продлений</t>
+          <t>по запросу (не публикуется). Публичной страницы тарифов нет (payop.com/pricing отдаёт 404), ни в FAQ, ни в Legal-разделе нет ни процента, ни фиксированной ставки, ни chargeback-фи, ни месячного минимума. Единственная публичная цифра по удержаниям — rolling reserve 5–10%.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Заявка физлица возможна (форма + Telegram/email); требование юрлица не заявлено</t>
+          <t>Принимаются и компания, и individual entrepreneur: "You can create and verify a merchant account for a company or an individual entrepreneur." Для ИП: официальный документ о госрегистрации ИП, подтверждение налоговой регистрации, паспорт/ID, proof of residence. Для компании: Certificate of Incorporation, реестры директоров и акционеров, паспорта и proof of residence директоров и UBO, Memorandum &amp; Articles of Association, Certificate of Good Standing/Extract (если компании больше 2 лет). Для Betting/Gambling/Crypto/Forex — лицензия на деятельность и Payment Agent Agreement. Все документы на английском или с заверенным переводом, proof of residence — не старше 3 месяцев. Обязателен сайт: логотипы платёжных систем, Contact us, данные компании (название, адрес, страна регистрации), условия доставки, подробное описание товаров и услуг, Privacy Policy, Return &amp; Cancellation Policy, SSL. Требование VAT/GST-номера не упоминается — не подтверждено. Pre-check ≤ 2 рабочих дня, далее верификация через платформу KYCB.</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Партнёрская ссылка и личный кабинет; API автовыдачи доступа не заявлен</t>
+          <t>REST API (документация: github.com/Payop/payop-api-doc), hosted checkout page, плагины/CMS, отчёты, массовые выплаты через API, merchant panel с проектами и ключами (public/secret key на проект). Storefront-бот в Telegram без сайта не подойдёт: у Payop "a project is your website used to make sales", а верификация проекта требует сайта с полным набором политик. Сложность интеграции: 3 — стандартный REST API + hosted checkout и понятная документация, но обязательны полноценный сайт с политиками, KYCB с документами на ИП/юрлицо и риск-проверка; плюс критичный блокер по РФ..</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>HideMy.name (партнёрка)</t>
+          <t>Unlimit (ранее Unlimint, ранее Cardpay); в документах и отзывах фигурируют UNLIMINT EU LTD (Кипр) и UNLIMINT PSP FZ-LLC (ОАЭ)</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
+          <t>High-risk эквайринг/PSP — глобальный acquiring PSP + BaaS + crypto on/off-ramp; НЕ MoR</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Разрешено: провайдер сам продаёт VPN и приглашает партнёров</t>
+          <t>серая зона. Единого глобального Acceptable Use / Banned Category List на unlimit.com нет: сайт публикует только Website Terms of Use (last updated 24.04.2024), где отраслевых ограничений нет вообще, а раздел "Prohibited use" относится к использованию самого сайта, а не к деятельности мерчанта. Публичный Banned Category List существует только у индийской структуры группы (in.unlimit.com) — и в нём VPN, proxy, anonymizer и circumvention НЕ упомянуты. Запрещены смежные «обходные» категории (modification chips, cable descramblers/black boxes, hacking and cracking materials), плюс очень широкая формулировка про бизнесы, работающие в юридически неоднозначной зоне. Явного разрешения VPN нет, явного запрета тоже нет.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>До 50% с привлечённых покупок и 25% со всех продлений без ограничения по времени</t>
+          <t>по запросу (не публикуется). На unlimit.com нет ни процентов, ни фиксированной ставки, ни chargeback-фи, ни месячного минимума. Сторонний справочник paymentproviders.io указывает модель "Custom" (цена по запросу) и ставок не приводит.</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Регистрация партнёра; требование юрлица не заявлено</t>
+          <t>Публичных требований к онбордингу группа не публикует: страница acquiring-onboarding на глобальном домене отдаёт 404, списка документов KYC/KYB нет, требований к сайту нет. Практически речь о юрлице (в отзывах фигурируют корпоративные структуры группы), но подтверждения возможности ИП/самозанятого, требований к VAT/GST и к сайту найти не удалось — не подтверждено.</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Реферальная ссылка; API автовыдачи не заявлен</t>
+          <t>REST API + SDK (публичный iOS SDK: github.com/cardpay/unlimit-ios-sdk), hosted payment page, gateway mode, server-to-server, sandbox/demo (demo.unlimit.com/ma-new), документация integration.unlimit.com, webhooks (подтверждается сторонними справочниками и Gr4vy-коннектором). Данных о приёме магазина-бота в Telegram без сайта нет — не подтверждено; процесс онбординга предполагает наличие сайта/продукта. Сложность интеграции: 4 — технически всё стандартно (API/SDK/hosted page/sandbox), но это крупный enterprise-эквайер: KYB, отсутствие публичных тарифов и публичного AUP, непрозрачная политика по РФ и высокорисковым нишам. Для нового мелкого VPN-проекта без истории процессинга шансы не подтверждены и, скорее, низкие..</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>AdGuard VPN (партнёрка)</t>
+          <t>Praxis Cashier (Praxis Tech Ltd., Лимасол, Кипр)</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
+          <t>НЕ эквайринг и НЕ PSP: платёжный оркестратор / hosted cashier. Дословно: "we do not process or settle transactions, nor do we handle client funds."</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Разрешено: провайдер продвигает партнёрскую программу</t>
+          <t>серая зона (скорее нет). В Client Acceptance Policy перечислены только три допустимые отрасли — iGaming, Trading / Forex, E-commerce — плюс требование быть лицензированным зарегистрированным бизнесом; VPN не назван ни в разрешённых, ни в запрещённых. В запретах есть "Malware or cybercrime tools", к чему VPN формально не относится, но также сказано, что клиенты в ограниченных и санкционных юрисдикциях, "including the United States", не допускаются. Практически важнее другое: даже при успешном онбординге Praxis не решает задачу приёма денег — свой эквайер/PSP всё равно нужен отдельно.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Ставка на странице программы не извлечена (страница отдаётся JS-рендером) — не подтверждено</t>
+          <t>по запросу (не публикуется). Страницы тарифов нет (praxis.tech/pricing отдаёт 404). Единственная публичная цифра — не подтверждённое компанией утверждение клиента в отзыве Trustpilot от 16.06.2024: "We trusted Praxis Tech, believing they had four PSPs ready for us after paying $2200". Это отзыв, а не тариф.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Только зарегистрированный и проверяемый бизнес: "Operate a legally registered and verifiable business", "Hold valid and relevant licenses or regulatory registrations (when applicable)", "Have a transparent corporate structure with identifiable beneficial owners". Физлицо и самозанятый не подходят. KYB-проверка обязательна, обработка данных по GDPR, есть DPO. Для работы нужна точка входа для checkout (hosted page/iframe). Требование VAT/GST-номера не упоминается — не подтверждено.</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Партнёрская ссылка</t>
+          <t>Hosted Payment Page (Cashier) с redirect или iframe, Hosted Payment Fields (JS SDK, PCI-нагрузка на Praxis), Server-to-Server REST API (требует PCI Level 1 у мерчанта), Google Pay и Apple Pay, sandbox и тестирование, документация docs.praxis.tech, есть даже MCP-сервер; webhooks и return URLs/dynamic redirects. Для Telegram-бота без сайта неудобно: hosted cashier предполагает веб-страницу и redirect; прямой поддержки «витрины-бота» в документации нет — не подтверждено. Сложность интеграции: 4 — сама интеграция (hosted cashier) простая, но Praxis не даёт эквайринг: нужно самостоятельно получить PSP/эквайеров, готовых работать с VPN, а Praxis онбордит преимущественно лицензированные iGaming/Forex/E-commerce компании. Для маленького VPN без лицензии и без сайта — высокий риск отказа..</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>KeepSolid VPN Unlimited (partners)</t>
+          <t>PayDo (бренд Ecommerce Technologies LTD; лицензии FCA (UK) и FINTRAC (Канада))</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Партнёрская/реселлерская программа VPN-провайдера</t>
+          <t>High-risk эквайринг/PSP (не MoR: это EMI + платёжный чекаут/эквайринг, а не Merchant of Record)</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Разрешено: у провайдера есть раздел partnership для партнёров и партнёрская программа</t>
+          <t>серая зона. VPN как вид деятельности прямо не запрещён и не разрешён: в Schedule 2 запрещённых/ограниченных категорий VPN нет, но близкая категория «Computer Network / Information Services / Cyberlockers and similar remote digital file-sharing services» (MCC 4816) отнесена к деятельности, запрещённой без предварительного письменного одобрения PayDo. Отдельно PayDo прямо обязывает мерчанта выявлять использование VPN клиентами как попытку обхода гео-/KYC-контроля, то есть VPN-трафик плательщиков трактуется как риск-флаг. Практический блокер для проекта не в VPN, а в географии: Российская Федерация — в списке запрещённых юрисдикций и для компании/UBO/директоров, и для места отправки средств/локации плательщика.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Ставка не извлечена (страница отдаётся JS-рендером) — не подтверждено</t>
+          <t>Опубликованы тарифы бизнес-счёта (минимальные котировки на странице без заполнения анкеты о компании): setup fee 1500 EUR + 200 EUR/мес; другие показанные тарифы — 300 EUR setup + 125 EUR/мес и бесплатный setup + 100 EUR/мес. Карточные транзакции по счёту внутри EEA 1–4%, вне EEA 2–4%; SEPA исходящие 0.2–0.75% (min 3–15 EUR); cross-border 0.3–1% + 15–35 EUR; конвертация 1%; вывод в ATM и прочее по тарифу. По Checkout опубликованы только локальные методы: «0.2 USD + 3%…5.5%» за транзакцию (примеры: PayDo Wallet Bank transfer South Africa 0.2 USD + 5.5%, Mobile Money Ghana 0.2 USD + 4.7%, Oxxo Mexico 0.2 USD + 5.4%), refund fee «–». Ставка эквайринга по международным картам на странице не публикуется (таблица с карточными строками формируется только после ввода данных о компании) — по запросу (не публикуется). Chargeback fee и monthly minimum для эквайринга — по запросу (не публикуется).</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Только юридическое лицо: в Merchant Services Terms UK прямо сказано: «"Client" means any legal entity that has executed Annex 1 (Fees and Terms)» — индивидуальный предприниматель/самозанятый не подходит. KYC/KYB: документ о госрегистрации компании и документ о владении, ID + proof of address + CV или ссылки на соцсети для каждого UBO/директора/топ-менеджера; для бенефициаров вне EEA дополнительно proof of funds (например, банковская выписка). Проверка UBO с фото и совпадением лица, срок открытия счёта — до ~3 недель. Для чекаута требуется «merchant's website(s) and application(s)» — то есть сайт/приложение, а не только Telegram-бот. Требуется соответствие Card Scheme Rules: чёткие условия подписки, отмена, refund policy.</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Отдельно упоминается Telegram-бот VPN Unlimited</t>
+          <t>Есть hosted payment page + SDK/API, документация docs.paydo.com/overview, вебхуки и «Payment page, SDK, API» в терминах. Telegram-бот без сайта — рискованно: Terms описывают приём платежей через «website(s) and application(s)» мерчанта, а проверка сайта (контакты, refund/cancellation policy, privacy policy) — часть онбординга. Сложность интеграции: 3 — техническая интеграция стандартная (hosted page/API/docs), но высокая комплаенс-нагрузка: только юрлицо, письменное одобрение MCC 4816, GEO-блокировки, а главное — Россия в запрещённых юрисдикциях..</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>NordVPN (партнёрка/white label)</t>
+          <t>ZEN.COM (UAB ZEN.COM, Литва; услуги эквайринга — ZEN-UK Limited, Великобритания)</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
+          <t>High-risk эквайринг/PSP (EMI + карточный эквайер; не MoR)</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Разрешено провайдером; критично проверить ограничения по странам и санкциям для партнёра из РФ</t>
+          <t>серая зона. Прямого упоминания VPN нет НИ в «List of Prohibited Activities» (опубликован 14.11.2024), НИ в Schedule I «List of Prohibited Items» британских E-Commerce Terms (версия 1.01 от 05.11.2025) — VPN, proxy, anonymizer, «unblocking» и IP-masking там не названы. Запрещены только смежные вещи: «Cable descramblers and black boxes… devices and applications, intended to obtain and share internet TV signals – IPTV» и «copyright unlocking devices or other devices designed to circumvent copyright protection» — это про обход авторских прав/платного ТВ, а не про VPN. Отсутствие запрета ≠ разрешение: финальное решение принимает риск-подразделение ZEN, а «Merchant must not be … involved in any activity provided in the prohibited activities list». Отдельный блокер — география: Россия и Беларусь в prohibited jurisdictions, а Казахстан/Армения/Грузия/Кыргызстан/ОАЭ отсутствуют в списке разрешённых для онбординга юрисдикций.</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Ставка не подтверждена в этой проверке</t>
+          <t>Опубликованы в ZEN Business pricing (effective 7 января 2025) и на ценовой странице. Эквайринг: Visa и Mastercard — IF++ 0.89% + 0.30 EUR; Apple Pay/Google Pay — IF++ 0.89% + 0.30 EUR; BLIK/iDEAL/Bancontact/Trustly/Sofort/Polish PayByLinks — 0.89% + 0.30 EUR; Skrill (свыше 4 EUR) 4.20% + 0.30 EUR, Skrill micro (до 4 EUR) 7.20%, Skrill Rapid 2.20% + 0.30 EUR; Neteller 4.20% + 0.30 EUR; Paysafecard 10.20% + 0.30 EUR; Paysafecash 5.20% + 0.30 EUR; WeChat 2.20% + 0.30 EUR; UnionPay 2.20% + 0.30 EUR; Twisto 2.40% + 0.30 EUR; Neosurf 10.20% + 0.30 EUR. Refund 2.50 EUR. Chargeback fee — 35 EUR (при chargeback rate 0.00–0.30%), 40 EUR (0.30–0.50%), 45 EUR (0.50–0.70%), 50 EUR (0.70–1.00%), 60 EUR (&gt;1.00%); representment 10.00 EUR. Fraud Prevention Service: 0.00% + 0.07 EUR за транзакцию при низком fraud rate, до 2.00% + 0.07 EUR для high-risk merchant, плюс 200 EUR/мес в отдельных случаях. Обслуживание счёта: Smart 25.00 EUR/мес (спец. предложение — бесплатно), Enterprise 100.00 EUR/мес. ZEN Pay processing 0.35% + 0.10 EUR. Обязательный минимум оборота не публикуется.</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Обычно требуется партнёрская сеть (Admitad/Awin) и подтверждение личности; доступность для РФ не подтверждена</t>
+          <t>Мерчант должен быть «a legal person or a sole trader (or equivalent) registered in a jurisdiction that is not included in the Prohibited Jurisdictions List» — то есть ИП/самозанятый или аналог формально допустимы, но только из разрешённой юрисдикции (РФ — нет). KYC: подтверждение личности акционеров, директоров и UBO — фото ID/паспорта/водительских прав/ВНЖ + сравнение с фото лица, дополнительные документы по запросу; ZEN может отказать в регистрации без объяснения причин. Для карточных CNP-транзакций на сайте обязательны: юридическое имя мерчанта, полное описание товаров/услуг, return/refund/delivery policy, контакты поддержки (e-mail/телефон), физический адрес ведения деятельности, политика защиты данных покупателя; обязательна интеграция антифрод-инструмента docs.zen.com/payments/api-integration/fraud-collector; обрабатывать транзакции можно только по URL, явно одобренным ZEN (новые URL — по письменному согласованию, «The Merchant may only process Transactions through URLs explicitly approved by ZEN»).</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Партнёрские ссылки/промокоды</t>
+          <t>REST API + хостед-страница/редирект (Pages: «an Account Holder is redirected from the Merchant's website»), документация docs.zen.com, обязательная интеграция fraud-collector, вебхуки/нотификации в личном кабинете. Telegram-бот как единственная витрина — проблема: контракт требует одобренного URL/сайта с полным набором данных мерчанта, а Telegram-бот не является сайтом по правилам карточных схем. Сложность интеграции: 4 — API и хостед-страница стандартные, но объём требований большой (43-страничный договор, обязательный fraud collector, одобрение URL, KYC/UBO, Security Deposit по усмотрению ZEN) и по каждому пункту ZEN оставляет свободу отказа..</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Proton VPN (партнёрка)</t>
+          <t>eMerchantBroker (EMB), Emerchantbroker, LLC</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Партнёрская программа VPN-провайдера</t>
+          <t>High-risk эквайринг/PSP — фактически брокер-ISO, а не эквайер и не MoR</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Разрешено провайдером; доступность для РФ-партнёра не подтверждена</t>
+          <t>серая зона. VPN нигде явно не упомянут: ни в списке отраслей (online gaming, CBD, adult, e-cigarettes, nutraceuticals, collections, tech support, software &amp; e-books, VOIP/telecom), ни в Terms and Conditions (раздел Prohibited uses не содержит списка запрещённых индустрий — только общие формулировки про unlawful purpose и circumvention of security features). EMB позиционируется как высокорисковый брокер, который «берет» hard-to-place вертикали и цифровые товары, поэтому VPN теоретически может быть размещён через их банк-партнёр, но подтверждения нет: решение принимает sponsor bank (BMO Harris) в рамках underwriting.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Ставка не подтверждена</t>
+          <t>по запросу (не публикуется). На сайте нет ни ставок, ни тарифных планов: «Pricing varies depending on the merchant's industry, past credit card processing history...». Сторонний обзор CardFellow фиксирует, что EMB на своём сайте заявляет «high-risk merchant account rates may start as low as 2.99%», но без указания, к каким типам бизнеса и транзакций это относится. Chargeback fee, monthly minimum, PCI-плата и gateway-плата — не публикуются.</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Регистрация в партнёрской сети; доступность РФ не подтверждена</t>
+          <t>Для заявки: government-issued ID (паспорт/права), bank letter или pre-printed voided check, «A secure, working website», 3 месяца банковских выписок, 3 месяца processing statements (если есть), SSN или EIN, chargeback ratio ниже 2%. Отдельно заявлено, что работают с мерчантами без processing history, с плохим кредитом и с ранее закрытыми аккаунтами. Наличие работающего сайта обязательно — Telegram-бот без сайта не подойдёт.</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Партнёрские ссылки</t>
+          <t>Собственный шлюз Bankful + hosted checkout/виртуальный терминал; интеграции с Shopify, Wix, WooCommerce, BigCommerce, OpenCart, Shift4Shop, QuickBooks; Apple Pay. Публичной открытой API-документации на сайте EMB нет (только страница Payment gateways). Telegram-бот без сайта: нет — обязателен «secure, working website». Сложность интеграции: 4 — нет публичной документации API и тестового контура; интеграция идёт через сторонний шлюз Bankful и требует полноценного сайта с чекаутом, плюс ручной онбординг под hard-to-place вертикаль..</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Ivacy VPN (white label)</t>
+          <t>SMB Global (SMB Global Payments LLC)</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>White-label VPN</t>
+          <t>High-risk эквайринг/PSP — фактически посредник (intermediary) между мерчантом и банками, не прямой процессор</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Разрешено: у провайдера исторически есть white-label/affiliate предложение</t>
+          <t>серая зона. VPN не упомянут ни в списке отраслей на сайте (Dropshipping, Telemedicine, Firearms &amp; Tobacco, Nutraceuticals, Online Gaming, Adult &amp; Dating, Digital Marketing, Coaching Products, MLM &amp; Direct Sales, eCommerce, Travel &amp; Tourism), ни в описаниях решений. Публичного Acceptable Use / списка запрещённых индустрий у них нет вовсе; при этом компания заявляет, что «actively place accounts» для hard-to-place индустрий и работает через 20+ банков, поэтому цифровой сервис вроде VPN может быть рассмотрен — но подтверждения нет.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Ставка не подтверждена в этой проверке</t>
+          <t>по запросу (не публикуется). Ни ставок, ни тарифной сетки, ни примеров на сайте нет — только «Transparent pricing... No surprise reserves» без цифр; сторонние обзоры (GuidingDecisions, 2026; Merchant Maverick, 2024) подтверждают полное отсутствие раскрытия цен. Ориентиры по рынку, а не по SMB Global: high-risk типично 2,5–4% эффективной ставки — это оценка обозревателя, не публикация компании.</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Публичного перечня требований нет (не подтверждено). Известно из сторонних источников: аккредитация/андеррайтинг идёт через банк-партнёр, в ToS компании предусмотрен запрос в Experian по FCRA (GuidingDecisions, 2026), для offshore — минимум $50 000/мес оборота либо сильная финансовая история. Наличие юрлица, VAT/GST, требований к сайту компания не публикует.</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>White-label панель (не подтверждено)</t>
+          <t>Payment API, Mobile SDK, EMV SDK, hosted checkout (Collect Checkout), 175+ интеграций с корзинами, шлюзы NMI / Authorize.net / USA ePay. Документация слабая: интеграционный портал ведёт на общие ресурсы NMI, а не на гайды SMB Global (GuidingDecisions, 2026). Требование сайта для онбординга не публикуется, поэтому приемлемость Telegram-бота без сайта — не подтверждено. Сложность интеграции: 4 — отдельных фирменных документов и sandbox нет, интеграция сводится к сторонним шлюзам, а политика (резервы, лимиты, требования к сайту) полностью определяется банком-партнёром; для цифрового продукта без сайта ясности нет..</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>OrbVPN (reseller)</t>
+          <t>Soar Payments / SoarPay (Soar Payments LLC, DBA AltruPay LLC)</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Реселлерская программа VPN-провайдера</t>
+          <t>High-risk эквайринг/PSP — фактически брокер-ISO, не эквайер и не MoR</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Разрешено: у провайдера есть отдельная документация для реселлеров</t>
+          <t>серая зона с практическим «нет» для проекта. VPN нигде не упомянут: ни в списке из 50+ индустрий (SaaS, digital streaming, subscription/continuity, credit repair, nutraceuticals, firearms и т.д.), ни в списке запрещённых. Но у Soar есть жёсткие ограничения по мерчанту: сервис только для US-бизнесов с SSN владельца, а «offshore merchants and businesses headquartered outside the United States» прямо запрещены. То есть сама VPN-вертикаль не запрещена, но российский продавец (физлицо/самозанятый/РФ-юрлицо) не может быть онборднут.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>по запросу (не публикуется). Модель — interchange-plus («Your processing fee is the interchange rate set by the card networks plus a fixed markup from SoarPay»), но конкретные ставки только в персональном письменном предложении. Отдельно не публикуются: chargeback fee, monthly minimum, PCI-плата, ACH-ставки. Сторонний обзор GuidingDecisions (март 2026) указывает типичные ориентиры: gateway от $15/мес, tiered 2,5–4,0% для mid/high-risk, и что ETF на mid/high-risk контрактах высокий.</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Не подтверждено</t>
+          <t>Только US: бизнес в США + владелец с действующим SSN и US-issued photo ID (EIN недостаточен); обязателен бизнес-счёт для LLC/корпорации (личный счёт нельзя); документы: 3 месяца банковских выписок (для стартапов — личные выписки владельца), voided business check или bank letter, фото-ID, 3 месяца processing statements (если есть), proof of inventory для товарных бизнесов, sample customer contract/terms of sale, FFL для оружия, ARC/surety bond для travel. Кредитная проверка обязательна и не может быть отменена (hard или soft pull — зависит от банка). Сайт: “If you sell online, you need a functioning website with products and pricing” — то есть Telegram-бот без сайта не подойдёт. Запрещены: adult, cannabis/THC, peptides/SARMs/research chemicals, forex и нерегулируемые фининструменты, kratom, misleading tech support, offshore/не-US бизнесы, онлайн-казино и нелицензированный гэмблинг, payday loans, MATCH-listed мерчанты, hate speech.</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Есть документация для реселлеров на docs.orbvpn.com</t>
+          <t>Merchant account + сторонние шлюзы: Authorize.net (нативный для WooCommerce, Shopify, BigCommerce, Magento), NMI (3-D Secure 2.0, multi-processor routing), FluidPay, AcceptBlue; virtual terminal, recurring billing, ACH, Shopify-гайд (через Authorize.net alternative payment provider). Своего API нет — интеграция идёт через шлюз партнёра. Storefront в Telegram без сайта: нет (нужен работающий сайт с ценами). Сложность интеграции: 4 — технически подписки и шлюзы стандартные, но требуется US-юрлицо + SSN владельца + бизнес-счёт + сайт с ценами, а также обязательный кредитный чек; для Telegram-бота с российским основателем это блокирующие условия..</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Instant-delivery шопы (типовой магазин автовыдачи)</t>
+          <t>Maverick Payments (Maverick Bankcard, Inc.)</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Собственная витрина с автовыдачей, часто на бэкенде Digiseller</t>
+          <t>High-risk эквайринг/PSP — процессинговая платформа с собственным шлюзом и сетью банков-партнёров; продажи в основном через ISO/ISV-партнёров, не MoR</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Серая зона: правила задаёт владелец шопа, а не площадка; для приёма денег нужен собственный эквайринг или подключение к чужой кассе</t>
+          <t>серая зона. VPN/прокси нигде не упомянут. Раздел Specialty markets / High-risk перечисляет вертикали: Travel &amp; leisure, Health products, Education &amp; coaching, Dating &amp; social networks, E-commerce &amp; subscriptions, Tobacco &amp; vape, Financial &amp; lending, Firearms &amp; ammo, Gaming &amp; gambling — плюс, по сторонним обзорам, vapes/e-cig, nutraceuticals, direct response, MLM, lenders. Цифровые сервисы и подписки заявлены («Streamlined solutions for e-commerce and subscription models»), но VPN отдельно не назван и публичного Acceptable Use со списком запрещённых индустрий нет (Terms of use на сайте — только условия использования сайта).</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Комиссия платформы-бэкенда (Digiseller 1,5-6%) плюс комиссия эквайринга; плюс доля владельца шопа, если продаёте через него</t>
+          <t>по запросу (не публикуется). Своей тарифной страницы нет: «As is common for the industry, Maverick Payments does not list its rates for high-risk merchant accounts on its website. You must contact them for a quote» (Shark Processing). CardFellow: «Maverick doesn't publish pricing... Some fees that may apply include the transaction fee, PIN debit fee, AVS fee, statement fee, and internet gateway fee.» Ставки, chargeback fee, monthly minimum — не публикуются.</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Чаще всего достаточно регистрации; договор с продавцом часто отсутствует</t>
+          <t>Публично не раскрыто (не подтверждено): ни перечня документов, ни требований к юрлицу/индивидуальному предпринимательству, ни требований к сайту. Косвенно: онбординг идёт через партнёров (ISOs/agents) и Onboarding API, что подразумевает стандартный US-KYB (EIN, банковский счёт, owner ID). Приемлемость Telegram-бота без сайта — не подтверждено.</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Обычно есть API автовыдачи ключей</t>
+          <t>Собственный (proprietary) шлюз для карт и ACH, direct API, hosted forms, virtual terminal, Connect для сертифицированных решений, Onboarding API, white-label dashboard, документация для разработчиков на developers.maverickpayments.com, sandbox и API-документация (Shark Processing). Интеграции с CRM и корзинами; большой набор POS/Poynt/Vital. Telegram-бот как витрина: технически оплата возможна через API/hosted form, но политика по storefront без сайта не публикуется — не подтверждено. Сложность интеграции: 3 — есть нормальная API/developer-инфраструктура и hosted forms, но нет публичных тарифов и правил андеррайтинга, онбординг только через demo/партнёра, а VPN и бот-витрина не подтверждены..</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
+          <t>Host Merchant Services (HMS)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>High-risk эквайринг/PSP — ISO (не прямой эквайер, не MoR); high-risk направление через «alternate partners»</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>серая зона. VPN нигде не упомянут, хотя у HMS очень широкий high-risk каталог: adult, airlines/jet charter, auto warranty, bail bonds, CBD, coins, content downloads &amp; digital goods, continuity/subscription, credit repair, debt collection, document prep, vape/e-cig, gambling/casinos, firearms, insurance, MLM, nutraceuticals, offshore businesses, online dating, online pharmacy, pawn shops, self-defense, SEO/SEM, sports betting, tech support, telemedicine, timeshares, travel, web design, web hosting, weight loss. Цифровые товары и подписки прямо поддержаны, но VPN/прокси/анонимайзеры не названы нигде, и публичного Acceptable Use со списком запрещённых вертикалей нет.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Публикуются для стандартных программ (интерчейндж + марка): retail — interchange + 0,25% + $0,10 за транзакцию; рестораны — +0,20% + $0,09; e-commerce — +0,35% + $0,10; offshore — «interchange-plus pricing with low markups starting at 0.20%-0.35% + $0.09-$0.10 per transaction». Прочие платы (прайс-лист): gateway $14,99/мес, monthly fee $14,99/мес, PCI compliance $0,75, batch fee $0,75, PIN debit $0,20/батч, annual 1099 reporting $24/год, voice authorization $5,00/мес (опционально), AVS $0,00, closure fee $0,00. Для high-risk — custom quote: «High-risk merchants receive custom pricing through HMS's arrangement with Electronic Merchant Systems, and those rates require a direct conversation» (GuidingDecisions, 2026). Chargeback fee — не публикуется.</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Для стандартного онбординга: обычные бизнес-документы, 24–72 часа на одобрение (digital goods — 1–3 дня). Для high-risk: «We work with specialized acquiring banks and a team experienced in high risk industries» — конкретный список документов и требований не публикуется (не подтверждено); по данным GuidingDecisions 2026, андеррайтинг и условия идут через EMS. Для offshore: proof of address, passport и базовые данные; возможна помощь с инкорпорацией. Требования к сайту для цифрового сервиса не публикуются — приемлемость Telegram-бота без сайта не подтверждена.</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Собственный шлюз HMS Pay (карты + ACH, virtual terminal, batch, multi-location), API-driven gateway, hosted checkout/payment links/payment buttons, mobile SDK, QR, плагины для корзин, интеграции с QuickBooks/ERP/CRM; поддерживаются также Authorize.Net и NMI. Документация по API публично в открытом виде не выложена (страница Payment integration), поэтому Telegram-бот без сайта — не подтверждено. Сложность интеграции: 3 — есть hosted checkout, API, tokenised recurring и поддержка подписок, но high-risk-онбординг ручной и идёт через партнёрские банки, публичной API-документации и правил для storefront без сайта нет..</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Telegram Stars (Bot Payments)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Telegram-нативный</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Не регламентировано: модерации тематики нет, но цифровые товары в Telegram обязаны продаваться за Stars</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Спред Telegram 7,8%: покупка 1000 Stars = 1,41 USD, вывод 1000 Stars = 1,30 USD</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Только Telegram-аккаунт владельца бота и 2FA-пароль; документы, ИП, ООО, самозанятость не требуются</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Bot API sendInvoice currency=XTR + successful_payment; сложность 1 из 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Tribute</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Telegram-нативный посредник</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Серая зона: VPN, прокси и анонимайзеры в списке запрещённых категорий отсутствуют, но товар проходит ручную модерацию со статусами pending/approved/rejected</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>10% с каждой успешной транзакции, включая комиссию сервиса и платёжных провайдеров, плюс динамический сервисный сбор (размер зависит от суммы платежа, точные значения не опубликованы)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Регистрация через @tribute в Telegram; документы и статус не требуются; для выплат есть страница новых требований к данным, содержимое не проверено</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Платёжная ссылка + API + вебхук new_digital_product с HMAC-SHA256 в заголовке trbt-signature, ретраи 5 мин / 15 мин / 30 мин / 1 час / 10 часов; сложность 2 из 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>FunPay</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Площадка цифровых товаров</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Серая зона: прямого запрета VPN нет, но п. 2.2.5 запрещает подписки на сервисы без спецраздела, а п. 2.1.12 запрещает размещать объявления на других площадках под угрозой отказа в выплатах</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Не подтверждено: три слоя (сбор с продажи, сбор за вывод, стоимость платёжного метода), ставки не опубликованы</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Физлицо, регистрация свободная; документы для вывода не подтверждены</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Ручная или автоматическая выдача; автовыдача прямо запрещена для товаров, требующих общения или доп. услуг; сложность 2 из 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>PayMaster</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Серая зона: оферта молчит, требование общее - товары не должны входить в список запрещённых к продаже; VPN прямо не назван</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>2-5% с каждой успешной транзакции в зависимости от вида платежа; ежемесячных и скрытых платежей нет</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>Есть публичный вход для физлиц (кнопка У меня нет юр. лица) и отдельный для юрлиц и ИП; нужен готовый ресурс с товарами, ценами и офертой; заявленный срок подключения 2 дня</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>API, платёжный виджет, модули CMS, Payment notification POST-вебхук с MD5-подписью, защита от дублей, тестовый режим, подключение к Telegram; сложность 2 из 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>RollyPay</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Серая зона: в оферте и на сайте VPN, прокси и анонимайзеры не упомянуты, тематика решается менеджером после проверки проекта</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Крипта от 1%; по данным представителя сервиса СБП QR от 5% и карты РФ от 5% - это заявление в неофициальном канале, а не текст оферты</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Подключение доступно физлицам, самозанятым, ИП и компаниям после проверки проекта; публичной оферты с перечнем запретов нет</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>REST API, вебхуки, SDK на Node.js, PHP, Python, готовые модули и платёжные ссылки, тестовый режим; сложность 2 из 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Digiseller (digiseller.market)</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Платформа цифровых товаров и витрин (движок для GGsel и др.)</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Серая зона: VPN в запретах не упомянут; запрещены товары, нарушающие законодательство, и абстрактные/неописанные товары (п.1.2.4)</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Комиссия DS 1,5-6% в зависимости от тематики, но не менее 0,02 WM; сверху комиссия платёжного метода и стоимость вывода</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>П.1.2.1: клиентом DS может стать только лицо, прошедшее идентификацию в системе WebMoney; регистрация как физлицо возможна</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Есть API Digiseller для автоматической выдачи ключей и внешних витрин</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Plati.Market</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Маркетплейс цифровых товаров (та же экосистема, что Digiseller)</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Серая зона: в Приложении 1 (перечень запрещённых товаров) VPN не упомянут; прямо разрешены к продаже сервисы подписки</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Комиссия от 3% от суммы платежа (заявлено на странице для продавцов)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Физлицо без документов; при отрицательном отзыве без аттестата возможна блокировка счёта и продаж</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>API и автовыдача уникальных кодов (автоматически создаваемые уникальные коды)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>GGsel</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Витрина цифровых товаров на бэкенде Digiseller</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Серая зона: наследует правила Digiseller; VPN отдельно не упомянут</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Сбор площадки зависит от раздела и условий продавца; публичной ставки нет; расчёты идут через Digiseller, плюс стоимость платёжного метода и вывода</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Требуется идентификация WebMoney (наследуется от Digiseller)</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Автовыдача мгновенных кодов; API наследуется от Digiseller</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Google Play (In-App Purchase)</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Магазин приложений Google, продажа подписок через биллинг</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено с декларацией: приложение с VPN обязано использовать VpnService, пройти декларацию в Play Console, документировать использование в листинге и показывать prominent disclosure</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Стандартная шкала: 15% для первых 1 млн USD в год и 30% свыше; для автопродлеваемых подписок 15% независимо от выручки; в ряде рынков новая схема 10-25% плюс 5% billing fee</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Аккаунт разработчика Google Play; для организации нужен D-U-N-S; минимальный возраст — 18 лет (не подтверждено отдельным документом в этой проверке)</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Google Play Developer API, server-side проверка покупок</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Amnezia Premium (партнёрка)</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено: провайдер сам продаёт обфусцированный VPN и принимает партнёров</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>До 40% с продажи Amnezia Premium и 30% с каждого продления (по данным партнёрской страницы); пример: 100 полугодовых продаж = 1000 USD, 100 годовых = 1720 USD сразу плюс 30% с продлений</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Заявка физлица возможна (форма + Telegram/email); требование юрлица не заявлено</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрская ссылка и личный кабинет; API автовыдачи доступа не заявлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>HideMy.name (партнёрка)</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено: провайдер сам продаёт VPN и приглашает партнёров</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>До 50% с привлечённых покупок и 25% со всех продлений без ограничения по времени</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Регистрация партнёра; требование юрлица не заявлено</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Реферальная ссылка; API автовыдачи не заявлен</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>AdGuard VPN (партнёрка)</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено: провайдер продвигает партнёрскую программу</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Ставка на странице программы не извлечена (страница отдаётся JS-рендером) — не подтверждено</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрская ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>KeepSolid VPN Unlimited (partners)</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрская/реселлерская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено: у провайдера есть раздел partnership для партнёров и партнёрская программа</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Ставка не извлечена (страница отдаётся JS-рендером) — не подтверждено</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Отдельно упоминается Telegram-бот VPN Unlimited</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>NordVPN (партнёрка/white label)</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено провайдером; критично проверить ограничения по странам и санкциям для партнёра из РФ</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Ставка не подтверждена в этой проверке</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>Обычно требуется партнёрская сеть (Admitad/Awin) и подтверждение личности; доступность для РФ не подтверждена</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрские ссылки/промокоды</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Proton VPN (партнёрка)</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено провайдером; доступность для РФ-партнёра не подтверждена</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Ставка не подтверждена</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Регистрация в партнёрской сети; доступность РФ не подтверждена</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Партнёрские ссылки</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Ivacy VPN (white label)</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>White-label VPN</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено: у провайдера исторически есть white-label/affiliate предложение</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Ставка не подтверждена в этой проверке</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>White-label панель (не подтверждено)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>OrbVPN (reseller)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Реселлерская программа VPN-провайдера</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Разрешено: у провайдера есть отдельная документация для реселлеров</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>Не подтверждено</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Есть документация для реселлеров на docs.orbvpn.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Instant-delivery шопы (типовой магазин автовыдачи)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Собственная витрина с автовыдачей, часто на бэкенде Digiseller</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Серая зона: правила задаёт владелец шопа, а не площадка; для приёма денег нужен собственный эквайринг или подключение к чужой кассе</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Комиссия платформы-бэкенда (Digiseller 1,5-6%) плюс комиссия эквайринга; плюс доля владельца шопа, если продаёте через него</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>Чаще всего достаточно регистрации; договор с продавцом часто отсутствует</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Обычно есть API автовыдачи ключей</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
           <t>Telegram-боты-реселлеры (чужая касса)</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>Сторонний бот принимает деньги и передаёт вам заказ</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Серая зона: правила задаёт владелец бота; часто это перепродажа чужих цифровых товаров без документов</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Реселлер обычно забирает 10-30% маржи; точная ставка определяется договорённостью и не подтверждена</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>Физлицо; верификации нет</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>Автовыдача через API партнёра, если он его даёт</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F35"/>
+  <autoFilter ref="A1:F54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>